--- a/tests/test_data/ОН_ФЭВТ_4 курс 2023 lessons.xlsx
+++ b/tests/test_data/ОН_ФЭВТ_4 курс 2023 lessons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\Work\YDev\EOS\vstu-xls\vstu_xls\tests\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2F0497-B26C-4229-8320-1886DE897149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D1211F-3E96-49AB-B050-F7FD3D52421F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="84">
   <si>
     <t xml:space="preserve">    УТВЕРЖДАЮ:</t>
   </si>
@@ -263,6 +263,15 @@
   </si>
   <si>
     <t>В 1301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТЕСТИР. И222 </t>
+  </si>
+  <si>
+    <t>Мильчук444 Я.Г.</t>
+  </si>
+  <si>
+    <t>???????</t>
   </si>
 </sst>
 </file>
@@ -2221,7 +2230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="677">
+  <cellXfs count="680">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -2343,9 +2352,6 @@
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -4573,10 +4579,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4708,6 +4710,23 @@
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -5058,10 +5077,10 @@
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
-      <c r="AF1" s="584"/>
-      <c r="AG1" s="534"/>
-      <c r="AH1" s="534"/>
-      <c r="AI1" s="534"/>
+      <c r="AF1" s="583"/>
+      <c r="AG1" s="533"/>
+      <c r="AH1" s="533"/>
+      <c r="AI1" s="533"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="6"/>
       <c r="AL1" s="6"/>
@@ -6217,48 +6236,48 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="598" t="s">
+      <c r="H6" s="597" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="558"/>
-      <c r="J6" s="558"/>
-      <c r="K6" s="558"/>
-      <c r="L6" s="605" t="s">
+      <c r="I6" s="557"/>
+      <c r="J6" s="557"/>
+      <c r="K6" s="557"/>
+      <c r="L6" s="604" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="558"/>
-      <c r="N6" s="558"/>
-      <c r="O6" s="559"/>
-      <c r="P6" s="557" t="s">
+      <c r="M6" s="557"/>
+      <c r="N6" s="557"/>
+      <c r="O6" s="558"/>
+      <c r="P6" s="556" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="558"/>
-      <c r="R6" s="558"/>
-      <c r="S6" s="559"/>
-      <c r="T6" s="596" t="s">
+      <c r="Q6" s="557"/>
+      <c r="R6" s="557"/>
+      <c r="S6" s="558"/>
+      <c r="T6" s="595" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="558"/>
-      <c r="V6" s="558"/>
-      <c r="W6" s="597"/>
-      <c r="X6" s="586" t="s">
+      <c r="U6" s="557"/>
+      <c r="V6" s="557"/>
+      <c r="W6" s="596"/>
+      <c r="X6" s="585" t="s">
         <v>14</v>
       </c>
-      <c r="Y6" s="558"/>
-      <c r="Z6" s="558"/>
-      <c r="AA6" s="558"/>
-      <c r="AB6" s="605" t="s">
+      <c r="Y6" s="557"/>
+      <c r="Z6" s="557"/>
+      <c r="AA6" s="557"/>
+      <c r="AB6" s="604" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="558"/>
-      <c r="AD6" s="558"/>
-      <c r="AE6" s="559"/>
-      <c r="AF6" s="590" t="s">
+      <c r="AC6" s="557"/>
+      <c r="AD6" s="557"/>
+      <c r="AE6" s="558"/>
+      <c r="AF6" s="589" t="s">
         <v>16</v>
       </c>
-      <c r="AG6" s="558"/>
-      <c r="AH6" s="558"/>
-      <c r="AI6" s="583"/>
+      <c r="AG6" s="557"/>
+      <c r="AH6" s="557"/>
+      <c r="AI6" s="582"/>
       <c r="AJ6" s="14"/>
       <c r="AK6" s="6"/>
       <c r="AL6" s="6"/>
@@ -6457,42 +6476,42 @@
       <c r="HW6" s="6"/>
     </row>
     <row r="7" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="277"/>
-      <c r="B7" s="277"/>
-      <c r="C7" s="277"/>
-      <c r="D7" s="277"/>
-      <c r="E7" s="277"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="279"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118"/>
-      <c r="J7" s="118"/>
-      <c r="K7" s="118"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118"/>
-      <c r="N7" s="118"/>
-      <c r="O7" s="118"/>
-      <c r="P7" s="118"/>
-      <c r="Q7" s="118"/>
-      <c r="R7" s="118"/>
-      <c r="S7" s="118"/>
-      <c r="T7" s="118"/>
-      <c r="U7" s="118"/>
-      <c r="V7" s="118"/>
-      <c r="W7" s="118"/>
-      <c r="X7" s="118"/>
-      <c r="Y7" s="118"/>
-      <c r="Z7" s="118"/>
-      <c r="AA7" s="118"/>
-      <c r="AB7" s="118"/>
-      <c r="AC7" s="118"/>
-      <c r="AD7" s="118"/>
-      <c r="AE7" s="118"/>
-      <c r="AF7" s="118"/>
-      <c r="AG7" s="118"/>
-      <c r="AH7" s="118"/>
-      <c r="AI7" s="118"/>
-      <c r="AJ7" s="151"/>
+      <c r="A7" s="276"/>
+      <c r="B7" s="276"/>
+      <c r="C7" s="276"/>
+      <c r="D7" s="276"/>
+      <c r="E7" s="276"/>
+      <c r="F7" s="277"/>
+      <c r="G7" s="278"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+      <c r="N7" s="117"/>
+      <c r="O7" s="117"/>
+      <c r="P7" s="117"/>
+      <c r="Q7" s="117"/>
+      <c r="R7" s="117"/>
+      <c r="S7" s="117"/>
+      <c r="T7" s="117"/>
+      <c r="U7" s="117"/>
+      <c r="V7" s="117"/>
+      <c r="W7" s="117"/>
+      <c r="X7" s="117"/>
+      <c r="Y7" s="117"/>
+      <c r="Z7" s="117"/>
+      <c r="AA7" s="117"/>
+      <c r="AB7" s="117"/>
+      <c r="AC7" s="117"/>
+      <c r="AD7" s="117"/>
+      <c r="AE7" s="117"/>
+      <c r="AF7" s="117"/>
+      <c r="AG7" s="117"/>
+      <c r="AH7" s="117"/>
+      <c r="AI7" s="117"/>
+      <c r="AJ7" s="150"/>
       <c r="AK7" s="6"/>
       <c r="AL7" s="6"/>
       <c r="AM7" s="6"/>
@@ -6690,46 +6709,46 @@
       <c r="HW7" s="6"/>
     </row>
     <row r="8" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="538"/>
-      <c r="B8" s="538"/>
-      <c r="C8" s="538"/>
-      <c r="D8" s="538"/>
-      <c r="E8" s="538"/>
-      <c r="F8" s="593" t="s">
+      <c r="A8" s="537"/>
+      <c r="B8" s="537"/>
+      <c r="C8" s="537"/>
+      <c r="D8" s="537"/>
+      <c r="E8" s="537"/>
+      <c r="F8" s="592" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="626" t="s">
+      <c r="G8" s="625" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="280"/>
-      <c r="I8" s="281"/>
-      <c r="J8" s="281"/>
-      <c r="K8" s="282"/>
-      <c r="L8" s="181"/>
-      <c r="M8" s="181"/>
-      <c r="N8" s="181"/>
-      <c r="O8" s="182"/>
-      <c r="P8" s="283"/>
-      <c r="Q8" s="283"/>
-      <c r="R8" s="283"/>
-      <c r="S8" s="283"/>
-      <c r="T8" s="284"/>
-      <c r="U8" s="283"/>
-      <c r="V8" s="283"/>
-      <c r="W8" s="283"/>
-      <c r="X8" s="284"/>
-      <c r="Y8" s="283"/>
-      <c r="Z8" s="283"/>
-      <c r="AA8" s="285"/>
-      <c r="AB8" s="234"/>
-      <c r="AC8" s="181"/>
-      <c r="AD8" s="181"/>
-      <c r="AE8" s="182"/>
-      <c r="AF8" s="283"/>
-      <c r="AG8" s="283"/>
-      <c r="AH8" s="283"/>
-      <c r="AI8" s="285"/>
-      <c r="AJ8" s="157"/>
+      <c r="H8" s="279"/>
+      <c r="I8" s="280"/>
+      <c r="J8" s="280"/>
+      <c r="K8" s="281"/>
+      <c r="L8" s="180"/>
+      <c r="M8" s="180"/>
+      <c r="N8" s="180"/>
+      <c r="O8" s="181"/>
+      <c r="P8" s="282"/>
+      <c r="Q8" s="282"/>
+      <c r="R8" s="282"/>
+      <c r="S8" s="282"/>
+      <c r="T8" s="283"/>
+      <c r="U8" s="282"/>
+      <c r="V8" s="282"/>
+      <c r="W8" s="282"/>
+      <c r="X8" s="283"/>
+      <c r="Y8" s="282"/>
+      <c r="Z8" s="282"/>
+      <c r="AA8" s="284"/>
+      <c r="AB8" s="233"/>
+      <c r="AC8" s="180"/>
+      <c r="AD8" s="180"/>
+      <c r="AE8" s="181"/>
+      <c r="AF8" s="282"/>
+      <c r="AG8" s="282"/>
+      <c r="AH8" s="282"/>
+      <c r="AI8" s="284"/>
+      <c r="AJ8" s="156"/>
       <c r="AK8" s="6"/>
       <c r="AL8" s="6"/>
       <c r="AM8" s="6"/>
@@ -6927,42 +6946,42 @@
       <c r="HW8" s="6"/>
     </row>
     <row r="9" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="536"/>
-      <c r="B9" s="536"/>
-      <c r="C9" s="536"/>
-      <c r="D9" s="536"/>
-      <c r="E9" s="536"/>
-      <c r="F9" s="594"/>
-      <c r="G9" s="549"/>
-      <c r="H9" s="264"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="262"/>
+      <c r="A9" s="535"/>
+      <c r="B9" s="535"/>
+      <c r="C9" s="535"/>
+      <c r="D9" s="535"/>
+      <c r="E9" s="535"/>
+      <c r="F9" s="593"/>
+      <c r="G9" s="548"/>
+      <c r="H9" s="263"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="261"/>
       <c r="L9" s="26"/>
       <c r="M9" s="26"/>
       <c r="N9" s="26"/>
-      <c r="O9" s="167"/>
+      <c r="O9" s="166"/>
       <c r="P9" s="24"/>
       <c r="Q9" s="24"/>
       <c r="R9" s="24"/>
       <c r="S9" s="24"/>
-      <c r="T9" s="269"/>
+      <c r="T9" s="268"/>
       <c r="U9" s="24"/>
       <c r="V9" s="24"/>
       <c r="W9" s="24"/>
-      <c r="X9" s="269"/>
+      <c r="X9" s="268"/>
       <c r="Y9" s="24"/>
       <c r="Z9" s="24"/>
-      <c r="AA9" s="270"/>
-      <c r="AB9" s="168"/>
+      <c r="AA9" s="269"/>
+      <c r="AB9" s="167"/>
       <c r="AC9" s="26"/>
       <c r="AD9" s="26"/>
-      <c r="AE9" s="167"/>
+      <c r="AE9" s="166"/>
       <c r="AF9" s="29"/>
       <c r="AG9" s="29"/>
       <c r="AH9" s="29"/>
-      <c r="AI9" s="204"/>
-      <c r="AJ9" s="157"/>
+      <c r="AI9" s="203"/>
+      <c r="AJ9" s="156"/>
       <c r="AK9" s="6"/>
       <c r="AL9" s="6"/>
       <c r="AM9" s="6"/>
@@ -7160,42 +7179,42 @@
       <c r="HW9" s="6"/>
     </row>
     <row r="10" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="537"/>
-      <c r="B10" s="537"/>
-      <c r="C10" s="537"/>
-      <c r="D10" s="537"/>
-      <c r="E10" s="537"/>
-      <c r="F10" s="594"/>
-      <c r="G10" s="555"/>
-      <c r="H10" s="286"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="287"/>
+      <c r="A10" s="536"/>
+      <c r="B10" s="536"/>
+      <c r="C10" s="536"/>
+      <c r="D10" s="536"/>
+      <c r="E10" s="536"/>
+      <c r="F10" s="593"/>
+      <c r="G10" s="554"/>
+      <c r="H10" s="285"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="286"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
-      <c r="O10" s="167"/>
+      <c r="O10" s="166"/>
       <c r="P10" s="34"/>
       <c r="Q10" s="34"/>
       <c r="R10" s="34"/>
       <c r="S10" s="34"/>
-      <c r="T10" s="288"/>
+      <c r="T10" s="287"/>
       <c r="U10" s="34"/>
       <c r="V10" s="34"/>
       <c r="W10" s="34"/>
-      <c r="X10" s="289"/>
-      <c r="Y10" s="118"/>
+      <c r="X10" s="288"/>
+      <c r="Y10" s="117"/>
       <c r="Z10" s="34"/>
-      <c r="AA10" s="290"/>
-      <c r="AB10" s="168"/>
+      <c r="AA10" s="289"/>
+      <c r="AB10" s="167"/>
       <c r="AC10" s="26"/>
       <c r="AD10" s="26"/>
-      <c r="AE10" s="167"/>
+      <c r="AE10" s="166"/>
       <c r="AF10" s="32"/>
       <c r="AG10" s="32"/>
       <c r="AH10" s="33"/>
-      <c r="AI10" s="291"/>
-      <c r="AJ10" s="292"/>
+      <c r="AI10" s="290"/>
+      <c r="AJ10" s="291"/>
       <c r="AK10" s="6"/>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6"/>
@@ -7393,52 +7412,52 @@
       <c r="HW10" s="6"/>
     </row>
     <row r="11" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="629">
+      <c r="A11" s="628">
         <v>7</v>
       </c>
-      <c r="B11" s="539">
+      <c r="B11" s="538">
         <v>6</v>
       </c>
-      <c r="C11" s="539">
+      <c r="C11" s="538">
         <v>3</v>
       </c>
-      <c r="D11" s="539">
+      <c r="D11" s="538">
         <v>1</v>
       </c>
-      <c r="E11" s="541"/>
-      <c r="F11" s="594"/>
-      <c r="G11" s="561" t="s">
+      <c r="E11" s="540"/>
+      <c r="F11" s="593"/>
+      <c r="G11" s="560" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="264"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="265"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="106"/>
-      <c r="O11" s="185"/>
-      <c r="P11" s="257"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="293"/>
-      <c r="U11" s="294"/>
-      <c r="V11" s="294"/>
-      <c r="W11" s="294"/>
-      <c r="X11" s="295"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="296"/>
-      <c r="AB11" s="209"/>
-      <c r="AC11" s="210"/>
-      <c r="AD11" s="210"/>
-      <c r="AE11" s="211"/>
-      <c r="AF11" s="133"/>
-      <c r="AG11" s="133"/>
-      <c r="AH11" s="133"/>
-      <c r="AI11" s="275"/>
-      <c r="AJ11" s="122"/>
+      <c r="H11" s="263"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="184"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="292"/>
+      <c r="U11" s="293"/>
+      <c r="V11" s="293"/>
+      <c r="W11" s="293"/>
+      <c r="X11" s="294"/>
+      <c r="Y11" s="37"/>
+      <c r="Z11" s="37"/>
+      <c r="AA11" s="295"/>
+      <c r="AB11" s="208"/>
+      <c r="AC11" s="209"/>
+      <c r="AD11" s="209"/>
+      <c r="AE11" s="210"/>
+      <c r="AF11" s="132"/>
+      <c r="AG11" s="132"/>
+      <c r="AH11" s="132"/>
+      <c r="AI11" s="274"/>
+      <c r="AJ11" s="121"/>
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -7636,42 +7655,42 @@
       <c r="HW11" s="6"/>
     </row>
     <row r="12" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="536"/>
-      <c r="B12" s="536"/>
-      <c r="C12" s="536"/>
-      <c r="D12" s="536"/>
-      <c r="E12" s="536"/>
-      <c r="F12" s="594"/>
-      <c r="G12" s="549"/>
-      <c r="H12" s="264"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="262"/>
+      <c r="A12" s="535"/>
+      <c r="B12" s="535"/>
+      <c r="C12" s="535"/>
+      <c r="D12" s="535"/>
+      <c r="E12" s="535"/>
+      <c r="F12" s="593"/>
+      <c r="G12" s="548"/>
+      <c r="H12" s="263"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="261"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
       <c r="N12" s="26"/>
-      <c r="O12" s="167"/>
-      <c r="P12" s="264"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="297"/>
-      <c r="U12" s="86"/>
-      <c r="V12" s="86"/>
-      <c r="W12" s="163"/>
-      <c r="X12" s="203"/>
+      <c r="O12" s="166"/>
+      <c r="P12" s="263"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="296"/>
+      <c r="U12" s="85"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="162"/>
+      <c r="X12" s="202"/>
       <c r="Y12" s="32"/>
       <c r="Z12" s="32"/>
-      <c r="AA12" s="207"/>
-      <c r="AB12" s="153"/>
+      <c r="AA12" s="206"/>
+      <c r="AB12" s="152"/>
       <c r="AC12" s="10"/>
       <c r="AD12" s="10"/>
-      <c r="AE12" s="146"/>
+      <c r="AE12" s="145"/>
       <c r="AF12" s="29"/>
       <c r="AG12" s="29"/>
       <c r="AH12" s="29"/>
-      <c r="AI12" s="204"/>
-      <c r="AJ12" s="126"/>
+      <c r="AI12" s="203"/>
+      <c r="AJ12" s="125"/>
       <c r="AK12" s="6"/>
       <c r="AL12" s="6"/>
       <c r="AM12" s="6"/>
@@ -7869,42 +7888,42 @@
       <c r="HW12" s="6"/>
     </row>
     <row r="13" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="537"/>
-      <c r="B13" s="537"/>
-      <c r="C13" s="537"/>
-      <c r="D13" s="537"/>
-      <c r="E13" s="537"/>
-      <c r="F13" s="594"/>
-      <c r="G13" s="555"/>
-      <c r="H13" s="261"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="298"/>
+      <c r="A13" s="536"/>
+      <c r="B13" s="536"/>
+      <c r="C13" s="536"/>
+      <c r="D13" s="536"/>
+      <c r="E13" s="536"/>
+      <c r="F13" s="593"/>
+      <c r="G13" s="554"/>
+      <c r="H13" s="260"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="297"/>
       <c r="L13" s="26"/>
       <c r="M13" s="26"/>
       <c r="N13" s="26"/>
-      <c r="O13" s="167"/>
+      <c r="O13" s="166"/>
       <c r="P13" s="29"/>
       <c r="Q13" s="29"/>
       <c r="R13" s="29"/>
       <c r="S13" s="29"/>
-      <c r="T13" s="299"/>
-      <c r="U13" s="162"/>
-      <c r="V13" s="162"/>
+      <c r="T13" s="298"/>
+      <c r="U13" s="161"/>
+      <c r="V13" s="161"/>
       <c r="W13" s="10"/>
-      <c r="X13" s="300"/>
-      <c r="Y13" s="121"/>
-      <c r="Z13" s="121"/>
-      <c r="AA13" s="255"/>
-      <c r="AB13" s="153"/>
+      <c r="X13" s="299"/>
+      <c r="Y13" s="120"/>
+      <c r="Z13" s="120"/>
+      <c r="AA13" s="254"/>
+      <c r="AB13" s="152"/>
       <c r="AC13" s="10"/>
       <c r="AD13" s="10"/>
-      <c r="AE13" s="146"/>
-      <c r="AF13" s="51"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="129"/>
-      <c r="AI13" s="301"/>
-      <c r="AJ13" s="131"/>
+      <c r="AE13" s="145"/>
+      <c r="AF13" s="50"/>
+      <c r="AG13" s="50"/>
+      <c r="AH13" s="128"/>
+      <c r="AI13" s="300"/>
+      <c r="AJ13" s="130"/>
       <c r="AK13" s="6"/>
       <c r="AL13" s="6"/>
       <c r="AM13" s="6"/>
@@ -8102,58 +8121,58 @@
       <c r="HW13" s="6"/>
     </row>
     <row r="14" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="539">
+      <c r="A14" s="538">
         <v>20</v>
       </c>
-      <c r="B14" s="539">
+      <c r="B14" s="538">
         <v>20</v>
       </c>
-      <c r="C14" s="539">
+      <c r="C14" s="538">
         <v>17</v>
       </c>
-      <c r="D14" s="539">
+      <c r="D14" s="538">
         <v>15</v>
       </c>
-      <c r="E14" s="541"/>
-      <c r="F14" s="594"/>
-      <c r="G14" s="567" t="s">
+      <c r="E14" s="540"/>
+      <c r="F14" s="593"/>
+      <c r="G14" s="566" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="257"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="258"/>
-      <c r="L14" s="564"/>
-      <c r="M14" s="530"/>
-      <c r="N14" s="184"/>
-      <c r="O14" s="164"/>
-      <c r="P14" s="528"/>
-      <c r="Q14" s="530"/>
-      <c r="R14" s="302"/>
-      <c r="S14" s="303"/>
-      <c r="T14" s="565" t="s">
+      <c r="H14" s="256"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="257"/>
+      <c r="L14" s="563"/>
+      <c r="M14" s="529"/>
+      <c r="N14" s="183"/>
+      <c r="O14" s="163"/>
+      <c r="P14" s="527"/>
+      <c r="Q14" s="529"/>
+      <c r="R14" s="301"/>
+      <c r="S14" s="302"/>
+      <c r="T14" s="564" t="s">
         <v>45</v>
       </c>
-      <c r="U14" s="566"/>
-      <c r="V14" s="566"/>
-      <c r="W14" s="566"/>
-      <c r="X14" s="632" t="s">
+      <c r="U14" s="565"/>
+      <c r="V14" s="565"/>
+      <c r="W14" s="565"/>
+      <c r="X14" s="631" t="s">
         <v>42</v>
       </c>
-      <c r="Y14" s="566"/>
-      <c r="Z14" s="566"/>
-      <c r="AA14" s="633"/>
-      <c r="AB14" s="564" t="s">
+      <c r="Y14" s="565"/>
+      <c r="Z14" s="565"/>
+      <c r="AA14" s="632"/>
+      <c r="AB14" s="563" t="s">
         <v>46</v>
       </c>
-      <c r="AC14" s="529"/>
-      <c r="AD14" s="529"/>
-      <c r="AE14" s="530"/>
+      <c r="AC14" s="528"/>
+      <c r="AD14" s="528"/>
+      <c r="AE14" s="529"/>
       <c r="AF14" s="26"/>
       <c r="AG14" s="26"/>
       <c r="AH14" s="26"/>
-      <c r="AI14" s="167"/>
-      <c r="AJ14" s="157"/>
+      <c r="AI14" s="166"/>
+      <c r="AJ14" s="156"/>
       <c r="AK14" s="6"/>
       <c r="AL14" s="6"/>
       <c r="AM14" s="6"/>
@@ -8351,42 +8370,42 @@
       <c r="HW14" s="6"/>
     </row>
     <row r="15" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A15" s="536"/>
-      <c r="B15" s="536"/>
-      <c r="C15" s="536"/>
-      <c r="D15" s="536"/>
-      <c r="E15" s="536"/>
-      <c r="F15" s="594"/>
-      <c r="G15" s="549"/>
-      <c r="H15" s="304"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="260"/>
-      <c r="L15" s="569"/>
-      <c r="M15" s="532"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="244"/>
-      <c r="P15" s="551"/>
-      <c r="Q15" s="532"/>
-      <c r="R15" s="165"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="213"/>
-      <c r="U15" s="65"/>
-      <c r="V15" s="65"/>
+      <c r="A15" s="535"/>
+      <c r="B15" s="535"/>
+      <c r="C15" s="535"/>
+      <c r="D15" s="535"/>
+      <c r="E15" s="535"/>
+      <c r="F15" s="593"/>
+      <c r="G15" s="548"/>
+      <c r="H15" s="303"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="259"/>
+      <c r="L15" s="568"/>
+      <c r="M15" s="531"/>
+      <c r="N15" s="64"/>
+      <c r="O15" s="243"/>
+      <c r="P15" s="550"/>
+      <c r="Q15" s="531"/>
+      <c r="R15" s="164"/>
+      <c r="S15" s="61"/>
+      <c r="T15" s="212"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
       <c r="W15" s="6"/>
-      <c r="X15" s="171"/>
-      <c r="Y15" s="65"/>
-      <c r="Z15" s="65"/>
-      <c r="AA15" s="216"/>
-      <c r="AB15" s="213"/>
-      <c r="AC15" s="65"/>
-      <c r="AD15" s="65"/>
-      <c r="AE15" s="244"/>
+      <c r="X15" s="170"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="64"/>
+      <c r="AA15" s="215"/>
+      <c r="AB15" s="212"/>
+      <c r="AC15" s="64"/>
+      <c r="AD15" s="64"/>
+      <c r="AE15" s="243"/>
       <c r="AF15" s="26"/>
       <c r="AG15" s="26"/>
       <c r="AH15" s="26"/>
-      <c r="AI15" s="167"/>
-      <c r="AJ15" s="157"/>
+      <c r="AI15" s="166"/>
+      <c r="AJ15" s="156"/>
       <c r="AK15" s="6"/>
       <c r="AL15" s="6"/>
       <c r="AM15" s="6"/>
@@ -8584,54 +8603,54 @@
       <c r="HW15" s="6"/>
     </row>
     <row r="16" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A16" s="537"/>
-      <c r="B16" s="537"/>
-      <c r="C16" s="537"/>
-      <c r="D16" s="537"/>
-      <c r="E16" s="537"/>
-      <c r="F16" s="594"/>
-      <c r="G16" s="568"/>
-      <c r="H16" s="305"/>
-      <c r="I16" s="306"/>
-      <c r="J16" s="306"/>
-      <c r="K16" s="307"/>
-      <c r="L16" s="581"/>
-      <c r="M16" s="532"/>
-      <c r="N16" s="308"/>
-      <c r="O16" s="309"/>
-      <c r="P16" s="556"/>
-      <c r="Q16" s="532"/>
-      <c r="R16" s="310"/>
-      <c r="S16" s="215"/>
-      <c r="T16" s="311" t="s">
+      <c r="A16" s="536"/>
+      <c r="B16" s="536"/>
+      <c r="C16" s="536"/>
+      <c r="D16" s="536"/>
+      <c r="E16" s="536"/>
+      <c r="F16" s="593"/>
+      <c r="G16" s="567"/>
+      <c r="H16" s="304"/>
+      <c r="I16" s="305"/>
+      <c r="J16" s="305"/>
+      <c r="K16" s="306"/>
+      <c r="L16" s="580"/>
+      <c r="M16" s="531"/>
+      <c r="N16" s="307"/>
+      <c r="O16" s="308"/>
+      <c r="P16" s="555"/>
+      <c r="Q16" s="531"/>
+      <c r="R16" s="309"/>
+      <c r="S16" s="214"/>
+      <c r="T16" s="310" t="s">
         <v>48</v>
       </c>
-      <c r="U16" s="312"/>
-      <c r="V16" s="312"/>
-      <c r="W16" s="313" t="s">
+      <c r="U16" s="311"/>
+      <c r="V16" s="311"/>
+      <c r="W16" s="312" t="s">
         <v>38</v>
       </c>
-      <c r="X16" s="311" t="s">
+      <c r="X16" s="310" t="s">
         <v>37</v>
       </c>
-      <c r="Y16" s="312"/>
-      <c r="Z16" s="314"/>
-      <c r="AA16" s="315" t="s">
+      <c r="Y16" s="311"/>
+      <c r="Z16" s="313"/>
+      <c r="AA16" s="314" t="s">
         <v>31</v>
       </c>
-      <c r="AB16" s="311" t="s">
+      <c r="AB16" s="310" t="s">
         <v>21</v>
       </c>
-      <c r="AC16" s="312"/>
-      <c r="AD16" s="312"/>
-      <c r="AE16" s="315" t="s">
+      <c r="AC16" s="311"/>
+      <c r="AD16" s="311"/>
+      <c r="AE16" s="314" t="s">
         <v>40</v>
       </c>
       <c r="AF16" s="26"/>
       <c r="AG16" s="26"/>
       <c r="AH16" s="26"/>
-      <c r="AI16" s="167"/>
-      <c r="AJ16" s="316"/>
+      <c r="AI16" s="166"/>
+      <c r="AJ16" s="315"/>
       <c r="AK16" s="6"/>
       <c r="AL16" s="6"/>
       <c r="AM16" s="6"/>
@@ -8829,60 +8848,60 @@
       <c r="HW16" s="6"/>
     </row>
     <row r="17" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="541">
+      <c r="A17" s="540">
         <v>0</v>
       </c>
-      <c r="B17" s="541">
+      <c r="B17" s="540">
         <v>0</v>
       </c>
-      <c r="C17" s="541">
+      <c r="C17" s="540">
         <v>0</v>
       </c>
-      <c r="D17" s="539">
+      <c r="D17" s="538">
         <v>29</v>
       </c>
-      <c r="E17" s="541">
+      <c r="E17" s="540">
         <v>0</v>
       </c>
-      <c r="F17" s="594"/>
-      <c r="G17" s="570" t="s">
+      <c r="F17" s="593"/>
+      <c r="G17" s="569" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="317"/>
-      <c r="I17" s="318"/>
-      <c r="J17" s="318"/>
-      <c r="K17" s="319"/>
-      <c r="L17" s="547"/>
-      <c r="M17" s="532"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="320"/>
-      <c r="P17" s="560"/>
-      <c r="Q17" s="532"/>
+      <c r="H17" s="316"/>
+      <c r="I17" s="317"/>
+      <c r="J17" s="317"/>
+      <c r="K17" s="318"/>
+      <c r="L17" s="546"/>
+      <c r="M17" s="531"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="319"/>
+      <c r="P17" s="559"/>
+      <c r="Q17" s="531"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
-      <c r="T17" s="600" t="s">
+      <c r="T17" s="599" t="s">
         <v>43</v>
       </c>
-      <c r="U17" s="534"/>
-      <c r="V17" s="534"/>
-      <c r="W17" s="534"/>
-      <c r="X17" s="572" t="s">
+      <c r="U17" s="533"/>
+      <c r="V17" s="533"/>
+      <c r="W17" s="533"/>
+      <c r="X17" s="571" t="s">
         <v>44</v>
       </c>
-      <c r="Y17" s="534"/>
-      <c r="Z17" s="534"/>
-      <c r="AA17" s="532"/>
-      <c r="AB17" s="617" t="s">
+      <c r="Y17" s="533"/>
+      <c r="Z17" s="533"/>
+      <c r="AA17" s="531"/>
+      <c r="AB17" s="616" t="s">
         <v>47</v>
       </c>
-      <c r="AC17" s="618"/>
-      <c r="AD17" s="618"/>
-      <c r="AE17" s="619"/>
-      <c r="AF17" s="321"/>
-      <c r="AG17" s="321"/>
-      <c r="AH17" s="321"/>
-      <c r="AI17" s="322"/>
-      <c r="AJ17" s="143"/>
+      <c r="AC17" s="617"/>
+      <c r="AD17" s="617"/>
+      <c r="AE17" s="618"/>
+      <c r="AF17" s="320"/>
+      <c r="AG17" s="320"/>
+      <c r="AH17" s="320"/>
+      <c r="AI17" s="321"/>
+      <c r="AJ17" s="142"/>
       <c r="AK17" s="6"/>
       <c r="AL17" s="6"/>
       <c r="AM17" s="6"/>
@@ -9080,42 +9099,42 @@
       <c r="HW17" s="6"/>
     </row>
     <row r="18" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="536"/>
-      <c r="B18" s="536"/>
-      <c r="C18" s="536"/>
-      <c r="D18" s="536"/>
-      <c r="E18" s="536"/>
-      <c r="F18" s="594"/>
-      <c r="G18" s="549"/>
-      <c r="H18" s="259"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="260"/>
-      <c r="L18" s="155"/>
-      <c r="M18" s="156"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="244"/>
-      <c r="P18" s="76"/>
-      <c r="Q18" s="85"/>
+      <c r="A18" s="535"/>
+      <c r="B18" s="535"/>
+      <c r="C18" s="535"/>
+      <c r="D18" s="535"/>
+      <c r="E18" s="535"/>
+      <c r="F18" s="593"/>
+      <c r="G18" s="548"/>
+      <c r="H18" s="258"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="66"/>
+      <c r="K18" s="259"/>
+      <c r="L18" s="154"/>
+      <c r="M18" s="155"/>
+      <c r="N18" s="64"/>
+      <c r="O18" s="243"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="84"/>
       <c r="R18" s="6"/>
-      <c r="S18" s="173"/>
-      <c r="T18" s="171"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="65"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="213"/>
-      <c r="Y18" s="65"/>
-      <c r="Z18" s="65"/>
-      <c r="AA18" s="145"/>
-      <c r="AB18" s="213"/>
-      <c r="AC18" s="65"/>
-      <c r="AD18" s="65"/>
-      <c r="AE18" s="244"/>
+      <c r="S18" s="172"/>
+      <c r="T18" s="170"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="82"/>
+      <c r="X18" s="212"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="64"/>
+      <c r="AA18" s="144"/>
+      <c r="AB18" s="212"/>
+      <c r="AC18" s="64"/>
+      <c r="AD18" s="64"/>
+      <c r="AE18" s="243"/>
       <c r="AF18" s="26"/>
       <c r="AG18" s="26"/>
       <c r="AH18" s="26"/>
-      <c r="AI18" s="167"/>
-      <c r="AJ18" s="195"/>
+      <c r="AI18" s="166"/>
+      <c r="AJ18" s="194"/>
       <c r="AK18" s="6"/>
       <c r="AL18" s="6"/>
       <c r="AM18" s="6"/>
@@ -9313,54 +9332,54 @@
       <c r="HW18" s="6"/>
     </row>
     <row r="19" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="537"/>
-      <c r="B19" s="537"/>
-      <c r="C19" s="537"/>
-      <c r="D19" s="537"/>
-      <c r="E19" s="537"/>
-      <c r="F19" s="594"/>
-      <c r="G19" s="555"/>
-      <c r="H19" s="323"/>
-      <c r="I19" s="324"/>
-      <c r="J19" s="89"/>
-      <c r="K19" s="267"/>
-      <c r="L19" s="628"/>
-      <c r="M19" s="553"/>
-      <c r="N19" s="116"/>
-      <c r="O19" s="251"/>
-      <c r="P19" s="577"/>
-      <c r="Q19" s="553"/>
-      <c r="R19" s="196"/>
-      <c r="S19" s="325"/>
-      <c r="T19" s="221" t="s">
+      <c r="A19" s="536"/>
+      <c r="B19" s="536"/>
+      <c r="C19" s="536"/>
+      <c r="D19" s="536"/>
+      <c r="E19" s="536"/>
+      <c r="F19" s="593"/>
+      <c r="G19" s="554"/>
+      <c r="H19" s="322"/>
+      <c r="I19" s="323"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="266"/>
+      <c r="L19" s="627"/>
+      <c r="M19" s="552"/>
+      <c r="N19" s="115"/>
+      <c r="O19" s="250"/>
+      <c r="P19" s="576"/>
+      <c r="Q19" s="552"/>
+      <c r="R19" s="195"/>
+      <c r="S19" s="324"/>
+      <c r="T19" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="U19" s="101"/>
-      <c r="V19" s="326"/>
-      <c r="W19" s="103" t="s">
+      <c r="U19" s="100"/>
+      <c r="V19" s="325"/>
+      <c r="W19" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="X19" s="221" t="s">
+      <c r="X19" s="220" t="s">
         <v>49</v>
       </c>
-      <c r="Y19" s="101"/>
-      <c r="Z19" s="101"/>
-      <c r="AA19" s="222" t="s">
+      <c r="Y19" s="100"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="221" t="s">
         <v>39</v>
       </c>
-      <c r="AB19" s="221" t="s">
+      <c r="AB19" s="220" t="s">
         <v>23</v>
       </c>
-      <c r="AC19" s="101"/>
-      <c r="AD19" s="101"/>
-      <c r="AE19" s="222" t="s">
+      <c r="AC19" s="100"/>
+      <c r="AD19" s="100"/>
+      <c r="AE19" s="221" t="s">
         <v>41</v>
       </c>
       <c r="AF19" s="26"/>
       <c r="AG19" s="26"/>
       <c r="AH19" s="26"/>
-      <c r="AI19" s="167"/>
-      <c r="AJ19" s="131"/>
+      <c r="AI19" s="166"/>
+      <c r="AJ19" s="130"/>
       <c r="AK19" s="6"/>
       <c r="AL19" s="6"/>
       <c r="AM19" s="6"/>
@@ -9558,43 +9577,43 @@
       <c r="HW19" s="6"/>
     </row>
     <row r="20" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="542"/>
-      <c r="B20" s="542"/>
-      <c r="C20" s="542"/>
-      <c r="D20" s="542"/>
-      <c r="E20" s="542"/>
-      <c r="F20" s="594"/>
-      <c r="G20" s="570" t="s">
+      <c r="A20" s="541"/>
+      <c r="B20" s="541"/>
+      <c r="C20" s="541"/>
+      <c r="D20" s="541"/>
+      <c r="E20" s="541"/>
+      <c r="F20" s="593"/>
+      <c r="G20" s="569" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="168"/>
+      <c r="H20" s="167"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
-      <c r="K20" s="167"/>
-      <c r="L20" s="224"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="630"/>
-      <c r="O20" s="532"/>
-      <c r="P20" s="157"/>
-      <c r="Q20" s="158"/>
-      <c r="R20" s="585"/>
-      <c r="S20" s="534"/>
-      <c r="T20" s="153"/>
+      <c r="K20" s="166"/>
+      <c r="L20" s="223"/>
+      <c r="M20" s="144"/>
+      <c r="N20" s="629"/>
+      <c r="O20" s="531"/>
+      <c r="P20" s="156"/>
+      <c r="Q20" s="157"/>
+      <c r="R20" s="584"/>
+      <c r="S20" s="533"/>
+      <c r="T20" s="152"/>
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
       <c r="W20" s="10"/>
-      <c r="X20" s="153"/>
+      <c r="X20" s="152"/>
       <c r="Y20" s="10"/>
       <c r="Z20" s="10"/>
-      <c r="AA20" s="146"/>
-      <c r="AB20" s="153"/>
+      <c r="AA20" s="145"/>
+      <c r="AB20" s="152"/>
       <c r="AC20" s="10"/>
       <c r="AD20" s="10"/>
-      <c r="AE20" s="146"/>
-      <c r="AF20" s="327"/>
-      <c r="AG20" s="327"/>
-      <c r="AH20" s="327"/>
-      <c r="AI20" s="328"/>
+      <c r="AE20" s="145"/>
+      <c r="AF20" s="326"/>
+      <c r="AG20" s="326"/>
+      <c r="AH20" s="326"/>
+      <c r="AI20" s="327"/>
       <c r="AJ20" s="8"/>
       <c r="AK20" s="6"/>
       <c r="AL20" s="6"/>
@@ -9793,41 +9812,41 @@
       <c r="HW20" s="6"/>
     </row>
     <row r="21" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="536"/>
-      <c r="B21" s="536"/>
-      <c r="C21" s="536"/>
-      <c r="D21" s="536"/>
-      <c r="E21" s="536"/>
-      <c r="F21" s="594"/>
-      <c r="G21" s="549"/>
-      <c r="H21" s="168"/>
+      <c r="A21" s="535"/>
+      <c r="B21" s="535"/>
+      <c r="C21" s="535"/>
+      <c r="D21" s="535"/>
+      <c r="E21" s="535"/>
+      <c r="F21" s="593"/>
+      <c r="G21" s="548"/>
+      <c r="H21" s="167"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
-      <c r="K21" s="167"/>
-      <c r="L21" s="224"/>
-      <c r="M21" s="145"/>
-      <c r="N21" s="634"/>
-      <c r="O21" s="532"/>
-      <c r="P21" s="157"/>
-      <c r="Q21" s="158"/>
-      <c r="R21" s="604"/>
-      <c r="S21" s="534"/>
-      <c r="T21" s="153"/>
+      <c r="K21" s="166"/>
+      <c r="L21" s="223"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="633"/>
+      <c r="O21" s="531"/>
+      <c r="P21" s="156"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="603"/>
+      <c r="S21" s="533"/>
+      <c r="T21" s="152"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
-      <c r="X21" s="153"/>
+      <c r="X21" s="152"/>
       <c r="Y21" s="10"/>
       <c r="Z21" s="10"/>
-      <c r="AA21" s="146"/>
-      <c r="AB21" s="153"/>
+      <c r="AA21" s="145"/>
+      <c r="AB21" s="152"/>
       <c r="AC21" s="10"/>
       <c r="AD21" s="10"/>
-      <c r="AE21" s="146"/>
-      <c r="AF21" s="329"/>
-      <c r="AG21" s="329"/>
-      <c r="AH21" s="329"/>
-      <c r="AI21" s="330"/>
+      <c r="AE21" s="145"/>
+      <c r="AF21" s="328"/>
+      <c r="AG21" s="328"/>
+      <c r="AH21" s="328"/>
+      <c r="AI21" s="329"/>
       <c r="AJ21" s="8"/>
       <c r="AK21" s="6"/>
       <c r="AL21" s="6"/>
@@ -10026,41 +10045,41 @@
       <c r="HW21" s="6"/>
     </row>
     <row r="22" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="537"/>
-      <c r="B22" s="537"/>
-      <c r="C22" s="537"/>
-      <c r="D22" s="537"/>
-      <c r="E22" s="537"/>
-      <c r="F22" s="594"/>
-      <c r="G22" s="555"/>
-      <c r="H22" s="331"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="89"/>
-      <c r="K22" s="193"/>
-      <c r="L22" s="332"/>
-      <c r="M22" s="333"/>
-      <c r="N22" s="556"/>
-      <c r="O22" s="532"/>
-      <c r="P22" s="334"/>
-      <c r="Q22" s="335"/>
-      <c r="R22" s="571"/>
-      <c r="S22" s="534"/>
-      <c r="T22" s="229"/>
-      <c r="U22" s="91"/>
-      <c r="V22" s="91"/>
-      <c r="W22" s="91"/>
-      <c r="X22" s="229"/>
-      <c r="Y22" s="91"/>
-      <c r="Z22" s="91"/>
-      <c r="AA22" s="230"/>
-      <c r="AB22" s="153"/>
+      <c r="A22" s="536"/>
+      <c r="B22" s="536"/>
+      <c r="C22" s="536"/>
+      <c r="D22" s="536"/>
+      <c r="E22" s="536"/>
+      <c r="F22" s="593"/>
+      <c r="G22" s="554"/>
+      <c r="H22" s="330"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="192"/>
+      <c r="L22" s="331"/>
+      <c r="M22" s="332"/>
+      <c r="N22" s="555"/>
+      <c r="O22" s="531"/>
+      <c r="P22" s="333"/>
+      <c r="Q22" s="334"/>
+      <c r="R22" s="570"/>
+      <c r="S22" s="533"/>
+      <c r="T22" s="228"/>
+      <c r="U22" s="90"/>
+      <c r="V22" s="90"/>
+      <c r="W22" s="90"/>
+      <c r="X22" s="228"/>
+      <c r="Y22" s="90"/>
+      <c r="Z22" s="90"/>
+      <c r="AA22" s="229"/>
+      <c r="AB22" s="152"/>
       <c r="AC22" s="10"/>
       <c r="AD22" s="10"/>
-      <c r="AE22" s="146"/>
-      <c r="AF22" s="336"/>
-      <c r="AG22" s="337"/>
-      <c r="AH22" s="337"/>
-      <c r="AI22" s="338"/>
+      <c r="AE22" s="145"/>
+      <c r="AF22" s="335"/>
+      <c r="AG22" s="336"/>
+      <c r="AH22" s="336"/>
+      <c r="AI22" s="337"/>
       <c r="AJ22" s="8"/>
       <c r="AK22" s="6"/>
       <c r="AL22" s="6"/>
@@ -10259,43 +10278,43 @@
       <c r="HW22" s="6"/>
     </row>
     <row r="23" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="542"/>
-      <c r="B23" s="542"/>
-      <c r="C23" s="542"/>
-      <c r="D23" s="542"/>
-      <c r="E23" s="542"/>
-      <c r="F23" s="594"/>
-      <c r="G23" s="601" t="s">
+      <c r="A23" s="541"/>
+      <c r="B23" s="541"/>
+      <c r="C23" s="541"/>
+      <c r="D23" s="541"/>
+      <c r="E23" s="541"/>
+      <c r="F23" s="593"/>
+      <c r="G23" s="600" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="168"/>
+      <c r="H23" s="167"/>
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
-      <c r="K23" s="167"/>
-      <c r="L23" s="224"/>
-      <c r="M23" s="145"/>
-      <c r="N23" s="560"/>
-      <c r="O23" s="532"/>
-      <c r="P23" s="292"/>
-      <c r="Q23" s="339"/>
-      <c r="R23" s="625"/>
-      <c r="S23" s="534"/>
-      <c r="T23" s="288"/>
+      <c r="K23" s="166"/>
+      <c r="L23" s="223"/>
+      <c r="M23" s="144"/>
+      <c r="N23" s="559"/>
+      <c r="O23" s="531"/>
+      <c r="P23" s="291"/>
+      <c r="Q23" s="338"/>
+      <c r="R23" s="624"/>
+      <c r="S23" s="533"/>
+      <c r="T23" s="287"/>
       <c r="U23" s="34"/>
       <c r="V23" s="34"/>
       <c r="W23" s="34"/>
-      <c r="X23" s="153"/>
+      <c r="X23" s="152"/>
       <c r="Y23" s="10"/>
       <c r="Z23" s="10"/>
-      <c r="AA23" s="146"/>
-      <c r="AB23" s="209"/>
-      <c r="AC23" s="210"/>
-      <c r="AD23" s="210"/>
-      <c r="AE23" s="211"/>
+      <c r="AA23" s="145"/>
+      <c r="AB23" s="208"/>
+      <c r="AC23" s="209"/>
+      <c r="AD23" s="209"/>
+      <c r="AE23" s="210"/>
       <c r="AF23" s="29"/>
       <c r="AG23" s="29"/>
       <c r="AH23" s="34"/>
-      <c r="AI23" s="276"/>
+      <c r="AI23" s="275"/>
       <c r="AJ23" s="8"/>
       <c r="AK23" s="6"/>
       <c r="AL23" s="6"/>
@@ -10494,41 +10513,41 @@
       <c r="HW23" s="6"/>
     </row>
     <row r="24" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="536"/>
-      <c r="B24" s="536"/>
-      <c r="C24" s="536"/>
-      <c r="D24" s="536"/>
-      <c r="E24" s="536"/>
-      <c r="F24" s="594"/>
-      <c r="G24" s="549"/>
-      <c r="H24" s="168"/>
+      <c r="A24" s="535"/>
+      <c r="B24" s="535"/>
+      <c r="C24" s="535"/>
+      <c r="D24" s="535"/>
+      <c r="E24" s="535"/>
+      <c r="F24" s="593"/>
+      <c r="G24" s="548"/>
+      <c r="H24" s="167"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
-      <c r="K24" s="167"/>
-      <c r="L24" s="224"/>
-      <c r="M24" s="145"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="292"/>
-      <c r="Q24" s="339"/>
-      <c r="R24" s="76"/>
-      <c r="S24" s="173"/>
-      <c r="T24" s="288"/>
+      <c r="K24" s="166"/>
+      <c r="L24" s="223"/>
+      <c r="M24" s="144"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="84"/>
+      <c r="P24" s="291"/>
+      <c r="Q24" s="338"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="172"/>
+      <c r="T24" s="287"/>
       <c r="U24" s="34"/>
       <c r="V24" s="34"/>
       <c r="W24" s="34"/>
-      <c r="X24" s="153"/>
+      <c r="X24" s="152"/>
       <c r="Y24" s="10"/>
       <c r="Z24" s="10"/>
-      <c r="AA24" s="146"/>
-      <c r="AB24" s="153"/>
+      <c r="AA24" s="145"/>
+      <c r="AB24" s="152"/>
       <c r="AC24" s="10"/>
       <c r="AD24" s="10"/>
-      <c r="AE24" s="146"/>
+      <c r="AE24" s="145"/>
       <c r="AF24" s="29"/>
       <c r="AG24" s="29"/>
       <c r="AH24" s="34"/>
-      <c r="AI24" s="276"/>
+      <c r="AI24" s="275"/>
       <c r="AJ24" s="8"/>
       <c r="AK24" s="6"/>
       <c r="AL24" s="6"/>
@@ -10727,42 +10746,42 @@
       <c r="HW24" s="6"/>
     </row>
     <row r="25" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="537"/>
-      <c r="B25" s="537"/>
-      <c r="C25" s="537"/>
-      <c r="D25" s="537"/>
-      <c r="E25" s="537"/>
-      <c r="F25" s="595"/>
-      <c r="G25" s="602"/>
-      <c r="H25" s="168"/>
+      <c r="A25" s="536"/>
+      <c r="B25" s="536"/>
+      <c r="C25" s="536"/>
+      <c r="D25" s="536"/>
+      <c r="E25" s="536"/>
+      <c r="F25" s="594"/>
+      <c r="G25" s="601"/>
+      <c r="H25" s="167"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
-      <c r="K25" s="167"/>
-      <c r="L25" s="340"/>
-      <c r="M25" s="341"/>
-      <c r="N25" s="531"/>
-      <c r="O25" s="532"/>
-      <c r="P25" s="342"/>
-      <c r="Q25" s="343"/>
-      <c r="R25" s="533"/>
-      <c r="S25" s="534"/>
-      <c r="T25" s="288"/>
+      <c r="K25" s="166"/>
+      <c r="L25" s="339"/>
+      <c r="M25" s="340"/>
+      <c r="N25" s="530"/>
+      <c r="O25" s="531"/>
+      <c r="P25" s="341"/>
+      <c r="Q25" s="342"/>
+      <c r="R25" s="532"/>
+      <c r="S25" s="533"/>
+      <c r="T25" s="287"/>
       <c r="U25" s="34"/>
       <c r="V25" s="34"/>
       <c r="W25" s="34"/>
-      <c r="X25" s="153"/>
+      <c r="X25" s="152"/>
       <c r="Y25" s="10"/>
       <c r="Z25" s="10"/>
-      <c r="AA25" s="146"/>
-      <c r="AB25" s="153"/>
+      <c r="AA25" s="145"/>
+      <c r="AB25" s="152"/>
       <c r="AC25" s="10"/>
       <c r="AD25" s="10"/>
-      <c r="AE25" s="146"/>
-      <c r="AF25" s="344"/>
-      <c r="AG25" s="344"/>
-      <c r="AH25" s="345"/>
-      <c r="AI25" s="346"/>
-      <c r="AJ25" s="151"/>
+      <c r="AE25" s="145"/>
+      <c r="AF25" s="343"/>
+      <c r="AG25" s="343"/>
+      <c r="AH25" s="344"/>
+      <c r="AI25" s="345"/>
+      <c r="AJ25" s="150"/>
       <c r="AK25" s="6"/>
       <c r="AL25" s="6"/>
       <c r="AM25" s="6"/>
@@ -10960,48 +10979,48 @@
       <c r="HW25" s="6"/>
     </row>
     <row r="26" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="542"/>
-      <c r="B26" s="538"/>
-      <c r="C26" s="538"/>
-      <c r="D26" s="538"/>
-      <c r="E26" s="538"/>
-      <c r="F26" s="579" t="s">
+      <c r="A26" s="541"/>
+      <c r="B26" s="537"/>
+      <c r="C26" s="537"/>
+      <c r="D26" s="537"/>
+      <c r="E26" s="537"/>
+      <c r="F26" s="578" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="554" t="s">
+      <c r="G26" s="553" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="672" t="s">
+      <c r="H26" s="670" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="534"/>
-      <c r="J26" s="534"/>
-      <c r="K26" s="534"/>
-      <c r="L26" s="252"/>
-      <c r="M26" s="252"/>
-      <c r="N26" s="252"/>
-      <c r="O26" s="252"/>
-      <c r="P26" s="347"/>
-      <c r="Q26" s="252"/>
-      <c r="R26" s="252"/>
-      <c r="S26" s="252"/>
-      <c r="T26" s="348"/>
+      <c r="I26" s="533"/>
+      <c r="J26" s="533"/>
+      <c r="K26" s="533"/>
+      <c r="L26" s="251"/>
+      <c r="M26" s="251"/>
+      <c r="N26" s="251"/>
+      <c r="O26" s="251"/>
+      <c r="P26" s="346"/>
+      <c r="Q26" s="251"/>
+      <c r="R26" s="251"/>
+      <c r="S26" s="251"/>
+      <c r="T26" s="347"/>
       <c r="U26" s="19"/>
       <c r="V26" s="19"/>
       <c r="W26" s="19"/>
-      <c r="X26" s="349"/>
+      <c r="X26" s="348"/>
       <c r="Y26" s="15"/>
       <c r="Z26" s="15"/>
-      <c r="AA26" s="350"/>
-      <c r="AB26" s="280"/>
-      <c r="AC26" s="281"/>
-      <c r="AD26" s="281"/>
-      <c r="AE26" s="282"/>
+      <c r="AA26" s="349"/>
+      <c r="AB26" s="279"/>
+      <c r="AC26" s="280"/>
+      <c r="AD26" s="280"/>
+      <c r="AE26" s="281"/>
       <c r="AF26" s="24"/>
       <c r="AG26" s="24"/>
       <c r="AH26" s="24"/>
       <c r="AI26" s="16"/>
-      <c r="AJ26" s="143"/>
+      <c r="AJ26" s="142"/>
       <c r="AK26" s="6"/>
       <c r="AL26" s="6"/>
       <c r="AM26" s="6"/>
@@ -11199,19 +11218,19 @@
       <c r="HW26" s="6"/>
     </row>
     <row r="27" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="536"/>
-      <c r="B27" s="536"/>
-      <c r="C27" s="536"/>
-      <c r="D27" s="536"/>
-      <c r="E27" s="536"/>
-      <c r="F27" s="544"/>
-      <c r="G27" s="549"/>
-      <c r="H27" s="673"/>
-      <c r="I27" s="625" t="s">
+      <c r="A27" s="535"/>
+      <c r="B27" s="535"/>
+      <c r="C27" s="535"/>
+      <c r="D27" s="535"/>
+      <c r="E27" s="535"/>
+      <c r="F27" s="543"/>
+      <c r="G27" s="548"/>
+      <c r="H27" s="671"/>
+      <c r="I27" s="624" t="s">
         <v>56</v>
       </c>
-      <c r="J27" s="534"/>
-      <c r="K27" s="65"/>
+      <c r="J27" s="533"/>
+      <c r="K27" s="64"/>
       <c r="L27" s="26"/>
       <c r="M27" s="26"/>
       <c r="N27" s="26"/>
@@ -11220,23 +11239,23 @@
       <c r="Q27" s="26"/>
       <c r="R27" s="26"/>
       <c r="S27" s="26"/>
-      <c r="T27" s="168"/>
+      <c r="T27" s="167"/>
       <c r="U27" s="26"/>
       <c r="V27" s="26"/>
       <c r="W27" s="26"/>
-      <c r="X27" s="271"/>
+      <c r="X27" s="270"/>
       <c r="Y27" s="29"/>
       <c r="Z27" s="29"/>
-      <c r="AA27" s="204"/>
-      <c r="AB27" s="259"/>
-      <c r="AC27" s="73"/>
-      <c r="AD27" s="73"/>
-      <c r="AE27" s="260"/>
+      <c r="AA27" s="203"/>
+      <c r="AB27" s="258"/>
+      <c r="AC27" s="72"/>
+      <c r="AD27" s="72"/>
+      <c r="AE27" s="259"/>
       <c r="AF27" s="29"/>
       <c r="AG27" s="29"/>
       <c r="AH27" s="29"/>
       <c r="AI27" s="30"/>
-      <c r="AJ27" s="195"/>
+      <c r="AJ27" s="194"/>
       <c r="AK27" s="6"/>
       <c r="AL27" s="6"/>
       <c r="AM27" s="6"/>
@@ -11434,21 +11453,21 @@
       <c r="HW27" s="6"/>
     </row>
     <row r="28" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="537"/>
-      <c r="B28" s="537"/>
-      <c r="C28" s="537"/>
-      <c r="D28" s="537"/>
-      <c r="E28" s="537"/>
-      <c r="F28" s="544"/>
-      <c r="G28" s="555"/>
-      <c r="H28" s="609" t="s">
+      <c r="A28" s="536"/>
+      <c r="B28" s="536"/>
+      <c r="C28" s="536"/>
+      <c r="D28" s="536"/>
+      <c r="E28" s="536"/>
+      <c r="F28" s="543"/>
+      <c r="G28" s="554"/>
+      <c r="H28" s="608" t="s">
         <v>75</v>
       </c>
-      <c r="I28" s="532"/>
-      <c r="J28" s="625" t="s">
+      <c r="I28" s="531"/>
+      <c r="J28" s="624" t="s">
         <v>76</v>
       </c>
-      <c r="K28" s="534"/>
+      <c r="K28" s="533"/>
       <c r="L28" s="26"/>
       <c r="M28" s="26"/>
       <c r="N28" s="26"/>
@@ -11457,23 +11476,23 @@
       <c r="Q28" s="26"/>
       <c r="R28" s="26"/>
       <c r="S28" s="26"/>
-      <c r="T28" s="168"/>
+      <c r="T28" s="167"/>
       <c r="U28" s="26"/>
       <c r="V28" s="26"/>
       <c r="W28" s="26"/>
-      <c r="X28" s="203"/>
+      <c r="X28" s="202"/>
       <c r="Y28" s="32"/>
       <c r="Z28" s="32"/>
-      <c r="AA28" s="255"/>
-      <c r="AB28" s="286"/>
-      <c r="AC28" s="93"/>
-      <c r="AD28" s="93"/>
-      <c r="AE28" s="351"/>
+      <c r="AA28" s="254"/>
+      <c r="AB28" s="285"/>
+      <c r="AC28" s="92"/>
+      <c r="AD28" s="92"/>
+      <c r="AE28" s="350"/>
       <c r="AF28" s="32"/>
       <c r="AG28" s="32"/>
       <c r="AH28" s="32"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="131"/>
+      <c r="AI28" s="43"/>
+      <c r="AJ28" s="130"/>
       <c r="AK28" s="6"/>
       <c r="AL28" s="6"/>
       <c r="AM28" s="6"/>
@@ -11671,56 +11690,56 @@
       <c r="HW28" s="6"/>
     </row>
     <row r="29" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="535">
+      <c r="A29" s="534">
         <v>8</v>
       </c>
-      <c r="B29" s="539">
+      <c r="B29" s="538">
         <v>7</v>
       </c>
-      <c r="C29" s="539">
+      <c r="C29" s="538">
         <v>4</v>
       </c>
-      <c r="D29" s="539">
+      <c r="D29" s="538">
         <v>2</v>
       </c>
-      <c r="E29" s="541"/>
-      <c r="F29" s="544"/>
-      <c r="G29" s="561" t="s">
+      <c r="E29" s="540"/>
+      <c r="F29" s="543"/>
+      <c r="G29" s="560" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="674" t="s">
+      <c r="H29" s="672" t="s">
         <v>77</v>
       </c>
-      <c r="I29" s="532"/>
-      <c r="J29" s="675" t="s">
+      <c r="I29" s="531"/>
+      <c r="J29" s="673" t="s">
         <v>78</v>
       </c>
-      <c r="K29" s="534"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="106"/>
-      <c r="N29" s="106"/>
-      <c r="O29" s="106"/>
-      <c r="P29" s="105"/>
-      <c r="Q29" s="106"/>
-      <c r="R29" s="106"/>
-      <c r="S29" s="106"/>
-      <c r="T29" s="354"/>
-      <c r="U29" s="106"/>
-      <c r="V29" s="106"/>
-      <c r="W29" s="106"/>
-      <c r="X29" s="257"/>
-      <c r="Y29" s="58"/>
-      <c r="Z29" s="58"/>
-      <c r="AA29" s="258"/>
-      <c r="AB29" s="153"/>
+      <c r="K29" s="533"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="105"/>
+      <c r="N29" s="105"/>
+      <c r="O29" s="105"/>
+      <c r="P29" s="104"/>
+      <c r="Q29" s="105"/>
+      <c r="R29" s="105"/>
+      <c r="S29" s="105"/>
+      <c r="T29" s="353"/>
+      <c r="U29" s="105"/>
+      <c r="V29" s="105"/>
+      <c r="W29" s="105"/>
+      <c r="X29" s="256"/>
+      <c r="Y29" s="57"/>
+      <c r="Z29" s="57"/>
+      <c r="AA29" s="257"/>
+      <c r="AB29" s="152"/>
       <c r="AC29" s="10"/>
       <c r="AD29" s="10"/>
-      <c r="AE29" s="146"/>
-      <c r="AF29" s="37"/>
-      <c r="AG29" s="37"/>
-      <c r="AH29" s="37"/>
-      <c r="AI29" s="40"/>
-      <c r="AJ29" s="143"/>
+      <c r="AE29" s="145"/>
+      <c r="AF29" s="36"/>
+      <c r="AG29" s="36"/>
+      <c r="AH29" s="36"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="142"/>
       <c r="AK29" s="6"/>
       <c r="AL29" s="6"/>
       <c r="AM29" s="6"/>
@@ -11918,17 +11937,17 @@
       <c r="HW29" s="6"/>
     </row>
     <row r="30" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="536"/>
-      <c r="B30" s="536"/>
-      <c r="C30" s="536"/>
-      <c r="D30" s="536"/>
-      <c r="E30" s="536"/>
-      <c r="F30" s="544"/>
-      <c r="G30" s="549"/>
-      <c r="H30" s="676"/>
-      <c r="I30" s="86"/>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
+      <c r="A30" s="535"/>
+      <c r="B30" s="535"/>
+      <c r="C30" s="535"/>
+      <c r="D30" s="535"/>
+      <c r="E30" s="535"/>
+      <c r="F30" s="543"/>
+      <c r="G30" s="548"/>
+      <c r="H30" s="674"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
       <c r="L30" s="26"/>
       <c r="M30" s="26"/>
       <c r="N30" s="26"/>
@@ -11937,23 +11956,23 @@
       <c r="Q30" s="26"/>
       <c r="R30" s="26"/>
       <c r="S30" s="26"/>
-      <c r="T30" s="168"/>
+      <c r="T30" s="167"/>
       <c r="U30" s="26"/>
       <c r="V30" s="26"/>
       <c r="W30" s="26"/>
-      <c r="X30" s="259"/>
-      <c r="Y30" s="67"/>
-      <c r="Z30" s="67"/>
-      <c r="AA30" s="262"/>
-      <c r="AB30" s="153"/>
+      <c r="X30" s="258"/>
+      <c r="Y30" s="66"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="261"/>
+      <c r="AB30" s="152"/>
       <c r="AC30" s="10"/>
       <c r="AD30" s="10"/>
-      <c r="AE30" s="146"/>
+      <c r="AE30" s="145"/>
       <c r="AF30" s="10"/>
       <c r="AG30" s="10"/>
       <c r="AH30" s="10"/>
-      <c r="AI30" s="45"/>
-      <c r="AJ30" s="195"/>
+      <c r="AI30" s="44"/>
+      <c r="AJ30" s="194"/>
       <c r="AK30" s="6"/>
       <c r="AL30" s="6"/>
       <c r="AM30" s="6"/>
@@ -12151,46 +12170,46 @@
       <c r="HW30" s="6"/>
     </row>
     <row r="31" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A31" s="537"/>
-      <c r="B31" s="537"/>
-      <c r="C31" s="537"/>
-      <c r="D31" s="537"/>
-      <c r="E31" s="537"/>
-      <c r="F31" s="544"/>
-      <c r="G31" s="555"/>
-      <c r="H31" s="671" t="s">
+      <c r="A31" s="536"/>
+      <c r="B31" s="536"/>
+      <c r="C31" s="536"/>
+      <c r="D31" s="536"/>
+      <c r="E31" s="536"/>
+      <c r="F31" s="543"/>
+      <c r="G31" s="554"/>
+      <c r="H31" s="669" t="s">
         <v>79</v>
       </c>
-      <c r="I31" s="136"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="116" t="s">
+      <c r="I31" s="135"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="L31" s="89"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="89"/>
+      <c r="L31" s="88"/>
+      <c r="M31" s="88"/>
+      <c r="N31" s="88"/>
       <c r="O31" s="26"/>
       <c r="P31" s="27"/>
       <c r="Q31" s="26"/>
       <c r="R31" s="26"/>
       <c r="S31" s="28"/>
-      <c r="T31" s="89"/>
-      <c r="U31" s="89"/>
-      <c r="V31" s="89"/>
-      <c r="W31" s="89"/>
-      <c r="X31" s="355"/>
-      <c r="Y31" s="246"/>
-      <c r="Z31" s="94"/>
-      <c r="AA31" s="167"/>
-      <c r="AB31" s="224"/>
+      <c r="T31" s="88"/>
+      <c r="U31" s="88"/>
+      <c r="V31" s="88"/>
+      <c r="W31" s="88"/>
+      <c r="X31" s="354"/>
+      <c r="Y31" s="245"/>
+      <c r="Z31" s="93"/>
+      <c r="AA31" s="166"/>
+      <c r="AB31" s="223"/>
       <c r="AC31" s="6"/>
       <c r="AD31" s="6"/>
-      <c r="AE31" s="145"/>
+      <c r="AE31" s="144"/>
       <c r="AF31" s="6"/>
       <c r="AG31" s="6"/>
       <c r="AH31" s="6"/>
-      <c r="AI31" s="150"/>
-      <c r="AJ31" s="131"/>
+      <c r="AI31" s="149"/>
+      <c r="AJ31" s="130"/>
       <c r="AK31" s="6"/>
       <c r="AL31" s="6"/>
       <c r="AM31" s="6"/>
@@ -12388,54 +12407,54 @@
       <c r="HW31" s="6"/>
     </row>
     <row r="32" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="539">
+      <c r="A32" s="538">
         <v>21</v>
       </c>
-      <c r="B32" s="539">
+      <c r="B32" s="538">
         <v>21</v>
       </c>
-      <c r="C32" s="539">
+      <c r="C32" s="538">
         <v>18</v>
       </c>
-      <c r="D32" s="539">
+      <c r="D32" s="538">
         <v>16</v>
       </c>
-      <c r="E32" s="541"/>
-      <c r="F32" s="544"/>
-      <c r="G32" s="640" t="s">
+      <c r="E32" s="540"/>
+      <c r="F32" s="543"/>
+      <c r="G32" s="639" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="572"/>
-      <c r="I32" s="532"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="106"/>
+      <c r="H32" s="571"/>
+      <c r="I32" s="531"/>
+      <c r="J32" s="140"/>
+      <c r="K32" s="141"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
       <c r="N32" s="26"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="57"/>
-      <c r="Q32" s="58"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="59"/>
-      <c r="T32" s="575" t="s">
+      <c r="O32" s="54"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="57"/>
+      <c r="S32" s="58"/>
+      <c r="T32" s="574" t="s">
         <v>70</v>
       </c>
-      <c r="U32" s="529"/>
-      <c r="V32" s="529"/>
-      <c r="W32" s="529"/>
-      <c r="X32" s="356"/>
-      <c r="Y32" s="357"/>
-      <c r="Z32" s="357"/>
-      <c r="AA32" s="358"/>
-      <c r="AB32" s="359"/>
-      <c r="AC32" s="360"/>
-      <c r="AD32" s="360"/>
-      <c r="AE32" s="361"/>
-      <c r="AF32" s="528"/>
-      <c r="AG32" s="529"/>
-      <c r="AH32" s="529"/>
-      <c r="AI32" s="530"/>
-      <c r="AJ32" s="143"/>
+      <c r="U32" s="528"/>
+      <c r="V32" s="528"/>
+      <c r="W32" s="528"/>
+      <c r="X32" s="355"/>
+      <c r="Y32" s="356"/>
+      <c r="Z32" s="356"/>
+      <c r="AA32" s="357"/>
+      <c r="AB32" s="358"/>
+      <c r="AC32" s="359"/>
+      <c r="AD32" s="359"/>
+      <c r="AE32" s="360"/>
+      <c r="AF32" s="527"/>
+      <c r="AG32" s="528"/>
+      <c r="AH32" s="528"/>
+      <c r="AI32" s="529"/>
+      <c r="AJ32" s="142"/>
       <c r="AK32" s="6"/>
       <c r="AL32" s="6"/>
       <c r="AM32" s="6"/>
@@ -12633,44 +12652,44 @@
       <c r="HW32" s="6"/>
     </row>
     <row r="33" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="536"/>
-      <c r="B33" s="536"/>
-      <c r="C33" s="536"/>
-      <c r="D33" s="536"/>
-      <c r="E33" s="536"/>
-      <c r="F33" s="544"/>
-      <c r="G33" s="549"/>
-      <c r="H33" s="569"/>
-      <c r="I33" s="532"/>
+      <c r="A33" s="535"/>
+      <c r="B33" s="535"/>
+      <c r="C33" s="535"/>
+      <c r="D33" s="535"/>
+      <c r="E33" s="535"/>
+      <c r="F33" s="543"/>
+      <c r="G33" s="548"/>
+      <c r="H33" s="568"/>
+      <c r="I33" s="531"/>
       <c r="J33" s="6"/>
-      <c r="K33" s="145"/>
+      <c r="K33" s="144"/>
       <c r="L33" s="26"/>
       <c r="M33" s="26"/>
       <c r="N33" s="26"/>
       <c r="O33" s="26"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="61"/>
-      <c r="R33" s="61"/>
-      <c r="S33" s="99"/>
-      <c r="T33" s="667" t="s">
+      <c r="P33" s="59"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="60"/>
+      <c r="S33" s="98"/>
+      <c r="T33" s="665" t="s">
         <v>71</v>
       </c>
-      <c r="U33" s="534"/>
-      <c r="V33" s="534"/>
-      <c r="W33" s="534"/>
-      <c r="X33" s="362"/>
-      <c r="Y33" s="187"/>
-      <c r="Z33" s="316"/>
-      <c r="AA33" s="189"/>
+      <c r="U33" s="533"/>
+      <c r="V33" s="533"/>
+      <c r="W33" s="533"/>
+      <c r="X33" s="361"/>
+      <c r="Y33" s="186"/>
+      <c r="Z33" s="315"/>
+      <c r="AA33" s="188"/>
       <c r="AB33" s="6"/>
       <c r="AC33" s="6"/>
       <c r="AD33" s="6"/>
       <c r="AE33" s="6"/>
-      <c r="AF33" s="64"/>
-      <c r="AG33" s="65"/>
-      <c r="AH33" s="65"/>
-      <c r="AI33" s="77"/>
-      <c r="AJ33" s="195"/>
+      <c r="AF33" s="63"/>
+      <c r="AG33" s="64"/>
+      <c r="AH33" s="64"/>
+      <c r="AI33" s="76"/>
+      <c r="AJ33" s="194"/>
       <c r="AK33" s="6"/>
       <c r="AL33" s="6"/>
       <c r="AM33" s="6"/>
@@ -12868,44 +12887,44 @@
       <c r="HW33" s="6"/>
     </row>
     <row r="34" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="537"/>
-      <c r="B34" s="537"/>
-      <c r="C34" s="537"/>
-      <c r="D34" s="537"/>
-      <c r="E34" s="537"/>
-      <c r="F34" s="544"/>
-      <c r="G34" s="611"/>
-      <c r="H34" s="581"/>
-      <c r="I34" s="532"/>
-      <c r="J34" s="148"/>
-      <c r="K34" s="363"/>
-      <c r="L34" s="149"/>
-      <c r="M34" s="149"/>
-      <c r="N34" s="149"/>
-      <c r="O34" s="149"/>
-      <c r="P34" s="248"/>
-      <c r="Q34" s="73"/>
-      <c r="R34" s="73"/>
-      <c r="S34" s="100"/>
-      <c r="T34" s="668"/>
-      <c r="U34" s="571" t="s">
+      <c r="A34" s="536"/>
+      <c r="B34" s="536"/>
+      <c r="C34" s="536"/>
+      <c r="D34" s="536"/>
+      <c r="E34" s="536"/>
+      <c r="F34" s="543"/>
+      <c r="G34" s="610"/>
+      <c r="H34" s="580"/>
+      <c r="I34" s="531"/>
+      <c r="J34" s="147"/>
+      <c r="K34" s="362"/>
+      <c r="L34" s="148"/>
+      <c r="M34" s="148"/>
+      <c r="N34" s="148"/>
+      <c r="O34" s="148"/>
+      <c r="P34" s="247"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="99"/>
+      <c r="T34" s="666"/>
+      <c r="U34" s="570" t="s">
         <v>56</v>
       </c>
-      <c r="V34" s="534"/>
-      <c r="W34" s="227"/>
-      <c r="X34" s="364"/>
-      <c r="Y34" s="316"/>
-      <c r="Z34" s="316"/>
-      <c r="AA34" s="188"/>
-      <c r="AB34" s="241"/>
-      <c r="AC34" s="241"/>
-      <c r="AD34" s="241"/>
-      <c r="AE34" s="241"/>
-      <c r="AF34" s="190"/>
-      <c r="AG34" s="191"/>
-      <c r="AH34" s="191"/>
-      <c r="AI34" s="214"/>
-      <c r="AJ34" s="131"/>
+      <c r="V34" s="533"/>
+      <c r="W34" s="226"/>
+      <c r="X34" s="363"/>
+      <c r="Y34" s="315"/>
+      <c r="Z34" s="315"/>
+      <c r="AA34" s="187"/>
+      <c r="AB34" s="240"/>
+      <c r="AC34" s="240"/>
+      <c r="AD34" s="240"/>
+      <c r="AE34" s="240"/>
+      <c r="AF34" s="189"/>
+      <c r="AG34" s="190"/>
+      <c r="AH34" s="190"/>
+      <c r="AI34" s="213"/>
+      <c r="AJ34" s="130"/>
       <c r="AK34" s="6"/>
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
@@ -13103,52 +13122,52 @@
       <c r="HW34" s="6"/>
     </row>
     <row r="35" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="541">
+      <c r="A35" s="540">
         <v>0</v>
       </c>
-      <c r="B35" s="541">
+      <c r="B35" s="540">
         <v>0</v>
       </c>
-      <c r="C35" s="541">
+      <c r="C35" s="540">
         <v>0</v>
       </c>
-      <c r="D35" s="539">
+      <c r="D35" s="538">
         <v>30</v>
       </c>
-      <c r="E35" s="541"/>
-      <c r="F35" s="544"/>
-      <c r="G35" s="570" t="s">
+      <c r="E35" s="540"/>
+      <c r="F35" s="543"/>
+      <c r="G35" s="569" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="547"/>
-      <c r="I35" s="532"/>
+      <c r="H35" s="546"/>
+      <c r="I35" s="531"/>
       <c r="J35" s="6"/>
-      <c r="K35" s="145"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="54"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="365"/>
-      <c r="Q35" s="366"/>
-      <c r="R35" s="79"/>
-      <c r="S35" s="80"/>
-      <c r="T35" s="669"/>
-      <c r="U35" s="124"/>
+      <c r="K35" s="144"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="53"/>
+      <c r="P35" s="364"/>
+      <c r="Q35" s="365"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="667"/>
+      <c r="U35" s="123"/>
       <c r="V35" s="6"/>
-      <c r="W35" s="150"/>
-      <c r="X35" s="367"/>
-      <c r="Y35" s="368"/>
-      <c r="Z35" s="368"/>
-      <c r="AA35" s="369"/>
+      <c r="W35" s="149"/>
+      <c r="X35" s="366"/>
+      <c r="Y35" s="367"/>
+      <c r="Z35" s="367"/>
+      <c r="AA35" s="368"/>
       <c r="AB35" s="10"/>
       <c r="AC35" s="10"/>
       <c r="AD35" s="10"/>
       <c r="AE35" s="10"/>
-      <c r="AF35" s="563"/>
-      <c r="AG35" s="534"/>
-      <c r="AH35" s="534"/>
-      <c r="AI35" s="532"/>
-      <c r="AJ35" s="151"/>
+      <c r="AF35" s="562"/>
+      <c r="AG35" s="533"/>
+      <c r="AH35" s="533"/>
+      <c r="AI35" s="531"/>
+      <c r="AJ35" s="150"/>
       <c r="AK35" s="6"/>
       <c r="AL35" s="6"/>
       <c r="AM35" s="6"/>
@@ -13346,42 +13365,42 @@
       <c r="HW35" s="6"/>
     </row>
     <row r="36" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="536"/>
-      <c r="B36" s="536"/>
-      <c r="C36" s="536"/>
-      <c r="D36" s="536"/>
-      <c r="E36" s="536"/>
-      <c r="F36" s="544"/>
-      <c r="G36" s="549"/>
-      <c r="H36" s="224"/>
-      <c r="I36" s="85"/>
+      <c r="A36" s="535"/>
+      <c r="B36" s="535"/>
+      <c r="C36" s="535"/>
+      <c r="D36" s="535"/>
+      <c r="E36" s="535"/>
+      <c r="F36" s="543"/>
+      <c r="G36" s="548"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="84"/>
       <c r="J36" s="6"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="67"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="212"/>
-      <c r="Q36" s="84"/>
+      <c r="K36" s="144"/>
+      <c r="L36" s="66"/>
+      <c r="M36" s="66"/>
+      <c r="N36" s="66"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="211"/>
+      <c r="Q36" s="83"/>
       <c r="R36" s="26"/>
-      <c r="S36" s="112"/>
-      <c r="T36" s="670"/>
-      <c r="U36" s="173"/>
+      <c r="S36" s="111"/>
+      <c r="T36" s="668"/>
+      <c r="U36" s="172"/>
       <c r="V36" s="6"/>
-      <c r="W36" s="85"/>
-      <c r="X36" s="186"/>
-      <c r="Y36" s="187"/>
-      <c r="Z36" s="316"/>
-      <c r="AA36" s="188"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="185"/>
+      <c r="Y36" s="186"/>
+      <c r="Z36" s="315"/>
+      <c r="AA36" s="187"/>
       <c r="AB36" s="10"/>
       <c r="AC36" s="10"/>
       <c r="AD36" s="10"/>
       <c r="AE36" s="10"/>
-      <c r="AF36" s="64"/>
-      <c r="AG36" s="65"/>
-      <c r="AH36" s="65"/>
-      <c r="AI36" s="150"/>
-      <c r="AJ36" s="245"/>
+      <c r="AF36" s="63"/>
+      <c r="AG36" s="64"/>
+      <c r="AH36" s="64"/>
+      <c r="AI36" s="149"/>
+      <c r="AJ36" s="244"/>
       <c r="AK36" s="6"/>
       <c r="AL36" s="6"/>
       <c r="AM36" s="6"/>
@@ -13579,46 +13598,46 @@
       <c r="HW36" s="6"/>
     </row>
     <row r="37" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A37" s="537"/>
-      <c r="B37" s="537"/>
-      <c r="C37" s="537"/>
-      <c r="D37" s="537"/>
-      <c r="E37" s="537"/>
-      <c r="F37" s="544"/>
-      <c r="G37" s="555"/>
-      <c r="H37" s="635"/>
-      <c r="I37" s="553"/>
+      <c r="A37" s="536"/>
+      <c r="B37" s="536"/>
+      <c r="C37" s="536"/>
+      <c r="D37" s="536"/>
+      <c r="E37" s="536"/>
+      <c r="F37" s="543"/>
+      <c r="G37" s="554"/>
+      <c r="H37" s="634"/>
+      <c r="I37" s="552"/>
       <c r="J37" s="6"/>
-      <c r="K37" s="145"/>
-      <c r="L37" s="94"/>
-      <c r="M37" s="94"/>
-      <c r="N37" s="246"/>
-      <c r="O37" s="95"/>
-      <c r="P37" s="370"/>
-      <c r="Q37" s="371"/>
-      <c r="R37" s="89"/>
-      <c r="S37" s="372"/>
-      <c r="T37" s="671" t="s">
+      <c r="K37" s="144"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="245"/>
+      <c r="O37" s="94"/>
+      <c r="P37" s="369"/>
+      <c r="Q37" s="370"/>
+      <c r="R37" s="88"/>
+      <c r="S37" s="371"/>
+      <c r="T37" s="669" t="s">
         <v>72</v>
       </c>
-      <c r="U37" s="92"/>
-      <c r="V37" s="196"/>
-      <c r="W37" s="325" t="s">
+      <c r="U37" s="91"/>
+      <c r="V37" s="195"/>
+      <c r="W37" s="324" t="s">
         <v>73</v>
       </c>
-      <c r="X37" s="373"/>
-      <c r="Y37" s="334"/>
-      <c r="Z37" s="334"/>
-      <c r="AA37" s="335"/>
+      <c r="X37" s="372"/>
+      <c r="Y37" s="333"/>
+      <c r="Z37" s="333"/>
+      <c r="AA37" s="334"/>
       <c r="AB37" s="10"/>
       <c r="AC37" s="10"/>
       <c r="AD37" s="10"/>
       <c r="AE37" s="10"/>
-      <c r="AF37" s="190"/>
-      <c r="AG37" s="191"/>
-      <c r="AH37" s="191"/>
-      <c r="AI37" s="192"/>
-      <c r="AJ37" s="151"/>
+      <c r="AF37" s="189"/>
+      <c r="AG37" s="190"/>
+      <c r="AH37" s="190"/>
+      <c r="AI37" s="191"/>
+      <c r="AJ37" s="150"/>
       <c r="AK37" s="6"/>
       <c r="AL37" s="6"/>
       <c r="AM37" s="6"/>
@@ -13816,48 +13835,48 @@
       <c r="HW37" s="6"/>
     </row>
     <row r="38" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="542"/>
-      <c r="B38" s="542"/>
-      <c r="C38" s="542"/>
-      <c r="D38" s="542"/>
-      <c r="E38" s="542"/>
-      <c r="F38" s="544"/>
-      <c r="G38" s="570" t="s">
+      <c r="A38" s="541"/>
+      <c r="B38" s="541"/>
+      <c r="C38" s="541"/>
+      <c r="D38" s="541"/>
+      <c r="E38" s="541"/>
+      <c r="F38" s="543"/>
+      <c r="G38" s="569" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="224"/>
+      <c r="H38" s="223"/>
       <c r="I38" s="6"/>
-      <c r="J38" s="540"/>
-      <c r="K38" s="530"/>
-      <c r="L38" s="374"/>
-      <c r="M38" s="110"/>
-      <c r="N38" s="110"/>
-      <c r="O38" s="110"/>
-      <c r="P38" s="109"/>
-      <c r="Q38" s="645"/>
-      <c r="R38" s="540" t="s">
+      <c r="J38" s="539"/>
+      <c r="K38" s="529"/>
+      <c r="L38" s="373"/>
+      <c r="M38" s="109"/>
+      <c r="N38" s="109"/>
+      <c r="O38" s="109"/>
+      <c r="P38" s="108"/>
+      <c r="Q38" s="643"/>
+      <c r="R38" s="539" t="s">
         <v>54</v>
       </c>
-      <c r="S38" s="530"/>
-      <c r="T38" s="642" t="s">
+      <c r="S38" s="529"/>
+      <c r="T38" s="640" t="s">
         <v>50</v>
       </c>
-      <c r="U38" s="566"/>
-      <c r="V38" s="566"/>
-      <c r="W38" s="566"/>
-      <c r="X38" s="566"/>
-      <c r="Y38" s="566"/>
-      <c r="Z38" s="566"/>
-      <c r="AA38" s="566"/>
-      <c r="AB38" s="575"/>
-      <c r="AC38" s="529"/>
-      <c r="AD38" s="529"/>
-      <c r="AE38" s="529"/>
-      <c r="AF38" s="588"/>
-      <c r="AG38" s="566"/>
-      <c r="AH38" s="566"/>
-      <c r="AI38" s="589"/>
-      <c r="AJ38" s="151"/>
+      <c r="U38" s="565"/>
+      <c r="V38" s="565"/>
+      <c r="W38" s="565"/>
+      <c r="X38" s="565"/>
+      <c r="Y38" s="565"/>
+      <c r="Z38" s="565"/>
+      <c r="AA38" s="565"/>
+      <c r="AB38" s="574"/>
+      <c r="AC38" s="528"/>
+      <c r="AD38" s="528"/>
+      <c r="AE38" s="528"/>
+      <c r="AF38" s="587"/>
+      <c r="AG38" s="565"/>
+      <c r="AH38" s="565"/>
+      <c r="AI38" s="588"/>
+      <c r="AJ38" s="150"/>
       <c r="AK38" s="6"/>
       <c r="AL38" s="6"/>
       <c r="AM38" s="6"/>
@@ -14055,44 +14074,44 @@
       <c r="HW38" s="6"/>
     </row>
     <row r="39" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="536"/>
-      <c r="B39" s="536"/>
-      <c r="C39" s="536"/>
-      <c r="D39" s="536"/>
-      <c r="E39" s="536"/>
-      <c r="F39" s="544"/>
-      <c r="G39" s="549"/>
-      <c r="H39" s="224"/>
+      <c r="A39" s="535"/>
+      <c r="B39" s="535"/>
+      <c r="C39" s="535"/>
+      <c r="D39" s="535"/>
+      <c r="E39" s="535"/>
+      <c r="F39" s="543"/>
+      <c r="G39" s="548"/>
+      <c r="H39" s="223"/>
       <c r="I39" s="6"/>
-      <c r="J39" s="551"/>
-      <c r="K39" s="532"/>
-      <c r="L39" s="375"/>
-      <c r="M39" s="121"/>
-      <c r="N39" s="121"/>
-      <c r="O39" s="121"/>
-      <c r="P39" s="646"/>
-      <c r="Q39" s="121"/>
-      <c r="R39" s="551" t="s">
+      <c r="J39" s="550"/>
+      <c r="K39" s="531"/>
+      <c r="L39" s="374"/>
+      <c r="M39" s="120"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="120"/>
+      <c r="P39" s="644"/>
+      <c r="Q39" s="120"/>
+      <c r="R39" s="550" t="s">
         <v>55</v>
       </c>
-      <c r="S39" s="532"/>
-      <c r="T39" s="534"/>
-      <c r="U39" s="534"/>
-      <c r="V39" s="534"/>
-      <c r="W39" s="534"/>
-      <c r="X39" s="534"/>
-      <c r="Y39" s="534"/>
-      <c r="Z39" s="534"/>
-      <c r="AA39" s="534"/>
-      <c r="AB39" s="64"/>
-      <c r="AC39" s="65"/>
-      <c r="AD39" s="65"/>
-      <c r="AE39" s="83"/>
-      <c r="AF39" s="144"/>
-      <c r="AG39" s="316"/>
-      <c r="AH39" s="74"/>
-      <c r="AI39" s="376"/>
-      <c r="AJ39" s="151"/>
+      <c r="S39" s="531"/>
+      <c r="T39" s="533"/>
+      <c r="U39" s="533"/>
+      <c r="V39" s="533"/>
+      <c r="W39" s="533"/>
+      <c r="X39" s="533"/>
+      <c r="Y39" s="533"/>
+      <c r="Z39" s="533"/>
+      <c r="AA39" s="533"/>
+      <c r="AB39" s="63"/>
+      <c r="AC39" s="64"/>
+      <c r="AD39" s="64"/>
+      <c r="AE39" s="82"/>
+      <c r="AF39" s="143"/>
+      <c r="AG39" s="315"/>
+      <c r="AH39" s="73"/>
+      <c r="AI39" s="375"/>
+      <c r="AJ39" s="150"/>
       <c r="AK39" s="6"/>
       <c r="AL39" s="6"/>
       <c r="AM39" s="6"/>
@@ -14290,48 +14309,48 @@
       <c r="HW39" s="6"/>
     </row>
     <row r="40" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="537"/>
-      <c r="B40" s="537"/>
-      <c r="C40" s="537"/>
-      <c r="D40" s="537"/>
-      <c r="E40" s="537"/>
-      <c r="F40" s="544"/>
-      <c r="G40" s="555"/>
-      <c r="H40" s="224"/>
+      <c r="A40" s="536"/>
+      <c r="B40" s="536"/>
+      <c r="C40" s="536"/>
+      <c r="D40" s="536"/>
+      <c r="E40" s="536"/>
+      <c r="F40" s="543"/>
+      <c r="G40" s="554"/>
+      <c r="H40" s="223"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="620"/>
-      <c r="K40" s="532"/>
-      <c r="L40" s="235"/>
-      <c r="M40" s="377"/>
-      <c r="N40" s="377"/>
-      <c r="O40" s="377"/>
-      <c r="P40" s="647"/>
-      <c r="Q40" s="377"/>
-      <c r="R40" s="620" t="s">
+      <c r="J40" s="619"/>
+      <c r="K40" s="531"/>
+      <c r="L40" s="234"/>
+      <c r="M40" s="376"/>
+      <c r="N40" s="376"/>
+      <c r="O40" s="376"/>
+      <c r="P40" s="645"/>
+      <c r="Q40" s="376"/>
+      <c r="R40" s="619" t="s">
         <v>56</v>
       </c>
-      <c r="S40" s="532"/>
-      <c r="T40" s="101" t="s">
+      <c r="S40" s="531"/>
+      <c r="T40" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="U40" s="101"/>
-      <c r="V40" s="101"/>
-      <c r="W40" s="102"/>
-      <c r="X40" s="643"/>
-      <c r="Y40" s="643"/>
-      <c r="Z40" s="102"/>
-      <c r="AA40" s="103">
+      <c r="U40" s="100"/>
+      <c r="V40" s="100"/>
+      <c r="W40" s="101"/>
+      <c r="X40" s="641"/>
+      <c r="Y40" s="641"/>
+      <c r="Z40" s="101"/>
+      <c r="AA40" s="102">
         <v>400</v>
       </c>
-      <c r="AB40" s="75"/>
-      <c r="AC40" s="76"/>
-      <c r="AD40" s="76"/>
+      <c r="AB40" s="74"/>
+      <c r="AC40" s="75"/>
+      <c r="AD40" s="75"/>
       <c r="AE40" s="6"/>
-      <c r="AF40" s="87"/>
-      <c r="AG40" s="334"/>
-      <c r="AH40" s="334"/>
-      <c r="AI40" s="104"/>
-      <c r="AJ40" s="151"/>
+      <c r="AF40" s="86"/>
+      <c r="AG40" s="333"/>
+      <c r="AH40" s="333"/>
+      <c r="AI40" s="103"/>
+      <c r="AJ40" s="150"/>
       <c r="AK40" s="6"/>
       <c r="AL40" s="6"/>
       <c r="AM40" s="6"/>
@@ -14529,48 +14548,48 @@
       <c r="HW40" s="6"/>
     </row>
     <row r="41" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="542"/>
-      <c r="B41" s="542"/>
-      <c r="C41" s="542"/>
-      <c r="D41" s="542"/>
-      <c r="E41" s="542"/>
-      <c r="F41" s="544"/>
-      <c r="G41" s="601" t="s">
+      <c r="A41" s="541"/>
+      <c r="B41" s="541"/>
+      <c r="C41" s="541"/>
+      <c r="D41" s="541"/>
+      <c r="E41" s="541"/>
+      <c r="F41" s="543"/>
+      <c r="G41" s="600" t="s">
         <v>25</v>
       </c>
-      <c r="H41" s="378"/>
-      <c r="I41" s="141"/>
-      <c r="J41" s="609"/>
-      <c r="K41" s="532"/>
+      <c r="H41" s="377"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="608"/>
+      <c r="K41" s="531"/>
       <c r="L41" s="26"/>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
       <c r="O41" s="26"/>
-      <c r="P41" s="648"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="609" t="s">
+      <c r="P41" s="646"/>
+      <c r="Q41" s="53"/>
+      <c r="R41" s="608" t="s">
         <v>57</v>
       </c>
-      <c r="S41" s="532"/>
-      <c r="T41" s="644" t="s">
+      <c r="S41" s="531"/>
+      <c r="T41" s="642" t="s">
         <v>52</v>
       </c>
-      <c r="U41" s="613"/>
-      <c r="V41" s="613"/>
-      <c r="W41" s="613"/>
-      <c r="X41" s="613"/>
-      <c r="Y41" s="613"/>
-      <c r="Z41" s="613"/>
-      <c r="AA41" s="613"/>
-      <c r="AB41" s="575"/>
-      <c r="AC41" s="529"/>
-      <c r="AD41" s="529"/>
-      <c r="AE41" s="529"/>
-      <c r="AF41" s="53"/>
-      <c r="AG41" s="54"/>
-      <c r="AH41" s="54"/>
-      <c r="AI41" s="63"/>
-      <c r="AJ41" s="151"/>
+      <c r="U41" s="612"/>
+      <c r="V41" s="612"/>
+      <c r="W41" s="612"/>
+      <c r="X41" s="612"/>
+      <c r="Y41" s="612"/>
+      <c r="Z41" s="612"/>
+      <c r="AA41" s="612"/>
+      <c r="AB41" s="574"/>
+      <c r="AC41" s="528"/>
+      <c r="AD41" s="528"/>
+      <c r="AE41" s="528"/>
+      <c r="AF41" s="52"/>
+      <c r="AG41" s="53"/>
+      <c r="AH41" s="53"/>
+      <c r="AI41" s="62"/>
+      <c r="AJ41" s="150"/>
       <c r="AK41" s="6"/>
       <c r="AL41" s="6"/>
       <c r="AM41" s="6"/>
@@ -14768,42 +14787,42 @@
       <c r="HW41" s="6"/>
     </row>
     <row r="42" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="536"/>
-      <c r="B42" s="536"/>
-      <c r="C42" s="536"/>
-      <c r="D42" s="536"/>
-      <c r="E42" s="536"/>
-      <c r="F42" s="544"/>
-      <c r="G42" s="549"/>
-      <c r="H42" s="224"/>
+      <c r="A42" s="535"/>
+      <c r="B42" s="535"/>
+      <c r="C42" s="535"/>
+      <c r="D42" s="535"/>
+      <c r="E42" s="535"/>
+      <c r="F42" s="543"/>
+      <c r="G42" s="548"/>
+      <c r="H42" s="223"/>
       <c r="I42" s="6"/>
-      <c r="J42" s="144"/>
-      <c r="K42" s="156"/>
+      <c r="J42" s="143"/>
+      <c r="K42" s="155"/>
       <c r="L42" s="26"/>
       <c r="M42" s="26"/>
       <c r="N42" s="26"/>
       <c r="O42" s="26"/>
-      <c r="P42" s="649"/>
-      <c r="Q42" s="67"/>
-      <c r="R42" s="650"/>
-      <c r="S42" s="85"/>
-      <c r="T42" s="534"/>
-      <c r="U42" s="534"/>
-      <c r="V42" s="534"/>
-      <c r="W42" s="534"/>
-      <c r="X42" s="534"/>
-      <c r="Y42" s="534"/>
-      <c r="Z42" s="534"/>
-      <c r="AA42" s="534"/>
-      <c r="AB42" s="64"/>
-      <c r="AC42" s="65"/>
-      <c r="AD42" s="65"/>
-      <c r="AE42" s="65"/>
-      <c r="AF42" s="135"/>
-      <c r="AG42" s="67"/>
-      <c r="AH42" s="231"/>
-      <c r="AI42" s="68"/>
-      <c r="AJ42" s="151"/>
+      <c r="P42" s="647"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="648"/>
+      <c r="S42" s="84"/>
+      <c r="T42" s="533"/>
+      <c r="U42" s="533"/>
+      <c r="V42" s="533"/>
+      <c r="W42" s="533"/>
+      <c r="X42" s="533"/>
+      <c r="Y42" s="533"/>
+      <c r="Z42" s="533"/>
+      <c r="AA42" s="533"/>
+      <c r="AB42" s="63"/>
+      <c r="AC42" s="64"/>
+      <c r="AD42" s="64"/>
+      <c r="AE42" s="64"/>
+      <c r="AF42" s="134"/>
+      <c r="AG42" s="66"/>
+      <c r="AH42" s="230"/>
+      <c r="AI42" s="67"/>
+      <c r="AJ42" s="150"/>
       <c r="AK42" s="6"/>
       <c r="AL42" s="6"/>
       <c r="AM42" s="6"/>
@@ -15001,48 +15020,48 @@
       <c r="HW42" s="6"/>
     </row>
     <row r="43" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="537"/>
-      <c r="B43" s="537"/>
-      <c r="C43" s="537"/>
-      <c r="D43" s="537"/>
-      <c r="E43" s="537"/>
-      <c r="F43" s="545"/>
-      <c r="G43" s="602"/>
-      <c r="H43" s="379"/>
-      <c r="I43" s="113"/>
-      <c r="J43" s="552"/>
-      <c r="K43" s="553"/>
-      <c r="L43" s="114"/>
-      <c r="M43" s="113"/>
-      <c r="N43" s="113"/>
-      <c r="O43" s="380"/>
-      <c r="P43" s="381"/>
-      <c r="Q43" s="380"/>
-      <c r="R43" s="573" t="s">
+      <c r="A43" s="536"/>
+      <c r="B43" s="536"/>
+      <c r="C43" s="536"/>
+      <c r="D43" s="536"/>
+      <c r="E43" s="536"/>
+      <c r="F43" s="544"/>
+      <c r="G43" s="601"/>
+      <c r="H43" s="378"/>
+      <c r="I43" s="112"/>
+      <c r="J43" s="551"/>
+      <c r="K43" s="552"/>
+      <c r="L43" s="113"/>
+      <c r="M43" s="112"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="379"/>
+      <c r="P43" s="380"/>
+      <c r="Q43" s="379"/>
+      <c r="R43" s="572" t="s">
         <v>58</v>
       </c>
-      <c r="S43" s="574"/>
-      <c r="T43" s="96" t="s">
+      <c r="S43" s="573"/>
+      <c r="T43" s="95" t="s">
         <v>53</v>
       </c>
-      <c r="U43" s="76"/>
-      <c r="V43" s="76"/>
-      <c r="W43" s="74"/>
-      <c r="X43" s="74"/>
+      <c r="U43" s="75"/>
+      <c r="V43" s="75"/>
+      <c r="W43" s="73"/>
+      <c r="X43" s="73"/>
       <c r="Y43" s="6"/>
       <c r="Z43" s="6"/>
-      <c r="AA43" s="116">
+      <c r="AA43" s="115">
         <v>400</v>
       </c>
-      <c r="AB43" s="75"/>
-      <c r="AC43" s="76"/>
-      <c r="AD43" s="76"/>
-      <c r="AE43" s="83"/>
-      <c r="AF43" s="382"/>
-      <c r="AG43" s="200"/>
-      <c r="AH43" s="200"/>
-      <c r="AI43" s="201"/>
-      <c r="AJ43" s="151"/>
+      <c r="AB43" s="74"/>
+      <c r="AC43" s="75"/>
+      <c r="AD43" s="75"/>
+      <c r="AE43" s="82"/>
+      <c r="AF43" s="381"/>
+      <c r="AG43" s="199"/>
+      <c r="AH43" s="199"/>
+      <c r="AI43" s="200"/>
+      <c r="AJ43" s="150"/>
       <c r="AK43" s="6"/>
       <c r="AL43" s="6"/>
       <c r="AM43" s="6"/>
@@ -15240,29 +15259,29 @@
       <c r="HW43" s="6"/>
     </row>
     <row r="44" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="542"/>
-      <c r="B44" s="538"/>
-      <c r="C44" s="538"/>
-      <c r="D44" s="538"/>
-      <c r="E44" s="538"/>
-      <c r="F44" s="580" t="s">
+      <c r="A44" s="541"/>
+      <c r="B44" s="537"/>
+      <c r="C44" s="537"/>
+      <c r="D44" s="537"/>
+      <c r="E44" s="537"/>
+      <c r="F44" s="579" t="s">
         <v>27</v>
       </c>
-      <c r="G44" s="570" t="s">
+      <c r="G44" s="569" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="383"/>
+      <c r="H44" s="382"/>
       <c r="I44" s="17"/>
-      <c r="J44" s="232"/>
-      <c r="K44" s="254"/>
-      <c r="L44" s="232"/>
-      <c r="M44" s="232"/>
-      <c r="N44" s="232"/>
-      <c r="O44" s="233"/>
-      <c r="P44" s="651" t="s">
+      <c r="J44" s="231"/>
+      <c r="K44" s="253"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="231"/>
+      <c r="N44" s="231"/>
+      <c r="O44" s="232"/>
+      <c r="P44" s="649" t="s">
         <v>59</v>
       </c>
-      <c r="Q44" s="616"/>
+      <c r="Q44" s="615"/>
       <c r="R44" s="10"/>
       <c r="S44" s="10"/>
       <c r="T44" s="18"/>
@@ -15479,25 +15498,25 @@
       <c r="HW44" s="6"/>
     </row>
     <row r="45" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="536"/>
-      <c r="B45" s="536"/>
-      <c r="C45" s="536"/>
-      <c r="D45" s="536"/>
-      <c r="E45" s="536"/>
-      <c r="F45" s="544"/>
-      <c r="G45" s="549"/>
-      <c r="H45" s="384"/>
-      <c r="I45" s="61"/>
+      <c r="A45" s="535"/>
+      <c r="B45" s="535"/>
+      <c r="C45" s="535"/>
+      <c r="D45" s="535"/>
+      <c r="E45" s="535"/>
+      <c r="F45" s="543"/>
+      <c r="G45" s="548"/>
+      <c r="H45" s="383"/>
+      <c r="I45" s="60"/>
       <c r="J45" s="29"/>
-      <c r="K45" s="204"/>
-      <c r="L45" s="385"/>
-      <c r="M45" s="385"/>
-      <c r="N45" s="385"/>
-      <c r="O45" s="386"/>
-      <c r="P45" s="551" t="s">
+      <c r="K45" s="203"/>
+      <c r="L45" s="384"/>
+      <c r="M45" s="384"/>
+      <c r="N45" s="384"/>
+      <c r="O45" s="385"/>
+      <c r="P45" s="550" t="s">
         <v>60</v>
       </c>
-      <c r="Q45" s="532"/>
+      <c r="Q45" s="531"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="27"/>
@@ -15714,27 +15733,27 @@
       <c r="HW45" s="6"/>
     </row>
     <row r="46" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="537"/>
-      <c r="B46" s="537"/>
-      <c r="C46" s="537"/>
-      <c r="D46" s="537"/>
-      <c r="E46" s="537"/>
-      <c r="F46" s="544"/>
-      <c r="G46" s="555"/>
-      <c r="H46" s="387"/>
-      <c r="I46" s="206"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="388"/>
-      <c r="L46" s="389"/>
-      <c r="M46" s="389"/>
-      <c r="N46" s="389"/>
-      <c r="O46" s="376"/>
-      <c r="P46" s="652" t="s">
+      <c r="A46" s="536"/>
+      <c r="B46" s="536"/>
+      <c r="C46" s="536"/>
+      <c r="D46" s="536"/>
+      <c r="E46" s="536"/>
+      <c r="F46" s="543"/>
+      <c r="G46" s="554"/>
+      <c r="H46" s="386"/>
+      <c r="I46" s="205"/>
+      <c r="J46" s="51"/>
+      <c r="K46" s="387"/>
+      <c r="L46" s="388"/>
+      <c r="M46" s="388"/>
+      <c r="N46" s="388"/>
+      <c r="O46" s="375"/>
+      <c r="P46" s="650" t="s">
         <v>56</v>
       </c>
-      <c r="Q46" s="532"/>
-      <c r="R46" s="196"/>
-      <c r="S46" s="196"/>
+      <c r="Q46" s="531"/>
+      <c r="R46" s="195"/>
+      <c r="S46" s="195"/>
       <c r="T46" s="27"/>
       <c r="U46" s="26"/>
       <c r="V46" s="26"/>
@@ -15742,7 +15761,7 @@
       <c r="X46" s="26"/>
       <c r="Y46" s="26"/>
       <c r="Z46" s="34"/>
-      <c r="AA46" s="128"/>
+      <c r="AA46" s="127"/>
       <c r="AB46" s="27"/>
       <c r="AC46" s="26"/>
       <c r="AD46" s="26"/>
@@ -15949,53 +15968,54 @@
       <c r="HW46" s="6"/>
     </row>
     <row r="47" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A47" s="535">
+      <c r="A47" s="534">
         <v>9</v>
       </c>
-      <c r="B47" s="539">
+      <c r="B47" s="538">
         <v>8</v>
       </c>
-      <c r="C47" s="539">
+      <c r="C47" s="538">
         <v>5</v>
       </c>
-      <c r="D47" s="539">
+      <c r="D47" s="538">
         <v>3</v>
       </c>
-      <c r="E47" s="539"/>
-      <c r="F47" s="544"/>
-      <c r="G47" s="561" t="s">
+      <c r="E47" s="538"/>
+      <c r="F47" s="543"/>
+      <c r="G47" s="560" t="s">
         <v>19</v>
       </c>
-      <c r="H47" s="257"/>
-      <c r="I47" s="58"/>
-      <c r="J47" s="58"/>
-      <c r="K47" s="258"/>
-      <c r="L47" s="390"/>
-      <c r="M47" s="390"/>
-      <c r="N47" s="390"/>
-      <c r="O47" s="391"/>
-      <c r="P47" s="653" t="s">
+      <c r="H47" s="256"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="257"/>
+      <c r="L47" s="389"/>
+      <c r="M47" s="389"/>
+      <c r="N47" s="389"/>
+      <c r="O47" s="390"/>
+      <c r="P47" s="651" t="s">
         <v>57</v>
       </c>
-      <c r="Q47" s="532"/>
+      <c r="Q47" s="531"/>
       <c r="R47" s="6"/>
       <c r="S47" s="6"/>
-      <c r="T47" s="392"/>
-      <c r="U47" s="393"/>
-      <c r="V47" s="393"/>
-      <c r="W47" s="394"/>
-      <c r="X47" s="393"/>
-      <c r="Y47" s="393"/>
-      <c r="Z47" s="393"/>
-      <c r="AA47" s="393"/>
-      <c r="AB47" s="36"/>
-      <c r="AC47" s="37"/>
-      <c r="AD47" s="37"/>
-      <c r="AE47" s="40"/>
-      <c r="AF47" s="38"/>
-      <c r="AG47" s="38"/>
-      <c r="AH47" s="38"/>
-      <c r="AI47" s="39"/>
+      <c r="T47" s="391"/>
+      <c r="U47" s="392"/>
+      <c r="V47" s="392"/>
+      <c r="W47" s="393"/>
+      <c r="X47" s="392"/>
+      <c r="Y47" s="392"/>
+      <c r="Z47" s="392"/>
+      <c r="AA47" s="392"/>
+      <c r="AB47" s="563" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC47" s="529"/>
+      <c r="AD47" s="36"/>
+      <c r="AF47" s="37"/>
+      <c r="AG47" s="37"/>
+      <c r="AH47" s="37"/>
+      <c r="AI47" s="38"/>
       <c r="AJ47" s="6"/>
       <c r="AK47" s="6"/>
       <c r="AL47" s="6"/>
@@ -16193,24 +16213,24 @@
       <c r="HV47" s="6"/>
       <c r="HW47" s="6"/>
     </row>
-    <row r="48" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="536"/>
-      <c r="B48" s="536"/>
-      <c r="C48" s="536"/>
-      <c r="D48" s="536"/>
-      <c r="E48" s="536"/>
-      <c r="F48" s="544"/>
-      <c r="G48" s="549"/>
-      <c r="H48" s="264"/>
-      <c r="I48" s="54"/>
-      <c r="J48" s="54"/>
-      <c r="K48" s="262"/>
-      <c r="L48" s="385"/>
-      <c r="M48" s="385"/>
-      <c r="N48" s="385"/>
-      <c r="O48" s="386"/>
-      <c r="P48" s="76"/>
-      <c r="Q48" s="85"/>
+    <row r="48" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A48" s="535"/>
+      <c r="B48" s="535"/>
+      <c r="C48" s="535"/>
+      <c r="D48" s="535"/>
+      <c r="E48" s="535"/>
+      <c r="F48" s="543"/>
+      <c r="G48" s="548"/>
+      <c r="H48" s="263"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="261"/>
+      <c r="L48" s="384"/>
+      <c r="M48" s="384"/>
+      <c r="N48" s="384"/>
+      <c r="O48" s="385"/>
+      <c r="P48" s="75"/>
+      <c r="Q48" s="84"/>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
       <c r="T48" s="23"/>
@@ -16221,14 +16241,18 @@
       <c r="Y48" s="24"/>
       <c r="Z48" s="24"/>
       <c r="AA48" s="24"/>
-      <c r="AB48" s="43"/>
-      <c r="AC48" s="10"/>
+      <c r="AB48" s="603" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC48" s="603"/>
       <c r="AD48" s="10"/>
-      <c r="AE48" s="45"/>
+      <c r="AE48" s="39" t="s">
+        <v>83</v>
+      </c>
       <c r="AF48" s="32"/>
       <c r="AG48" s="32"/>
       <c r="AH48" s="32"/>
-      <c r="AI48" s="44"/>
+      <c r="AI48" s="43"/>
       <c r="AJ48" s="6"/>
       <c r="AK48" s="6"/>
       <c r="AL48" s="6"/>
@@ -16427,43 +16451,45 @@
       <c r="HW48" s="6"/>
     </row>
     <row r="49" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A49" s="537"/>
-      <c r="B49" s="537"/>
-      <c r="C49" s="537"/>
-      <c r="D49" s="537"/>
-      <c r="E49" s="537"/>
-      <c r="F49" s="544"/>
-      <c r="G49" s="555"/>
-      <c r="H49" s="304"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="70"/>
-      <c r="K49" s="167"/>
-      <c r="L49" s="389"/>
-      <c r="M49" s="389"/>
-      <c r="N49" s="389"/>
-      <c r="O49" s="376"/>
-      <c r="P49" s="654" t="s">
+      <c r="A49" s="536"/>
+      <c r="B49" s="536"/>
+      <c r="C49" s="536"/>
+      <c r="D49" s="536"/>
+      <c r="E49" s="536"/>
+      <c r="F49" s="543"/>
+      <c r="G49" s="554"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="83"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="166"/>
+      <c r="L49" s="388"/>
+      <c r="M49" s="388"/>
+      <c r="N49" s="388"/>
+      <c r="O49" s="375"/>
+      <c r="P49" s="652" t="s">
         <v>61</v>
       </c>
-      <c r="Q49" s="532"/>
+      <c r="Q49" s="531"/>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
-      <c r="T49" s="395"/>
-      <c r="U49" s="396"/>
-      <c r="V49" s="396"/>
-      <c r="W49" s="268"/>
-      <c r="X49" s="397"/>
-      <c r="Y49" s="396"/>
-      <c r="Z49" s="396"/>
-      <c r="AA49" s="51"/>
-      <c r="AB49" s="46"/>
-      <c r="AC49" s="47"/>
-      <c r="AD49" s="47"/>
-      <c r="AE49" s="98"/>
-      <c r="AF49" s="50"/>
-      <c r="AG49" s="48"/>
-      <c r="AH49" s="48"/>
-      <c r="AI49" s="49"/>
+      <c r="T49" s="394"/>
+      <c r="U49" s="395"/>
+      <c r="V49" s="395"/>
+      <c r="W49" s="267"/>
+      <c r="X49" s="396"/>
+      <c r="Y49" s="395"/>
+      <c r="Z49" s="395"/>
+      <c r="AA49" s="50"/>
+      <c r="AB49" s="580" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC49" s="531"/>
+      <c r="AD49" s="46"/>
+      <c r="AE49" s="97"/>
+      <c r="AF49" s="49"/>
+      <c r="AG49" s="47"/>
+      <c r="AH49" s="47"/>
+      <c r="AI49" s="48"/>
       <c r="AJ49" s="6"/>
       <c r="AK49" s="6"/>
       <c r="AL49" s="6"/>
@@ -16662,62 +16688,64 @@
       <c r="HW49" s="6"/>
     </row>
     <row r="50" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="539">
+      <c r="A50" s="538">
         <v>22</v>
       </c>
-      <c r="B50" s="539">
+      <c r="B50" s="538">
         <v>22</v>
       </c>
-      <c r="C50" s="539">
+      <c r="C50" s="538">
         <v>19</v>
       </c>
-      <c r="D50" s="539">
+      <c r="D50" s="538">
         <v>17</v>
       </c>
-      <c r="E50" s="541"/>
-      <c r="F50" s="544"/>
-      <c r="G50" s="567" t="s">
+      <c r="E50" s="540"/>
+      <c r="F50" s="543"/>
+      <c r="G50" s="566" t="s">
         <v>20</v>
       </c>
-      <c r="H50" s="564"/>
-      <c r="I50" s="529"/>
-      <c r="J50" s="529"/>
-      <c r="K50" s="530"/>
-      <c r="L50" s="564" t="s">
+      <c r="H50" s="563"/>
+      <c r="I50" s="528"/>
+      <c r="J50" s="528"/>
+      <c r="K50" s="529"/>
+      <c r="L50" s="563" t="s">
         <v>62</v>
       </c>
-      <c r="M50" s="530"/>
-      <c r="N50" s="658" t="s">
+      <c r="M50" s="529"/>
+      <c r="N50" s="656" t="s">
         <v>63</v>
       </c>
-      <c r="O50" s="530"/>
-      <c r="P50" s="655"/>
-      <c r="Q50" s="656"/>
-      <c r="R50" s="657" t="s">
+      <c r="O50" s="529"/>
+      <c r="P50" s="653"/>
+      <c r="Q50" s="654"/>
+      <c r="R50" s="655" t="s">
         <v>59</v>
       </c>
-      <c r="S50" s="529"/>
-      <c r="T50" s="57"/>
-      <c r="U50" s="58"/>
-      <c r="V50" s="58"/>
-      <c r="W50" s="59"/>
-      <c r="X50" s="58"/>
-      <c r="Y50" s="58"/>
-      <c r="Z50" s="58"/>
-      <c r="AA50" s="58"/>
-      <c r="AB50" s="43"/>
-      <c r="AC50" s="10"/>
+      <c r="S50" s="528"/>
+      <c r="T50" s="56"/>
+      <c r="U50" s="57"/>
+      <c r="V50" s="57"/>
+      <c r="W50" s="58"/>
+      <c r="X50" s="57"/>
+      <c r="Y50" s="57"/>
+      <c r="Z50" s="57"/>
+      <c r="AA50" s="57"/>
+      <c r="AB50" s="546" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC50" s="531"/>
       <c r="AD50" s="10"/>
-      <c r="AE50" s="45"/>
-      <c r="AF50" s="528"/>
-      <c r="AG50" s="529"/>
-      <c r="AH50" s="529"/>
-      <c r="AI50" s="530"/>
+      <c r="AE50" s="44"/>
+      <c r="AF50" s="527"/>
+      <c r="AG50" s="528"/>
+      <c r="AH50" s="528"/>
+      <c r="AI50" s="529"/>
       <c r="AJ50" s="6"/>
-      <c r="AK50" s="152"/>
-      <c r="AL50" s="152"/>
-      <c r="AM50" s="152"/>
-      <c r="AN50" s="152"/>
+      <c r="AK50" s="151"/>
+      <c r="AL50" s="151"/>
+      <c r="AM50" s="151"/>
+      <c r="AN50" s="151"/>
       <c r="AO50" s="6"/>
       <c r="AP50" s="6"/>
       <c r="AQ50" s="6"/>
@@ -16911,52 +16939,52 @@
       <c r="HW50" s="6"/>
     </row>
     <row r="51" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A51" s="536"/>
-      <c r="B51" s="536"/>
-      <c r="C51" s="536"/>
-      <c r="D51" s="536"/>
-      <c r="E51" s="536"/>
-      <c r="F51" s="544"/>
-      <c r="G51" s="549"/>
-      <c r="H51" s="398"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="82"/>
-      <c r="K51" s="216"/>
-      <c r="L51" s="569" t="s">
+      <c r="A51" s="535"/>
+      <c r="B51" s="535"/>
+      <c r="C51" s="535"/>
+      <c r="D51" s="535"/>
+      <c r="E51" s="535"/>
+      <c r="F51" s="543"/>
+      <c r="G51" s="548"/>
+      <c r="H51" s="397"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="215"/>
+      <c r="L51" s="568" t="s">
         <v>64</v>
       </c>
-      <c r="M51" s="532"/>
-      <c r="N51" s="659" t="s">
+      <c r="M51" s="531"/>
+      <c r="N51" s="657" t="s">
         <v>65</v>
       </c>
-      <c r="O51" s="532"/>
+      <c r="O51" s="531"/>
       <c r="P51" s="6"/>
-      <c r="Q51" s="150"/>
-      <c r="R51" s="604" t="s">
+      <c r="Q51" s="149"/>
+      <c r="R51" s="603" t="s">
         <v>60</v>
       </c>
-      <c r="S51" s="534"/>
-      <c r="T51" s="60"/>
-      <c r="U51" s="61"/>
-      <c r="V51" s="61"/>
-      <c r="W51" s="99"/>
-      <c r="X51" s="61"/>
-      <c r="Y51" s="61"/>
-      <c r="Z51" s="61"/>
-      <c r="AA51" s="61"/>
-      <c r="AB51" s="43"/>
-      <c r="AC51" s="10"/>
+      <c r="S51" s="533"/>
+      <c r="T51" s="59"/>
+      <c r="U51" s="60"/>
+      <c r="V51" s="60"/>
+      <c r="W51" s="98"/>
+      <c r="X51" s="60"/>
+      <c r="Y51" s="60"/>
+      <c r="Z51" s="60"/>
+      <c r="AA51" s="60"/>
+      <c r="AB51" s="658"/>
+      <c r="AC51" s="659"/>
       <c r="AD51" s="10"/>
-      <c r="AE51" s="45"/>
-      <c r="AF51" s="399"/>
-      <c r="AG51" s="546"/>
-      <c r="AH51" s="534"/>
-      <c r="AI51" s="400"/>
+      <c r="AE51" s="44"/>
+      <c r="AF51" s="398"/>
+      <c r="AG51" s="545"/>
+      <c r="AH51" s="533"/>
+      <c r="AI51" s="399"/>
       <c r="AJ51" s="6"/>
-      <c r="AK51" s="86"/>
-      <c r="AL51" s="86"/>
-      <c r="AM51" s="86"/>
-      <c r="AN51" s="86"/>
+      <c r="AK51" s="85"/>
+      <c r="AL51" s="85"/>
+      <c r="AM51" s="85"/>
+      <c r="AN51" s="85"/>
       <c r="AO51" s="6"/>
       <c r="AP51" s="6"/>
       <c r="AQ51" s="6"/>
@@ -17150,52 +17178,54 @@
       <c r="HW51" s="6"/>
     </row>
     <row r="52" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A52" s="537"/>
-      <c r="B52" s="537"/>
-      <c r="C52" s="537"/>
-      <c r="D52" s="537"/>
-      <c r="E52" s="537"/>
-      <c r="F52" s="544"/>
-      <c r="G52" s="568"/>
-      <c r="H52" s="401"/>
-      <c r="I52" s="191"/>
-      <c r="J52" s="191"/>
-      <c r="K52" s="363"/>
-      <c r="L52" s="581" t="s">
+      <c r="A52" s="536"/>
+      <c r="B52" s="536"/>
+      <c r="C52" s="536"/>
+      <c r="D52" s="536"/>
+      <c r="E52" s="536"/>
+      <c r="F52" s="543"/>
+      <c r="G52" s="567"/>
+      <c r="H52" s="400"/>
+      <c r="I52" s="190"/>
+      <c r="J52" s="190"/>
+      <c r="K52" s="362"/>
+      <c r="L52" s="580" t="s">
         <v>56</v>
       </c>
-      <c r="M52" s="532"/>
-      <c r="N52" s="652" t="s">
+      <c r="M52" s="531"/>
+      <c r="N52" s="650" t="s">
         <v>56</v>
       </c>
-      <c r="O52" s="532"/>
-      <c r="P52" s="148"/>
-      <c r="Q52" s="214"/>
-      <c r="R52" s="571" t="s">
+      <c r="O52" s="531"/>
+      <c r="P52" s="147"/>
+      <c r="Q52" s="213"/>
+      <c r="R52" s="570" t="s">
         <v>56</v>
       </c>
-      <c r="S52" s="534"/>
-      <c r="T52" s="248"/>
-      <c r="U52" s="73"/>
-      <c r="V52" s="73"/>
-      <c r="W52" s="100"/>
-      <c r="X52" s="249"/>
-      <c r="Y52" s="73"/>
-      <c r="Z52" s="73"/>
-      <c r="AA52" s="73"/>
-      <c r="AB52" s="43"/>
-      <c r="AC52" s="10"/>
+      <c r="S52" s="533"/>
+      <c r="T52" s="247"/>
+      <c r="U52" s="72"/>
+      <c r="V52" s="72"/>
+      <c r="W52" s="99"/>
+      <c r="X52" s="248"/>
+      <c r="Y52" s="72"/>
+      <c r="Z52" s="72"/>
+      <c r="AA52" s="72"/>
+      <c r="AB52" s="591" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC52" s="531"/>
       <c r="AD52" s="10"/>
-      <c r="AE52" s="45"/>
-      <c r="AF52" s="217"/>
-      <c r="AG52" s="217"/>
-      <c r="AH52" s="218"/>
-      <c r="AI52" s="402"/>
+      <c r="AE52" s="44"/>
+      <c r="AF52" s="216"/>
+      <c r="AG52" s="216"/>
+      <c r="AH52" s="217"/>
+      <c r="AI52" s="401"/>
       <c r="AJ52" s="6"/>
-      <c r="AK52" s="162"/>
-      <c r="AL52" s="162"/>
-      <c r="AM52" s="162"/>
-      <c r="AN52" s="163"/>
+      <c r="AK52" s="161"/>
+      <c r="AL52" s="161"/>
+      <c r="AM52" s="161"/>
+      <c r="AN52" s="162"/>
       <c r="AO52" s="6"/>
       <c r="AP52" s="6"/>
       <c r="AQ52" s="6"/>
@@ -17389,64 +17419,64 @@
       <c r="HW52" s="6"/>
     </row>
     <row r="53" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A53" s="541">
+      <c r="A53" s="540">
         <v>0</v>
       </c>
-      <c r="B53" s="541">
+      <c r="B53" s="540">
         <v>0</v>
       </c>
-      <c r="C53" s="541">
+      <c r="C53" s="540">
         <v>0</v>
       </c>
-      <c r="D53" s="539">
+      <c r="D53" s="538">
         <v>31</v>
       </c>
-      <c r="E53" s="541">
+      <c r="E53" s="540">
         <v>0</v>
       </c>
-      <c r="F53" s="544"/>
-      <c r="G53" s="548" t="s">
+      <c r="F53" s="543"/>
+      <c r="G53" s="547" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="572"/>
-      <c r="I53" s="534"/>
-      <c r="J53" s="534"/>
-      <c r="K53" s="532"/>
-      <c r="L53" s="547" t="s">
+      <c r="H53" s="571"/>
+      <c r="I53" s="533"/>
+      <c r="J53" s="533"/>
+      <c r="K53" s="531"/>
+      <c r="L53" s="546" t="s">
         <v>66</v>
       </c>
-      <c r="M53" s="532"/>
-      <c r="N53" s="653" t="s">
+      <c r="M53" s="531"/>
+      <c r="N53" s="651" t="s">
         <v>67</v>
       </c>
-      <c r="O53" s="532"/>
+      <c r="O53" s="531"/>
       <c r="P53" s="6"/>
-      <c r="Q53" s="150"/>
-      <c r="R53" s="625" t="s">
+      <c r="Q53" s="149"/>
+      <c r="R53" s="624" t="s">
         <v>57</v>
       </c>
-      <c r="S53" s="534"/>
-      <c r="T53" s="365"/>
-      <c r="U53" s="366"/>
-      <c r="V53" s="79"/>
-      <c r="W53" s="80"/>
-      <c r="X53" s="366"/>
-      <c r="Y53" s="366"/>
-      <c r="Z53" s="79"/>
-      <c r="AA53" s="79"/>
-      <c r="AB53" s="641"/>
-      <c r="AC53" s="613"/>
-      <c r="AD53" s="613"/>
-      <c r="AE53" s="614"/>
-      <c r="AF53" s="562"/>
-      <c r="AG53" s="534"/>
-      <c r="AH53" s="534"/>
-      <c r="AI53" s="532"/>
+      <c r="S53" s="533"/>
+      <c r="T53" s="364"/>
+      <c r="U53" s="365"/>
+      <c r="V53" s="78"/>
+      <c r="W53" s="79"/>
+      <c r="X53" s="365"/>
+      <c r="Y53" s="365"/>
+      <c r="Z53" s="78"/>
+      <c r="AA53" s="78"/>
+      <c r="AB53" s="675"/>
+      <c r="AC53" s="676"/>
+      <c r="AD53" s="676"/>
+      <c r="AE53" s="677"/>
+      <c r="AF53" s="561"/>
+      <c r="AG53" s="533"/>
+      <c r="AH53" s="533"/>
+      <c r="AI53" s="531"/>
       <c r="AJ53" s="3"/>
-      <c r="AK53" s="152"/>
-      <c r="AL53" s="152"/>
-      <c r="AM53" s="152"/>
-      <c r="AN53" s="152"/>
+      <c r="AK53" s="151"/>
+      <c r="AL53" s="151"/>
+      <c r="AM53" s="151"/>
+      <c r="AN53" s="151"/>
       <c r="AO53" s="6"/>
       <c r="AP53" s="6"/>
       <c r="AQ53" s="6"/>
@@ -17640,46 +17670,46 @@
       <c r="HW53" s="6"/>
     </row>
     <row r="54" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="536"/>
-      <c r="B54" s="536"/>
-      <c r="C54" s="536"/>
-      <c r="D54" s="536"/>
-      <c r="E54" s="536"/>
-      <c r="F54" s="544"/>
-      <c r="G54" s="549"/>
-      <c r="H54" s="398"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="216"/>
-      <c r="L54" s="660"/>
-      <c r="M54" s="661"/>
+      <c r="A54" s="535"/>
+      <c r="B54" s="535"/>
+      <c r="C54" s="535"/>
+      <c r="D54" s="535"/>
+      <c r="E54" s="535"/>
+      <c r="F54" s="543"/>
+      <c r="G54" s="548"/>
+      <c r="H54" s="397"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="215"/>
+      <c r="L54" s="658"/>
+      <c r="M54" s="659"/>
       <c r="N54" s="6"/>
-      <c r="O54" s="85"/>
+      <c r="O54" s="84"/>
       <c r="P54" s="6"/>
-      <c r="Q54" s="150"/>
-      <c r="R54" s="76"/>
-      <c r="S54" s="85"/>
-      <c r="T54" s="212"/>
-      <c r="U54" s="84"/>
+      <c r="Q54" s="149"/>
+      <c r="R54" s="75"/>
+      <c r="S54" s="84"/>
+      <c r="T54" s="211"/>
+      <c r="U54" s="83"/>
       <c r="V54" s="26"/>
-      <c r="W54" s="112"/>
-      <c r="X54" s="212"/>
-      <c r="Y54" s="84"/>
+      <c r="W54" s="111"/>
+      <c r="X54" s="211"/>
+      <c r="Y54" s="83"/>
       <c r="Z54" s="26"/>
-      <c r="AA54" s="84"/>
-      <c r="AB54" s="64"/>
-      <c r="AC54" s="65"/>
-      <c r="AD54" s="65"/>
-      <c r="AE54" s="66"/>
-      <c r="AF54" s="220"/>
-      <c r="AG54" s="220"/>
+      <c r="AA54" s="83"/>
+      <c r="AB54" s="63"/>
+      <c r="AC54" s="64"/>
+      <c r="AD54" s="64"/>
+      <c r="AE54" s="65"/>
+      <c r="AF54" s="219"/>
+      <c r="AG54" s="219"/>
       <c r="AH54" s="10"/>
-      <c r="AI54" s="219"/>
+      <c r="AI54" s="218"/>
       <c r="AJ54" s="3"/>
-      <c r="AK54" s="86"/>
-      <c r="AL54" s="86"/>
-      <c r="AM54" s="86"/>
-      <c r="AN54" s="86"/>
+      <c r="AK54" s="85"/>
+      <c r="AL54" s="85"/>
+      <c r="AM54" s="85"/>
+      <c r="AN54" s="85"/>
       <c r="AO54" s="6"/>
       <c r="AP54" s="6"/>
       <c r="AQ54" s="6"/>
@@ -17873,52 +17903,52 @@
       <c r="HW54" s="6"/>
     </row>
     <row r="55" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A55" s="537"/>
-      <c r="B55" s="537"/>
-      <c r="C55" s="537"/>
-      <c r="D55" s="537"/>
-      <c r="E55" s="537"/>
-      <c r="F55" s="544"/>
-      <c r="G55" s="550"/>
-      <c r="H55" s="403"/>
-      <c r="I55" s="136"/>
-      <c r="J55" s="88"/>
-      <c r="K55" s="159"/>
-      <c r="L55" s="592" t="s">
+      <c r="A55" s="536"/>
+      <c r="B55" s="536"/>
+      <c r="C55" s="536"/>
+      <c r="D55" s="536"/>
+      <c r="E55" s="536"/>
+      <c r="F55" s="543"/>
+      <c r="G55" s="549"/>
+      <c r="H55" s="402"/>
+      <c r="I55" s="135"/>
+      <c r="J55" s="87"/>
+      <c r="K55" s="158"/>
+      <c r="L55" s="591" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="532"/>
-      <c r="N55" s="662" t="s">
+      <c r="M55" s="531"/>
+      <c r="N55" s="660" t="s">
         <v>69</v>
       </c>
-      <c r="O55" s="532"/>
-      <c r="P55" s="196"/>
-      <c r="Q55" s="104"/>
-      <c r="R55" s="654" t="s">
+      <c r="O55" s="531"/>
+      <c r="P55" s="195"/>
+      <c r="Q55" s="103"/>
+      <c r="R55" s="652" t="s">
         <v>61</v>
       </c>
-      <c r="S55" s="532"/>
-      <c r="T55" s="370"/>
-      <c r="U55" s="371"/>
-      <c r="V55" s="371"/>
-      <c r="W55" s="404"/>
-      <c r="X55" s="370"/>
-      <c r="Y55" s="371"/>
-      <c r="Z55" s="371"/>
-      <c r="AA55" s="371"/>
-      <c r="AB55" s="87"/>
-      <c r="AC55" s="96"/>
-      <c r="AD55" s="96"/>
-      <c r="AE55" s="97"/>
-      <c r="AF55" s="292"/>
-      <c r="AG55" s="220"/>
-      <c r="AH55" s="220"/>
-      <c r="AI55" s="405"/>
+      <c r="S55" s="531"/>
+      <c r="T55" s="369"/>
+      <c r="U55" s="370"/>
+      <c r="V55" s="370"/>
+      <c r="W55" s="403"/>
+      <c r="X55" s="369"/>
+      <c r="Y55" s="370"/>
+      <c r="Z55" s="370"/>
+      <c r="AA55" s="370"/>
+      <c r="AB55" s="86"/>
+      <c r="AC55" s="95"/>
+      <c r="AD55" s="95"/>
+      <c r="AE55" s="96"/>
+      <c r="AF55" s="291"/>
+      <c r="AG55" s="219"/>
+      <c r="AH55" s="219"/>
+      <c r="AI55" s="404"/>
       <c r="AJ55" s="8"/>
-      <c r="AK55" s="162"/>
-      <c r="AL55" s="162"/>
-      <c r="AM55" s="162"/>
-      <c r="AN55" s="163"/>
+      <c r="AK55" s="161"/>
+      <c r="AL55" s="161"/>
+      <c r="AM55" s="161"/>
+      <c r="AN55" s="162"/>
       <c r="AO55" s="6"/>
       <c r="AP55" s="6"/>
       <c r="AQ55" s="6"/>
@@ -18112,50 +18142,52 @@
       <c r="HW55" s="6"/>
     </row>
     <row r="56" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A56" s="542"/>
-      <c r="B56" s="542"/>
-      <c r="C56" s="542"/>
-      <c r="D56" s="542"/>
-      <c r="E56" s="542"/>
-      <c r="F56" s="544"/>
-      <c r="G56" s="561" t="s">
+      <c r="A56" s="541"/>
+      <c r="B56" s="541"/>
+      <c r="C56" s="541"/>
+      <c r="D56" s="541"/>
+      <c r="E56" s="541"/>
+      <c r="F56" s="543"/>
+      <c r="G56" s="560" t="s">
         <v>24</v>
       </c>
-      <c r="H56" s="354"/>
-      <c r="I56" s="106"/>
-      <c r="J56" s="106"/>
-      <c r="K56" s="185"/>
-      <c r="L56" s="378"/>
-      <c r="M56" s="663"/>
-      <c r="N56" s="658" t="s">
+      <c r="H56" s="353"/>
+      <c r="I56" s="105"/>
+      <c r="J56" s="105"/>
+      <c r="K56" s="184"/>
+      <c r="L56" s="377"/>
+      <c r="M56" s="661"/>
+      <c r="N56" s="656" t="s">
         <v>62</v>
       </c>
-      <c r="O56" s="530"/>
-      <c r="P56" s="406"/>
-      <c r="Q56" s="406"/>
-      <c r="R56" s="406"/>
-      <c r="S56" s="407"/>
-      <c r="T56" s="81"/>
-      <c r="U56" s="82"/>
-      <c r="V56" s="82"/>
-      <c r="W56" s="225"/>
-      <c r="X56" s="81"/>
-      <c r="Y56" s="82"/>
-      <c r="Z56" s="82"/>
-      <c r="AA56" s="225"/>
-      <c r="AB56" s="563"/>
-      <c r="AC56" s="534"/>
-      <c r="AD56" s="534"/>
-      <c r="AE56" s="532"/>
-      <c r="AF56" s="37"/>
-      <c r="AG56" s="37"/>
-      <c r="AH56" s="37"/>
-      <c r="AI56" s="40"/>
-      <c r="AJ56" s="408"/>
-      <c r="AK56" s="152"/>
-      <c r="AL56" s="152"/>
-      <c r="AM56" s="152"/>
-      <c r="AN56" s="152"/>
+      <c r="O56" s="529"/>
+      <c r="P56" s="405"/>
+      <c r="Q56" s="405"/>
+      <c r="R56" s="405"/>
+      <c r="S56" s="406"/>
+      <c r="T56" s="80"/>
+      <c r="U56" s="81"/>
+      <c r="V56" s="81"/>
+      <c r="W56" s="224"/>
+      <c r="X56" s="80"/>
+      <c r="Y56" s="81"/>
+      <c r="Z56" s="81"/>
+      <c r="AA56" s="224"/>
+      <c r="AB56" s="678"/>
+      <c r="AC56" s="679"/>
+      <c r="AD56" s="655" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE56" s="528"/>
+      <c r="AF56" s="36"/>
+      <c r="AG56" s="36"/>
+      <c r="AH56" s="36"/>
+      <c r="AI56" s="39"/>
+      <c r="AJ56" s="407"/>
+      <c r="AK56" s="151"/>
+      <c r="AL56" s="151"/>
+      <c r="AM56" s="151"/>
+      <c r="AN56" s="151"/>
       <c r="AO56" s="6"/>
       <c r="AP56" s="6"/>
       <c r="AQ56" s="6"/>
@@ -18349,48 +18381,50 @@
       <c r="HW56" s="6"/>
     </row>
     <row r="57" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A57" s="536"/>
-      <c r="B57" s="536"/>
-      <c r="C57" s="536"/>
-      <c r="D57" s="536"/>
-      <c r="E57" s="536"/>
-      <c r="F57" s="544"/>
-      <c r="G57" s="549"/>
-      <c r="H57" s="168"/>
+      <c r="A57" s="535"/>
+      <c r="B57" s="535"/>
+      <c r="C57" s="535"/>
+      <c r="D57" s="535"/>
+      <c r="E57" s="535"/>
+      <c r="F57" s="543"/>
+      <c r="G57" s="548"/>
+      <c r="H57" s="167"/>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
-      <c r="K57" s="167"/>
-      <c r="L57" s="664"/>
-      <c r="M57" s="665"/>
-      <c r="N57" s="659" t="s">
+      <c r="K57" s="166"/>
+      <c r="L57" s="662"/>
+      <c r="M57" s="663"/>
+      <c r="N57" s="657" t="s">
         <v>64</v>
       </c>
-      <c r="O57" s="532"/>
-      <c r="P57" s="157"/>
-      <c r="Q57" s="157"/>
-      <c r="R57" s="157"/>
-      <c r="S57" s="158"/>
-      <c r="T57" s="165"/>
-      <c r="U57" s="62"/>
-      <c r="V57" s="62"/>
-      <c r="W57" s="166"/>
-      <c r="X57" s="165"/>
-      <c r="Y57" s="62"/>
-      <c r="Z57" s="62"/>
-      <c r="AA57" s="166"/>
-      <c r="AB57" s="64"/>
-      <c r="AC57" s="65"/>
-      <c r="AD57" s="65"/>
-      <c r="AE57" s="66"/>
+      <c r="O57" s="531"/>
+      <c r="P57" s="156"/>
+      <c r="Q57" s="156"/>
+      <c r="R57" s="156"/>
+      <c r="S57" s="157"/>
+      <c r="T57" s="164"/>
+      <c r="U57" s="61"/>
+      <c r="V57" s="61"/>
+      <c r="W57" s="165"/>
+      <c r="X57" s="164"/>
+      <c r="Y57" s="61"/>
+      <c r="Z57" s="61"/>
+      <c r="AA57" s="165"/>
+      <c r="AB57" s="63"/>
+      <c r="AC57" s="64"/>
+      <c r="AD57" s="603" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE57" s="533"/>
       <c r="AF57" s="10"/>
       <c r="AG57" s="10"/>
       <c r="AH57" s="10"/>
-      <c r="AI57" s="45"/>
-      <c r="AJ57" s="408"/>
-      <c r="AK57" s="86"/>
-      <c r="AL57" s="86"/>
-      <c r="AM57" s="86"/>
-      <c r="AN57" s="86"/>
+      <c r="AI57" s="44"/>
+      <c r="AJ57" s="407"/>
+      <c r="AK57" s="85"/>
+      <c r="AL57" s="85"/>
+      <c r="AM57" s="85"/>
+      <c r="AN57" s="85"/>
       <c r="AO57" s="6"/>
       <c r="AP57" s="6"/>
       <c r="AQ57" s="6"/>
@@ -18584,48 +18618,50 @@
       <c r="HW57" s="6"/>
     </row>
     <row r="58" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A58" s="537"/>
-      <c r="B58" s="537"/>
-      <c r="C58" s="537"/>
-      <c r="D58" s="537"/>
-      <c r="E58" s="537"/>
-      <c r="F58" s="544"/>
-      <c r="G58" s="555"/>
-      <c r="H58" s="331"/>
-      <c r="I58" s="89"/>
-      <c r="J58" s="89"/>
-      <c r="K58" s="193"/>
-      <c r="L58" s="332"/>
-      <c r="M58" s="666"/>
-      <c r="N58" s="652" t="s">
+      <c r="A58" s="536"/>
+      <c r="B58" s="536"/>
+      <c r="C58" s="536"/>
+      <c r="D58" s="536"/>
+      <c r="E58" s="536"/>
+      <c r="F58" s="543"/>
+      <c r="G58" s="554"/>
+      <c r="H58" s="330"/>
+      <c r="I58" s="88"/>
+      <c r="J58" s="88"/>
+      <c r="K58" s="192"/>
+      <c r="L58" s="331"/>
+      <c r="M58" s="664"/>
+      <c r="N58" s="650" t="s">
         <v>56</v>
       </c>
-      <c r="O58" s="532"/>
-      <c r="P58" s="334"/>
-      <c r="Q58" s="334"/>
-      <c r="R58" s="160"/>
-      <c r="S58" s="161"/>
-      <c r="T58" s="409"/>
-      <c r="U58" s="410"/>
-      <c r="V58" s="410"/>
-      <c r="W58" s="247"/>
-      <c r="X58" s="411"/>
-      <c r="Y58" s="410"/>
-      <c r="Z58" s="410"/>
-      <c r="AA58" s="412"/>
-      <c r="AB58" s="87"/>
-      <c r="AC58" s="96"/>
-      <c r="AD58" s="96"/>
-      <c r="AE58" s="97"/>
-      <c r="AF58" s="47"/>
-      <c r="AG58" s="47"/>
-      <c r="AH58" s="47"/>
-      <c r="AI58" s="98"/>
-      <c r="AJ58" s="408"/>
-      <c r="AK58" s="162"/>
-      <c r="AL58" s="162"/>
-      <c r="AM58" s="162"/>
-      <c r="AN58" s="163"/>
+      <c r="O58" s="531"/>
+      <c r="P58" s="333"/>
+      <c r="Q58" s="333"/>
+      <c r="R58" s="159"/>
+      <c r="S58" s="160"/>
+      <c r="T58" s="408"/>
+      <c r="U58" s="409"/>
+      <c r="V58" s="409"/>
+      <c r="W58" s="246"/>
+      <c r="X58" s="410"/>
+      <c r="Y58" s="409"/>
+      <c r="Z58" s="409"/>
+      <c r="AA58" s="411"/>
+      <c r="AB58" s="86"/>
+      <c r="AC58" s="95"/>
+      <c r="AD58" s="570" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE58" s="533"/>
+      <c r="AF58" s="46"/>
+      <c r="AG58" s="46"/>
+      <c r="AH58" s="46"/>
+      <c r="AI58" s="97"/>
+      <c r="AJ58" s="407"/>
+      <c r="AK58" s="161"/>
+      <c r="AL58" s="161"/>
+      <c r="AM58" s="161"/>
+      <c r="AN58" s="162"/>
       <c r="AO58" s="6"/>
       <c r="AP58" s="6"/>
       <c r="AQ58" s="6"/>
@@ -18819,46 +18855,48 @@
       <c r="HW58" s="6"/>
     </row>
     <row r="59" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A59" s="542"/>
-      <c r="B59" s="542"/>
-      <c r="C59" s="542"/>
-      <c r="D59" s="542"/>
-      <c r="E59" s="542"/>
-      <c r="F59" s="544"/>
-      <c r="G59" s="603" t="s">
+      <c r="A59" s="541"/>
+      <c r="B59" s="541"/>
+      <c r="C59" s="541"/>
+      <c r="D59" s="541"/>
+      <c r="E59" s="541"/>
+      <c r="F59" s="543"/>
+      <c r="G59" s="602" t="s">
         <v>25</v>
       </c>
-      <c r="H59" s="168"/>
+      <c r="H59" s="167"/>
       <c r="I59" s="26"/>
       <c r="J59" s="26"/>
-      <c r="K59" s="167"/>
-      <c r="L59" s="664"/>
-      <c r="M59" s="665"/>
-      <c r="N59" s="653" t="s">
+      <c r="K59" s="166"/>
+      <c r="L59" s="662"/>
+      <c r="M59" s="663"/>
+      <c r="N59" s="651" t="s">
         <v>66</v>
       </c>
-      <c r="O59" s="532"/>
-      <c r="P59" s="82"/>
-      <c r="Q59" s="82"/>
-      <c r="R59" s="82"/>
-      <c r="S59" s="223"/>
-      <c r="T59" s="169"/>
-      <c r="U59" s="124"/>
+      <c r="O59" s="531"/>
+      <c r="P59" s="81"/>
+      <c r="Q59" s="81"/>
+      <c r="R59" s="81"/>
+      <c r="S59" s="222"/>
+      <c r="T59" s="168"/>
+      <c r="U59" s="123"/>
       <c r="V59" s="6"/>
-      <c r="W59" s="150"/>
-      <c r="X59" s="170"/>
-      <c r="Y59" s="124"/>
+      <c r="W59" s="149"/>
+      <c r="X59" s="169"/>
+      <c r="Y59" s="123"/>
       <c r="Z59" s="6"/>
       <c r="AA59" s="10"/>
-      <c r="AB59" s="43"/>
+      <c r="AB59" s="42"/>
       <c r="AC59" s="10"/>
-      <c r="AD59" s="10"/>
-      <c r="AE59" s="45"/>
+      <c r="AD59" s="624" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE59" s="533"/>
       <c r="AF59" s="10"/>
       <c r="AG59" s="10"/>
       <c r="AH59" s="10"/>
-      <c r="AI59" s="45"/>
-      <c r="AJ59" s="408"/>
+      <c r="AI59" s="44"/>
+      <c r="AJ59" s="407"/>
       <c r="AK59" s="6"/>
       <c r="AL59" s="6"/>
       <c r="AM59" s="6"/>
@@ -19056,42 +19094,42 @@
       <c r="HW59" s="6"/>
     </row>
     <row r="60" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="536"/>
-      <c r="B60" s="536"/>
-      <c r="C60" s="536"/>
-      <c r="D60" s="536"/>
-      <c r="E60" s="536"/>
-      <c r="F60" s="544"/>
-      <c r="G60" s="549"/>
-      <c r="H60" s="168"/>
+      <c r="A60" s="535"/>
+      <c r="B60" s="535"/>
+      <c r="C60" s="535"/>
+      <c r="D60" s="535"/>
+      <c r="E60" s="535"/>
+      <c r="F60" s="543"/>
+      <c r="G60" s="548"/>
+      <c r="H60" s="167"/>
       <c r="I60" s="26"/>
       <c r="J60" s="26"/>
-      <c r="K60" s="167"/>
-      <c r="L60" s="664"/>
-      <c r="M60" s="665"/>
-      <c r="N60" s="76"/>
-      <c r="O60" s="85"/>
-      <c r="P60" s="82"/>
-      <c r="Q60" s="82"/>
-      <c r="R60" s="82"/>
-      <c r="S60" s="225"/>
-      <c r="T60" s="123"/>
-      <c r="U60" s="172"/>
+      <c r="K60" s="166"/>
+      <c r="L60" s="662"/>
+      <c r="M60" s="663"/>
+      <c r="N60" s="75"/>
+      <c r="O60" s="84"/>
+      <c r="P60" s="81"/>
+      <c r="Q60" s="81"/>
+      <c r="R60" s="81"/>
+      <c r="S60" s="224"/>
+      <c r="T60" s="122"/>
+      <c r="U60" s="171"/>
       <c r="V60" s="10"/>
-      <c r="W60" s="85"/>
-      <c r="X60" s="123"/>
-      <c r="Y60" s="173"/>
+      <c r="W60" s="84"/>
+      <c r="X60" s="122"/>
+      <c r="Y60" s="172"/>
       <c r="Z60" s="6"/>
-      <c r="AA60" s="173"/>
+      <c r="AA60" s="172"/>
       <c r="AB60" s="27"/>
       <c r="AC60" s="26"/>
-      <c r="AD60" s="26"/>
-      <c r="AE60" s="28"/>
+      <c r="AD60" s="75"/>
+      <c r="AE60" s="84"/>
       <c r="AF60" s="10"/>
       <c r="AG60" s="10"/>
       <c r="AH60" s="10"/>
-      <c r="AI60" s="45"/>
-      <c r="AJ60" s="408"/>
+      <c r="AI60" s="44"/>
+      <c r="AJ60" s="407"/>
       <c r="AK60" s="6"/>
       <c r="AL60" s="6"/>
       <c r="AM60" s="6"/>
@@ -19289,44 +19327,46 @@
       <c r="HW60" s="6"/>
     </row>
     <row r="61" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A61" s="537"/>
-      <c r="B61" s="537"/>
-      <c r="C61" s="537"/>
-      <c r="D61" s="537"/>
-      <c r="E61" s="537"/>
-      <c r="F61" s="544"/>
-      <c r="G61" s="602"/>
-      <c r="H61" s="168"/>
+      <c r="A61" s="536"/>
+      <c r="B61" s="536"/>
+      <c r="C61" s="536"/>
+      <c r="D61" s="536"/>
+      <c r="E61" s="536"/>
+      <c r="F61" s="543"/>
+      <c r="G61" s="601"/>
+      <c r="H61" s="167"/>
       <c r="I61" s="26"/>
       <c r="J61" s="26"/>
-      <c r="K61" s="167"/>
-      <c r="L61" s="413"/>
-      <c r="M61" s="414"/>
-      <c r="N61" s="654" t="s">
+      <c r="K61" s="166"/>
+      <c r="L61" s="412"/>
+      <c r="M61" s="413"/>
+      <c r="N61" s="652" t="s">
         <v>68</v>
       </c>
-      <c r="O61" s="532"/>
-      <c r="P61" s="196"/>
-      <c r="Q61" s="196"/>
-      <c r="R61" s="196"/>
-      <c r="S61" s="150"/>
-      <c r="T61" s="174"/>
-      <c r="U61" s="175"/>
-      <c r="V61" s="115"/>
-      <c r="W61" s="176"/>
-      <c r="X61" s="174"/>
-      <c r="Y61" s="177"/>
-      <c r="Z61" s="178"/>
-      <c r="AA61" s="179"/>
+      <c r="O61" s="531"/>
+      <c r="P61" s="195"/>
+      <c r="Q61" s="195"/>
+      <c r="R61" s="195"/>
+      <c r="S61" s="149"/>
+      <c r="T61" s="173"/>
+      <c r="U61" s="174"/>
+      <c r="V61" s="114"/>
+      <c r="W61" s="175"/>
+      <c r="X61" s="173"/>
+      <c r="Y61" s="176"/>
+      <c r="Z61" s="177"/>
+      <c r="AA61" s="178"/>
       <c r="AB61" s="27"/>
       <c r="AC61" s="26"/>
-      <c r="AD61" s="26"/>
-      <c r="AE61" s="28"/>
+      <c r="AD61" s="652" t="s">
+        <v>82</v>
+      </c>
+      <c r="AE61" s="531"/>
       <c r="AF61" s="10"/>
       <c r="AG61" s="10"/>
       <c r="AH61" s="10"/>
-      <c r="AI61" s="45"/>
-      <c r="AJ61" s="408"/>
+      <c r="AI61" s="44"/>
+      <c r="AJ61" s="407"/>
       <c r="AK61" s="6"/>
       <c r="AL61" s="6"/>
       <c r="AM61" s="6"/>
@@ -19524,29 +19564,29 @@
       <c r="HW61" s="6"/>
     </row>
     <row r="62" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="542"/>
-      <c r="B62" s="538"/>
-      <c r="C62" s="538"/>
-      <c r="D62" s="538"/>
-      <c r="E62" s="631"/>
-      <c r="F62" s="543" t="s">
+      <c r="A62" s="541"/>
+      <c r="B62" s="537"/>
+      <c r="C62" s="537"/>
+      <c r="D62" s="537"/>
+      <c r="E62" s="630"/>
+      <c r="F62" s="542" t="s">
         <v>28</v>
       </c>
-      <c r="G62" s="615" t="s">
+      <c r="G62" s="614" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="284"/>
-      <c r="I62" s="283"/>
-      <c r="J62" s="283"/>
-      <c r="K62" s="285"/>
-      <c r="L62" s="415"/>
-      <c r="M62" s="415"/>
-      <c r="N62" s="415"/>
-      <c r="O62" s="416"/>
-      <c r="P62" s="417"/>
-      <c r="Q62" s="417"/>
-      <c r="R62" s="417"/>
-      <c r="S62" s="418"/>
+      <c r="H62" s="283"/>
+      <c r="I62" s="282"/>
+      <c r="J62" s="282"/>
+      <c r="K62" s="284"/>
+      <c r="L62" s="414"/>
+      <c r="M62" s="414"/>
+      <c r="N62" s="414"/>
+      <c r="O62" s="415"/>
+      <c r="P62" s="416"/>
+      <c r="Q62" s="416"/>
+      <c r="R62" s="416"/>
+      <c r="S62" s="417"/>
       <c r="T62" s="18"/>
       <c r="U62" s="19"/>
       <c r="V62" s="19"/>
@@ -19555,15 +19595,15 @@
       <c r="Y62" s="19"/>
       <c r="Z62" s="19"/>
       <c r="AA62" s="19"/>
-      <c r="AB62" s="419"/>
-      <c r="AC62" s="181"/>
-      <c r="AD62" s="181"/>
-      <c r="AE62" s="420"/>
-      <c r="AF62" s="421"/>
-      <c r="AG62" s="421"/>
-      <c r="AH62" s="421"/>
-      <c r="AI62" s="422"/>
-      <c r="AJ62" s="143"/>
+      <c r="AB62" s="418"/>
+      <c r="AC62" s="180"/>
+      <c r="AD62" s="180"/>
+      <c r="AE62" s="419"/>
+      <c r="AF62" s="420"/>
+      <c r="AG62" s="420"/>
+      <c r="AH62" s="420"/>
+      <c r="AI62" s="421"/>
+      <c r="AJ62" s="142"/>
       <c r="AK62" s="6"/>
       <c r="AL62" s="6"/>
       <c r="AM62" s="6"/>
@@ -19761,25 +19801,25 @@
       <c r="HW62" s="6"/>
     </row>
     <row r="63" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="536"/>
-      <c r="B63" s="536"/>
-      <c r="C63" s="536"/>
-      <c r="D63" s="536"/>
-      <c r="E63" s="536"/>
-      <c r="F63" s="544"/>
-      <c r="G63" s="549"/>
-      <c r="H63" s="271"/>
+      <c r="A63" s="535"/>
+      <c r="B63" s="535"/>
+      <c r="C63" s="535"/>
+      <c r="D63" s="535"/>
+      <c r="E63" s="535"/>
+      <c r="F63" s="543"/>
+      <c r="G63" s="548"/>
+      <c r="H63" s="270"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
-      <c r="K63" s="204"/>
+      <c r="K63" s="203"/>
       <c r="L63" s="29"/>
       <c r="M63" s="29"/>
       <c r="N63" s="29"/>
       <c r="O63" s="30"/>
-      <c r="P63" s="237"/>
-      <c r="Q63" s="237"/>
-      <c r="R63" s="237"/>
-      <c r="S63" s="238"/>
+      <c r="P63" s="236"/>
+      <c r="Q63" s="236"/>
+      <c r="R63" s="236"/>
+      <c r="S63" s="237"/>
       <c r="T63" s="27"/>
       <c r="U63" s="26"/>
       <c r="V63" s="26"/>
@@ -19796,7 +19836,7 @@
       <c r="AG63" s="24"/>
       <c r="AH63" s="24"/>
       <c r="AI63" s="25"/>
-      <c r="AJ63" s="143"/>
+      <c r="AJ63" s="142"/>
       <c r="AK63" s="6"/>
       <c r="AL63" s="6"/>
       <c r="AM63" s="6"/>
@@ -19994,21 +20034,21 @@
       <c r="HW63" s="6"/>
     </row>
     <row r="64" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A64" s="537"/>
-      <c r="B64" s="537"/>
-      <c r="C64" s="537"/>
-      <c r="D64" s="537"/>
-      <c r="E64" s="537"/>
-      <c r="F64" s="544"/>
-      <c r="G64" s="549"/>
-      <c r="H64" s="203"/>
+      <c r="A64" s="536"/>
+      <c r="B64" s="536"/>
+      <c r="C64" s="536"/>
+      <c r="D64" s="536"/>
+      <c r="E64" s="536"/>
+      <c r="F64" s="543"/>
+      <c r="G64" s="548"/>
+      <c r="H64" s="202"/>
       <c r="I64" s="32"/>
       <c r="J64" s="32"/>
-      <c r="K64" s="255"/>
-      <c r="L64" s="127"/>
-      <c r="M64" s="127"/>
-      <c r="N64" s="127"/>
-      <c r="O64" s="117"/>
+      <c r="K64" s="254"/>
+      <c r="L64" s="126"/>
+      <c r="M64" s="126"/>
+      <c r="N64" s="126"/>
+      <c r="O64" s="116"/>
       <c r="P64" s="29"/>
       <c r="Q64" s="29"/>
       <c r="R64" s="29"/>
@@ -20025,10 +20065,10 @@
       <c r="AC64" s="26"/>
       <c r="AD64" s="26"/>
       <c r="AE64" s="28"/>
-      <c r="AF64" s="397"/>
-      <c r="AG64" s="51"/>
-      <c r="AH64" s="51"/>
-      <c r="AI64" s="199"/>
+      <c r="AF64" s="396"/>
+      <c r="AG64" s="50"/>
+      <c r="AH64" s="50"/>
+      <c r="AI64" s="198"/>
       <c r="AJ64" s="8"/>
       <c r="AK64" s="6"/>
       <c r="AL64" s="6"/>
@@ -20227,54 +20267,54 @@
       <c r="HW64" s="6"/>
     </row>
     <row r="65" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A65" s="539">
+      <c r="A65" s="538">
         <v>9</v>
       </c>
-      <c r="B65" s="539">
+      <c r="B65" s="538">
         <v>9</v>
       </c>
-      <c r="C65" s="539">
+      <c r="C65" s="538">
         <v>6</v>
       </c>
-      <c r="D65" s="539">
+      <c r="D65" s="538">
         <v>4</v>
       </c>
-      <c r="E65" s="539">
+      <c r="E65" s="538">
         <v>1</v>
       </c>
-      <c r="F65" s="544"/>
-      <c r="G65" s="561" t="s">
+      <c r="F65" s="543"/>
+      <c r="G65" s="560" t="s">
         <v>19</v>
       </c>
-      <c r="H65" s="354"/>
-      <c r="I65" s="106"/>
-      <c r="J65" s="106"/>
-      <c r="K65" s="185"/>
-      <c r="L65" s="41"/>
-      <c r="M65" s="41"/>
-      <c r="N65" s="41"/>
-      <c r="O65" s="42"/>
-      <c r="P65" s="423"/>
-      <c r="Q65" s="423"/>
-      <c r="R65" s="423"/>
-      <c r="S65" s="424"/>
-      <c r="T65" s="105"/>
-      <c r="U65" s="106"/>
-      <c r="V65" s="106"/>
-      <c r="W65" s="132"/>
-      <c r="X65" s="106"/>
-      <c r="Y65" s="106"/>
-      <c r="Z65" s="106"/>
-      <c r="AA65" s="132"/>
-      <c r="AB65" s="638"/>
-      <c r="AC65" s="529"/>
-      <c r="AD65" s="529"/>
-      <c r="AE65" s="639"/>
-      <c r="AF65" s="43"/>
+      <c r="H65" s="353"/>
+      <c r="I65" s="105"/>
+      <c r="J65" s="105"/>
+      <c r="K65" s="184"/>
+      <c r="L65" s="40"/>
+      <c r="M65" s="40"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="41"/>
+      <c r="P65" s="422"/>
+      <c r="Q65" s="422"/>
+      <c r="R65" s="422"/>
+      <c r="S65" s="423"/>
+      <c r="T65" s="104"/>
+      <c r="U65" s="105"/>
+      <c r="V65" s="105"/>
+      <c r="W65" s="131"/>
+      <c r="X65" s="105"/>
+      <c r="Y65" s="105"/>
+      <c r="Z65" s="105"/>
+      <c r="AA65" s="131"/>
+      <c r="AB65" s="637"/>
+      <c r="AC65" s="528"/>
+      <c r="AD65" s="528"/>
+      <c r="AE65" s="638"/>
+      <c r="AF65" s="42"/>
       <c r="AG65" s="10"/>
       <c r="AH65" s="10"/>
-      <c r="AI65" s="45"/>
-      <c r="AJ65" s="197"/>
+      <c r="AI65" s="44"/>
+      <c r="AJ65" s="196"/>
       <c r="AK65" s="6"/>
       <c r="AL65" s="6"/>
       <c r="AM65" s="6"/>
@@ -20472,25 +20512,25 @@
       <c r="HW65" s="6"/>
     </row>
     <row r="66" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="536"/>
-      <c r="B66" s="536"/>
-      <c r="C66" s="536"/>
-      <c r="D66" s="536"/>
-      <c r="E66" s="536"/>
-      <c r="F66" s="544"/>
-      <c r="G66" s="549"/>
-      <c r="H66" s="168"/>
+      <c r="A66" s="535"/>
+      <c r="B66" s="535"/>
+      <c r="C66" s="535"/>
+      <c r="D66" s="535"/>
+      <c r="E66" s="535"/>
+      <c r="F66" s="543"/>
+      <c r="G66" s="548"/>
+      <c r="H66" s="167"/>
       <c r="I66" s="26"/>
       <c r="J66" s="26"/>
-      <c r="K66" s="167"/>
+      <c r="K66" s="166"/>
       <c r="L66" s="32"/>
       <c r="M66" s="32"/>
       <c r="N66" s="32"/>
-      <c r="O66" s="44"/>
+      <c r="O66" s="43"/>
       <c r="P66" s="32"/>
       <c r="Q66" s="32"/>
       <c r="R66" s="32"/>
-      <c r="S66" s="44"/>
+      <c r="S66" s="43"/>
       <c r="T66" s="27"/>
       <c r="U66" s="26"/>
       <c r="V66" s="26"/>
@@ -20499,15 +20539,15 @@
       <c r="Y66" s="26"/>
       <c r="Z66" s="26"/>
       <c r="AA66" s="28"/>
-      <c r="AB66" s="64"/>
-      <c r="AC66" s="65"/>
-      <c r="AD66" s="65"/>
-      <c r="AE66" s="66"/>
-      <c r="AF66" s="43"/>
+      <c r="AB66" s="63"/>
+      <c r="AC66" s="64"/>
+      <c r="AD66" s="64"/>
+      <c r="AE66" s="65"/>
+      <c r="AF66" s="42"/>
       <c r="AG66" s="10"/>
       <c r="AH66" s="10"/>
-      <c r="AI66" s="45"/>
-      <c r="AJ66" s="197"/>
+      <c r="AI66" s="44"/>
+      <c r="AJ66" s="196"/>
       <c r="AK66" s="6"/>
       <c r="AL66" s="6"/>
       <c r="AM66" s="6"/>
@@ -20705,42 +20745,42 @@
       <c r="HW66" s="6"/>
     </row>
     <row r="67" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A67" s="537"/>
-      <c r="B67" s="537"/>
-      <c r="C67" s="537"/>
-      <c r="D67" s="537"/>
-      <c r="E67" s="537"/>
-      <c r="F67" s="544"/>
-      <c r="G67" s="555"/>
-      <c r="H67" s="331"/>
-      <c r="I67" s="89"/>
-      <c r="J67" s="89"/>
-      <c r="K67" s="193"/>
-      <c r="L67" s="51"/>
-      <c r="M67" s="51"/>
-      <c r="N67" s="51"/>
-      <c r="O67" s="268"/>
-      <c r="P67" s="51"/>
-      <c r="Q67" s="51"/>
-      <c r="R67" s="51"/>
-      <c r="S67" s="268"/>
-      <c r="T67" s="137"/>
-      <c r="U67" s="89"/>
-      <c r="V67" s="89"/>
-      <c r="W67" s="90"/>
-      <c r="X67" s="89"/>
-      <c r="Y67" s="89"/>
-      <c r="Z67" s="89"/>
-      <c r="AA67" s="90"/>
-      <c r="AB67" s="87"/>
-      <c r="AC67" s="96"/>
-      <c r="AD67" s="96"/>
-      <c r="AE67" s="97"/>
-      <c r="AF67" s="43"/>
+      <c r="A67" s="536"/>
+      <c r="B67" s="536"/>
+      <c r="C67" s="536"/>
+      <c r="D67" s="536"/>
+      <c r="E67" s="536"/>
+      <c r="F67" s="543"/>
+      <c r="G67" s="554"/>
+      <c r="H67" s="330"/>
+      <c r="I67" s="88"/>
+      <c r="J67" s="88"/>
+      <c r="K67" s="192"/>
+      <c r="L67" s="50"/>
+      <c r="M67" s="50"/>
+      <c r="N67" s="50"/>
+      <c r="O67" s="267"/>
+      <c r="P67" s="50"/>
+      <c r="Q67" s="50"/>
+      <c r="R67" s="50"/>
+      <c r="S67" s="267"/>
+      <c r="T67" s="136"/>
+      <c r="U67" s="88"/>
+      <c r="V67" s="88"/>
+      <c r="W67" s="89"/>
+      <c r="X67" s="88"/>
+      <c r="Y67" s="88"/>
+      <c r="Z67" s="88"/>
+      <c r="AA67" s="89"/>
+      <c r="AB67" s="86"/>
+      <c r="AC67" s="95"/>
+      <c r="AD67" s="95"/>
+      <c r="AE67" s="96"/>
+      <c r="AF67" s="42"/>
       <c r="AG67" s="10"/>
       <c r="AH67" s="10"/>
-      <c r="AI67" s="45"/>
-      <c r="AJ67" s="197"/>
+      <c r="AI67" s="44"/>
+      <c r="AJ67" s="196"/>
       <c r="AK67" s="6"/>
       <c r="AL67" s="6"/>
       <c r="AM67" s="6"/>
@@ -20938,29 +20978,29 @@
       <c r="HW67" s="6"/>
     </row>
     <row r="68" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="539">
+      <c r="A68" s="538">
         <v>23</v>
       </c>
-      <c r="B68" s="539">
+      <c r="B68" s="538">
         <v>23</v>
       </c>
-      <c r="C68" s="539">
+      <c r="C68" s="538">
         <v>20</v>
       </c>
-      <c r="D68" s="539">
+      <c r="D68" s="538">
         <v>18</v>
       </c>
-      <c r="E68" s="539"/>
-      <c r="F68" s="544"/>
-      <c r="G68" s="610" t="s">
+      <c r="E68" s="538"/>
+      <c r="F68" s="543"/>
+      <c r="G68" s="609" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="564"/>
-      <c r="I68" s="529"/>
-      <c r="J68" s="529"/>
-      <c r="K68" s="530"/>
-      <c r="L68" s="257"/>
-      <c r="M68" s="58"/>
+      <c r="H68" s="563"/>
+      <c r="I68" s="528"/>
+      <c r="J68" s="528"/>
+      <c r="K68" s="529"/>
+      <c r="L68" s="256"/>
+      <c r="M68" s="57"/>
       <c r="N68" s="26"/>
       <c r="O68" s="28"/>
       <c r="P68" s="10"/>
@@ -20975,15 +21015,15 @@
       <c r="Y68" s="26"/>
       <c r="Z68" s="26"/>
       <c r="AA68" s="28"/>
-      <c r="AB68" s="636"/>
-      <c r="AC68" s="613"/>
-      <c r="AD68" s="613"/>
-      <c r="AE68" s="637"/>
-      <c r="AF68" s="540"/>
-      <c r="AG68" s="529"/>
-      <c r="AH68" s="529"/>
-      <c r="AI68" s="530"/>
-      <c r="AJ68" s="122"/>
+      <c r="AB68" s="635"/>
+      <c r="AC68" s="612"/>
+      <c r="AD68" s="612"/>
+      <c r="AE68" s="636"/>
+      <c r="AF68" s="539"/>
+      <c r="AG68" s="528"/>
+      <c r="AH68" s="528"/>
+      <c r="AI68" s="529"/>
+      <c r="AJ68" s="121"/>
       <c r="AK68" s="6"/>
       <c r="AL68" s="6"/>
       <c r="AM68" s="6"/>
@@ -21181,19 +21221,19 @@
       <c r="HW68" s="6"/>
     </row>
     <row r="69" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A69" s="536"/>
-      <c r="B69" s="536"/>
-      <c r="C69" s="536"/>
-      <c r="D69" s="536"/>
-      <c r="E69" s="536"/>
-      <c r="F69" s="544"/>
-      <c r="G69" s="549"/>
-      <c r="H69" s="398"/>
-      <c r="I69" s="82"/>
-      <c r="J69" s="82"/>
-      <c r="K69" s="216"/>
-      <c r="L69" s="384"/>
-      <c r="M69" s="61"/>
+      <c r="A69" s="535"/>
+      <c r="B69" s="535"/>
+      <c r="C69" s="535"/>
+      <c r="D69" s="535"/>
+      <c r="E69" s="535"/>
+      <c r="F69" s="543"/>
+      <c r="G69" s="548"/>
+      <c r="H69" s="397"/>
+      <c r="I69" s="81"/>
+      <c r="J69" s="81"/>
+      <c r="K69" s="215"/>
+      <c r="L69" s="383"/>
+      <c r="M69" s="60"/>
       <c r="N69" s="26"/>
       <c r="O69" s="28"/>
       <c r="P69" s="10"/>
@@ -21208,15 +21248,15 @@
       <c r="Y69" s="26"/>
       <c r="Z69" s="26"/>
       <c r="AA69" s="28"/>
-      <c r="AB69" s="64"/>
-      <c r="AC69" s="65"/>
-      <c r="AD69" s="65"/>
-      <c r="AE69" s="66"/>
-      <c r="AF69" s="64"/>
-      <c r="AG69" s="65"/>
-      <c r="AH69" s="65"/>
-      <c r="AI69" s="77"/>
-      <c r="AJ69" s="126"/>
+      <c r="AB69" s="63"/>
+      <c r="AC69" s="64"/>
+      <c r="AD69" s="64"/>
+      <c r="AE69" s="65"/>
+      <c r="AF69" s="63"/>
+      <c r="AG69" s="64"/>
+      <c r="AH69" s="64"/>
+      <c r="AI69" s="76"/>
+      <c r="AJ69" s="125"/>
       <c r="AK69" s="6"/>
       <c r="AL69" s="6"/>
       <c r="AM69" s="6"/>
@@ -21414,19 +21454,19 @@
       <c r="HW69" s="6"/>
     </row>
     <row r="70" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A70" s="537"/>
-      <c r="B70" s="537"/>
-      <c r="C70" s="537"/>
-      <c r="D70" s="537"/>
-      <c r="E70" s="537"/>
-      <c r="F70" s="544"/>
-      <c r="G70" s="611"/>
-      <c r="H70" s="401"/>
-      <c r="I70" s="191"/>
-      <c r="J70" s="191"/>
-      <c r="K70" s="363"/>
-      <c r="L70" s="425"/>
-      <c r="M70" s="426"/>
+      <c r="A70" s="536"/>
+      <c r="B70" s="536"/>
+      <c r="C70" s="536"/>
+      <c r="D70" s="536"/>
+      <c r="E70" s="536"/>
+      <c r="F70" s="543"/>
+      <c r="G70" s="610"/>
+      <c r="H70" s="400"/>
+      <c r="I70" s="190"/>
+      <c r="J70" s="190"/>
+      <c r="K70" s="362"/>
+      <c r="L70" s="424"/>
+      <c r="M70" s="425"/>
       <c r="N70" s="26"/>
       <c r="O70" s="28"/>
       <c r="P70" s="10"/>
@@ -21441,15 +21481,15 @@
       <c r="Y70" s="26"/>
       <c r="Z70" s="26"/>
       <c r="AA70" s="28"/>
-      <c r="AB70" s="190"/>
-      <c r="AC70" s="191"/>
-      <c r="AD70" s="191"/>
-      <c r="AE70" s="192"/>
-      <c r="AF70" s="190"/>
-      <c r="AG70" s="191"/>
-      <c r="AH70" s="191"/>
-      <c r="AI70" s="427"/>
-      <c r="AJ70" s="131"/>
+      <c r="AB70" s="189"/>
+      <c r="AC70" s="190"/>
+      <c r="AD70" s="190"/>
+      <c r="AE70" s="191"/>
+      <c r="AF70" s="189"/>
+      <c r="AG70" s="190"/>
+      <c r="AH70" s="190"/>
+      <c r="AI70" s="426"/>
+      <c r="AJ70" s="130"/>
       <c r="AK70" s="6"/>
       <c r="AL70" s="6"/>
       <c r="AM70" s="6"/>
@@ -21647,54 +21687,54 @@
       <c r="HW70" s="6"/>
     </row>
     <row r="71" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="541">
+      <c r="A71" s="540">
         <v>0</v>
       </c>
-      <c r="B71" s="541">
+      <c r="B71" s="540">
         <v>0</v>
       </c>
-      <c r="C71" s="541">
+      <c r="C71" s="540">
         <v>0</v>
       </c>
-      <c r="D71" s="541">
+      <c r="D71" s="540">
         <v>0</v>
       </c>
-      <c r="E71" s="539">
+      <c r="E71" s="538">
         <v>0</v>
       </c>
-      <c r="F71" s="544"/>
-      <c r="G71" s="621" t="s">
+      <c r="F71" s="543"/>
+      <c r="G71" s="620" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="612"/>
-      <c r="I71" s="613"/>
-      <c r="J71" s="613"/>
-      <c r="K71" s="614"/>
-      <c r="L71" s="612"/>
-      <c r="M71" s="613"/>
-      <c r="N71" s="613"/>
-      <c r="O71" s="614"/>
-      <c r="P71" s="624"/>
-      <c r="Q71" s="613"/>
-      <c r="R71" s="613"/>
-      <c r="S71" s="614"/>
-      <c r="T71" s="242"/>
-      <c r="U71" s="243"/>
-      <c r="V71" s="243"/>
-      <c r="W71" s="428"/>
-      <c r="X71" s="243"/>
-      <c r="Y71" s="243"/>
-      <c r="Z71" s="243"/>
-      <c r="AA71" s="428"/>
-      <c r="AB71" s="591"/>
-      <c r="AC71" s="534"/>
-      <c r="AD71" s="534"/>
-      <c r="AE71" s="534"/>
-      <c r="AF71" s="563"/>
-      <c r="AG71" s="534"/>
-      <c r="AH71" s="534"/>
-      <c r="AI71" s="532"/>
-      <c r="AJ71" s="122"/>
+      <c r="H71" s="611"/>
+      <c r="I71" s="612"/>
+      <c r="J71" s="612"/>
+      <c r="K71" s="613"/>
+      <c r="L71" s="611"/>
+      <c r="M71" s="612"/>
+      <c r="N71" s="612"/>
+      <c r="O71" s="613"/>
+      <c r="P71" s="623"/>
+      <c r="Q71" s="612"/>
+      <c r="R71" s="612"/>
+      <c r="S71" s="613"/>
+      <c r="T71" s="241"/>
+      <c r="U71" s="242"/>
+      <c r="V71" s="242"/>
+      <c r="W71" s="427"/>
+      <c r="X71" s="242"/>
+      <c r="Y71" s="242"/>
+      <c r="Z71" s="242"/>
+      <c r="AA71" s="427"/>
+      <c r="AB71" s="590"/>
+      <c r="AC71" s="533"/>
+      <c r="AD71" s="533"/>
+      <c r="AE71" s="533"/>
+      <c r="AF71" s="562"/>
+      <c r="AG71" s="533"/>
+      <c r="AH71" s="533"/>
+      <c r="AI71" s="531"/>
+      <c r="AJ71" s="121"/>
       <c r="AK71" s="6"/>
       <c r="AL71" s="6"/>
       <c r="AM71" s="6"/>
@@ -21892,42 +21932,42 @@
       <c r="HW71" s="6"/>
     </row>
     <row r="72" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A72" s="536"/>
-      <c r="B72" s="536"/>
-      <c r="C72" s="536"/>
-      <c r="D72" s="536"/>
-      <c r="E72" s="536"/>
-      <c r="F72" s="544"/>
-      <c r="G72" s="549"/>
-      <c r="H72" s="398"/>
-      <c r="I72" s="82"/>
-      <c r="J72" s="82"/>
-      <c r="K72" s="216"/>
-      <c r="L72" s="213"/>
-      <c r="M72" s="65"/>
-      <c r="N72" s="65"/>
-      <c r="O72" s="216"/>
-      <c r="P72" s="65"/>
-      <c r="Q72" s="65"/>
-      <c r="R72" s="65"/>
-      <c r="S72" s="77"/>
-      <c r="T72" s="53"/>
-      <c r="U72" s="54"/>
-      <c r="V72" s="54"/>
-      <c r="W72" s="63"/>
-      <c r="X72" s="54"/>
-      <c r="Y72" s="54"/>
-      <c r="Z72" s="54"/>
-      <c r="AA72" s="63"/>
-      <c r="AB72" s="64"/>
-      <c r="AC72" s="65"/>
-      <c r="AD72" s="65"/>
-      <c r="AE72" s="65"/>
-      <c r="AF72" s="64"/>
-      <c r="AG72" s="65"/>
-      <c r="AH72" s="65"/>
-      <c r="AI72" s="77"/>
-      <c r="AJ72" s="126"/>
+      <c r="A72" s="535"/>
+      <c r="B72" s="535"/>
+      <c r="C72" s="535"/>
+      <c r="D72" s="535"/>
+      <c r="E72" s="535"/>
+      <c r="F72" s="543"/>
+      <c r="G72" s="548"/>
+      <c r="H72" s="397"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="215"/>
+      <c r="L72" s="212"/>
+      <c r="M72" s="64"/>
+      <c r="N72" s="64"/>
+      <c r="O72" s="215"/>
+      <c r="P72" s="64"/>
+      <c r="Q72" s="64"/>
+      <c r="R72" s="64"/>
+      <c r="S72" s="76"/>
+      <c r="T72" s="52"/>
+      <c r="U72" s="53"/>
+      <c r="V72" s="53"/>
+      <c r="W72" s="62"/>
+      <c r="X72" s="53"/>
+      <c r="Y72" s="53"/>
+      <c r="Z72" s="53"/>
+      <c r="AA72" s="62"/>
+      <c r="AB72" s="63"/>
+      <c r="AC72" s="64"/>
+      <c r="AD72" s="64"/>
+      <c r="AE72" s="64"/>
+      <c r="AF72" s="63"/>
+      <c r="AG72" s="64"/>
+      <c r="AH72" s="64"/>
+      <c r="AI72" s="76"/>
+      <c r="AJ72" s="125"/>
       <c r="AK72" s="6"/>
       <c r="AL72" s="6"/>
       <c r="AM72" s="6"/>
@@ -22125,42 +22165,42 @@
       <c r="HW72" s="6"/>
     </row>
     <row r="73" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A73" s="537"/>
-      <c r="B73" s="537"/>
-      <c r="C73" s="537"/>
-      <c r="D73" s="537"/>
-      <c r="E73" s="537"/>
-      <c r="F73" s="544"/>
-      <c r="G73" s="555"/>
-      <c r="H73" s="250"/>
-      <c r="I73" s="96"/>
-      <c r="J73" s="96"/>
-      <c r="K73" s="333"/>
-      <c r="L73" s="250"/>
-      <c r="M73" s="96"/>
-      <c r="N73" s="96"/>
-      <c r="O73" s="333"/>
-      <c r="P73" s="96"/>
-      <c r="Q73" s="96"/>
-      <c r="R73" s="96"/>
-      <c r="S73" s="104"/>
-      <c r="T73" s="138"/>
-      <c r="U73" s="94"/>
-      <c r="V73" s="94"/>
-      <c r="W73" s="429"/>
-      <c r="X73" s="94"/>
-      <c r="Y73" s="89"/>
-      <c r="Z73" s="89"/>
-      <c r="AA73" s="139"/>
-      <c r="AB73" s="87"/>
-      <c r="AC73" s="96"/>
-      <c r="AD73" s="96"/>
-      <c r="AE73" s="116"/>
-      <c r="AF73" s="87"/>
-      <c r="AG73" s="96"/>
-      <c r="AH73" s="96"/>
-      <c r="AI73" s="97"/>
-      <c r="AJ73" s="131"/>
+      <c r="A73" s="536"/>
+      <c r="B73" s="536"/>
+      <c r="C73" s="536"/>
+      <c r="D73" s="536"/>
+      <c r="E73" s="536"/>
+      <c r="F73" s="543"/>
+      <c r="G73" s="554"/>
+      <c r="H73" s="249"/>
+      <c r="I73" s="95"/>
+      <c r="J73" s="95"/>
+      <c r="K73" s="332"/>
+      <c r="L73" s="249"/>
+      <c r="M73" s="95"/>
+      <c r="N73" s="95"/>
+      <c r="O73" s="332"/>
+      <c r="P73" s="95"/>
+      <c r="Q73" s="95"/>
+      <c r="R73" s="95"/>
+      <c r="S73" s="103"/>
+      <c r="T73" s="137"/>
+      <c r="U73" s="93"/>
+      <c r="V73" s="93"/>
+      <c r="W73" s="428"/>
+      <c r="X73" s="93"/>
+      <c r="Y73" s="88"/>
+      <c r="Z73" s="88"/>
+      <c r="AA73" s="138"/>
+      <c r="AB73" s="86"/>
+      <c r="AC73" s="95"/>
+      <c r="AD73" s="95"/>
+      <c r="AE73" s="115"/>
+      <c r="AF73" s="86"/>
+      <c r="AG73" s="95"/>
+      <c r="AH73" s="95"/>
+      <c r="AI73" s="96"/>
+      <c r="AJ73" s="130"/>
       <c r="AK73" s="6"/>
       <c r="AL73" s="6"/>
       <c r="AM73" s="6"/>
@@ -22358,44 +22398,44 @@
       <c r="HW73" s="6"/>
     </row>
     <row r="74" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="542"/>
-      <c r="B74" s="542"/>
-      <c r="C74" s="542"/>
-      <c r="D74" s="542"/>
-      <c r="E74" s="578"/>
-      <c r="F74" s="544"/>
-      <c r="G74" s="570" t="s">
+      <c r="A74" s="541"/>
+      <c r="B74" s="541"/>
+      <c r="C74" s="541"/>
+      <c r="D74" s="541"/>
+      <c r="E74" s="577"/>
+      <c r="F74" s="543"/>
+      <c r="G74" s="569" t="s">
         <v>24</v>
       </c>
-      <c r="H74" s="224"/>
+      <c r="H74" s="223"/>
       <c r="I74" s="6"/>
-      <c r="J74" s="563"/>
-      <c r="K74" s="532"/>
-      <c r="L74" s="563"/>
-      <c r="M74" s="534"/>
-      <c r="N74" s="534"/>
-      <c r="O74" s="534"/>
-      <c r="P74" s="534"/>
-      <c r="Q74" s="534"/>
-      <c r="R74" s="534"/>
-      <c r="S74" s="532"/>
-      <c r="T74" s="540"/>
-      <c r="U74" s="529"/>
-      <c r="V74" s="529"/>
-      <c r="W74" s="530"/>
-      <c r="X74" s="540"/>
-      <c r="Y74" s="529"/>
-      <c r="Z74" s="529"/>
-      <c r="AA74" s="530"/>
-      <c r="AB74" s="575"/>
-      <c r="AC74" s="529"/>
-      <c r="AD74" s="529"/>
-      <c r="AE74" s="529"/>
-      <c r="AF74" s="144"/>
+      <c r="J74" s="562"/>
+      <c r="K74" s="531"/>
+      <c r="L74" s="562"/>
+      <c r="M74" s="533"/>
+      <c r="N74" s="533"/>
+      <c r="O74" s="533"/>
+      <c r="P74" s="533"/>
+      <c r="Q74" s="533"/>
+      <c r="R74" s="533"/>
+      <c r="S74" s="531"/>
+      <c r="T74" s="539"/>
+      <c r="U74" s="528"/>
+      <c r="V74" s="528"/>
+      <c r="W74" s="529"/>
+      <c r="X74" s="539"/>
+      <c r="Y74" s="528"/>
+      <c r="Z74" s="528"/>
+      <c r="AA74" s="529"/>
+      <c r="AB74" s="574"/>
+      <c r="AC74" s="528"/>
+      <c r="AD74" s="528"/>
+      <c r="AE74" s="528"/>
+      <c r="AF74" s="143"/>
       <c r="AG74" s="6"/>
       <c r="AH74" s="6"/>
-      <c r="AI74" s="150"/>
-      <c r="AJ74" s="151"/>
+      <c r="AI74" s="149"/>
+      <c r="AJ74" s="150"/>
       <c r="AK74" s="6"/>
       <c r="AL74" s="6"/>
       <c r="AM74" s="6"/>
@@ -22593,42 +22633,42 @@
       <c r="HW74" s="6"/>
     </row>
     <row r="75" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A75" s="536"/>
-      <c r="B75" s="536"/>
-      <c r="C75" s="536"/>
-      <c r="D75" s="536"/>
-      <c r="E75" s="536"/>
-      <c r="F75" s="544"/>
-      <c r="G75" s="549"/>
-      <c r="H75" s="224"/>
+      <c r="A75" s="535"/>
+      <c r="B75" s="535"/>
+      <c r="C75" s="535"/>
+      <c r="D75" s="535"/>
+      <c r="E75" s="535"/>
+      <c r="F75" s="543"/>
+      <c r="G75" s="548"/>
+      <c r="H75" s="223"/>
       <c r="I75" s="6"/>
-      <c r="J75" s="551"/>
-      <c r="K75" s="532"/>
-      <c r="L75" s="549"/>
-      <c r="M75" s="534"/>
-      <c r="N75" s="534"/>
-      <c r="O75" s="534"/>
-      <c r="P75" s="534"/>
-      <c r="Q75" s="534"/>
-      <c r="R75" s="534"/>
-      <c r="S75" s="532"/>
-      <c r="T75" s="551"/>
-      <c r="U75" s="534"/>
-      <c r="V75" s="534"/>
-      <c r="W75" s="532"/>
-      <c r="X75" s="551"/>
-      <c r="Y75" s="534"/>
-      <c r="Z75" s="534"/>
-      <c r="AA75" s="532"/>
-      <c r="AB75" s="64"/>
-      <c r="AC75" s="65"/>
-      <c r="AD75" s="65"/>
-      <c r="AE75" s="65"/>
-      <c r="AF75" s="144"/>
+      <c r="J75" s="550"/>
+      <c r="K75" s="531"/>
+      <c r="L75" s="548"/>
+      <c r="M75" s="533"/>
+      <c r="N75" s="533"/>
+      <c r="O75" s="533"/>
+      <c r="P75" s="533"/>
+      <c r="Q75" s="533"/>
+      <c r="R75" s="533"/>
+      <c r="S75" s="531"/>
+      <c r="T75" s="550"/>
+      <c r="U75" s="533"/>
+      <c r="V75" s="533"/>
+      <c r="W75" s="531"/>
+      <c r="X75" s="550"/>
+      <c r="Y75" s="533"/>
+      <c r="Z75" s="533"/>
+      <c r="AA75" s="531"/>
+      <c r="AB75" s="63"/>
+      <c r="AC75" s="64"/>
+      <c r="AD75" s="64"/>
+      <c r="AE75" s="64"/>
+      <c r="AF75" s="143"/>
       <c r="AG75" s="6"/>
       <c r="AH75" s="6"/>
-      <c r="AI75" s="150"/>
-      <c r="AJ75" s="151"/>
+      <c r="AI75" s="149"/>
+      <c r="AJ75" s="150"/>
       <c r="AK75" s="6"/>
       <c r="AL75" s="6"/>
       <c r="AM75" s="6"/>
@@ -22826,42 +22866,42 @@
       <c r="HW75" s="6"/>
     </row>
     <row r="76" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A76" s="537"/>
-      <c r="B76" s="537"/>
-      <c r="C76" s="537"/>
-      <c r="D76" s="537"/>
-      <c r="E76" s="537"/>
-      <c r="F76" s="544"/>
-      <c r="G76" s="555"/>
-      <c r="H76" s="332"/>
-      <c r="I76" s="196"/>
-      <c r="J76" s="620"/>
-      <c r="K76" s="532"/>
-      <c r="L76" s="87"/>
-      <c r="M76" s="96"/>
-      <c r="N76" s="96"/>
-      <c r="O76" s="96"/>
-      <c r="P76" s="96"/>
-      <c r="Q76" s="196"/>
-      <c r="R76" s="196"/>
-      <c r="S76" s="97"/>
-      <c r="T76" s="226"/>
-      <c r="U76" s="571"/>
-      <c r="V76" s="534"/>
-      <c r="W76" s="227"/>
-      <c r="X76" s="228"/>
-      <c r="Y76" s="571"/>
-      <c r="Z76" s="534"/>
-      <c r="AA76" s="430"/>
-      <c r="AB76" s="87"/>
-      <c r="AC76" s="96"/>
-      <c r="AD76" s="96"/>
-      <c r="AE76" s="116"/>
-      <c r="AF76" s="46"/>
-      <c r="AG76" s="47"/>
-      <c r="AH76" s="47"/>
-      <c r="AI76" s="98"/>
-      <c r="AJ76" s="151"/>
+      <c r="A76" s="536"/>
+      <c r="B76" s="536"/>
+      <c r="C76" s="536"/>
+      <c r="D76" s="536"/>
+      <c r="E76" s="536"/>
+      <c r="F76" s="543"/>
+      <c r="G76" s="554"/>
+      <c r="H76" s="331"/>
+      <c r="I76" s="195"/>
+      <c r="J76" s="619"/>
+      <c r="K76" s="531"/>
+      <c r="L76" s="86"/>
+      <c r="M76" s="95"/>
+      <c r="N76" s="95"/>
+      <c r="O76" s="95"/>
+      <c r="P76" s="95"/>
+      <c r="Q76" s="195"/>
+      <c r="R76" s="195"/>
+      <c r="S76" s="96"/>
+      <c r="T76" s="225"/>
+      <c r="U76" s="570"/>
+      <c r="V76" s="533"/>
+      <c r="W76" s="226"/>
+      <c r="X76" s="227"/>
+      <c r="Y76" s="570"/>
+      <c r="Z76" s="533"/>
+      <c r="AA76" s="429"/>
+      <c r="AB76" s="86"/>
+      <c r="AC76" s="95"/>
+      <c r="AD76" s="95"/>
+      <c r="AE76" s="115"/>
+      <c r="AF76" s="45"/>
+      <c r="AG76" s="46"/>
+      <c r="AH76" s="46"/>
+      <c r="AI76" s="97"/>
+      <c r="AJ76" s="150"/>
       <c r="AK76" s="6"/>
       <c r="AL76" s="6"/>
       <c r="AM76" s="6"/>
@@ -23059,44 +23099,44 @@
       <c r="HW76" s="6"/>
     </row>
     <row r="77" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A77" s="542"/>
-      <c r="B77" s="542"/>
-      <c r="C77" s="542"/>
-      <c r="D77" s="542"/>
-      <c r="E77" s="578"/>
-      <c r="F77" s="544"/>
-      <c r="G77" s="603" t="s">
+      <c r="A77" s="541"/>
+      <c r="B77" s="541"/>
+      <c r="C77" s="541"/>
+      <c r="D77" s="541"/>
+      <c r="E77" s="577"/>
+      <c r="F77" s="543"/>
+      <c r="G77" s="602" t="s">
         <v>25</v>
       </c>
-      <c r="H77" s="224"/>
+      <c r="H77" s="223"/>
       <c r="I77" s="6"/>
-      <c r="J77" s="609"/>
-      <c r="K77" s="532"/>
+      <c r="J77" s="608"/>
+      <c r="K77" s="531"/>
       <c r="L77" s="6"/>
-      <c r="M77" s="141"/>
-      <c r="N77" s="431"/>
-      <c r="O77" s="432"/>
-      <c r="P77" s="144"/>
+      <c r="M77" s="140"/>
+      <c r="N77" s="430"/>
+      <c r="O77" s="431"/>
+      <c r="P77" s="143"/>
       <c r="Q77" s="6"/>
       <c r="R77" s="6"/>
-      <c r="S77" s="150"/>
-      <c r="T77" s="169"/>
-      <c r="U77" s="124"/>
+      <c r="S77" s="149"/>
+      <c r="T77" s="168"/>
+      <c r="U77" s="123"/>
       <c r="V77" s="6"/>
-      <c r="W77" s="150"/>
-      <c r="X77" s="170"/>
-      <c r="Y77" s="124"/>
+      <c r="W77" s="149"/>
+      <c r="X77" s="169"/>
+      <c r="Y77" s="123"/>
       <c r="Z77" s="6"/>
-      <c r="AA77" s="45"/>
-      <c r="AB77" s="293"/>
-      <c r="AC77" s="294"/>
-      <c r="AD77" s="294"/>
-      <c r="AE77" s="433"/>
-      <c r="AF77" s="43"/>
+      <c r="AA77" s="44"/>
+      <c r="AB77" s="292"/>
+      <c r="AC77" s="293"/>
+      <c r="AD77" s="293"/>
+      <c r="AE77" s="432"/>
+      <c r="AF77" s="42"/>
       <c r="AG77" s="10"/>
       <c r="AH77" s="10"/>
-      <c r="AI77" s="45"/>
-      <c r="AJ77" s="151"/>
+      <c r="AI77" s="44"/>
+      <c r="AJ77" s="150"/>
       <c r="AK77" s="6"/>
       <c r="AL77" s="6"/>
       <c r="AM77" s="6"/>
@@ -23294,42 +23334,42 @@
       <c r="HW77" s="6"/>
     </row>
     <row r="78" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A78" s="536"/>
-      <c r="B78" s="536"/>
-      <c r="C78" s="536"/>
-      <c r="D78" s="536"/>
-      <c r="E78" s="536"/>
-      <c r="F78" s="544"/>
-      <c r="G78" s="549"/>
-      <c r="H78" s="168"/>
+      <c r="A78" s="535"/>
+      <c r="B78" s="535"/>
+      <c r="C78" s="535"/>
+      <c r="D78" s="535"/>
+      <c r="E78" s="535"/>
+      <c r="F78" s="543"/>
+      <c r="G78" s="548"/>
+      <c r="H78" s="167"/>
       <c r="I78" s="26"/>
-      <c r="J78" s="43"/>
-      <c r="K78" s="434"/>
+      <c r="J78" s="42"/>
+      <c r="K78" s="433"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
-      <c r="N78" s="76"/>
-      <c r="O78" s="150"/>
-      <c r="P78" s="144"/>
+      <c r="N78" s="75"/>
+      <c r="O78" s="149"/>
+      <c r="P78" s="143"/>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
-      <c r="S78" s="150"/>
-      <c r="T78" s="123"/>
-      <c r="U78" s="172"/>
+      <c r="S78" s="149"/>
+      <c r="T78" s="122"/>
+      <c r="U78" s="171"/>
       <c r="V78" s="10"/>
-      <c r="W78" s="85"/>
-      <c r="X78" s="123"/>
-      <c r="Y78" s="173"/>
+      <c r="W78" s="84"/>
+      <c r="X78" s="122"/>
+      <c r="Y78" s="172"/>
       <c r="Z78" s="6"/>
-      <c r="AA78" s="85"/>
-      <c r="AB78" s="297"/>
-      <c r="AC78" s="86"/>
-      <c r="AD78" s="86"/>
-      <c r="AE78" s="163"/>
-      <c r="AF78" s="43"/>
+      <c r="AA78" s="84"/>
+      <c r="AB78" s="296"/>
+      <c r="AC78" s="85"/>
+      <c r="AD78" s="85"/>
+      <c r="AE78" s="162"/>
+      <c r="AF78" s="42"/>
       <c r="AG78" s="10"/>
       <c r="AH78" s="10"/>
-      <c r="AI78" s="45"/>
-      <c r="AJ78" s="151"/>
+      <c r="AI78" s="44"/>
+      <c r="AJ78" s="150"/>
       <c r="AK78" s="6"/>
       <c r="AL78" s="6"/>
       <c r="AM78" s="6"/>
@@ -23527,42 +23567,42 @@
       <c r="HW78" s="6"/>
     </row>
     <row r="79" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A79" s="537"/>
-      <c r="B79" s="537"/>
-      <c r="C79" s="537"/>
-      <c r="D79" s="537"/>
-      <c r="E79" s="537"/>
-      <c r="F79" s="545"/>
-      <c r="G79" s="602"/>
-      <c r="H79" s="168"/>
+      <c r="A79" s="536"/>
+      <c r="B79" s="536"/>
+      <c r="C79" s="536"/>
+      <c r="D79" s="536"/>
+      <c r="E79" s="536"/>
+      <c r="F79" s="544"/>
+      <c r="G79" s="601"/>
+      <c r="H79" s="167"/>
       <c r="I79" s="26"/>
-      <c r="J79" s="622"/>
-      <c r="K79" s="553"/>
-      <c r="L79" s="202"/>
-      <c r="M79" s="202"/>
-      <c r="N79" s="345"/>
-      <c r="O79" s="435"/>
+      <c r="J79" s="621"/>
+      <c r="K79" s="552"/>
+      <c r="L79" s="201"/>
+      <c r="M79" s="201"/>
+      <c r="N79" s="344"/>
+      <c r="O79" s="434"/>
       <c r="P79" s="27"/>
       <c r="Q79" s="26"/>
       <c r="R79" s="26"/>
-      <c r="S79" s="150"/>
-      <c r="T79" s="174"/>
-      <c r="U79" s="175"/>
-      <c r="V79" s="115"/>
-      <c r="W79" s="176"/>
-      <c r="X79" s="174"/>
-      <c r="Y79" s="177"/>
-      <c r="Z79" s="178"/>
-      <c r="AA79" s="176"/>
-      <c r="AB79" s="436"/>
-      <c r="AC79" s="194"/>
-      <c r="AD79" s="437"/>
-      <c r="AE79" s="438"/>
-      <c r="AF79" s="43"/>
+      <c r="S79" s="149"/>
+      <c r="T79" s="173"/>
+      <c r="U79" s="174"/>
+      <c r="V79" s="114"/>
+      <c r="W79" s="175"/>
+      <c r="X79" s="173"/>
+      <c r="Y79" s="176"/>
+      <c r="Z79" s="177"/>
+      <c r="AA79" s="175"/>
+      <c r="AB79" s="435"/>
+      <c r="AC79" s="193"/>
+      <c r="AD79" s="436"/>
+      <c r="AE79" s="437"/>
+      <c r="AF79" s="42"/>
       <c r="AG79" s="10"/>
       <c r="AH79" s="10"/>
-      <c r="AI79" s="45"/>
-      <c r="AJ79" s="151"/>
+      <c r="AI79" s="44"/>
+      <c r="AJ79" s="150"/>
       <c r="AK79" s="6"/>
       <c r="AL79" s="6"/>
       <c r="AM79" s="6"/>
@@ -23760,46 +23800,46 @@
       <c r="HW79" s="6"/>
     </row>
     <row r="80" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="542"/>
-      <c r="B80" s="538"/>
-      <c r="C80" s="538"/>
-      <c r="D80" s="538"/>
-      <c r="E80" s="538"/>
-      <c r="F80" s="543" t="s">
+      <c r="A80" s="541"/>
+      <c r="B80" s="537"/>
+      <c r="C80" s="537"/>
+      <c r="D80" s="537"/>
+      <c r="E80" s="537"/>
+      <c r="F80" s="542" t="s">
         <v>29</v>
       </c>
-      <c r="G80" s="626" t="s">
+      <c r="G80" s="625" t="s">
         <v>18</v>
       </c>
-      <c r="H80" s="234"/>
-      <c r="I80" s="181"/>
-      <c r="J80" s="181"/>
-      <c r="K80" s="182"/>
-      <c r="L80" s="181"/>
-      <c r="M80" s="181"/>
-      <c r="N80" s="181"/>
-      <c r="O80" s="182"/>
-      <c r="P80" s="439"/>
-      <c r="Q80" s="439"/>
-      <c r="R80" s="439"/>
-      <c r="S80" s="440"/>
-      <c r="T80" s="441"/>
-      <c r="U80" s="439"/>
-      <c r="V80" s="439"/>
-      <c r="W80" s="440"/>
-      <c r="X80" s="283"/>
-      <c r="Y80" s="283"/>
-      <c r="Z80" s="283"/>
-      <c r="AA80" s="283"/>
-      <c r="AB80" s="442"/>
-      <c r="AC80" s="415"/>
-      <c r="AD80" s="415"/>
-      <c r="AE80" s="416"/>
-      <c r="AF80" s="443"/>
-      <c r="AG80" s="283"/>
-      <c r="AH80" s="283"/>
-      <c r="AI80" s="444"/>
-      <c r="AJ80" s="143"/>
+      <c r="H80" s="233"/>
+      <c r="I80" s="180"/>
+      <c r="J80" s="180"/>
+      <c r="K80" s="181"/>
+      <c r="L80" s="180"/>
+      <c r="M80" s="180"/>
+      <c r="N80" s="180"/>
+      <c r="O80" s="181"/>
+      <c r="P80" s="438"/>
+      <c r="Q80" s="438"/>
+      <c r="R80" s="438"/>
+      <c r="S80" s="439"/>
+      <c r="T80" s="440"/>
+      <c r="U80" s="438"/>
+      <c r="V80" s="438"/>
+      <c r="W80" s="439"/>
+      <c r="X80" s="282"/>
+      <c r="Y80" s="282"/>
+      <c r="Z80" s="282"/>
+      <c r="AA80" s="282"/>
+      <c r="AB80" s="441"/>
+      <c r="AC80" s="414"/>
+      <c r="AD80" s="414"/>
+      <c r="AE80" s="415"/>
+      <c r="AF80" s="442"/>
+      <c r="AG80" s="282"/>
+      <c r="AH80" s="282"/>
+      <c r="AI80" s="443"/>
+      <c r="AJ80" s="142"/>
       <c r="AK80" s="6"/>
       <c r="AL80" s="6"/>
       <c r="AM80" s="6"/>
@@ -23997,42 +24037,42 @@
       <c r="HW80" s="6"/>
     </row>
     <row r="81" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="536"/>
-      <c r="B81" s="536"/>
-      <c r="C81" s="536"/>
-      <c r="D81" s="536"/>
-      <c r="E81" s="536"/>
-      <c r="F81" s="544"/>
-      <c r="G81" s="549"/>
-      <c r="H81" s="168"/>
+      <c r="A81" s="535"/>
+      <c r="B81" s="535"/>
+      <c r="C81" s="535"/>
+      <c r="D81" s="535"/>
+      <c r="E81" s="535"/>
+      <c r="F81" s="543"/>
+      <c r="G81" s="548"/>
+      <c r="H81" s="167"/>
       <c r="I81" s="26"/>
       <c r="J81" s="26"/>
-      <c r="K81" s="167"/>
+      <c r="K81" s="166"/>
       <c r="L81" s="26"/>
       <c r="M81" s="26"/>
       <c r="N81" s="26"/>
-      <c r="O81" s="167"/>
-      <c r="P81" s="237"/>
-      <c r="Q81" s="237"/>
-      <c r="R81" s="237"/>
-      <c r="S81" s="238"/>
-      <c r="T81" s="236"/>
-      <c r="U81" s="237"/>
-      <c r="V81" s="237"/>
-      <c r="W81" s="238"/>
+      <c r="O81" s="166"/>
+      <c r="P81" s="236"/>
+      <c r="Q81" s="236"/>
+      <c r="R81" s="236"/>
+      <c r="S81" s="237"/>
+      <c r="T81" s="235"/>
+      <c r="U81" s="236"/>
+      <c r="V81" s="236"/>
+      <c r="W81" s="237"/>
       <c r="X81" s="29"/>
       <c r="Y81" s="29"/>
       <c r="Z81" s="29"/>
       <c r="AA81" s="29"/>
-      <c r="AB81" s="445"/>
-      <c r="AC81" s="385"/>
-      <c r="AD81" s="385"/>
-      <c r="AE81" s="386"/>
-      <c r="AF81" s="125"/>
+      <c r="AB81" s="444"/>
+      <c r="AC81" s="384"/>
+      <c r="AD81" s="384"/>
+      <c r="AE81" s="385"/>
+      <c r="AF81" s="124"/>
       <c r="AG81" s="29"/>
       <c r="AH81" s="29"/>
       <c r="AI81" s="30"/>
-      <c r="AJ81" s="195"/>
+      <c r="AJ81" s="194"/>
       <c r="AK81" s="6"/>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
@@ -24230,42 +24270,42 @@
       <c r="HW81" s="6"/>
     </row>
     <row r="82" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A82" s="537"/>
-      <c r="B82" s="537"/>
-      <c r="C82" s="537"/>
-      <c r="D82" s="537"/>
-      <c r="E82" s="537"/>
-      <c r="F82" s="544"/>
-      <c r="G82" s="555"/>
-      <c r="H82" s="168"/>
+      <c r="A82" s="536"/>
+      <c r="B82" s="536"/>
+      <c r="C82" s="536"/>
+      <c r="D82" s="536"/>
+      <c r="E82" s="536"/>
+      <c r="F82" s="543"/>
+      <c r="G82" s="554"/>
+      <c r="H82" s="167"/>
       <c r="I82" s="26"/>
       <c r="J82" s="26"/>
-      <c r="K82" s="167"/>
+      <c r="K82" s="166"/>
       <c r="L82" s="26"/>
       <c r="M82" s="26"/>
       <c r="N82" s="26"/>
-      <c r="O82" s="167"/>
+      <c r="O82" s="166"/>
       <c r="P82" s="34"/>
       <c r="Q82" s="34"/>
       <c r="R82" s="34"/>
-      <c r="S82" s="111"/>
-      <c r="T82" s="239"/>
-      <c r="U82" s="240"/>
-      <c r="V82" s="240"/>
-      <c r="W82" s="140"/>
-      <c r="X82" s="147"/>
-      <c r="Y82" s="147"/>
-      <c r="Z82" s="147"/>
-      <c r="AA82" s="446"/>
-      <c r="AB82" s="447"/>
-      <c r="AC82" s="334"/>
-      <c r="AD82" s="160"/>
-      <c r="AE82" s="448"/>
-      <c r="AF82" s="449"/>
-      <c r="AG82" s="51"/>
-      <c r="AH82" s="129"/>
-      <c r="AI82" s="130"/>
-      <c r="AJ82" s="131"/>
+      <c r="S82" s="110"/>
+      <c r="T82" s="238"/>
+      <c r="U82" s="239"/>
+      <c r="V82" s="239"/>
+      <c r="W82" s="139"/>
+      <c r="X82" s="146"/>
+      <c r="Y82" s="146"/>
+      <c r="Z82" s="146"/>
+      <c r="AA82" s="445"/>
+      <c r="AB82" s="446"/>
+      <c r="AC82" s="333"/>
+      <c r="AD82" s="159"/>
+      <c r="AE82" s="447"/>
+      <c r="AF82" s="448"/>
+      <c r="AG82" s="50"/>
+      <c r="AH82" s="128"/>
+      <c r="AI82" s="129"/>
+      <c r="AJ82" s="130"/>
       <c r="AK82" s="6"/>
       <c r="AL82" s="6"/>
       <c r="AM82" s="6"/>
@@ -24463,54 +24503,54 @@
       <c r="HW82" s="6"/>
     </row>
     <row r="83" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A83" s="539">
+      <c r="A83" s="538">
         <v>10</v>
       </c>
-      <c r="B83" s="539">
+      <c r="B83" s="538">
         <v>10</v>
       </c>
-      <c r="C83" s="539">
+      <c r="C83" s="538">
         <v>7</v>
       </c>
-      <c r="D83" s="627">
+      <c r="D83" s="626">
         <v>5</v>
       </c>
-      <c r="E83" s="539">
+      <c r="E83" s="538">
         <v>2</v>
       </c>
-      <c r="F83" s="544"/>
-      <c r="G83" s="561" t="s">
+      <c r="F83" s="543"/>
+      <c r="G83" s="560" t="s">
         <v>19</v>
       </c>
-      <c r="H83" s="354"/>
-      <c r="I83" s="106"/>
-      <c r="J83" s="106"/>
-      <c r="K83" s="185"/>
-      <c r="L83" s="450"/>
-      <c r="M83" s="56"/>
-      <c r="N83" s="56"/>
-      <c r="O83" s="451"/>
-      <c r="P83" s="632"/>
-      <c r="Q83" s="566"/>
-      <c r="R83" s="566"/>
-      <c r="S83" s="633"/>
-      <c r="T83" s="452"/>
-      <c r="U83" s="452"/>
-      <c r="V83" s="452"/>
-      <c r="W83" s="453"/>
-      <c r="X83" s="133"/>
-      <c r="Y83" s="133"/>
-      <c r="Z83" s="133"/>
-      <c r="AA83" s="133"/>
-      <c r="AB83" s="224"/>
+      <c r="H83" s="353"/>
+      <c r="I83" s="105"/>
+      <c r="J83" s="105"/>
+      <c r="K83" s="184"/>
+      <c r="L83" s="449"/>
+      <c r="M83" s="55"/>
+      <c r="N83" s="55"/>
+      <c r="O83" s="450"/>
+      <c r="P83" s="631"/>
+      <c r="Q83" s="565"/>
+      <c r="R83" s="565"/>
+      <c r="S83" s="632"/>
+      <c r="T83" s="451"/>
+      <c r="U83" s="451"/>
+      <c r="V83" s="451"/>
+      <c r="W83" s="452"/>
+      <c r="X83" s="132"/>
+      <c r="Y83" s="132"/>
+      <c r="Z83" s="132"/>
+      <c r="AA83" s="132"/>
+      <c r="AB83" s="223"/>
       <c r="AC83" s="6"/>
       <c r="AD83" s="6"/>
-      <c r="AE83" s="150"/>
+      <c r="AE83" s="149"/>
       <c r="AF83" s="27"/>
       <c r="AG83" s="26"/>
       <c r="AH83" s="26"/>
       <c r="AI83" s="28"/>
-      <c r="AJ83" s="454"/>
+      <c r="AJ83" s="453"/>
       <c r="AK83" s="6"/>
       <c r="AL83" s="6"/>
       <c r="AM83" s="6"/>
@@ -24708,25 +24748,25 @@
       <c r="HW83" s="6"/>
     </row>
     <row r="84" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A84" s="536"/>
-      <c r="B84" s="536"/>
-      <c r="C84" s="536"/>
-      <c r="D84" s="536"/>
-      <c r="E84" s="536"/>
-      <c r="F84" s="544"/>
-      <c r="G84" s="549"/>
-      <c r="H84" s="168"/>
+      <c r="A84" s="535"/>
+      <c r="B84" s="535"/>
+      <c r="C84" s="535"/>
+      <c r="D84" s="535"/>
+      <c r="E84" s="535"/>
+      <c r="F84" s="543"/>
+      <c r="G84" s="548"/>
+      <c r="H84" s="167"/>
       <c r="I84" s="26"/>
       <c r="J84" s="26"/>
-      <c r="K84" s="167"/>
-      <c r="L84" s="398"/>
-      <c r="M84" s="82"/>
-      <c r="N84" s="82"/>
-      <c r="O84" s="216"/>
-      <c r="P84" s="213"/>
-      <c r="Q84" s="65"/>
-      <c r="R84" s="65"/>
-      <c r="S84" s="145"/>
+      <c r="K84" s="166"/>
+      <c r="L84" s="397"/>
+      <c r="M84" s="81"/>
+      <c r="N84" s="81"/>
+      <c r="O84" s="215"/>
+      <c r="P84" s="212"/>
+      <c r="Q84" s="64"/>
+      <c r="R84" s="64"/>
+      <c r="S84" s="144"/>
       <c r="T84" s="29"/>
       <c r="U84" s="29"/>
       <c r="V84" s="29"/>
@@ -24735,15 +24775,15 @@
       <c r="Y84" s="29"/>
       <c r="Z84" s="29"/>
       <c r="AA84" s="29"/>
-      <c r="AB84" s="224"/>
+      <c r="AB84" s="223"/>
       <c r="AC84" s="6"/>
       <c r="AD84" s="6"/>
-      <c r="AE84" s="150"/>
+      <c r="AE84" s="149"/>
       <c r="AF84" s="27"/>
       <c r="AG84" s="26"/>
       <c r="AH84" s="26"/>
       <c r="AI84" s="28"/>
-      <c r="AJ84" s="454"/>
+      <c r="AJ84" s="453"/>
       <c r="AK84" s="6"/>
       <c r="AL84" s="6"/>
       <c r="AM84" s="6"/>
@@ -24941,42 +24981,42 @@
       <c r="HW84" s="6"/>
     </row>
     <row r="85" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A85" s="537"/>
-      <c r="B85" s="537"/>
-      <c r="C85" s="537"/>
-      <c r="D85" s="537"/>
-      <c r="E85" s="537"/>
-      <c r="F85" s="544"/>
-      <c r="G85" s="555"/>
-      <c r="H85" s="168"/>
+      <c r="A85" s="536"/>
+      <c r="B85" s="536"/>
+      <c r="C85" s="536"/>
+      <c r="D85" s="536"/>
+      <c r="E85" s="536"/>
+      <c r="F85" s="543"/>
+      <c r="G85" s="554"/>
+      <c r="H85" s="167"/>
       <c r="I85" s="26"/>
       <c r="J85" s="26"/>
-      <c r="K85" s="167"/>
-      <c r="L85" s="250"/>
-      <c r="M85" s="96"/>
-      <c r="N85" s="96"/>
-      <c r="O85" s="333"/>
-      <c r="P85" s="250"/>
-      <c r="Q85" s="96"/>
-      <c r="R85" s="96"/>
-      <c r="S85" s="251"/>
-      <c r="T85" s="198"/>
-      <c r="U85" s="198"/>
-      <c r="V85" s="198"/>
-      <c r="W85" s="199"/>
-      <c r="X85" s="51"/>
-      <c r="Y85" s="51"/>
-      <c r="Z85" s="51"/>
-      <c r="AA85" s="198"/>
-      <c r="AB85" s="224"/>
+      <c r="K85" s="166"/>
+      <c r="L85" s="249"/>
+      <c r="M85" s="95"/>
+      <c r="N85" s="95"/>
+      <c r="O85" s="332"/>
+      <c r="P85" s="249"/>
+      <c r="Q85" s="95"/>
+      <c r="R85" s="95"/>
+      <c r="S85" s="250"/>
+      <c r="T85" s="197"/>
+      <c r="U85" s="197"/>
+      <c r="V85" s="197"/>
+      <c r="W85" s="198"/>
+      <c r="X85" s="50"/>
+      <c r="Y85" s="50"/>
+      <c r="Z85" s="50"/>
+      <c r="AA85" s="197"/>
+      <c r="AB85" s="223"/>
       <c r="AC85" s="6"/>
       <c r="AD85" s="6"/>
-      <c r="AE85" s="150"/>
+      <c r="AE85" s="149"/>
       <c r="AF85" s="27"/>
       <c r="AG85" s="26"/>
       <c r="AH85" s="26"/>
       <c r="AI85" s="28"/>
-      <c r="AJ85" s="455"/>
+      <c r="AJ85" s="454"/>
       <c r="AK85" s="6"/>
       <c r="AL85" s="6"/>
       <c r="AM85" s="6"/>
@@ -25174,52 +25214,52 @@
       <c r="HW85" s="6"/>
     </row>
     <row r="86" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="539">
+      <c r="A86" s="538">
         <v>24</v>
       </c>
-      <c r="B86" s="539">
+      <c r="B86" s="538">
         <v>24</v>
       </c>
-      <c r="C86" s="539">
+      <c r="C86" s="538">
         <v>21</v>
       </c>
-      <c r="D86" s="627">
+      <c r="D86" s="626">
         <v>19</v>
       </c>
-      <c r="E86" s="541"/>
-      <c r="F86" s="544"/>
-      <c r="G86" s="610" t="s">
+      <c r="E86" s="540"/>
+      <c r="F86" s="543"/>
+      <c r="G86" s="609" t="s">
         <v>20</v>
       </c>
-      <c r="H86" s="352"/>
-      <c r="I86" s="37"/>
-      <c r="J86" s="37"/>
-      <c r="K86" s="353"/>
-      <c r="L86" s="564"/>
-      <c r="M86" s="529"/>
-      <c r="N86" s="529"/>
-      <c r="O86" s="529"/>
-      <c r="P86" s="529"/>
-      <c r="Q86" s="529"/>
-      <c r="R86" s="529"/>
-      <c r="S86" s="530"/>
-      <c r="T86" s="57"/>
-      <c r="U86" s="58"/>
-      <c r="V86" s="58"/>
-      <c r="W86" s="59"/>
-      <c r="X86" s="57"/>
-      <c r="Y86" s="58"/>
-      <c r="Z86" s="58"/>
-      <c r="AA86" s="58"/>
-      <c r="AB86" s="564"/>
-      <c r="AC86" s="529"/>
-      <c r="AD86" s="529"/>
-      <c r="AE86" s="530"/>
-      <c r="AF86" s="57"/>
-      <c r="AG86" s="58"/>
-      <c r="AH86" s="58"/>
-      <c r="AI86" s="59"/>
-      <c r="AJ86" s="143"/>
+      <c r="H86" s="351"/>
+      <c r="I86" s="36"/>
+      <c r="J86" s="36"/>
+      <c r="K86" s="352"/>
+      <c r="L86" s="563"/>
+      <c r="M86" s="528"/>
+      <c r="N86" s="528"/>
+      <c r="O86" s="528"/>
+      <c r="P86" s="528"/>
+      <c r="Q86" s="528"/>
+      <c r="R86" s="528"/>
+      <c r="S86" s="529"/>
+      <c r="T86" s="56"/>
+      <c r="U86" s="57"/>
+      <c r="V86" s="57"/>
+      <c r="W86" s="58"/>
+      <c r="X86" s="56"/>
+      <c r="Y86" s="57"/>
+      <c r="Z86" s="57"/>
+      <c r="AA86" s="57"/>
+      <c r="AB86" s="563"/>
+      <c r="AC86" s="528"/>
+      <c r="AD86" s="528"/>
+      <c r="AE86" s="529"/>
+      <c r="AF86" s="56"/>
+      <c r="AG86" s="57"/>
+      <c r="AH86" s="57"/>
+      <c r="AI86" s="58"/>
+      <c r="AJ86" s="142"/>
       <c r="AK86" s="6"/>
       <c r="AL86" s="6"/>
       <c r="AM86" s="6"/>
@@ -25417,42 +25457,42 @@
       <c r="HW86" s="6"/>
     </row>
     <row r="87" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A87" s="536"/>
-      <c r="B87" s="536"/>
-      <c r="C87" s="536"/>
-      <c r="D87" s="536"/>
-      <c r="E87" s="536"/>
-      <c r="F87" s="544"/>
-      <c r="G87" s="549"/>
-      <c r="H87" s="153"/>
+      <c r="A87" s="535"/>
+      <c r="B87" s="535"/>
+      <c r="C87" s="535"/>
+      <c r="D87" s="535"/>
+      <c r="E87" s="535"/>
+      <c r="F87" s="543"/>
+      <c r="G87" s="548"/>
+      <c r="H87" s="152"/>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
-      <c r="K87" s="146"/>
-      <c r="L87" s="587"/>
-      <c r="M87" s="534"/>
-      <c r="N87" s="534"/>
-      <c r="O87" s="534"/>
-      <c r="P87" s="534"/>
-      <c r="Q87" s="534"/>
-      <c r="R87" s="534"/>
-      <c r="S87" s="532"/>
-      <c r="T87" s="60"/>
-      <c r="U87" s="61"/>
-      <c r="V87" s="61"/>
-      <c r="W87" s="99"/>
-      <c r="X87" s="60"/>
-      <c r="Y87" s="61"/>
-      <c r="Z87" s="61"/>
-      <c r="AA87" s="61"/>
-      <c r="AB87" s="572"/>
-      <c r="AC87" s="534"/>
-      <c r="AD87" s="534"/>
-      <c r="AE87" s="532"/>
-      <c r="AF87" s="135"/>
-      <c r="AG87" s="67"/>
-      <c r="AH87" s="67"/>
-      <c r="AI87" s="68"/>
-      <c r="AJ87" s="143"/>
+      <c r="K87" s="145"/>
+      <c r="L87" s="586"/>
+      <c r="M87" s="533"/>
+      <c r="N87" s="533"/>
+      <c r="O87" s="533"/>
+      <c r="P87" s="533"/>
+      <c r="Q87" s="533"/>
+      <c r="R87" s="533"/>
+      <c r="S87" s="531"/>
+      <c r="T87" s="59"/>
+      <c r="U87" s="60"/>
+      <c r="V87" s="60"/>
+      <c r="W87" s="98"/>
+      <c r="X87" s="59"/>
+      <c r="Y87" s="60"/>
+      <c r="Z87" s="60"/>
+      <c r="AA87" s="60"/>
+      <c r="AB87" s="571"/>
+      <c r="AC87" s="533"/>
+      <c r="AD87" s="533"/>
+      <c r="AE87" s="531"/>
+      <c r="AF87" s="134"/>
+      <c r="AG87" s="66"/>
+      <c r="AH87" s="66"/>
+      <c r="AI87" s="67"/>
+      <c r="AJ87" s="142"/>
       <c r="AK87" s="6"/>
       <c r="AL87" s="6"/>
       <c r="AM87" s="6"/>
@@ -25650,42 +25690,42 @@
       <c r="HW87" s="6"/>
     </row>
     <row r="88" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A88" s="537"/>
-      <c r="B88" s="537"/>
-      <c r="C88" s="537"/>
-      <c r="D88" s="537"/>
-      <c r="E88" s="537"/>
-      <c r="F88" s="544"/>
-      <c r="G88" s="611"/>
-      <c r="H88" s="456"/>
-      <c r="I88" s="457"/>
-      <c r="J88" s="457"/>
-      <c r="K88" s="458"/>
-      <c r="L88" s="190"/>
-      <c r="M88" s="191"/>
-      <c r="N88" s="191"/>
-      <c r="O88" s="191"/>
-      <c r="P88" s="191"/>
-      <c r="Q88" s="148"/>
-      <c r="R88" s="148"/>
-      <c r="S88" s="192"/>
-      <c r="T88" s="249"/>
-      <c r="U88" s="73"/>
-      <c r="V88" s="73"/>
-      <c r="W88" s="73"/>
-      <c r="X88" s="248"/>
-      <c r="Y88" s="73"/>
-      <c r="Z88" s="73"/>
-      <c r="AA88" s="73"/>
-      <c r="AB88" s="224"/>
-      <c r="AC88" s="571"/>
-      <c r="AD88" s="534"/>
-      <c r="AE88" s="150"/>
-      <c r="AF88" s="459"/>
-      <c r="AG88" s="263"/>
-      <c r="AH88" s="263"/>
-      <c r="AI88" s="460"/>
-      <c r="AJ88" s="151"/>
+      <c r="A88" s="536"/>
+      <c r="B88" s="536"/>
+      <c r="C88" s="536"/>
+      <c r="D88" s="536"/>
+      <c r="E88" s="536"/>
+      <c r="F88" s="543"/>
+      <c r="G88" s="610"/>
+      <c r="H88" s="455"/>
+      <c r="I88" s="456"/>
+      <c r="J88" s="456"/>
+      <c r="K88" s="457"/>
+      <c r="L88" s="189"/>
+      <c r="M88" s="190"/>
+      <c r="N88" s="190"/>
+      <c r="O88" s="190"/>
+      <c r="P88" s="190"/>
+      <c r="Q88" s="147"/>
+      <c r="R88" s="147"/>
+      <c r="S88" s="191"/>
+      <c r="T88" s="248"/>
+      <c r="U88" s="72"/>
+      <c r="V88" s="72"/>
+      <c r="W88" s="72"/>
+      <c r="X88" s="247"/>
+      <c r="Y88" s="72"/>
+      <c r="Z88" s="72"/>
+      <c r="AA88" s="72"/>
+      <c r="AB88" s="223"/>
+      <c r="AC88" s="570"/>
+      <c r="AD88" s="533"/>
+      <c r="AE88" s="149"/>
+      <c r="AF88" s="458"/>
+      <c r="AG88" s="262"/>
+      <c r="AH88" s="262"/>
+      <c r="AI88" s="459"/>
+      <c r="AJ88" s="150"/>
       <c r="AK88" s="6"/>
       <c r="AL88" s="6"/>
       <c r="AM88" s="6"/>
@@ -25883,54 +25923,54 @@
       <c r="HW88" s="6"/>
     </row>
     <row r="89" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A89" s="541">
+      <c r="A89" s="540">
         <v>0</v>
       </c>
-      <c r="B89" s="541">
+      <c r="B89" s="540">
         <v>0</v>
       </c>
-      <c r="C89" s="541">
+      <c r="C89" s="540">
         <v>0</v>
       </c>
-      <c r="D89" s="541">
+      <c r="D89" s="540">
         <v>0</v>
       </c>
-      <c r="E89" s="541">
+      <c r="E89" s="540">
         <v>0</v>
       </c>
-      <c r="F89" s="544"/>
-      <c r="G89" s="623" t="s">
+      <c r="F89" s="543"/>
+      <c r="G89" s="622" t="s">
         <v>22</v>
       </c>
-      <c r="H89" s="264"/>
-      <c r="I89" s="54"/>
-      <c r="J89" s="54"/>
-      <c r="K89" s="265"/>
-      <c r="L89" s="563"/>
-      <c r="M89" s="534"/>
-      <c r="N89" s="534"/>
-      <c r="O89" s="534"/>
-      <c r="P89" s="534"/>
-      <c r="Q89" s="534"/>
-      <c r="R89" s="534"/>
-      <c r="S89" s="532"/>
-      <c r="T89" s="365"/>
-      <c r="U89" s="366"/>
-      <c r="V89" s="79"/>
-      <c r="W89" s="79"/>
-      <c r="X89" s="365"/>
-      <c r="Y89" s="366"/>
-      <c r="Z89" s="79"/>
-      <c r="AA89" s="79"/>
-      <c r="AB89" s="398"/>
-      <c r="AC89" s="82"/>
-      <c r="AD89" s="82"/>
-      <c r="AE89" s="225"/>
-      <c r="AF89" s="242"/>
-      <c r="AG89" s="243"/>
-      <c r="AH89" s="243"/>
-      <c r="AI89" s="428"/>
-      <c r="AJ89" s="455"/>
+      <c r="H89" s="263"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="264"/>
+      <c r="L89" s="562"/>
+      <c r="M89" s="533"/>
+      <c r="N89" s="533"/>
+      <c r="O89" s="533"/>
+      <c r="P89" s="533"/>
+      <c r="Q89" s="533"/>
+      <c r="R89" s="533"/>
+      <c r="S89" s="531"/>
+      <c r="T89" s="364"/>
+      <c r="U89" s="365"/>
+      <c r="V89" s="78"/>
+      <c r="W89" s="78"/>
+      <c r="X89" s="364"/>
+      <c r="Y89" s="365"/>
+      <c r="Z89" s="78"/>
+      <c r="AA89" s="78"/>
+      <c r="AB89" s="397"/>
+      <c r="AC89" s="81"/>
+      <c r="AD89" s="81"/>
+      <c r="AE89" s="224"/>
+      <c r="AF89" s="241"/>
+      <c r="AG89" s="242"/>
+      <c r="AH89" s="242"/>
+      <c r="AI89" s="427"/>
+      <c r="AJ89" s="454"/>
       <c r="AK89" s="6"/>
       <c r="AL89" s="6"/>
       <c r="AM89" s="6"/>
@@ -26128,42 +26168,42 @@
       <c r="HW89" s="6"/>
     </row>
     <row r="90" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A90" s="536"/>
-      <c r="B90" s="536"/>
-      <c r="C90" s="536"/>
-      <c r="D90" s="536"/>
-      <c r="E90" s="536"/>
-      <c r="F90" s="544"/>
-      <c r="G90" s="549"/>
-      <c r="H90" s="264"/>
-      <c r="I90" s="54"/>
-      <c r="J90" s="54"/>
-      <c r="K90" s="262"/>
-      <c r="L90" s="549"/>
-      <c r="M90" s="534"/>
-      <c r="N90" s="534"/>
-      <c r="O90" s="534"/>
-      <c r="P90" s="534"/>
-      <c r="Q90" s="534"/>
-      <c r="R90" s="534"/>
-      <c r="S90" s="532"/>
-      <c r="T90" s="212"/>
-      <c r="U90" s="84"/>
+      <c r="A90" s="535"/>
+      <c r="B90" s="535"/>
+      <c r="C90" s="535"/>
+      <c r="D90" s="535"/>
+      <c r="E90" s="535"/>
+      <c r="F90" s="543"/>
+      <c r="G90" s="548"/>
+      <c r="H90" s="263"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="261"/>
+      <c r="L90" s="548"/>
+      <c r="M90" s="533"/>
+      <c r="N90" s="533"/>
+      <c r="O90" s="533"/>
+      <c r="P90" s="533"/>
+      <c r="Q90" s="533"/>
+      <c r="R90" s="533"/>
+      <c r="S90" s="531"/>
+      <c r="T90" s="211"/>
+      <c r="U90" s="83"/>
       <c r="V90" s="26"/>
-      <c r="W90" s="84"/>
-      <c r="X90" s="212"/>
-      <c r="Y90" s="84"/>
+      <c r="W90" s="83"/>
+      <c r="X90" s="211"/>
+      <c r="Y90" s="83"/>
       <c r="Z90" s="26"/>
-      <c r="AA90" s="84"/>
-      <c r="AB90" s="213"/>
-      <c r="AC90" s="74"/>
-      <c r="AD90" s="74"/>
-      <c r="AE90" s="66"/>
-      <c r="AF90" s="135"/>
-      <c r="AG90" s="67"/>
-      <c r="AH90" s="67"/>
-      <c r="AI90" s="68"/>
-      <c r="AJ90" s="455"/>
+      <c r="AA90" s="83"/>
+      <c r="AB90" s="212"/>
+      <c r="AC90" s="73"/>
+      <c r="AD90" s="73"/>
+      <c r="AE90" s="65"/>
+      <c r="AF90" s="134"/>
+      <c r="AG90" s="66"/>
+      <c r="AH90" s="66"/>
+      <c r="AI90" s="67"/>
+      <c r="AJ90" s="454"/>
       <c r="AK90" s="6"/>
       <c r="AL90" s="6"/>
       <c r="AM90" s="6"/>
@@ -26361,42 +26401,42 @@
       <c r="HW90" s="6"/>
     </row>
     <row r="91" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A91" s="537"/>
-      <c r="B91" s="537"/>
-      <c r="C91" s="537"/>
-      <c r="D91" s="537"/>
-      <c r="E91" s="537"/>
-      <c r="F91" s="544"/>
-      <c r="G91" s="549"/>
-      <c r="H91" s="261"/>
-      <c r="I91" s="70"/>
-      <c r="J91" s="70"/>
-      <c r="K91" s="167"/>
-      <c r="L91" s="87"/>
-      <c r="M91" s="96"/>
-      <c r="N91" s="96"/>
-      <c r="O91" s="96"/>
-      <c r="P91" s="96"/>
-      <c r="Q91" s="196"/>
-      <c r="R91" s="196"/>
-      <c r="S91" s="97"/>
-      <c r="T91" s="370"/>
-      <c r="U91" s="371"/>
-      <c r="V91" s="89"/>
-      <c r="W91" s="461"/>
-      <c r="X91" s="462"/>
-      <c r="Y91" s="324"/>
-      <c r="Z91" s="89"/>
-      <c r="AA91" s="461"/>
-      <c r="AB91" s="250"/>
-      <c r="AC91" s="96"/>
-      <c r="AD91" s="96"/>
-      <c r="AE91" s="97"/>
-      <c r="AF91" s="69"/>
-      <c r="AG91" s="70"/>
-      <c r="AH91" s="70"/>
-      <c r="AI91" s="78"/>
-      <c r="AJ91" s="455"/>
+      <c r="A91" s="536"/>
+      <c r="B91" s="536"/>
+      <c r="C91" s="536"/>
+      <c r="D91" s="536"/>
+      <c r="E91" s="536"/>
+      <c r="F91" s="543"/>
+      <c r="G91" s="548"/>
+      <c r="H91" s="260"/>
+      <c r="I91" s="69"/>
+      <c r="J91" s="69"/>
+      <c r="K91" s="166"/>
+      <c r="L91" s="86"/>
+      <c r="M91" s="95"/>
+      <c r="N91" s="95"/>
+      <c r="O91" s="95"/>
+      <c r="P91" s="95"/>
+      <c r="Q91" s="195"/>
+      <c r="R91" s="195"/>
+      <c r="S91" s="96"/>
+      <c r="T91" s="369"/>
+      <c r="U91" s="370"/>
+      <c r="V91" s="88"/>
+      <c r="W91" s="460"/>
+      <c r="X91" s="461"/>
+      <c r="Y91" s="323"/>
+      <c r="Z91" s="88"/>
+      <c r="AA91" s="460"/>
+      <c r="AB91" s="249"/>
+      <c r="AC91" s="95"/>
+      <c r="AD91" s="95"/>
+      <c r="AE91" s="96"/>
+      <c r="AF91" s="68"/>
+      <c r="AG91" s="69"/>
+      <c r="AH91" s="69"/>
+      <c r="AI91" s="77"/>
+      <c r="AJ91" s="454"/>
       <c r="AK91" s="6"/>
       <c r="AL91" s="6"/>
       <c r="AM91" s="6"/>
@@ -26594,44 +26634,44 @@
       <c r="HW91" s="6"/>
     </row>
     <row r="92" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A92" s="542"/>
-      <c r="B92" s="542"/>
-      <c r="C92" s="542"/>
-      <c r="D92" s="542"/>
-      <c r="E92" s="542"/>
-      <c r="F92" s="544"/>
-      <c r="G92" s="561" t="s">
+      <c r="A92" s="541"/>
+      <c r="B92" s="541"/>
+      <c r="C92" s="541"/>
+      <c r="D92" s="541"/>
+      <c r="E92" s="541"/>
+      <c r="F92" s="543"/>
+      <c r="G92" s="560" t="s">
         <v>24</v>
       </c>
-      <c r="H92" s="257"/>
-      <c r="I92" s="58"/>
-      <c r="J92" s="58"/>
-      <c r="K92" s="258"/>
-      <c r="L92" s="463"/>
-      <c r="M92" s="464"/>
-      <c r="N92" s="464"/>
-      <c r="O92" s="465"/>
+      <c r="H92" s="256"/>
+      <c r="I92" s="57"/>
+      <c r="J92" s="57"/>
+      <c r="K92" s="257"/>
+      <c r="L92" s="462"/>
+      <c r="M92" s="463"/>
+      <c r="N92" s="463"/>
+      <c r="O92" s="464"/>
       <c r="P92" s="10"/>
       <c r="Q92" s="10"/>
-      <c r="R92" s="37"/>
-      <c r="S92" s="40"/>
-      <c r="T92" s="133"/>
-      <c r="U92" s="133"/>
-      <c r="V92" s="133"/>
-      <c r="W92" s="134"/>
-      <c r="X92" s="106"/>
-      <c r="Y92" s="106"/>
-      <c r="Z92" s="106"/>
-      <c r="AA92" s="106"/>
-      <c r="AB92" s="378"/>
-      <c r="AC92" s="141"/>
-      <c r="AD92" s="141"/>
-      <c r="AE92" s="183"/>
-      <c r="AF92" s="392"/>
-      <c r="AG92" s="393"/>
-      <c r="AH92" s="393"/>
-      <c r="AI92" s="394"/>
-      <c r="AJ92" s="455"/>
+      <c r="R92" s="36"/>
+      <c r="S92" s="39"/>
+      <c r="T92" s="132"/>
+      <c r="U92" s="132"/>
+      <c r="V92" s="132"/>
+      <c r="W92" s="133"/>
+      <c r="X92" s="105"/>
+      <c r="Y92" s="105"/>
+      <c r="Z92" s="105"/>
+      <c r="AA92" s="105"/>
+      <c r="AB92" s="377"/>
+      <c r="AC92" s="140"/>
+      <c r="AD92" s="140"/>
+      <c r="AE92" s="182"/>
+      <c r="AF92" s="391"/>
+      <c r="AG92" s="392"/>
+      <c r="AH92" s="392"/>
+      <c r="AI92" s="393"/>
+      <c r="AJ92" s="454"/>
       <c r="AK92" s="6"/>
       <c r="AL92" s="6"/>
       <c r="AM92" s="6"/>
@@ -26829,25 +26869,25 @@
       <c r="HW92" s="6"/>
     </row>
     <row r="93" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A93" s="536"/>
-      <c r="B93" s="536"/>
-      <c r="C93" s="536"/>
-      <c r="D93" s="536"/>
-      <c r="E93" s="536"/>
-      <c r="F93" s="544"/>
-      <c r="G93" s="549"/>
-      <c r="H93" s="259"/>
-      <c r="I93" s="67"/>
-      <c r="J93" s="67"/>
-      <c r="K93" s="262"/>
-      <c r="L93" s="466"/>
-      <c r="M93" s="466"/>
-      <c r="N93" s="466"/>
-      <c r="O93" s="467"/>
+      <c r="A93" s="535"/>
+      <c r="B93" s="535"/>
+      <c r="C93" s="535"/>
+      <c r="D93" s="535"/>
+      <c r="E93" s="535"/>
+      <c r="F93" s="543"/>
+      <c r="G93" s="548"/>
+      <c r="H93" s="258"/>
+      <c r="I93" s="66"/>
+      <c r="J93" s="66"/>
+      <c r="K93" s="261"/>
+      <c r="L93" s="465"/>
+      <c r="M93" s="465"/>
+      <c r="N93" s="465"/>
+      <c r="O93" s="466"/>
       <c r="P93" s="10"/>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
-      <c r="S93" s="45"/>
+      <c r="S93" s="44"/>
       <c r="T93" s="24"/>
       <c r="U93" s="24"/>
       <c r="V93" s="24"/>
@@ -26856,15 +26896,15 @@
       <c r="Y93" s="26"/>
       <c r="Z93" s="26"/>
       <c r="AA93" s="26"/>
-      <c r="AB93" s="224"/>
+      <c r="AB93" s="223"/>
       <c r="AC93" s="6"/>
       <c r="AD93" s="6"/>
-      <c r="AE93" s="150"/>
+      <c r="AE93" s="149"/>
       <c r="AF93" s="23"/>
       <c r="AG93" s="24"/>
       <c r="AH93" s="24"/>
       <c r="AI93" s="25"/>
-      <c r="AJ93" s="455"/>
+      <c r="AJ93" s="454"/>
       <c r="AK93" s="6"/>
       <c r="AL93" s="6"/>
       <c r="AM93" s="6"/>
@@ -27062,42 +27102,42 @@
       <c r="HW93" s="6"/>
     </row>
     <row r="94" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A94" s="537"/>
-      <c r="B94" s="537"/>
-      <c r="C94" s="537"/>
-      <c r="D94" s="537"/>
-      <c r="E94" s="537"/>
-      <c r="F94" s="544"/>
-      <c r="G94" s="555"/>
-      <c r="H94" s="266"/>
-      <c r="I94" s="94"/>
-      <c r="J94" s="94"/>
-      <c r="K94" s="468"/>
-      <c r="L94" s="469"/>
-      <c r="M94" s="470"/>
-      <c r="N94" s="470"/>
-      <c r="O94" s="471"/>
-      <c r="P94" s="47"/>
-      <c r="Q94" s="47"/>
-      <c r="R94" s="47"/>
-      <c r="S94" s="98"/>
-      <c r="T94" s="272"/>
-      <c r="U94" s="272"/>
-      <c r="V94" s="272"/>
-      <c r="W94" s="273"/>
-      <c r="X94" s="89"/>
-      <c r="Y94" s="89"/>
-      <c r="Z94" s="89"/>
-      <c r="AA94" s="89"/>
-      <c r="AB94" s="472"/>
-      <c r="AC94" s="102"/>
-      <c r="AD94" s="102"/>
-      <c r="AE94" s="473"/>
-      <c r="AF94" s="395"/>
-      <c r="AG94" s="396"/>
-      <c r="AH94" s="396"/>
-      <c r="AI94" s="268"/>
-      <c r="AJ94" s="455"/>
+      <c r="A94" s="536"/>
+      <c r="B94" s="536"/>
+      <c r="C94" s="536"/>
+      <c r="D94" s="536"/>
+      <c r="E94" s="536"/>
+      <c r="F94" s="543"/>
+      <c r="G94" s="554"/>
+      <c r="H94" s="265"/>
+      <c r="I94" s="93"/>
+      <c r="J94" s="93"/>
+      <c r="K94" s="467"/>
+      <c r="L94" s="468"/>
+      <c r="M94" s="469"/>
+      <c r="N94" s="469"/>
+      <c r="O94" s="470"/>
+      <c r="P94" s="46"/>
+      <c r="Q94" s="46"/>
+      <c r="R94" s="46"/>
+      <c r="S94" s="97"/>
+      <c r="T94" s="271"/>
+      <c r="U94" s="271"/>
+      <c r="V94" s="271"/>
+      <c r="W94" s="272"/>
+      <c r="X94" s="88"/>
+      <c r="Y94" s="88"/>
+      <c r="Z94" s="88"/>
+      <c r="AA94" s="88"/>
+      <c r="AB94" s="471"/>
+      <c r="AC94" s="101"/>
+      <c r="AD94" s="101"/>
+      <c r="AE94" s="472"/>
+      <c r="AF94" s="394"/>
+      <c r="AG94" s="395"/>
+      <c r="AH94" s="395"/>
+      <c r="AI94" s="267"/>
+      <c r="AJ94" s="454"/>
       <c r="AK94" s="6"/>
       <c r="AL94" s="6"/>
       <c r="AM94" s="6"/>
@@ -27295,44 +27335,44 @@
       <c r="HW94" s="6"/>
     </row>
     <row r="95" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A95" s="542"/>
-      <c r="B95" s="542"/>
-      <c r="C95" s="542"/>
-      <c r="D95" s="542"/>
-      <c r="E95" s="542"/>
-      <c r="F95" s="544"/>
-      <c r="G95" s="603" t="s">
+      <c r="A95" s="541"/>
+      <c r="B95" s="541"/>
+      <c r="C95" s="541"/>
+      <c r="D95" s="541"/>
+      <c r="E95" s="541"/>
+      <c r="F95" s="543"/>
+      <c r="G95" s="602" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="168"/>
+      <c r="H95" s="167"/>
       <c r="I95" s="26"/>
       <c r="J95" s="26"/>
-      <c r="K95" s="167"/>
-      <c r="L95" s="37"/>
-      <c r="M95" s="37"/>
-      <c r="N95" s="37"/>
-      <c r="O95" s="353"/>
+      <c r="K95" s="166"/>
+      <c r="L95" s="36"/>
+      <c r="M95" s="36"/>
+      <c r="N95" s="36"/>
+      <c r="O95" s="352"/>
       <c r="P95" s="10"/>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
-      <c r="S95" s="45"/>
+      <c r="S95" s="44"/>
       <c r="T95" s="34"/>
       <c r="U95" s="34"/>
       <c r="V95" s="34"/>
-      <c r="W95" s="111"/>
+      <c r="W95" s="110"/>
       <c r="X95" s="26"/>
       <c r="Y95" s="26"/>
       <c r="Z95" s="26"/>
       <c r="AA95" s="26"/>
-      <c r="AB95" s="224"/>
+      <c r="AB95" s="223"/>
       <c r="AC95" s="6"/>
       <c r="AD95" s="6"/>
-      <c r="AE95" s="150"/>
-      <c r="AF95" s="125"/>
+      <c r="AE95" s="149"/>
+      <c r="AF95" s="124"/>
       <c r="AG95" s="29"/>
       <c r="AH95" s="34"/>
-      <c r="AI95" s="111"/>
-      <c r="AJ95" s="151"/>
+      <c r="AI95" s="110"/>
+      <c r="AJ95" s="150"/>
       <c r="AK95" s="6"/>
       <c r="AL95" s="6"/>
       <c r="AM95" s="6"/>
@@ -27530,21 +27570,21 @@
       <c r="HW95" s="6"/>
     </row>
     <row r="96" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A96" s="536"/>
-      <c r="B96" s="536"/>
-      <c r="C96" s="536"/>
-      <c r="D96" s="536"/>
-      <c r="E96" s="536"/>
-      <c r="F96" s="544"/>
-      <c r="G96" s="549"/>
-      <c r="H96" s="168"/>
+      <c r="A96" s="535"/>
+      <c r="B96" s="535"/>
+      <c r="C96" s="535"/>
+      <c r="D96" s="535"/>
+      <c r="E96" s="535"/>
+      <c r="F96" s="543"/>
+      <c r="G96" s="548"/>
+      <c r="H96" s="167"/>
       <c r="I96" s="26"/>
       <c r="J96" s="26"/>
-      <c r="K96" s="167"/>
+      <c r="K96" s="166"/>
       <c r="L96" s="26"/>
       <c r="M96" s="26"/>
       <c r="N96" s="26"/>
-      <c r="O96" s="167"/>
+      <c r="O96" s="166"/>
       <c r="P96" s="26"/>
       <c r="Q96" s="26"/>
       <c r="R96" s="26"/>
@@ -27552,20 +27592,20 @@
       <c r="T96" s="34"/>
       <c r="U96" s="34"/>
       <c r="V96" s="34"/>
-      <c r="W96" s="111"/>
+      <c r="W96" s="110"/>
       <c r="X96" s="26"/>
       <c r="Y96" s="26"/>
       <c r="Z96" s="26"/>
       <c r="AA96" s="26"/>
-      <c r="AB96" s="224"/>
+      <c r="AB96" s="223"/>
       <c r="AC96" s="6"/>
       <c r="AD96" s="6"/>
-      <c r="AE96" s="150"/>
-      <c r="AF96" s="125"/>
+      <c r="AE96" s="149"/>
+      <c r="AF96" s="124"/>
       <c r="AG96" s="29"/>
       <c r="AH96" s="34"/>
-      <c r="AI96" s="111"/>
-      <c r="AJ96" s="151"/>
+      <c r="AI96" s="110"/>
+      <c r="AJ96" s="150"/>
       <c r="AK96" s="6"/>
       <c r="AL96" s="6"/>
       <c r="AM96" s="6"/>
@@ -27763,21 +27803,21 @@
       <c r="HW96" s="6"/>
     </row>
     <row r="97" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A97" s="537"/>
-      <c r="B97" s="537"/>
-      <c r="C97" s="537"/>
-      <c r="D97" s="537"/>
-      <c r="E97" s="537"/>
-      <c r="F97" s="545"/>
-      <c r="G97" s="602"/>
-      <c r="H97" s="168"/>
+      <c r="A97" s="536"/>
+      <c r="B97" s="536"/>
+      <c r="C97" s="536"/>
+      <c r="D97" s="536"/>
+      <c r="E97" s="536"/>
+      <c r="F97" s="544"/>
+      <c r="G97" s="601"/>
+      <c r="H97" s="167"/>
       <c r="I97" s="26"/>
       <c r="J97" s="26"/>
-      <c r="K97" s="167"/>
+      <c r="K97" s="166"/>
       <c r="L97" s="26"/>
       <c r="M97" s="26"/>
       <c r="N97" s="26"/>
-      <c r="O97" s="167"/>
+      <c r="O97" s="166"/>
       <c r="P97" s="26"/>
       <c r="Q97" s="26"/>
       <c r="R97" s="26"/>
@@ -27785,20 +27825,20 @@
       <c r="T97" s="34"/>
       <c r="U97" s="34"/>
       <c r="V97" s="34"/>
-      <c r="W97" s="111"/>
+      <c r="W97" s="110"/>
       <c r="X97" s="26"/>
       <c r="Y97" s="26"/>
       <c r="Z97" s="26"/>
       <c r="AA97" s="26"/>
-      <c r="AB97" s="224"/>
+      <c r="AB97" s="223"/>
       <c r="AC97" s="6"/>
       <c r="AD97" s="6"/>
-      <c r="AE97" s="150"/>
-      <c r="AF97" s="474"/>
-      <c r="AG97" s="118"/>
+      <c r="AE97" s="149"/>
+      <c r="AF97" s="473"/>
+      <c r="AG97" s="117"/>
       <c r="AH97" s="34"/>
-      <c r="AI97" s="111"/>
-      <c r="AJ97" s="151"/>
+      <c r="AI97" s="110"/>
+      <c r="AJ97" s="150"/>
       <c r="AK97" s="6"/>
       <c r="AL97" s="6"/>
       <c r="AM97" s="6"/>
@@ -27996,29 +28036,29 @@
       <c r="HW97" s="6"/>
     </row>
     <row r="98" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A98" s="542"/>
-      <c r="B98" s="542"/>
-      <c r="C98" s="542"/>
-      <c r="D98" s="542"/>
-      <c r="E98" s="542"/>
-      <c r="F98" s="580" t="s">
+      <c r="A98" s="541"/>
+      <c r="B98" s="541"/>
+      <c r="C98" s="541"/>
+      <c r="D98" s="541"/>
+      <c r="E98" s="541"/>
+      <c r="F98" s="579" t="s">
         <v>30</v>
       </c>
-      <c r="G98" s="576" t="s">
+      <c r="G98" s="575" t="s">
         <v>18</v>
       </c>
-      <c r="H98" s="475"/>
-      <c r="I98" s="252"/>
-      <c r="J98" s="252"/>
-      <c r="K98" s="476"/>
+      <c r="H98" s="474"/>
+      <c r="I98" s="251"/>
+      <c r="J98" s="251"/>
+      <c r="K98" s="475"/>
       <c r="L98" s="19"/>
       <c r="M98" s="19"/>
       <c r="N98" s="19"/>
-      <c r="O98" s="477"/>
+      <c r="O98" s="476"/>
       <c r="P98" s="17"/>
       <c r="Q98" s="17"/>
       <c r="R98" s="17"/>
-      <c r="S98" s="180"/>
+      <c r="S98" s="179"/>
       <c r="T98" s="21"/>
       <c r="U98" s="21"/>
       <c r="V98" s="21"/>
@@ -28027,15 +28067,15 @@
       <c r="Y98" s="19"/>
       <c r="Z98" s="19"/>
       <c r="AA98" s="19"/>
-      <c r="AB98" s="478"/>
-      <c r="AC98" s="479"/>
-      <c r="AD98" s="479"/>
-      <c r="AE98" s="480"/>
-      <c r="AF98" s="253"/>
+      <c r="AB98" s="477"/>
+      <c r="AC98" s="478"/>
+      <c r="AD98" s="478"/>
+      <c r="AE98" s="479"/>
+      <c r="AF98" s="252"/>
       <c r="AG98" s="21"/>
       <c r="AH98" s="21"/>
       <c r="AI98" s="22"/>
-      <c r="AJ98" s="143"/>
+      <c r="AJ98" s="142"/>
       <c r="AK98" s="6"/>
       <c r="AL98" s="6"/>
       <c r="AM98" s="6"/>
@@ -28233,25 +28273,25 @@
       <c r="HW98" s="6"/>
     </row>
     <row r="99" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="536"/>
-      <c r="B99" s="536"/>
-      <c r="C99" s="536"/>
-      <c r="D99" s="536"/>
-      <c r="E99" s="536"/>
-      <c r="F99" s="544"/>
-      <c r="G99" s="549"/>
-      <c r="H99" s="224"/>
+      <c r="A99" s="535"/>
+      <c r="B99" s="535"/>
+      <c r="C99" s="535"/>
+      <c r="D99" s="535"/>
+      <c r="E99" s="535"/>
+      <c r="F99" s="543"/>
+      <c r="G99" s="548"/>
+      <c r="H99" s="223"/>
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
-      <c r="K99" s="145"/>
+      <c r="K99" s="144"/>
       <c r="L99" s="26"/>
       <c r="M99" s="26"/>
       <c r="N99" s="26"/>
       <c r="O99" s="28"/>
-      <c r="P99" s="135"/>
-      <c r="Q99" s="67"/>
-      <c r="R99" s="67"/>
-      <c r="S99" s="68"/>
+      <c r="P99" s="134"/>
+      <c r="Q99" s="66"/>
+      <c r="R99" s="66"/>
+      <c r="S99" s="67"/>
       <c r="T99" s="29"/>
       <c r="U99" s="29"/>
       <c r="V99" s="29"/>
@@ -28260,15 +28300,15 @@
       <c r="Y99" s="26"/>
       <c r="Z99" s="26"/>
       <c r="AA99" s="26"/>
-      <c r="AB99" s="203"/>
+      <c r="AB99" s="202"/>
       <c r="AC99" s="32"/>
       <c r="AD99" s="32"/>
       <c r="AE99" s="32"/>
-      <c r="AF99" s="125"/>
+      <c r="AF99" s="124"/>
       <c r="AG99" s="29"/>
       <c r="AH99" s="29"/>
       <c r="AI99" s="30"/>
-      <c r="AJ99" s="195"/>
+      <c r="AJ99" s="194"/>
       <c r="AK99" s="6"/>
       <c r="AL99" s="6"/>
       <c r="AM99" s="6"/>
@@ -28466,42 +28506,42 @@
       <c r="HW99" s="6"/>
     </row>
     <row r="100" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A100" s="537"/>
-      <c r="B100" s="537"/>
-      <c r="C100" s="537"/>
-      <c r="D100" s="537"/>
-      <c r="E100" s="537"/>
-      <c r="F100" s="544"/>
-      <c r="G100" s="549"/>
-      <c r="H100" s="224"/>
+      <c r="A100" s="536"/>
+      <c r="B100" s="536"/>
+      <c r="C100" s="536"/>
+      <c r="D100" s="536"/>
+      <c r="E100" s="536"/>
+      <c r="F100" s="543"/>
+      <c r="G100" s="548"/>
+      <c r="H100" s="223"/>
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
-      <c r="K100" s="145"/>
+      <c r="K100" s="144"/>
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
       <c r="N100" s="26"/>
       <c r="O100" s="28"/>
-      <c r="P100" s="481"/>
-      <c r="Q100" s="71"/>
-      <c r="R100" s="71"/>
-      <c r="S100" s="78"/>
-      <c r="T100" s="128"/>
-      <c r="U100" s="128"/>
-      <c r="V100" s="128"/>
+      <c r="P100" s="480"/>
+      <c r="Q100" s="70"/>
+      <c r="R100" s="70"/>
+      <c r="S100" s="77"/>
+      <c r="T100" s="127"/>
+      <c r="U100" s="127"/>
+      <c r="V100" s="127"/>
       <c r="W100" s="35"/>
       <c r="X100" s="26"/>
       <c r="Y100" s="26"/>
       <c r="Z100" s="26"/>
       <c r="AA100" s="26"/>
-      <c r="AB100" s="203"/>
+      <c r="AB100" s="202"/>
       <c r="AC100" s="29"/>
       <c r="AD100" s="29"/>
       <c r="AE100" s="29"/>
-      <c r="AF100" s="274"/>
+      <c r="AF100" s="273"/>
       <c r="AG100" s="33"/>
       <c r="AH100" s="34"/>
       <c r="AI100" s="35"/>
-      <c r="AJ100" s="131"/>
+      <c r="AJ100" s="130"/>
       <c r="AK100" s="6"/>
       <c r="AL100" s="6"/>
       <c r="AM100" s="6"/>
@@ -28699,52 +28739,52 @@
       <c r="HW100" s="6"/>
     </row>
     <row r="101" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="539">
+      <c r="A101" s="538">
         <v>11</v>
       </c>
-      <c r="B101" s="539">
+      <c r="B101" s="538">
         <v>11</v>
       </c>
-      <c r="C101" s="539">
+      <c r="C101" s="538">
         <v>8</v>
       </c>
-      <c r="D101" s="539">
+      <c r="D101" s="538">
         <v>6</v>
       </c>
-      <c r="E101" s="541"/>
-      <c r="F101" s="544"/>
-      <c r="G101" s="561" t="s">
+      <c r="E101" s="540"/>
+      <c r="F101" s="543"/>
+      <c r="G101" s="560" t="s">
         <v>19</v>
       </c>
-      <c r="H101" s="352"/>
-      <c r="I101" s="37"/>
-      <c r="J101" s="37"/>
-      <c r="K101" s="353"/>
-      <c r="L101" s="58"/>
-      <c r="M101" s="58"/>
-      <c r="N101" s="58"/>
-      <c r="O101" s="59"/>
-      <c r="P101" s="57"/>
-      <c r="Q101" s="58"/>
-      <c r="R101" s="58"/>
-      <c r="S101" s="59"/>
-      <c r="T101" s="41"/>
-      <c r="U101" s="41"/>
-      <c r="V101" s="41"/>
-      <c r="W101" s="42"/>
-      <c r="X101" s="106"/>
-      <c r="Y101" s="106"/>
-      <c r="Z101" s="106"/>
-      <c r="AA101" s="106"/>
-      <c r="AB101" s="257"/>
-      <c r="AC101" s="58"/>
-      <c r="AD101" s="58"/>
-      <c r="AE101" s="58"/>
-      <c r="AF101" s="256"/>
-      <c r="AG101" s="41"/>
-      <c r="AH101" s="41"/>
-      <c r="AI101" s="42"/>
-      <c r="AJ101" s="143"/>
+      <c r="H101" s="351"/>
+      <c r="I101" s="36"/>
+      <c r="J101" s="36"/>
+      <c r="K101" s="352"/>
+      <c r="L101" s="57"/>
+      <c r="M101" s="57"/>
+      <c r="N101" s="57"/>
+      <c r="O101" s="58"/>
+      <c r="P101" s="56"/>
+      <c r="Q101" s="57"/>
+      <c r="R101" s="57"/>
+      <c r="S101" s="58"/>
+      <c r="T101" s="40"/>
+      <c r="U101" s="40"/>
+      <c r="V101" s="40"/>
+      <c r="W101" s="41"/>
+      <c r="X101" s="105"/>
+      <c r="Y101" s="105"/>
+      <c r="Z101" s="105"/>
+      <c r="AA101" s="105"/>
+      <c r="AB101" s="256"/>
+      <c r="AC101" s="57"/>
+      <c r="AD101" s="57"/>
+      <c r="AE101" s="57"/>
+      <c r="AF101" s="255"/>
+      <c r="AG101" s="40"/>
+      <c r="AH101" s="40"/>
+      <c r="AI101" s="41"/>
+      <c r="AJ101" s="142"/>
       <c r="AK101" s="6"/>
       <c r="AL101" s="6"/>
       <c r="AM101" s="6"/>
@@ -28942,25 +28982,25 @@
       <c r="HW101" s="6"/>
     </row>
     <row r="102" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A102" s="536"/>
-      <c r="B102" s="536"/>
-      <c r="C102" s="536"/>
-      <c r="D102" s="536"/>
-      <c r="E102" s="536"/>
-      <c r="F102" s="544"/>
-      <c r="G102" s="549"/>
-      <c r="H102" s="153"/>
+      <c r="A102" s="535"/>
+      <c r="B102" s="535"/>
+      <c r="C102" s="535"/>
+      <c r="D102" s="535"/>
+      <c r="E102" s="535"/>
+      <c r="F102" s="543"/>
+      <c r="G102" s="548"/>
+      <c r="H102" s="152"/>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
-      <c r="K102" s="146"/>
-      <c r="L102" s="61"/>
-      <c r="M102" s="61"/>
-      <c r="N102" s="67"/>
-      <c r="O102" s="68"/>
-      <c r="P102" s="60"/>
-      <c r="Q102" s="61"/>
-      <c r="R102" s="61"/>
-      <c r="S102" s="99"/>
+      <c r="K102" s="145"/>
+      <c r="L102" s="60"/>
+      <c r="M102" s="60"/>
+      <c r="N102" s="66"/>
+      <c r="O102" s="67"/>
+      <c r="P102" s="59"/>
+      <c r="Q102" s="60"/>
+      <c r="R102" s="60"/>
+      <c r="S102" s="98"/>
       <c r="T102" s="29"/>
       <c r="U102" s="29"/>
       <c r="V102" s="29"/>
@@ -28969,15 +29009,15 @@
       <c r="Y102" s="26"/>
       <c r="Z102" s="26"/>
       <c r="AA102" s="26"/>
-      <c r="AB102" s="259"/>
-      <c r="AC102" s="67"/>
-      <c r="AD102" s="67"/>
-      <c r="AE102" s="67"/>
-      <c r="AF102" s="125"/>
+      <c r="AB102" s="258"/>
+      <c r="AC102" s="66"/>
+      <c r="AD102" s="66"/>
+      <c r="AE102" s="66"/>
+      <c r="AF102" s="124"/>
       <c r="AG102" s="29"/>
       <c r="AH102" s="29"/>
       <c r="AI102" s="30"/>
-      <c r="AJ102" s="195"/>
+      <c r="AJ102" s="194"/>
       <c r="AK102" s="6"/>
       <c r="AL102" s="6"/>
       <c r="AM102" s="6"/>
@@ -29175,25 +29215,25 @@
       <c r="HW102" s="6"/>
     </row>
     <row r="103" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A103" s="537"/>
-      <c r="B103" s="537"/>
-      <c r="C103" s="537"/>
-      <c r="D103" s="537"/>
-      <c r="E103" s="537"/>
-      <c r="F103" s="544"/>
-      <c r="G103" s="555"/>
-      <c r="H103" s="482"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="47"/>
-      <c r="K103" s="159"/>
-      <c r="L103" s="206"/>
-      <c r="M103" s="206"/>
-      <c r="N103" s="95"/>
-      <c r="O103" s="139"/>
-      <c r="P103" s="205"/>
-      <c r="Q103" s="206"/>
-      <c r="R103" s="73"/>
-      <c r="S103" s="100"/>
+      <c r="A103" s="536"/>
+      <c r="B103" s="536"/>
+      <c r="C103" s="536"/>
+      <c r="D103" s="536"/>
+      <c r="E103" s="536"/>
+      <c r="F103" s="543"/>
+      <c r="G103" s="554"/>
+      <c r="H103" s="481"/>
+      <c r="I103" s="46"/>
+      <c r="J103" s="46"/>
+      <c r="K103" s="158"/>
+      <c r="L103" s="205"/>
+      <c r="M103" s="205"/>
+      <c r="N103" s="94"/>
+      <c r="O103" s="138"/>
+      <c r="P103" s="204"/>
+      <c r="Q103" s="205"/>
+      <c r="R103" s="72"/>
+      <c r="S103" s="99"/>
       <c r="T103" s="29"/>
       <c r="U103" s="29"/>
       <c r="V103" s="29"/>
@@ -29202,15 +29242,15 @@
       <c r="Y103" s="26"/>
       <c r="Z103" s="26"/>
       <c r="AA103" s="26"/>
-      <c r="AB103" s="261"/>
-      <c r="AC103" s="70"/>
-      <c r="AD103" s="70"/>
-      <c r="AE103" s="71"/>
+      <c r="AB103" s="260"/>
+      <c r="AC103" s="69"/>
+      <c r="AD103" s="69"/>
+      <c r="AE103" s="70"/>
       <c r="AF103" s="31"/>
       <c r="AG103" s="29"/>
       <c r="AH103" s="29"/>
       <c r="AI103" s="30"/>
-      <c r="AJ103" s="131"/>
+      <c r="AJ103" s="130"/>
       <c r="AK103" s="6"/>
       <c r="AL103" s="6"/>
       <c r="AM103" s="6"/>
@@ -29408,54 +29448,54 @@
       <c r="HW103" s="6"/>
     </row>
     <row r="104" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="539">
+      <c r="A104" s="538">
         <v>25</v>
       </c>
-      <c r="B104" s="539">
+      <c r="B104" s="538">
         <v>25</v>
       </c>
-      <c r="C104" s="539">
+      <c r="C104" s="538">
         <v>22</v>
       </c>
-      <c r="D104" s="539">
+      <c r="D104" s="538">
         <v>20</v>
       </c>
-      <c r="E104" s="541">
+      <c r="E104" s="540">
         <v>0</v>
       </c>
-      <c r="F104" s="544"/>
-      <c r="G104" s="567" t="s">
+      <c r="F104" s="543"/>
+      <c r="G104" s="566" t="s">
         <v>20</v>
       </c>
-      <c r="H104" s="352"/>
-      <c r="I104" s="37"/>
-      <c r="J104" s="37"/>
-      <c r="K104" s="353"/>
-      <c r="L104" s="107"/>
-      <c r="M104" s="107"/>
-      <c r="N104" s="41"/>
-      <c r="O104" s="42"/>
-      <c r="P104" s="208"/>
-      <c r="Q104" s="107"/>
-      <c r="R104" s="107"/>
-      <c r="S104" s="108"/>
-      <c r="T104" s="41"/>
-      <c r="U104" s="41"/>
-      <c r="V104" s="41"/>
-      <c r="W104" s="42"/>
-      <c r="X104" s="58"/>
-      <c r="Y104" s="58"/>
-      <c r="Z104" s="58"/>
-      <c r="AA104" s="58"/>
-      <c r="AB104" s="257"/>
-      <c r="AC104" s="58"/>
-      <c r="AD104" s="58"/>
-      <c r="AE104" s="58"/>
-      <c r="AF104" s="256"/>
-      <c r="AG104" s="41"/>
-      <c r="AH104" s="41"/>
-      <c r="AI104" s="42"/>
-      <c r="AJ104" s="143"/>
+      <c r="H104" s="351"/>
+      <c r="I104" s="36"/>
+      <c r="J104" s="36"/>
+      <c r="K104" s="352"/>
+      <c r="L104" s="106"/>
+      <c r="M104" s="106"/>
+      <c r="N104" s="40"/>
+      <c r="O104" s="41"/>
+      <c r="P104" s="207"/>
+      <c r="Q104" s="106"/>
+      <c r="R104" s="106"/>
+      <c r="S104" s="107"/>
+      <c r="T104" s="40"/>
+      <c r="U104" s="40"/>
+      <c r="V104" s="40"/>
+      <c r="W104" s="41"/>
+      <c r="X104" s="57"/>
+      <c r="Y104" s="57"/>
+      <c r="Z104" s="57"/>
+      <c r="AA104" s="57"/>
+      <c r="AB104" s="256"/>
+      <c r="AC104" s="57"/>
+      <c r="AD104" s="57"/>
+      <c r="AE104" s="57"/>
+      <c r="AF104" s="255"/>
+      <c r="AG104" s="40"/>
+      <c r="AH104" s="40"/>
+      <c r="AI104" s="41"/>
+      <c r="AJ104" s="142"/>
       <c r="AK104" s="6"/>
       <c r="AL104" s="6"/>
       <c r="AM104" s="6"/>
@@ -29653,25 +29693,25 @@
       <c r="HW104" s="6"/>
     </row>
     <row r="105" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="536"/>
-      <c r="B105" s="536"/>
-      <c r="C105" s="536"/>
-      <c r="D105" s="536"/>
-      <c r="E105" s="536"/>
-      <c r="F105" s="544"/>
-      <c r="G105" s="549"/>
-      <c r="H105" s="153"/>
+      <c r="A105" s="535"/>
+      <c r="B105" s="535"/>
+      <c r="C105" s="535"/>
+      <c r="D105" s="535"/>
+      <c r="E105" s="535"/>
+      <c r="F105" s="543"/>
+      <c r="G105" s="548"/>
+      <c r="H105" s="152"/>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
-      <c r="K105" s="146"/>
+      <c r="K105" s="145"/>
       <c r="L105" s="26"/>
-      <c r="M105" s="84"/>
+      <c r="M105" s="83"/>
       <c r="N105" s="32"/>
-      <c r="O105" s="44"/>
+      <c r="O105" s="43"/>
       <c r="P105" s="27"/>
-      <c r="Q105" s="84"/>
+      <c r="Q105" s="83"/>
       <c r="R105" s="26"/>
-      <c r="S105" s="112"/>
+      <c r="S105" s="111"/>
       <c r="T105" s="29"/>
       <c r="U105" s="29"/>
       <c r="V105" s="29"/>
@@ -29680,15 +29720,15 @@
       <c r="Y105" s="26"/>
       <c r="Z105" s="26"/>
       <c r="AA105" s="26"/>
-      <c r="AB105" s="259"/>
-      <c r="AC105" s="67"/>
-      <c r="AD105" s="231"/>
-      <c r="AE105" s="67"/>
-      <c r="AF105" s="125"/>
+      <c r="AB105" s="258"/>
+      <c r="AC105" s="66"/>
+      <c r="AD105" s="230"/>
+      <c r="AE105" s="66"/>
+      <c r="AF105" s="124"/>
       <c r="AG105" s="29"/>
       <c r="AH105" s="29"/>
       <c r="AI105" s="30"/>
-      <c r="AJ105" s="195"/>
+      <c r="AJ105" s="194"/>
       <c r="AK105" s="6"/>
       <c r="AL105" s="6"/>
       <c r="AM105" s="6"/>
@@ -29886,42 +29926,42 @@
       <c r="HW105" s="6"/>
     </row>
     <row r="106" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A106" s="537"/>
-      <c r="B106" s="537"/>
-      <c r="C106" s="537"/>
-      <c r="D106" s="537"/>
-      <c r="E106" s="537"/>
-      <c r="F106" s="544"/>
-      <c r="G106" s="568"/>
-      <c r="H106" s="456"/>
-      <c r="I106" s="457"/>
-      <c r="J106" s="457"/>
-      <c r="K106" s="458"/>
-      <c r="L106" s="306"/>
-      <c r="M106" s="306"/>
-      <c r="N106" s="147"/>
-      <c r="O106" s="483"/>
-      <c r="P106" s="484"/>
-      <c r="Q106" s="306"/>
-      <c r="R106" s="485"/>
-      <c r="S106" s="486"/>
-      <c r="T106" s="487"/>
-      <c r="U106" s="487"/>
-      <c r="V106" s="487"/>
-      <c r="W106" s="488"/>
-      <c r="X106" s="147"/>
-      <c r="Y106" s="147"/>
-      <c r="Z106" s="147"/>
-      <c r="AA106" s="147"/>
-      <c r="AB106" s="459"/>
-      <c r="AC106" s="263"/>
-      <c r="AD106" s="263"/>
-      <c r="AE106" s="489"/>
-      <c r="AF106" s="490"/>
-      <c r="AG106" s="487"/>
-      <c r="AH106" s="487"/>
-      <c r="AI106" s="488"/>
-      <c r="AJ106" s="131"/>
+      <c r="A106" s="536"/>
+      <c r="B106" s="536"/>
+      <c r="C106" s="536"/>
+      <c r="D106" s="536"/>
+      <c r="E106" s="536"/>
+      <c r="F106" s="543"/>
+      <c r="G106" s="567"/>
+      <c r="H106" s="455"/>
+      <c r="I106" s="456"/>
+      <c r="J106" s="456"/>
+      <c r="K106" s="457"/>
+      <c r="L106" s="305"/>
+      <c r="M106" s="305"/>
+      <c r="N106" s="146"/>
+      <c r="O106" s="482"/>
+      <c r="P106" s="483"/>
+      <c r="Q106" s="305"/>
+      <c r="R106" s="484"/>
+      <c r="S106" s="485"/>
+      <c r="T106" s="486"/>
+      <c r="U106" s="486"/>
+      <c r="V106" s="486"/>
+      <c r="W106" s="487"/>
+      <c r="X106" s="146"/>
+      <c r="Y106" s="146"/>
+      <c r="Z106" s="146"/>
+      <c r="AA106" s="146"/>
+      <c r="AB106" s="458"/>
+      <c r="AC106" s="262"/>
+      <c r="AD106" s="262"/>
+      <c r="AE106" s="488"/>
+      <c r="AF106" s="489"/>
+      <c r="AG106" s="486"/>
+      <c r="AH106" s="486"/>
+      <c r="AI106" s="487"/>
+      <c r="AJ106" s="130"/>
       <c r="AK106" s="6"/>
       <c r="AL106" s="6"/>
       <c r="AM106" s="6"/>
@@ -30119,37 +30159,37 @@
       <c r="HW106" s="6"/>
     </row>
     <row r="107" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A107" s="541">
+      <c r="A107" s="540">
         <v>0</v>
       </c>
-      <c r="B107" s="541">
+      <c r="B107" s="540">
         <v>0</v>
       </c>
-      <c r="C107" s="541">
+      <c r="C107" s="540">
         <v>0</v>
       </c>
-      <c r="D107" s="541">
+      <c r="D107" s="540">
         <v>0</v>
       </c>
-      <c r="E107" s="541">
+      <c r="E107" s="540">
         <v>0</v>
       </c>
-      <c r="F107" s="544"/>
-      <c r="G107" s="570" t="s">
+      <c r="F107" s="543"/>
+      <c r="G107" s="569" t="s">
         <v>22</v>
       </c>
-      <c r="H107" s="153"/>
+      <c r="H107" s="152"/>
       <c r="I107" s="10"/>
       <c r="J107" s="10"/>
-      <c r="K107" s="146"/>
+      <c r="K107" s="145"/>
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
-      <c r="N107" s="54"/>
-      <c r="O107" s="63"/>
-      <c r="P107" s="53"/>
-      <c r="Q107" s="54"/>
-      <c r="R107" s="54"/>
-      <c r="S107" s="63"/>
+      <c r="N107" s="53"/>
+      <c r="O107" s="62"/>
+      <c r="P107" s="52"/>
+      <c r="Q107" s="53"/>
+      <c r="R107" s="53"/>
+      <c r="S107" s="62"/>
       <c r="T107" s="29"/>
       <c r="U107" s="29"/>
       <c r="V107" s="29"/>
@@ -30158,15 +30198,15 @@
       <c r="Y107" s="34"/>
       <c r="Z107" s="34"/>
       <c r="AA107" s="34"/>
-      <c r="AB107" s="53"/>
-      <c r="AC107" s="54"/>
-      <c r="AD107" s="54"/>
-      <c r="AE107" s="54"/>
-      <c r="AF107" s="474"/>
+      <c r="AB107" s="52"/>
+      <c r="AC107" s="53"/>
+      <c r="AD107" s="53"/>
+      <c r="AE107" s="53"/>
+      <c r="AF107" s="473"/>
       <c r="AG107" s="29"/>
       <c r="AH107" s="29"/>
       <c r="AI107" s="30"/>
-      <c r="AJ107" s="455"/>
+      <c r="AJ107" s="454"/>
       <c r="AK107" s="6"/>
       <c r="AL107" s="6"/>
       <c r="AM107" s="6"/>
@@ -30364,25 +30404,25 @@
       <c r="HW107" s="6"/>
     </row>
     <row r="108" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A108" s="536"/>
-      <c r="B108" s="536"/>
-      <c r="C108" s="536"/>
-      <c r="D108" s="536"/>
-      <c r="E108" s="536"/>
-      <c r="F108" s="544"/>
-      <c r="G108" s="549"/>
-      <c r="H108" s="153"/>
+      <c r="A108" s="535"/>
+      <c r="B108" s="535"/>
+      <c r="C108" s="535"/>
+      <c r="D108" s="535"/>
+      <c r="E108" s="535"/>
+      <c r="F108" s="543"/>
+      <c r="G108" s="548"/>
+      <c r="H108" s="152"/>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
-      <c r="K108" s="146"/>
+      <c r="K108" s="145"/>
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
-      <c r="N108" s="61"/>
-      <c r="O108" s="99"/>
-      <c r="P108" s="119"/>
-      <c r="Q108" s="120"/>
-      <c r="R108" s="61"/>
-      <c r="S108" s="99"/>
+      <c r="N108" s="60"/>
+      <c r="O108" s="98"/>
+      <c r="P108" s="118"/>
+      <c r="Q108" s="119"/>
+      <c r="R108" s="60"/>
+      <c r="S108" s="98"/>
       <c r="T108" s="29"/>
       <c r="U108" s="29"/>
       <c r="V108" s="29"/>
@@ -30391,15 +30431,15 @@
       <c r="Y108" s="32"/>
       <c r="Z108" s="32"/>
       <c r="AA108" s="32"/>
-      <c r="AB108" s="135"/>
-      <c r="AC108" s="67"/>
-      <c r="AD108" s="231"/>
-      <c r="AE108" s="67"/>
+      <c r="AB108" s="134"/>
+      <c r="AC108" s="66"/>
+      <c r="AD108" s="230"/>
+      <c r="AE108" s="66"/>
       <c r="AF108" s="31"/>
       <c r="AG108" s="29"/>
       <c r="AH108" s="29"/>
       <c r="AI108" s="30"/>
-      <c r="AJ108" s="491"/>
+      <c r="AJ108" s="490"/>
       <c r="AK108" s="6"/>
       <c r="AL108" s="6"/>
       <c r="AM108" s="6"/>
@@ -30597,25 +30637,25 @@
       <c r="HW108" s="6"/>
     </row>
     <row r="109" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A109" s="537"/>
-      <c r="B109" s="537"/>
-      <c r="C109" s="537"/>
-      <c r="D109" s="537"/>
-      <c r="E109" s="537"/>
-      <c r="F109" s="544"/>
-      <c r="G109" s="555"/>
-      <c r="H109" s="153"/>
+      <c r="A109" s="536"/>
+      <c r="B109" s="536"/>
+      <c r="C109" s="536"/>
+      <c r="D109" s="536"/>
+      <c r="E109" s="536"/>
+      <c r="F109" s="543"/>
+      <c r="G109" s="554"/>
+      <c r="H109" s="152"/>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
-      <c r="K109" s="146"/>
+      <c r="K109" s="145"/>
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
-      <c r="N109" s="73"/>
-      <c r="O109" s="100"/>
-      <c r="P109" s="72"/>
-      <c r="Q109" s="73"/>
-      <c r="R109" s="73"/>
-      <c r="S109" s="100"/>
+      <c r="N109" s="72"/>
+      <c r="O109" s="99"/>
+      <c r="P109" s="71"/>
+      <c r="Q109" s="72"/>
+      <c r="R109" s="72"/>
+      <c r="S109" s="99"/>
       <c r="T109" s="29"/>
       <c r="U109" s="29"/>
       <c r="V109" s="29"/>
@@ -30624,15 +30664,15 @@
       <c r="Y109" s="32"/>
       <c r="Z109" s="34"/>
       <c r="AA109" s="34"/>
-      <c r="AB109" s="69"/>
-      <c r="AC109" s="70"/>
-      <c r="AD109" s="70"/>
-      <c r="AE109" s="71"/>
+      <c r="AB109" s="68"/>
+      <c r="AC109" s="69"/>
+      <c r="AD109" s="69"/>
+      <c r="AE109" s="70"/>
       <c r="AF109" s="31"/>
       <c r="AG109" s="29"/>
       <c r="AH109" s="29"/>
       <c r="AI109" s="30"/>
-      <c r="AJ109" s="455"/>
+      <c r="AJ109" s="454"/>
       <c r="AK109" s="6"/>
       <c r="AL109" s="6"/>
       <c r="AM109" s="6"/>
@@ -30830,44 +30870,44 @@
       <c r="HW109" s="6"/>
     </row>
     <row r="110" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A110" s="542"/>
-      <c r="B110" s="542"/>
-      <c r="C110" s="542"/>
-      <c r="D110" s="542"/>
-      <c r="E110" s="542"/>
-      <c r="F110" s="544"/>
-      <c r="G110" s="561" t="s">
+      <c r="A110" s="541"/>
+      <c r="B110" s="541"/>
+      <c r="C110" s="541"/>
+      <c r="D110" s="541"/>
+      <c r="E110" s="541"/>
+      <c r="F110" s="543"/>
+      <c r="G110" s="560" t="s">
         <v>24</v>
       </c>
-      <c r="H110" s="492"/>
-      <c r="I110" s="493"/>
-      <c r="J110" s="493"/>
-      <c r="K110" s="494"/>
-      <c r="L110" s="37"/>
-      <c r="M110" s="37"/>
-      <c r="N110" s="495"/>
-      <c r="O110" s="496"/>
-      <c r="P110" s="497"/>
-      <c r="Q110" s="495"/>
-      <c r="R110" s="495"/>
-      <c r="S110" s="496"/>
-      <c r="T110" s="493"/>
-      <c r="U110" s="493"/>
-      <c r="V110" s="493"/>
-      <c r="W110" s="498"/>
-      <c r="X110" s="499"/>
-      <c r="Y110" s="499"/>
-      <c r="Z110" s="499"/>
-      <c r="AA110" s="499"/>
-      <c r="AB110" s="500"/>
-      <c r="AC110" s="493"/>
-      <c r="AD110" s="493"/>
-      <c r="AE110" s="493"/>
-      <c r="AF110" s="57"/>
-      <c r="AG110" s="58"/>
-      <c r="AH110" s="58"/>
-      <c r="AI110" s="59"/>
-      <c r="AJ110" s="151"/>
+      <c r="H110" s="491"/>
+      <c r="I110" s="492"/>
+      <c r="J110" s="492"/>
+      <c r="K110" s="493"/>
+      <c r="L110" s="36"/>
+      <c r="M110" s="36"/>
+      <c r="N110" s="494"/>
+      <c r="O110" s="495"/>
+      <c r="P110" s="496"/>
+      <c r="Q110" s="494"/>
+      <c r="R110" s="494"/>
+      <c r="S110" s="495"/>
+      <c r="T110" s="492"/>
+      <c r="U110" s="492"/>
+      <c r="V110" s="492"/>
+      <c r="W110" s="497"/>
+      <c r="X110" s="498"/>
+      <c r="Y110" s="498"/>
+      <c r="Z110" s="498"/>
+      <c r="AA110" s="498"/>
+      <c r="AB110" s="499"/>
+      <c r="AC110" s="492"/>
+      <c r="AD110" s="492"/>
+      <c r="AE110" s="492"/>
+      <c r="AF110" s="56"/>
+      <c r="AG110" s="57"/>
+      <c r="AH110" s="57"/>
+      <c r="AI110" s="58"/>
+      <c r="AJ110" s="150"/>
       <c r="AK110" s="6"/>
       <c r="AL110" s="6"/>
       <c r="AM110" s="6"/>
@@ -31065,42 +31105,42 @@
       <c r="HW110" s="6"/>
     </row>
     <row r="111" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A111" s="536"/>
-      <c r="B111" s="536"/>
-      <c r="C111" s="536"/>
-      <c r="D111" s="536"/>
-      <c r="E111" s="536"/>
-      <c r="F111" s="544"/>
-      <c r="G111" s="549"/>
-      <c r="H111" s="501"/>
-      <c r="I111" s="502"/>
-      <c r="J111" s="502"/>
-      <c r="K111" s="503"/>
+      <c r="A111" s="535"/>
+      <c r="B111" s="535"/>
+      <c r="C111" s="535"/>
+      <c r="D111" s="535"/>
+      <c r="E111" s="535"/>
+      <c r="F111" s="543"/>
+      <c r="G111" s="548"/>
+      <c r="H111" s="500"/>
+      <c r="I111" s="501"/>
+      <c r="J111" s="501"/>
+      <c r="K111" s="502"/>
       <c r="L111" s="10"/>
       <c r="M111" s="10"/>
       <c r="N111" s="10"/>
-      <c r="O111" s="154"/>
-      <c r="P111" s="43"/>
-      <c r="Q111" s="172"/>
+      <c r="O111" s="153"/>
+      <c r="P111" s="42"/>
+      <c r="Q111" s="171"/>
       <c r="R111" s="10"/>
-      <c r="S111" s="154"/>
-      <c r="T111" s="502"/>
-      <c r="U111" s="502"/>
-      <c r="V111" s="502"/>
-      <c r="W111" s="504"/>
+      <c r="S111" s="153"/>
+      <c r="T111" s="501"/>
+      <c r="U111" s="501"/>
+      <c r="V111" s="501"/>
+      <c r="W111" s="503"/>
       <c r="X111" s="10"/>
       <c r="Y111" s="10"/>
       <c r="Z111" s="10"/>
       <c r="AA111" s="10"/>
-      <c r="AB111" s="505"/>
-      <c r="AC111" s="502"/>
-      <c r="AD111" s="502"/>
-      <c r="AE111" s="502"/>
-      <c r="AF111" s="135"/>
-      <c r="AG111" s="67"/>
-      <c r="AH111" s="67"/>
-      <c r="AI111" s="78"/>
-      <c r="AJ111" s="151"/>
+      <c r="AB111" s="504"/>
+      <c r="AC111" s="501"/>
+      <c r="AD111" s="501"/>
+      <c r="AE111" s="501"/>
+      <c r="AF111" s="134"/>
+      <c r="AG111" s="66"/>
+      <c r="AH111" s="66"/>
+      <c r="AI111" s="77"/>
+      <c r="AJ111" s="150"/>
       <c r="AK111" s="6"/>
       <c r="AL111" s="6"/>
       <c r="AM111" s="6"/>
@@ -31298,42 +31338,42 @@
       <c r="HW111" s="6"/>
     </row>
     <row r="112" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A112" s="537"/>
-      <c r="B112" s="537"/>
-      <c r="C112" s="537"/>
-      <c r="D112" s="537"/>
-      <c r="E112" s="537"/>
-      <c r="F112" s="544"/>
-      <c r="G112" s="555"/>
-      <c r="H112" s="506"/>
-      <c r="I112" s="507"/>
-      <c r="J112" s="508"/>
-      <c r="K112" s="509"/>
-      <c r="L112" s="47"/>
-      <c r="M112" s="47"/>
-      <c r="N112" s="136"/>
-      <c r="O112" s="510"/>
-      <c r="P112" s="511"/>
-      <c r="Q112" s="136"/>
-      <c r="R112" s="136"/>
-      <c r="S112" s="510"/>
-      <c r="T112" s="512"/>
-      <c r="U112" s="512"/>
-      <c r="V112" s="512"/>
-      <c r="W112" s="513"/>
-      <c r="X112" s="507"/>
-      <c r="Y112" s="507"/>
-      <c r="Z112" s="507"/>
-      <c r="AA112" s="507"/>
-      <c r="AB112" s="514"/>
-      <c r="AC112" s="507"/>
-      <c r="AD112" s="508"/>
-      <c r="AE112" s="512"/>
-      <c r="AF112" s="515"/>
-      <c r="AG112" s="88"/>
-      <c r="AH112" s="88"/>
-      <c r="AI112" s="98"/>
-      <c r="AJ112" s="151"/>
+      <c r="A112" s="536"/>
+      <c r="B112" s="536"/>
+      <c r="C112" s="536"/>
+      <c r="D112" s="536"/>
+      <c r="E112" s="536"/>
+      <c r="F112" s="543"/>
+      <c r="G112" s="554"/>
+      <c r="H112" s="505"/>
+      <c r="I112" s="506"/>
+      <c r="J112" s="507"/>
+      <c r="K112" s="508"/>
+      <c r="L112" s="46"/>
+      <c r="M112" s="46"/>
+      <c r="N112" s="135"/>
+      <c r="O112" s="509"/>
+      <c r="P112" s="510"/>
+      <c r="Q112" s="135"/>
+      <c r="R112" s="135"/>
+      <c r="S112" s="509"/>
+      <c r="T112" s="511"/>
+      <c r="U112" s="511"/>
+      <c r="V112" s="511"/>
+      <c r="W112" s="512"/>
+      <c r="X112" s="506"/>
+      <c r="Y112" s="506"/>
+      <c r="Z112" s="506"/>
+      <c r="AA112" s="506"/>
+      <c r="AB112" s="513"/>
+      <c r="AC112" s="506"/>
+      <c r="AD112" s="507"/>
+      <c r="AE112" s="511"/>
+      <c r="AF112" s="514"/>
+      <c r="AG112" s="87"/>
+      <c r="AH112" s="87"/>
+      <c r="AI112" s="97"/>
+      <c r="AJ112" s="150"/>
       <c r="AK112" s="6"/>
       <c r="AL112" s="6"/>
       <c r="AM112" s="6"/>
@@ -31531,44 +31571,44 @@
       <c r="HW112" s="6"/>
     </row>
     <row r="113" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A113" s="542"/>
-      <c r="B113" s="542"/>
-      <c r="C113" s="542"/>
-      <c r="D113" s="542"/>
-      <c r="E113" s="542"/>
-      <c r="F113" s="544"/>
-      <c r="G113" s="607" t="s">
+      <c r="A113" s="541"/>
+      <c r="B113" s="541"/>
+      <c r="C113" s="541"/>
+      <c r="D113" s="541"/>
+      <c r="E113" s="541"/>
+      <c r="F113" s="543"/>
+      <c r="G113" s="606" t="s">
         <v>25</v>
       </c>
-      <c r="H113" s="501"/>
-      <c r="I113" s="502"/>
-      <c r="J113" s="220"/>
-      <c r="K113" s="516"/>
-      <c r="L113" s="220"/>
-      <c r="M113" s="220"/>
-      <c r="N113" s="172"/>
-      <c r="O113" s="154"/>
-      <c r="P113" s="517"/>
-      <c r="Q113" s="220"/>
-      <c r="R113" s="220"/>
-      <c r="S113" s="219"/>
-      <c r="T113" s="220"/>
-      <c r="U113" s="220"/>
-      <c r="V113" s="220"/>
-      <c r="W113" s="219"/>
-      <c r="X113" s="220"/>
-      <c r="Y113" s="220"/>
-      <c r="Z113" s="220"/>
-      <c r="AA113" s="220"/>
-      <c r="AB113" s="505"/>
-      <c r="AC113" s="502"/>
-      <c r="AD113" s="220"/>
-      <c r="AE113" s="220"/>
-      <c r="AF113" s="505"/>
-      <c r="AG113" s="502"/>
-      <c r="AH113" s="220"/>
-      <c r="AI113" s="219"/>
-      <c r="AJ113" s="151"/>
+      <c r="H113" s="500"/>
+      <c r="I113" s="501"/>
+      <c r="J113" s="219"/>
+      <c r="K113" s="515"/>
+      <c r="L113" s="219"/>
+      <c r="M113" s="219"/>
+      <c r="N113" s="171"/>
+      <c r="O113" s="153"/>
+      <c r="P113" s="516"/>
+      <c r="Q113" s="219"/>
+      <c r="R113" s="219"/>
+      <c r="S113" s="218"/>
+      <c r="T113" s="219"/>
+      <c r="U113" s="219"/>
+      <c r="V113" s="219"/>
+      <c r="W113" s="218"/>
+      <c r="X113" s="219"/>
+      <c r="Y113" s="219"/>
+      <c r="Z113" s="219"/>
+      <c r="AA113" s="219"/>
+      <c r="AB113" s="504"/>
+      <c r="AC113" s="501"/>
+      <c r="AD113" s="219"/>
+      <c r="AE113" s="219"/>
+      <c r="AF113" s="504"/>
+      <c r="AG113" s="501"/>
+      <c r="AH113" s="219"/>
+      <c r="AI113" s="218"/>
+      <c r="AJ113" s="150"/>
       <c r="AK113" s="6"/>
       <c r="AL113" s="6"/>
       <c r="AM113" s="6"/>
@@ -31766,42 +31806,42 @@
       <c r="HW113" s="6"/>
     </row>
     <row r="114" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A114" s="536"/>
-      <c r="B114" s="536"/>
-      <c r="C114" s="536"/>
-      <c r="D114" s="536"/>
-      <c r="E114" s="536"/>
-      <c r="F114" s="544"/>
-      <c r="G114" s="549"/>
-      <c r="H114" s="501"/>
-      <c r="I114" s="502"/>
-      <c r="J114" s="220"/>
-      <c r="K114" s="516"/>
-      <c r="L114" s="220"/>
-      <c r="M114" s="220"/>
+      <c r="A114" s="535"/>
+      <c r="B114" s="535"/>
+      <c r="C114" s="535"/>
+      <c r="D114" s="535"/>
+      <c r="E114" s="535"/>
+      <c r="F114" s="543"/>
+      <c r="G114" s="548"/>
+      <c r="H114" s="500"/>
+      <c r="I114" s="501"/>
+      <c r="J114" s="219"/>
+      <c r="K114" s="515"/>
+      <c r="L114" s="219"/>
+      <c r="M114" s="219"/>
       <c r="N114" s="10"/>
-      <c r="O114" s="154"/>
-      <c r="P114" s="517"/>
-      <c r="Q114" s="220"/>
-      <c r="R114" s="220"/>
-      <c r="S114" s="219"/>
-      <c r="T114" s="220"/>
-      <c r="U114" s="220"/>
-      <c r="V114" s="220"/>
-      <c r="W114" s="219"/>
-      <c r="X114" s="217"/>
-      <c r="Y114" s="217"/>
-      <c r="Z114" s="217"/>
-      <c r="AA114" s="217"/>
-      <c r="AB114" s="505"/>
-      <c r="AC114" s="502"/>
-      <c r="AD114" s="220"/>
-      <c r="AE114" s="220"/>
-      <c r="AF114" s="505"/>
-      <c r="AG114" s="502"/>
-      <c r="AH114" s="220"/>
-      <c r="AI114" s="219"/>
-      <c r="AJ114" s="151"/>
+      <c r="O114" s="153"/>
+      <c r="P114" s="516"/>
+      <c r="Q114" s="219"/>
+      <c r="R114" s="219"/>
+      <c r="S114" s="218"/>
+      <c r="T114" s="219"/>
+      <c r="U114" s="219"/>
+      <c r="V114" s="219"/>
+      <c r="W114" s="218"/>
+      <c r="X114" s="216"/>
+      <c r="Y114" s="216"/>
+      <c r="Z114" s="216"/>
+      <c r="AA114" s="216"/>
+      <c r="AB114" s="504"/>
+      <c r="AC114" s="501"/>
+      <c r="AD114" s="219"/>
+      <c r="AE114" s="219"/>
+      <c r="AF114" s="504"/>
+      <c r="AG114" s="501"/>
+      <c r="AH114" s="219"/>
+      <c r="AI114" s="218"/>
+      <c r="AJ114" s="150"/>
       <c r="AK114" s="6"/>
       <c r="AL114" s="6"/>
       <c r="AM114" s="6"/>
@@ -31999,42 +32039,42 @@
       <c r="HW114" s="6"/>
     </row>
     <row r="115" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A115" s="537"/>
-      <c r="B115" s="537"/>
-      <c r="C115" s="537"/>
-      <c r="D115" s="537"/>
-      <c r="E115" s="537"/>
-      <c r="F115" s="544"/>
-      <c r="G115" s="608"/>
-      <c r="H115" s="518"/>
-      <c r="I115" s="519"/>
-      <c r="J115" s="520"/>
-      <c r="K115" s="521"/>
-      <c r="L115" s="520"/>
-      <c r="M115" s="520"/>
-      <c r="N115" s="175"/>
-      <c r="O115" s="522"/>
-      <c r="P115" s="517"/>
-      <c r="Q115" s="220"/>
-      <c r="R115" s="220"/>
-      <c r="S115" s="219"/>
-      <c r="T115" s="220"/>
-      <c r="U115" s="220"/>
-      <c r="V115" s="220"/>
-      <c r="W115" s="219"/>
-      <c r="X115" s="217"/>
-      <c r="Y115" s="217"/>
-      <c r="Z115" s="220"/>
-      <c r="AA115" s="220"/>
-      <c r="AB115" s="523"/>
+      <c r="A115" s="536"/>
+      <c r="B115" s="536"/>
+      <c r="C115" s="536"/>
+      <c r="D115" s="536"/>
+      <c r="E115" s="536"/>
+      <c r="F115" s="543"/>
+      <c r="G115" s="607"/>
+      <c r="H115" s="517"/>
+      <c r="I115" s="518"/>
+      <c r="J115" s="519"/>
+      <c r="K115" s="520"/>
+      <c r="L115" s="519"/>
+      <c r="M115" s="519"/>
+      <c r="N115" s="174"/>
+      <c r="O115" s="521"/>
+      <c r="P115" s="516"/>
+      <c r="Q115" s="219"/>
+      <c r="R115" s="219"/>
+      <c r="S115" s="218"/>
+      <c r="T115" s="219"/>
+      <c r="U115" s="219"/>
+      <c r="V115" s="219"/>
+      <c r="W115" s="218"/>
+      <c r="X115" s="216"/>
+      <c r="Y115" s="216"/>
+      <c r="Z115" s="219"/>
+      <c r="AA115" s="219"/>
+      <c r="AB115" s="522"/>
       <c r="AC115" s="8"/>
-      <c r="AD115" s="220"/>
-      <c r="AE115" s="220"/>
-      <c r="AF115" s="523"/>
+      <c r="AD115" s="219"/>
+      <c r="AE115" s="219"/>
+      <c r="AF115" s="522"/>
       <c r="AG115" s="8"/>
-      <c r="AH115" s="220"/>
-      <c r="AI115" s="219"/>
-      <c r="AJ115" s="151"/>
+      <c r="AH115" s="219"/>
+      <c r="AI115" s="218"/>
+      <c r="AJ115" s="150"/>
       <c r="AK115" s="6"/>
       <c r="AL115" s="6"/>
       <c r="AM115" s="6"/>
@@ -32232,65 +32272,65 @@
       <c r="HW115" s="6"/>
     </row>
     <row r="116" spans="1:231" ht="80.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
-      <c r="A116" s="524" t="s">
+      <c r="A116" s="523" t="s">
         <v>5</v>
       </c>
-      <c r="B116" s="524" t="s">
+      <c r="B116" s="523" t="s">
         <v>6</v>
       </c>
-      <c r="C116" s="524" t="s">
+      <c r="C116" s="523" t="s">
         <v>7</v>
       </c>
-      <c r="D116" s="524" t="s">
+      <c r="D116" s="523" t="s">
         <v>8</v>
       </c>
-      <c r="E116" s="524" t="s">
+      <c r="E116" s="523" t="s">
         <v>9</v>
       </c>
-      <c r="F116" s="525"/>
-      <c r="G116" s="526"/>
-      <c r="H116" s="599" t="s">
+      <c r="F116" s="524"/>
+      <c r="G116" s="525"/>
+      <c r="H116" s="598" t="s">
         <v>10</v>
       </c>
-      <c r="I116" s="558"/>
-      <c r="J116" s="558"/>
-      <c r="K116" s="597"/>
-      <c r="L116" s="557" t="s">
+      <c r="I116" s="557"/>
+      <c r="J116" s="557"/>
+      <c r="K116" s="596"/>
+      <c r="L116" s="556" t="s">
         <v>11</v>
       </c>
-      <c r="M116" s="558"/>
-      <c r="N116" s="558"/>
-      <c r="O116" s="559"/>
-      <c r="P116" s="605" t="s">
+      <c r="M116" s="557"/>
+      <c r="N116" s="557"/>
+      <c r="O116" s="558"/>
+      <c r="P116" s="604" t="s">
         <v>12</v>
       </c>
-      <c r="Q116" s="558"/>
-      <c r="R116" s="558"/>
-      <c r="S116" s="559"/>
-      <c r="T116" s="606" t="s">
+      <c r="Q116" s="557"/>
+      <c r="R116" s="557"/>
+      <c r="S116" s="558"/>
+      <c r="T116" s="605" t="s">
         <v>13</v>
       </c>
-      <c r="U116" s="558"/>
-      <c r="V116" s="558"/>
-      <c r="W116" s="597"/>
-      <c r="X116" s="586" t="s">
+      <c r="U116" s="557"/>
+      <c r="V116" s="557"/>
+      <c r="W116" s="596"/>
+      <c r="X116" s="585" t="s">
         <v>14</v>
       </c>
-      <c r="Y116" s="558"/>
-      <c r="Z116" s="558"/>
-      <c r="AA116" s="558"/>
-      <c r="AB116" s="605" t="s">
+      <c r="Y116" s="557"/>
+      <c r="Z116" s="557"/>
+      <c r="AA116" s="557"/>
+      <c r="AB116" s="604" t="s">
         <v>15</v>
       </c>
-      <c r="AC116" s="558"/>
-      <c r="AD116" s="558"/>
-      <c r="AE116" s="559"/>
-      <c r="AF116" s="582" t="s">
+      <c r="AC116" s="557"/>
+      <c r="AD116" s="557"/>
+      <c r="AE116" s="558"/>
+      <c r="AF116" s="581" t="s">
         <v>16</v>
       </c>
-      <c r="AG116" s="558"/>
-      <c r="AH116" s="558"/>
-      <c r="AI116" s="583"/>
+      <c r="AG116" s="557"/>
+      <c r="AH116" s="557"/>
+      <c r="AI116" s="582"/>
       <c r="AJ116" s="6"/>
       <c r="AK116" s="6"/>
       <c r="AL116" s="6"/>
@@ -32724,7 +32764,7 @@
       <c r="HW117" s="6"/>
     </row>
     <row r="118" spans="1:231" ht="36.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A118" s="527" t="s">
+      <c r="A118" s="526" t="s">
         <v>33</v>
       </c>
       <c r="B118" s="1"/>
@@ -33107,7 +33147,17 @@
     <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="354">
+  <mergeCells count="362">
+    <mergeCell ref="AD61:AE61"/>
+    <mergeCell ref="AB47:AC47"/>
+    <mergeCell ref="AB48:AC48"/>
+    <mergeCell ref="AB49:AC49"/>
+    <mergeCell ref="AB50:AC50"/>
+    <mergeCell ref="AB52:AC52"/>
+    <mergeCell ref="AD56:AE56"/>
+    <mergeCell ref="AD57:AE57"/>
+    <mergeCell ref="AD58:AE58"/>
+    <mergeCell ref="AD59:AE59"/>
     <mergeCell ref="AB68:AE68"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="N55:O55"/>
@@ -33121,7 +33171,6 @@
     <mergeCell ref="G32:G34"/>
     <mergeCell ref="J40:K40"/>
     <mergeCell ref="AB41:AE41"/>
-    <mergeCell ref="AB53:AE53"/>
     <mergeCell ref="D86:D88"/>
     <mergeCell ref="E41:E43"/>
     <mergeCell ref="A77:A79"/>
@@ -33292,7 +33341,6 @@
     <mergeCell ref="R21:S21"/>
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="P116:S116"/>
-    <mergeCell ref="AB56:AE56"/>
     <mergeCell ref="G83:G85"/>
     <mergeCell ref="B74:B76"/>
     <mergeCell ref="T116:W116"/>

--- a/tests/test_data/ОН_ФЭВТ_4 курс 2023 lessons.xlsx
+++ b/tests/test_data/ОН_ФЭВТ_4 курс 2023 lessons.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D\Work\YDev\EOS\vstu-xls\vstu_xls\tests\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D1211F-3E96-49AB-B050-F7FD3D52421F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1119AA81-16F3-4E9E-A482-BD9C3667D786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
   <si>
     <t xml:space="preserve">    УТВЕРЖДАЮ:</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>???????</t>
+  </si>
+  <si>
+    <t>ЛР</t>
+  </si>
+  <si>
+    <t>ЛЕК</t>
   </si>
 </sst>
 </file>
@@ -2230,7 +2236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="680">
+  <cellXfs count="681">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -4161,572 +4167,575 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="127" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="89" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="134" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="123" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="129" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="127" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="132" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="117" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="131" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="133" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="124" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -5036,14 +5045,16 @@
   <cols>
     <col min="1" max="3" width="7.86328125" customWidth="1"/>
     <col min="4" max="6" width="7.6640625" customWidth="1"/>
-    <col min="7" max="34" width="9.6640625" customWidth="1"/>
+    <col min="7" max="30" width="9.6640625" customWidth="1"/>
+    <col min="31" max="31" width="12.86328125" customWidth="1"/>
+    <col min="32" max="34" width="9.6640625" customWidth="1"/>
     <col min="35" max="35" width="11.33203125" customWidth="1"/>
     <col min="36" max="36" width="7.86328125" customWidth="1"/>
     <col min="37" max="144" width="10.6640625" customWidth="1"/>
     <col min="145" max="256" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:231" ht="33" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:231" ht="12" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5077,10 +5088,10 @@
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
-      <c r="AF1" s="583"/>
-      <c r="AG1" s="533"/>
-      <c r="AH1" s="533"/>
-      <c r="AI1" s="533"/>
+      <c r="AF1" s="659"/>
+      <c r="AG1" s="563"/>
+      <c r="AH1" s="563"/>
+      <c r="AI1" s="563"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="6"/>
       <c r="AL1" s="6"/>
@@ -5278,7 +5289,7 @@
       <c r="HV1" s="6"/>
       <c r="HW1" s="6"/>
     </row>
-    <row r="2" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:231" ht="8.65" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5513,7 +5524,7 @@
       <c r="HV2" s="6"/>
       <c r="HW2" s="6"/>
     </row>
-    <row r="3" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:231" ht="10.5" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -5750,7 +5761,7 @@
       <c r="HV3" s="9"/>
       <c r="HW3" s="9"/>
     </row>
-    <row r="4" spans="1:231" ht="32.25" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:231" ht="12" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -6236,48 +6247,48 @@
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="13"/>
-      <c r="H6" s="597" t="s">
+      <c r="H6" s="656" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="557"/>
-      <c r="J6" s="557"/>
-      <c r="K6" s="557"/>
-      <c r="L6" s="604" t="s">
+      <c r="I6" s="587"/>
+      <c r="J6" s="587"/>
+      <c r="K6" s="587"/>
+      <c r="L6" s="586" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="557"/>
-      <c r="N6" s="557"/>
-      <c r="O6" s="558"/>
-      <c r="P6" s="556" t="s">
+      <c r="M6" s="587"/>
+      <c r="N6" s="587"/>
+      <c r="O6" s="588"/>
+      <c r="P6" s="629" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="557"/>
-      <c r="R6" s="557"/>
-      <c r="S6" s="558"/>
-      <c r="T6" s="595" t="s">
+      <c r="Q6" s="587"/>
+      <c r="R6" s="587"/>
+      <c r="S6" s="588"/>
+      <c r="T6" s="655" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="557"/>
-      <c r="V6" s="557"/>
-      <c r="W6" s="596"/>
-      <c r="X6" s="585" t="s">
+      <c r="U6" s="587"/>
+      <c r="V6" s="587"/>
+      <c r="W6" s="640"/>
+      <c r="X6" s="638" t="s">
         <v>14</v>
       </c>
-      <c r="Y6" s="557"/>
-      <c r="Z6" s="557"/>
-      <c r="AA6" s="557"/>
-      <c r="AB6" s="604" t="s">
+      <c r="Y6" s="587"/>
+      <c r="Z6" s="587"/>
+      <c r="AA6" s="587"/>
+      <c r="AB6" s="586" t="s">
         <v>15</v>
       </c>
-      <c r="AC6" s="557"/>
-      <c r="AD6" s="557"/>
-      <c r="AE6" s="558"/>
-      <c r="AF6" s="589" t="s">
+      <c r="AC6" s="587"/>
+      <c r="AD6" s="587"/>
+      <c r="AE6" s="588"/>
+      <c r="AF6" s="648" t="s">
         <v>16</v>
       </c>
-      <c r="AG6" s="557"/>
-      <c r="AH6" s="557"/>
-      <c r="AI6" s="582"/>
+      <c r="AG6" s="587"/>
+      <c r="AH6" s="587"/>
+      <c r="AI6" s="649"/>
       <c r="AJ6" s="14"/>
       <c r="AK6" s="6"/>
       <c r="AL6" s="6"/>
@@ -6709,15 +6720,15 @@
       <c r="HW7" s="6"/>
     </row>
     <row r="8" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="537"/>
-      <c r="B8" s="537"/>
-      <c r="C8" s="537"/>
-      <c r="D8" s="537"/>
-      <c r="E8" s="537"/>
-      <c r="F8" s="592" t="s">
+      <c r="A8" s="602"/>
+      <c r="B8" s="602"/>
+      <c r="C8" s="602"/>
+      <c r="D8" s="602"/>
+      <c r="E8" s="602"/>
+      <c r="F8" s="652" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="625" t="s">
+      <c r="G8" s="595" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="279"/>
@@ -6946,13 +6957,13 @@
       <c r="HW8" s="6"/>
     </row>
     <row r="9" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="535"/>
-      <c r="B9" s="535"/>
-      <c r="C9" s="535"/>
-      <c r="D9" s="535"/>
-      <c r="E9" s="535"/>
-      <c r="F9" s="593"/>
-      <c r="G9" s="548"/>
+      <c r="A9" s="570"/>
+      <c r="B9" s="570"/>
+      <c r="C9" s="570"/>
+      <c r="D9" s="570"/>
+      <c r="E9" s="570"/>
+      <c r="F9" s="653"/>
+      <c r="G9" s="580"/>
       <c r="H9" s="263"/>
       <c r="I9" s="53"/>
       <c r="J9" s="53"/>
@@ -7179,13 +7190,13 @@
       <c r="HW9" s="6"/>
     </row>
     <row r="10" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="536"/>
-      <c r="B10" s="536"/>
-      <c r="C10" s="536"/>
-      <c r="D10" s="536"/>
-      <c r="E10" s="536"/>
-      <c r="F10" s="593"/>
-      <c r="G10" s="554"/>
+      <c r="A10" s="571"/>
+      <c r="B10" s="571"/>
+      <c r="C10" s="571"/>
+      <c r="D10" s="571"/>
+      <c r="E10" s="571"/>
+      <c r="F10" s="653"/>
+      <c r="G10" s="592"/>
       <c r="H10" s="285"/>
       <c r="I10" s="92"/>
       <c r="J10" s="92"/>
@@ -7412,21 +7423,21 @@
       <c r="HW10" s="6"/>
     </row>
     <row r="11" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="628">
+      <c r="A11" s="614">
         <v>7</v>
       </c>
-      <c r="B11" s="538">
+      <c r="B11" s="585">
         <v>6</v>
       </c>
-      <c r="C11" s="538">
+      <c r="C11" s="585">
         <v>3</v>
       </c>
-      <c r="D11" s="538">
+      <c r="D11" s="585">
         <v>1</v>
       </c>
-      <c r="E11" s="540"/>
-      <c r="F11" s="593"/>
-      <c r="G11" s="560" t="s">
+      <c r="E11" s="569"/>
+      <c r="F11" s="653"/>
+      <c r="G11" s="591" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="263"/>
@@ -7655,13 +7666,13 @@
       <c r="HW11" s="6"/>
     </row>
     <row r="12" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="535"/>
-      <c r="B12" s="535"/>
-      <c r="C12" s="535"/>
-      <c r="D12" s="535"/>
-      <c r="E12" s="535"/>
-      <c r="F12" s="593"/>
-      <c r="G12" s="548"/>
+      <c r="A12" s="570"/>
+      <c r="B12" s="570"/>
+      <c r="C12" s="570"/>
+      <c r="D12" s="570"/>
+      <c r="E12" s="570"/>
+      <c r="F12" s="653"/>
+      <c r="G12" s="580"/>
       <c r="H12" s="263"/>
       <c r="I12" s="53"/>
       <c r="J12" s="53"/>
@@ -7888,13 +7899,13 @@
       <c r="HW12" s="6"/>
     </row>
     <row r="13" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="536"/>
-      <c r="B13" s="536"/>
-      <c r="C13" s="536"/>
-      <c r="D13" s="536"/>
-      <c r="E13" s="536"/>
-      <c r="F13" s="593"/>
-      <c r="G13" s="554"/>
+      <c r="A13" s="571"/>
+      <c r="B13" s="571"/>
+      <c r="C13" s="571"/>
+      <c r="D13" s="571"/>
+      <c r="E13" s="571"/>
+      <c r="F13" s="653"/>
+      <c r="G13" s="592"/>
       <c r="H13" s="260"/>
       <c r="I13" s="69"/>
       <c r="J13" s="69"/>
@@ -8121,61 +8132,67 @@
       <c r="HW13" s="6"/>
     </row>
     <row r="14" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="538">
+      <c r="A14" s="585">
         <v>20</v>
       </c>
-      <c r="B14" s="538">
+      <c r="B14" s="585">
         <v>20</v>
       </c>
-      <c r="C14" s="538">
+      <c r="C14" s="585">
         <v>17</v>
       </c>
-      <c r="D14" s="538">
+      <c r="D14" s="585">
         <v>15</v>
       </c>
-      <c r="E14" s="540"/>
-      <c r="F14" s="593"/>
-      <c r="G14" s="566" t="s">
+      <c r="E14" s="569"/>
+      <c r="F14" s="653"/>
+      <c r="G14" s="630" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="256"/>
       <c r="I14" s="57"/>
       <c r="J14" s="57"/>
       <c r="K14" s="257"/>
-      <c r="L14" s="563"/>
-      <c r="M14" s="529"/>
+      <c r="L14" s="555"/>
+      <c r="M14" s="556"/>
       <c r="N14" s="183"/>
       <c r="O14" s="163"/>
-      <c r="P14" s="527"/>
-      <c r="Q14" s="529"/>
+      <c r="P14" s="628"/>
+      <c r="Q14" s="556"/>
       <c r="R14" s="301"/>
       <c r="S14" s="302"/>
-      <c r="T14" s="564" t="s">
+      <c r="T14" s="661" t="s">
         <v>45</v>
       </c>
-      <c r="U14" s="565"/>
-      <c r="V14" s="565"/>
-      <c r="W14" s="565"/>
-      <c r="X14" s="631" t="s">
+      <c r="U14" s="604"/>
+      <c r="V14" s="604"/>
+      <c r="W14" s="604"/>
+      <c r="X14" s="611" t="s">
         <v>42</v>
       </c>
-      <c r="Y14" s="565"/>
-      <c r="Z14" s="565"/>
-      <c r="AA14" s="632"/>
-      <c r="AB14" s="563" t="s">
+      <c r="Y14" s="604"/>
+      <c r="Z14" s="604"/>
+      <c r="AA14" s="612"/>
+      <c r="AB14" s="555" t="s">
         <v>46</v>
       </c>
-      <c r="AC14" s="528"/>
-      <c r="AD14" s="528"/>
-      <c r="AE14" s="529"/>
+      <c r="AC14" s="562"/>
+      <c r="AD14" s="562"/>
+      <c r="AE14" s="556"/>
       <c r="AF14" s="26"/>
       <c r="AG14" s="26"/>
       <c r="AH14" s="26"/>
       <c r="AI14" s="166"/>
       <c r="AJ14" s="156"/>
-      <c r="AK14" s="6"/>
-      <c r="AL14" s="6"/>
-      <c r="AM14" s="6"/>
+      <c r="AK14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL14" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM14" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="AN14" s="6"/>
       <c r="AO14" s="6"/>
       <c r="AP14" s="6"/>
@@ -8370,23 +8387,23 @@
       <c r="HW14" s="6"/>
     </row>
     <row r="15" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A15" s="535"/>
-      <c r="B15" s="535"/>
-      <c r="C15" s="535"/>
-      <c r="D15" s="535"/>
-      <c r="E15" s="535"/>
-      <c r="F15" s="593"/>
-      <c r="G15" s="548"/>
+      <c r="A15" s="570"/>
+      <c r="B15" s="570"/>
+      <c r="C15" s="570"/>
+      <c r="D15" s="570"/>
+      <c r="E15" s="570"/>
+      <c r="F15" s="653"/>
+      <c r="G15" s="580"/>
       <c r="H15" s="303"/>
       <c r="I15" s="83"/>
       <c r="J15" s="83"/>
       <c r="K15" s="259"/>
-      <c r="L15" s="568"/>
-      <c r="M15" s="531"/>
+      <c r="L15" s="596"/>
+      <c r="M15" s="554"/>
       <c r="N15" s="64"/>
       <c r="O15" s="243"/>
-      <c r="P15" s="550"/>
-      <c r="Q15" s="531"/>
+      <c r="P15" s="600"/>
+      <c r="Q15" s="554"/>
       <c r="R15" s="164"/>
       <c r="S15" s="61"/>
       <c r="T15" s="212"/>
@@ -8406,9 +8423,15 @@
       <c r="AH15" s="26"/>
       <c r="AI15" s="166"/>
       <c r="AJ15" s="156"/>
-      <c r="AK15" s="6"/>
-      <c r="AL15" s="6"/>
-      <c r="AM15" s="6"/>
+      <c r="AK15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AL15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AM15" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="AN15" s="6"/>
       <c r="AO15" s="6"/>
       <c r="AP15" s="6"/>
@@ -8603,23 +8626,23 @@
       <c r="HW15" s="6"/>
     </row>
     <row r="16" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A16" s="536"/>
-      <c r="B16" s="536"/>
-      <c r="C16" s="536"/>
-      <c r="D16" s="536"/>
-      <c r="E16" s="536"/>
-      <c r="F16" s="593"/>
-      <c r="G16" s="567"/>
+      <c r="A16" s="571"/>
+      <c r="B16" s="571"/>
+      <c r="C16" s="571"/>
+      <c r="D16" s="571"/>
+      <c r="E16" s="571"/>
+      <c r="F16" s="653"/>
+      <c r="G16" s="631"/>
       <c r="H16" s="304"/>
       <c r="I16" s="305"/>
       <c r="J16" s="305"/>
       <c r="K16" s="306"/>
-      <c r="L16" s="580"/>
-      <c r="M16" s="531"/>
+      <c r="L16" s="558"/>
+      <c r="M16" s="554"/>
       <c r="N16" s="307"/>
       <c r="O16" s="308"/>
-      <c r="P16" s="555"/>
-      <c r="Q16" s="531"/>
+      <c r="P16" s="608"/>
+      <c r="Q16" s="554"/>
       <c r="R16" s="309"/>
       <c r="S16" s="214"/>
       <c r="T16" s="310" t="s">
@@ -8848,55 +8871,55 @@
       <c r="HW16" s="6"/>
     </row>
     <row r="17" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="540">
+      <c r="A17" s="569">
         <v>0</v>
       </c>
-      <c r="B17" s="540">
+      <c r="B17" s="569">
         <v>0</v>
       </c>
-      <c r="C17" s="540">
+      <c r="C17" s="569">
         <v>0</v>
       </c>
-      <c r="D17" s="538">
+      <c r="D17" s="585">
         <v>29</v>
       </c>
-      <c r="E17" s="540">
+      <c r="E17" s="569">
         <v>0</v>
       </c>
-      <c r="F17" s="593"/>
-      <c r="G17" s="569" t="s">
+      <c r="F17" s="653"/>
+      <c r="G17" s="610" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="316"/>
       <c r="I17" s="317"/>
       <c r="J17" s="317"/>
       <c r="K17" s="318"/>
-      <c r="L17" s="546"/>
-      <c r="M17" s="531"/>
+      <c r="L17" s="559"/>
+      <c r="M17" s="554"/>
       <c r="N17" s="81"/>
       <c r="O17" s="319"/>
-      <c r="P17" s="559"/>
-      <c r="Q17" s="531"/>
+      <c r="P17" s="607"/>
+      <c r="Q17" s="554"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
-      <c r="T17" s="599" t="s">
+      <c r="T17" s="641" t="s">
         <v>43</v>
       </c>
-      <c r="U17" s="533"/>
-      <c r="V17" s="533"/>
-      <c r="W17" s="533"/>
-      <c r="X17" s="571" t="s">
+      <c r="U17" s="563"/>
+      <c r="V17" s="563"/>
+      <c r="W17" s="563"/>
+      <c r="X17" s="601" t="s">
         <v>44</v>
       </c>
-      <c r="Y17" s="533"/>
-      <c r="Z17" s="533"/>
-      <c r="AA17" s="531"/>
-      <c r="AB17" s="616" t="s">
+      <c r="Y17" s="563"/>
+      <c r="Z17" s="563"/>
+      <c r="AA17" s="554"/>
+      <c r="AB17" s="618" t="s">
         <v>47</v>
       </c>
-      <c r="AC17" s="617"/>
-      <c r="AD17" s="617"/>
-      <c r="AE17" s="618"/>
+      <c r="AC17" s="619"/>
+      <c r="AD17" s="619"/>
+      <c r="AE17" s="620"/>
       <c r="AF17" s="320"/>
       <c r="AG17" s="320"/>
       <c r="AH17" s="320"/>
@@ -9099,13 +9122,13 @@
       <c r="HW17" s="6"/>
     </row>
     <row r="18" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="535"/>
-      <c r="B18" s="535"/>
-      <c r="C18" s="535"/>
-      <c r="D18" s="535"/>
-      <c r="E18" s="535"/>
-      <c r="F18" s="593"/>
-      <c r="G18" s="548"/>
+      <c r="A18" s="570"/>
+      <c r="B18" s="570"/>
+      <c r="C18" s="570"/>
+      <c r="D18" s="570"/>
+      <c r="E18" s="570"/>
+      <c r="F18" s="653"/>
+      <c r="G18" s="580"/>
       <c r="H18" s="258"/>
       <c r="I18" s="66"/>
       <c r="J18" s="66"/>
@@ -9332,23 +9355,23 @@
       <c r="HW18" s="6"/>
     </row>
     <row r="19" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A19" s="536"/>
-      <c r="B19" s="536"/>
-      <c r="C19" s="536"/>
-      <c r="D19" s="536"/>
-      <c r="E19" s="536"/>
-      <c r="F19" s="593"/>
-      <c r="G19" s="554"/>
+      <c r="A19" s="571"/>
+      <c r="B19" s="571"/>
+      <c r="C19" s="571"/>
+      <c r="D19" s="571"/>
+      <c r="E19" s="571"/>
+      <c r="F19" s="653"/>
+      <c r="G19" s="592"/>
       <c r="H19" s="322"/>
       <c r="I19" s="323"/>
       <c r="J19" s="88"/>
       <c r="K19" s="266"/>
-      <c r="L19" s="627"/>
-      <c r="M19" s="552"/>
+      <c r="L19" s="613"/>
+      <c r="M19" s="594"/>
       <c r="N19" s="115"/>
       <c r="O19" s="250"/>
-      <c r="P19" s="576"/>
-      <c r="Q19" s="552"/>
+      <c r="P19" s="665"/>
+      <c r="Q19" s="594"/>
       <c r="R19" s="195"/>
       <c r="S19" s="324"/>
       <c r="T19" s="220" t="s">
@@ -9577,13 +9600,13 @@
       <c r="HW19" s="6"/>
     </row>
     <row r="20" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="541"/>
-      <c r="B20" s="541"/>
-      <c r="C20" s="541"/>
-      <c r="D20" s="541"/>
-      <c r="E20" s="541"/>
-      <c r="F20" s="593"/>
-      <c r="G20" s="569" t="s">
+      <c r="A20" s="573"/>
+      <c r="B20" s="573"/>
+      <c r="C20" s="573"/>
+      <c r="D20" s="573"/>
+      <c r="E20" s="573"/>
+      <c r="F20" s="653"/>
+      <c r="G20" s="610" t="s">
         <v>24</v>
       </c>
       <c r="H20" s="167"/>
@@ -9592,12 +9615,12 @@
       <c r="K20" s="166"/>
       <c r="L20" s="223"/>
       <c r="M20" s="144"/>
-      <c r="N20" s="629"/>
-      <c r="O20" s="531"/>
+      <c r="N20" s="615"/>
+      <c r="O20" s="554"/>
       <c r="P20" s="156"/>
       <c r="Q20" s="157"/>
-      <c r="R20" s="584"/>
-      <c r="S20" s="533"/>
+      <c r="R20" s="660"/>
+      <c r="S20" s="563"/>
       <c r="T20" s="152"/>
       <c r="U20" s="10"/>
       <c r="V20" s="10"/>
@@ -9812,25 +9835,25 @@
       <c r="HW20" s="6"/>
     </row>
     <row r="21" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A21" s="535"/>
-      <c r="B21" s="535"/>
-      <c r="C21" s="535"/>
-      <c r="D21" s="535"/>
-      <c r="E21" s="535"/>
-      <c r="F21" s="593"/>
-      <c r="G21" s="548"/>
+      <c r="A21" s="570"/>
+      <c r="B21" s="570"/>
+      <c r="C21" s="570"/>
+      <c r="D21" s="570"/>
+      <c r="E21" s="570"/>
+      <c r="F21" s="653"/>
+      <c r="G21" s="580"/>
       <c r="H21" s="167"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
       <c r="K21" s="166"/>
       <c r="L21" s="223"/>
       <c r="M21" s="144"/>
-      <c r="N21" s="633"/>
-      <c r="O21" s="531"/>
+      <c r="N21" s="617"/>
+      <c r="O21" s="554"/>
       <c r="P21" s="156"/>
       <c r="Q21" s="157"/>
-      <c r="R21" s="603"/>
-      <c r="S21" s="533"/>
+      <c r="R21" s="557"/>
+      <c r="S21" s="563"/>
       <c r="T21" s="152"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
@@ -10045,25 +10068,25 @@
       <c r="HW21" s="6"/>
     </row>
     <row r="22" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="536"/>
-      <c r="B22" s="536"/>
-      <c r="C22" s="536"/>
-      <c r="D22" s="536"/>
-      <c r="E22" s="536"/>
-      <c r="F22" s="593"/>
-      <c r="G22" s="554"/>
+      <c r="A22" s="571"/>
+      <c r="B22" s="571"/>
+      <c r="C22" s="571"/>
+      <c r="D22" s="571"/>
+      <c r="E22" s="571"/>
+      <c r="F22" s="653"/>
+      <c r="G22" s="592"/>
       <c r="H22" s="330"/>
       <c r="I22" s="88"/>
       <c r="J22" s="88"/>
       <c r="K22" s="192"/>
       <c r="L22" s="331"/>
       <c r="M22" s="332"/>
-      <c r="N22" s="555"/>
-      <c r="O22" s="531"/>
+      <c r="N22" s="608"/>
+      <c r="O22" s="554"/>
       <c r="P22" s="333"/>
       <c r="Q22" s="334"/>
-      <c r="R22" s="570"/>
-      <c r="S22" s="533"/>
+      <c r="R22" s="564"/>
+      <c r="S22" s="563"/>
       <c r="T22" s="228"/>
       <c r="U22" s="90"/>
       <c r="V22" s="90"/>
@@ -10278,13 +10301,13 @@
       <c r="HW22" s="6"/>
     </row>
     <row r="23" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="541"/>
-      <c r="B23" s="541"/>
-      <c r="C23" s="541"/>
-      <c r="D23" s="541"/>
-      <c r="E23" s="541"/>
-      <c r="F23" s="593"/>
-      <c r="G23" s="600" t="s">
+      <c r="A23" s="573"/>
+      <c r="B23" s="573"/>
+      <c r="C23" s="573"/>
+      <c r="D23" s="573"/>
+      <c r="E23" s="573"/>
+      <c r="F23" s="653"/>
+      <c r="G23" s="609" t="s">
         <v>25</v>
       </c>
       <c r="H23" s="167"/>
@@ -10293,12 +10316,12 @@
       <c r="K23" s="166"/>
       <c r="L23" s="223"/>
       <c r="M23" s="144"/>
-      <c r="N23" s="559"/>
-      <c r="O23" s="531"/>
+      <c r="N23" s="607"/>
+      <c r="O23" s="554"/>
       <c r="P23" s="291"/>
       <c r="Q23" s="338"/>
-      <c r="R23" s="624"/>
-      <c r="S23" s="533"/>
+      <c r="R23" s="565"/>
+      <c r="S23" s="563"/>
       <c r="T23" s="287"/>
       <c r="U23" s="34"/>
       <c r="V23" s="34"/>
@@ -10513,13 +10536,13 @@
       <c r="HW23" s="6"/>
     </row>
     <row r="24" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="535"/>
-      <c r="B24" s="535"/>
-      <c r="C24" s="535"/>
-      <c r="D24" s="535"/>
-      <c r="E24" s="535"/>
-      <c r="F24" s="593"/>
-      <c r="G24" s="548"/>
+      <c r="A24" s="570"/>
+      <c r="B24" s="570"/>
+      <c r="C24" s="570"/>
+      <c r="D24" s="570"/>
+      <c r="E24" s="570"/>
+      <c r="F24" s="653"/>
+      <c r="G24" s="580"/>
       <c r="H24" s="167"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
@@ -10746,25 +10769,25 @@
       <c r="HW24" s="6"/>
     </row>
     <row r="25" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="536"/>
-      <c r="B25" s="536"/>
-      <c r="C25" s="536"/>
-      <c r="D25" s="536"/>
-      <c r="E25" s="536"/>
-      <c r="F25" s="594"/>
-      <c r="G25" s="601"/>
+      <c r="A25" s="571"/>
+      <c r="B25" s="571"/>
+      <c r="C25" s="571"/>
+      <c r="D25" s="571"/>
+      <c r="E25" s="571"/>
+      <c r="F25" s="654"/>
+      <c r="G25" s="590"/>
       <c r="H25" s="167"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
       <c r="K25" s="166"/>
       <c r="L25" s="339"/>
       <c r="M25" s="340"/>
-      <c r="N25" s="530"/>
-      <c r="O25" s="531"/>
+      <c r="N25" s="674"/>
+      <c r="O25" s="554"/>
       <c r="P25" s="341"/>
       <c r="Q25" s="342"/>
-      <c r="R25" s="532"/>
-      <c r="S25" s="533"/>
+      <c r="R25" s="677"/>
+      <c r="S25" s="563"/>
       <c r="T25" s="287"/>
       <c r="U25" s="34"/>
       <c r="V25" s="34"/>
@@ -10979,23 +11002,23 @@
       <c r="HW25" s="6"/>
     </row>
     <row r="26" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="541"/>
-      <c r="B26" s="537"/>
-      <c r="C26" s="537"/>
-      <c r="D26" s="537"/>
-      <c r="E26" s="537"/>
-      <c r="F26" s="578" t="s">
+      <c r="A26" s="573"/>
+      <c r="B26" s="602"/>
+      <c r="C26" s="602"/>
+      <c r="D26" s="602"/>
+      <c r="E26" s="602"/>
+      <c r="F26" s="669" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="553" t="s">
+      <c r="G26" s="672" t="s">
         <v>18</v>
       </c>
-      <c r="H26" s="670" t="s">
+      <c r="H26" s="597" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="533"/>
-      <c r="J26" s="533"/>
-      <c r="K26" s="533"/>
+      <c r="I26" s="563"/>
+      <c r="J26" s="563"/>
+      <c r="K26" s="563"/>
       <c r="L26" s="251"/>
       <c r="M26" s="251"/>
       <c r="N26" s="251"/>
@@ -11021,7 +11044,9 @@
       <c r="AH26" s="24"/>
       <c r="AI26" s="16"/>
       <c r="AJ26" s="142"/>
-      <c r="AK26" s="6"/>
+      <c r="AK26" s="680" t="s">
+        <v>84</v>
+      </c>
       <c r="AL26" s="6"/>
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
@@ -11218,18 +11243,18 @@
       <c r="HW26" s="6"/>
     </row>
     <row r="27" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A27" s="535"/>
-      <c r="B27" s="535"/>
-      <c r="C27" s="535"/>
-      <c r="D27" s="535"/>
-      <c r="E27" s="535"/>
-      <c r="F27" s="543"/>
-      <c r="G27" s="548"/>
-      <c r="H27" s="671"/>
-      <c r="I27" s="624" t="s">
+      <c r="A27" s="570"/>
+      <c r="B27" s="570"/>
+      <c r="C27" s="570"/>
+      <c r="D27" s="570"/>
+      <c r="E27" s="570"/>
+      <c r="F27" s="634"/>
+      <c r="G27" s="580"/>
+      <c r="H27" s="549"/>
+      <c r="I27" s="565" t="s">
         <v>56</v>
       </c>
-      <c r="J27" s="533"/>
+      <c r="J27" s="563"/>
       <c r="K27" s="64"/>
       <c r="L27" s="26"/>
       <c r="M27" s="26"/>
@@ -11453,21 +11478,21 @@
       <c r="HW27" s="6"/>
     </row>
     <row r="28" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="536"/>
-      <c r="B28" s="536"/>
-      <c r="C28" s="536"/>
-      <c r="D28" s="536"/>
-      <c r="E28" s="536"/>
-      <c r="F28" s="543"/>
-      <c r="G28" s="554"/>
-      <c r="H28" s="608" t="s">
+      <c r="A28" s="571"/>
+      <c r="B28" s="571"/>
+      <c r="C28" s="571"/>
+      <c r="D28" s="571"/>
+      <c r="E28" s="571"/>
+      <c r="F28" s="634"/>
+      <c r="G28" s="592"/>
+      <c r="H28" s="598" t="s">
         <v>75</v>
       </c>
-      <c r="I28" s="531"/>
-      <c r="J28" s="624" t="s">
+      <c r="I28" s="554"/>
+      <c r="J28" s="565" t="s">
         <v>76</v>
       </c>
-      <c r="K28" s="533"/>
+      <c r="K28" s="563"/>
       <c r="L28" s="26"/>
       <c r="M28" s="26"/>
       <c r="N28" s="26"/>
@@ -11690,31 +11715,31 @@
       <c r="HW28" s="6"/>
     </row>
     <row r="29" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A29" s="534">
+      <c r="A29" s="673">
         <v>8</v>
       </c>
-      <c r="B29" s="538">
+      <c r="B29" s="585">
         <v>7</v>
       </c>
-      <c r="C29" s="538">
+      <c r="C29" s="585">
         <v>4</v>
       </c>
-      <c r="D29" s="538">
+      <c r="D29" s="585">
         <v>2</v>
       </c>
-      <c r="E29" s="540"/>
-      <c r="F29" s="543"/>
-      <c r="G29" s="560" t="s">
+      <c r="E29" s="569"/>
+      <c r="F29" s="634"/>
+      <c r="G29" s="591" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="672" t="s">
+      <c r="H29" s="599" t="s">
         <v>77</v>
       </c>
-      <c r="I29" s="531"/>
-      <c r="J29" s="673" t="s">
+      <c r="I29" s="554"/>
+      <c r="J29" s="606" t="s">
         <v>78</v>
       </c>
-      <c r="K29" s="533"/>
+      <c r="K29" s="563"/>
       <c r="L29" s="105"/>
       <c r="M29" s="105"/>
       <c r="N29" s="105"/>
@@ -11937,14 +11962,14 @@
       <c r="HW29" s="6"/>
     </row>
     <row r="30" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="535"/>
-      <c r="B30" s="535"/>
-      <c r="C30" s="535"/>
-      <c r="D30" s="535"/>
-      <c r="E30" s="535"/>
-      <c r="F30" s="543"/>
-      <c r="G30" s="548"/>
-      <c r="H30" s="674"/>
+      <c r="A30" s="570"/>
+      <c r="B30" s="570"/>
+      <c r="C30" s="570"/>
+      <c r="D30" s="570"/>
+      <c r="E30" s="570"/>
+      <c r="F30" s="634"/>
+      <c r="G30" s="580"/>
+      <c r="H30" s="550"/>
       <c r="I30" s="85"/>
       <c r="J30" s="85"/>
       <c r="K30" s="85"/>
@@ -12170,14 +12195,14 @@
       <c r="HW30" s="6"/>
     </row>
     <row r="31" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A31" s="536"/>
-      <c r="B31" s="536"/>
-      <c r="C31" s="536"/>
-      <c r="D31" s="536"/>
-      <c r="E31" s="536"/>
-      <c r="F31" s="543"/>
-      <c r="G31" s="554"/>
-      <c r="H31" s="669" t="s">
+      <c r="A31" s="571"/>
+      <c r="B31" s="571"/>
+      <c r="C31" s="571"/>
+      <c r="D31" s="571"/>
+      <c r="E31" s="571"/>
+      <c r="F31" s="634"/>
+      <c r="G31" s="592"/>
+      <c r="H31" s="548" t="s">
         <v>79</v>
       </c>
       <c r="I31" s="135"/>
@@ -12210,7 +12235,9 @@
       <c r="AH31" s="6"/>
       <c r="AI31" s="149"/>
       <c r="AJ31" s="130"/>
-      <c r="AK31" s="6"/>
+      <c r="AK31" s="680" t="s">
+        <v>84</v>
+      </c>
       <c r="AL31" s="6"/>
       <c r="AM31" s="6"/>
       <c r="AN31" s="6"/>
@@ -12407,25 +12434,25 @@
       <c r="HW31" s="6"/>
     </row>
     <row r="32" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="538">
+      <c r="A32" s="585">
         <v>21</v>
       </c>
-      <c r="B32" s="538">
+      <c r="B32" s="585">
         <v>21</v>
       </c>
-      <c r="C32" s="538">
+      <c r="C32" s="585">
         <v>18</v>
       </c>
-      <c r="D32" s="538">
+      <c r="D32" s="585">
         <v>16</v>
       </c>
-      <c r="E32" s="540"/>
-      <c r="F32" s="543"/>
-      <c r="G32" s="639" t="s">
+      <c r="E32" s="569"/>
+      <c r="F32" s="634"/>
+      <c r="G32" s="579" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="571"/>
-      <c r="I32" s="531"/>
+      <c r="H32" s="601"/>
+      <c r="I32" s="554"/>
       <c r="J32" s="140"/>
       <c r="K32" s="141"/>
       <c r="L32" s="105"/>
@@ -12436,12 +12463,12 @@
       <c r="Q32" s="57"/>
       <c r="R32" s="57"/>
       <c r="S32" s="58"/>
-      <c r="T32" s="574" t="s">
+      <c r="T32" s="583" t="s">
         <v>70</v>
       </c>
-      <c r="U32" s="528"/>
-      <c r="V32" s="528"/>
-      <c r="W32" s="528"/>
+      <c r="U32" s="562"/>
+      <c r="V32" s="562"/>
+      <c r="W32" s="562"/>
       <c r="X32" s="355"/>
       <c r="Y32" s="356"/>
       <c r="Z32" s="356"/>
@@ -12450,10 +12477,10 @@
       <c r="AC32" s="359"/>
       <c r="AD32" s="359"/>
       <c r="AE32" s="360"/>
-      <c r="AF32" s="527"/>
-      <c r="AG32" s="528"/>
-      <c r="AH32" s="528"/>
-      <c r="AI32" s="529"/>
+      <c r="AF32" s="628"/>
+      <c r="AG32" s="562"/>
+      <c r="AH32" s="562"/>
+      <c r="AI32" s="556"/>
       <c r="AJ32" s="142"/>
       <c r="AK32" s="6"/>
       <c r="AL32" s="6"/>
@@ -12652,15 +12679,15 @@
       <c r="HW32" s="6"/>
     </row>
     <row r="33" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="535"/>
-      <c r="B33" s="535"/>
-      <c r="C33" s="535"/>
-      <c r="D33" s="535"/>
-      <c r="E33" s="535"/>
-      <c r="F33" s="543"/>
-      <c r="G33" s="548"/>
-      <c r="H33" s="568"/>
-      <c r="I33" s="531"/>
+      <c r="A33" s="570"/>
+      <c r="B33" s="570"/>
+      <c r="C33" s="570"/>
+      <c r="D33" s="570"/>
+      <c r="E33" s="570"/>
+      <c r="F33" s="634"/>
+      <c r="G33" s="580"/>
+      <c r="H33" s="596"/>
+      <c r="I33" s="554"/>
       <c r="J33" s="6"/>
       <c r="K33" s="144"/>
       <c r="L33" s="26"/>
@@ -12671,12 +12698,12 @@
       <c r="Q33" s="60"/>
       <c r="R33" s="60"/>
       <c r="S33" s="98"/>
-      <c r="T33" s="665" t="s">
+      <c r="T33" s="670" t="s">
         <v>71</v>
       </c>
-      <c r="U33" s="533"/>
-      <c r="V33" s="533"/>
-      <c r="W33" s="533"/>
+      <c r="U33" s="563"/>
+      <c r="V33" s="563"/>
+      <c r="W33" s="563"/>
       <c r="X33" s="361"/>
       <c r="Y33" s="186"/>
       <c r="Z33" s="315"/>
@@ -12887,15 +12914,15 @@
       <c r="HW33" s="6"/>
     </row>
     <row r="34" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="536"/>
-      <c r="B34" s="536"/>
-      <c r="C34" s="536"/>
-      <c r="D34" s="536"/>
-      <c r="E34" s="536"/>
-      <c r="F34" s="543"/>
-      <c r="G34" s="610"/>
-      <c r="H34" s="580"/>
-      <c r="I34" s="531"/>
+      <c r="A34" s="571"/>
+      <c r="B34" s="571"/>
+      <c r="C34" s="571"/>
+      <c r="D34" s="571"/>
+      <c r="E34" s="571"/>
+      <c r="F34" s="634"/>
+      <c r="G34" s="581"/>
+      <c r="H34" s="558"/>
+      <c r="I34" s="554"/>
       <c r="J34" s="147"/>
       <c r="K34" s="362"/>
       <c r="L34" s="148"/>
@@ -12906,11 +12933,11 @@
       <c r="Q34" s="72"/>
       <c r="R34" s="72"/>
       <c r="S34" s="99"/>
-      <c r="T34" s="666"/>
-      <c r="U34" s="570" t="s">
+      <c r="T34" s="545"/>
+      <c r="U34" s="564" t="s">
         <v>56</v>
       </c>
-      <c r="V34" s="533"/>
+      <c r="V34" s="563"/>
       <c r="W34" s="226"/>
       <c r="X34" s="363"/>
       <c r="Y34" s="315"/>
@@ -13122,25 +13149,25 @@
       <c r="HW34" s="6"/>
     </row>
     <row r="35" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A35" s="540">
+      <c r="A35" s="569">
         <v>0</v>
       </c>
-      <c r="B35" s="540">
+      <c r="B35" s="569">
         <v>0</v>
       </c>
-      <c r="C35" s="540">
+      <c r="C35" s="569">
         <v>0</v>
       </c>
-      <c r="D35" s="538">
+      <c r="D35" s="585">
         <v>30</v>
       </c>
-      <c r="E35" s="540"/>
-      <c r="F35" s="543"/>
-      <c r="G35" s="569" t="s">
+      <c r="E35" s="569"/>
+      <c r="F35" s="634"/>
+      <c r="G35" s="610" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="546"/>
-      <c r="I35" s="531"/>
+      <c r="H35" s="559"/>
+      <c r="I35" s="554"/>
       <c r="J35" s="6"/>
       <c r="K35" s="144"/>
       <c r="L35" s="53"/>
@@ -13151,7 +13178,7 @@
       <c r="Q35" s="365"/>
       <c r="R35" s="78"/>
       <c r="S35" s="79"/>
-      <c r="T35" s="667"/>
+      <c r="T35" s="546"/>
       <c r="U35" s="123"/>
       <c r="V35" s="6"/>
       <c r="W35" s="149"/>
@@ -13163,10 +13190,10 @@
       <c r="AC35" s="10"/>
       <c r="AD35" s="10"/>
       <c r="AE35" s="10"/>
-      <c r="AF35" s="562"/>
-      <c r="AG35" s="533"/>
-      <c r="AH35" s="533"/>
-      <c r="AI35" s="531"/>
+      <c r="AF35" s="622"/>
+      <c r="AG35" s="563"/>
+      <c r="AH35" s="563"/>
+      <c r="AI35" s="554"/>
       <c r="AJ35" s="150"/>
       <c r="AK35" s="6"/>
       <c r="AL35" s="6"/>
@@ -13365,13 +13392,13 @@
       <c r="HW35" s="6"/>
     </row>
     <row r="36" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="535"/>
-      <c r="B36" s="535"/>
-      <c r="C36" s="535"/>
-      <c r="D36" s="535"/>
-      <c r="E36" s="535"/>
-      <c r="F36" s="543"/>
-      <c r="G36" s="548"/>
+      <c r="A36" s="570"/>
+      <c r="B36" s="570"/>
+      <c r="C36" s="570"/>
+      <c r="D36" s="570"/>
+      <c r="E36" s="570"/>
+      <c r="F36" s="634"/>
+      <c r="G36" s="580"/>
       <c r="H36" s="223"/>
       <c r="I36" s="84"/>
       <c r="J36" s="6"/>
@@ -13384,7 +13411,7 @@
       <c r="Q36" s="83"/>
       <c r="R36" s="26"/>
       <c r="S36" s="111"/>
-      <c r="T36" s="668"/>
+      <c r="T36" s="547"/>
       <c r="U36" s="172"/>
       <c r="V36" s="6"/>
       <c r="W36" s="84"/>
@@ -13598,15 +13625,15 @@
       <c r="HW36" s="6"/>
     </row>
     <row r="37" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A37" s="536"/>
-      <c r="B37" s="536"/>
-      <c r="C37" s="536"/>
-      <c r="D37" s="536"/>
-      <c r="E37" s="536"/>
-      <c r="F37" s="543"/>
-      <c r="G37" s="554"/>
-      <c r="H37" s="634"/>
-      <c r="I37" s="552"/>
+      <c r="A37" s="571"/>
+      <c r="B37" s="571"/>
+      <c r="C37" s="571"/>
+      <c r="D37" s="571"/>
+      <c r="E37" s="571"/>
+      <c r="F37" s="634"/>
+      <c r="G37" s="592"/>
+      <c r="H37" s="593"/>
+      <c r="I37" s="594"/>
       <c r="J37" s="6"/>
       <c r="K37" s="144"/>
       <c r="L37" s="93"/>
@@ -13617,7 +13644,7 @@
       <c r="Q37" s="370"/>
       <c r="R37" s="88"/>
       <c r="S37" s="371"/>
-      <c r="T37" s="669" t="s">
+      <c r="T37" s="548" t="s">
         <v>72</v>
       </c>
       <c r="U37" s="91"/>
@@ -13835,50 +13862,54 @@
       <c r="HW37" s="6"/>
     </row>
     <row r="38" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="541"/>
-      <c r="B38" s="541"/>
-      <c r="C38" s="541"/>
-      <c r="D38" s="541"/>
-      <c r="E38" s="541"/>
-      <c r="F38" s="543"/>
-      <c r="G38" s="569" t="s">
+      <c r="A38" s="573"/>
+      <c r="B38" s="573"/>
+      <c r="C38" s="573"/>
+      <c r="D38" s="573"/>
+      <c r="E38" s="573"/>
+      <c r="F38" s="634"/>
+      <c r="G38" s="610" t="s">
         <v>24</v>
       </c>
       <c r="H38" s="223"/>
       <c r="I38" s="6"/>
-      <c r="J38" s="539"/>
-      <c r="K38" s="529"/>
+      <c r="J38" s="621"/>
+      <c r="K38" s="556"/>
       <c r="L38" s="373"/>
       <c r="M38" s="109"/>
       <c r="N38" s="109"/>
       <c r="O38" s="109"/>
       <c r="P38" s="108"/>
-      <c r="Q38" s="643"/>
-      <c r="R38" s="539" t="s">
+      <c r="Q38" s="531"/>
+      <c r="R38" s="621" t="s">
         <v>54</v>
       </c>
-      <c r="S38" s="529"/>
-      <c r="T38" s="640" t="s">
+      <c r="S38" s="556"/>
+      <c r="T38" s="603" t="s">
         <v>50</v>
       </c>
-      <c r="U38" s="565"/>
-      <c r="V38" s="565"/>
-      <c r="W38" s="565"/>
-      <c r="X38" s="565"/>
-      <c r="Y38" s="565"/>
-      <c r="Z38" s="565"/>
-      <c r="AA38" s="565"/>
-      <c r="AB38" s="574"/>
-      <c r="AC38" s="528"/>
-      <c r="AD38" s="528"/>
-      <c r="AE38" s="528"/>
-      <c r="AF38" s="587"/>
-      <c r="AG38" s="565"/>
-      <c r="AH38" s="565"/>
-      <c r="AI38" s="588"/>
+      <c r="U38" s="604"/>
+      <c r="V38" s="604"/>
+      <c r="W38" s="604"/>
+      <c r="X38" s="604"/>
+      <c r="Y38" s="604"/>
+      <c r="Z38" s="604"/>
+      <c r="AA38" s="604"/>
+      <c r="AB38" s="583"/>
+      <c r="AC38" s="562"/>
+      <c r="AD38" s="562"/>
+      <c r="AE38" s="562"/>
+      <c r="AF38" s="646"/>
+      <c r="AG38" s="604"/>
+      <c r="AH38" s="604"/>
+      <c r="AI38" s="647"/>
       <c r="AJ38" s="150"/>
-      <c r="AK38" s="6"/>
-      <c r="AL38" s="6"/>
+      <c r="AK38" s="680" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL38" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
       <c r="AO38" s="6"/>
@@ -14074,35 +14105,35 @@
       <c r="HW38" s="6"/>
     </row>
     <row r="39" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A39" s="535"/>
-      <c r="B39" s="535"/>
-      <c r="C39" s="535"/>
-      <c r="D39" s="535"/>
-      <c r="E39" s="535"/>
-      <c r="F39" s="543"/>
-      <c r="G39" s="548"/>
+      <c r="A39" s="570"/>
+      <c r="B39" s="570"/>
+      <c r="C39" s="570"/>
+      <c r="D39" s="570"/>
+      <c r="E39" s="570"/>
+      <c r="F39" s="634"/>
+      <c r="G39" s="580"/>
       <c r="H39" s="223"/>
       <c r="I39" s="6"/>
-      <c r="J39" s="550"/>
-      <c r="K39" s="531"/>
+      <c r="J39" s="600"/>
+      <c r="K39" s="554"/>
       <c r="L39" s="374"/>
       <c r="M39" s="120"/>
       <c r="N39" s="120"/>
       <c r="O39" s="120"/>
-      <c r="P39" s="644"/>
+      <c r="P39" s="532"/>
       <c r="Q39" s="120"/>
-      <c r="R39" s="550" t="s">
+      <c r="R39" s="600" t="s">
         <v>55</v>
       </c>
-      <c r="S39" s="531"/>
-      <c r="T39" s="533"/>
-      <c r="U39" s="533"/>
-      <c r="V39" s="533"/>
-      <c r="W39" s="533"/>
-      <c r="X39" s="533"/>
-      <c r="Y39" s="533"/>
-      <c r="Z39" s="533"/>
-      <c r="AA39" s="533"/>
+      <c r="S39" s="554"/>
+      <c r="T39" s="563"/>
+      <c r="U39" s="563"/>
+      <c r="V39" s="563"/>
+      <c r="W39" s="563"/>
+      <c r="X39" s="563"/>
+      <c r="Y39" s="563"/>
+      <c r="Z39" s="563"/>
+      <c r="AA39" s="563"/>
       <c r="AB39" s="63"/>
       <c r="AC39" s="64"/>
       <c r="AD39" s="64"/>
@@ -14309,35 +14340,35 @@
       <c r="HW39" s="6"/>
     </row>
     <row r="40" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="536"/>
-      <c r="B40" s="536"/>
-      <c r="C40" s="536"/>
-      <c r="D40" s="536"/>
-      <c r="E40" s="536"/>
-      <c r="F40" s="543"/>
-      <c r="G40" s="554"/>
+      <c r="A40" s="571"/>
+      <c r="B40" s="571"/>
+      <c r="C40" s="571"/>
+      <c r="D40" s="571"/>
+      <c r="E40" s="571"/>
+      <c r="F40" s="634"/>
+      <c r="G40" s="592"/>
       <c r="H40" s="223"/>
       <c r="I40" s="6"/>
-      <c r="J40" s="619"/>
-      <c r="K40" s="531"/>
+      <c r="J40" s="582"/>
+      <c r="K40" s="554"/>
       <c r="L40" s="234"/>
       <c r="M40" s="376"/>
       <c r="N40" s="376"/>
       <c r="O40" s="376"/>
-      <c r="P40" s="645"/>
+      <c r="P40" s="533"/>
       <c r="Q40" s="376"/>
-      <c r="R40" s="619" t="s">
+      <c r="R40" s="582" t="s">
         <v>56</v>
       </c>
-      <c r="S40" s="531"/>
+      <c r="S40" s="554"/>
       <c r="T40" s="100" t="s">
         <v>51</v>
       </c>
       <c r="U40" s="100"/>
       <c r="V40" s="100"/>
       <c r="W40" s="101"/>
-      <c r="X40" s="641"/>
-      <c r="Y40" s="641"/>
+      <c r="X40" s="530"/>
+      <c r="Y40" s="530"/>
       <c r="Z40" s="101"/>
       <c r="AA40" s="102">
         <v>400</v>
@@ -14548,50 +14579,52 @@
       <c r="HW40" s="6"/>
     </row>
     <row r="41" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A41" s="541"/>
-      <c r="B41" s="541"/>
-      <c r="C41" s="541"/>
-      <c r="D41" s="541"/>
-      <c r="E41" s="541"/>
-      <c r="F41" s="543"/>
-      <c r="G41" s="600" t="s">
+      <c r="A41" s="573"/>
+      <c r="B41" s="573"/>
+      <c r="C41" s="573"/>
+      <c r="D41" s="573"/>
+      <c r="E41" s="573"/>
+      <c r="F41" s="634"/>
+      <c r="G41" s="609" t="s">
         <v>25</v>
       </c>
       <c r="H41" s="377"/>
       <c r="I41" s="140"/>
-      <c r="J41" s="608"/>
-      <c r="K41" s="531"/>
+      <c r="J41" s="598"/>
+      <c r="K41" s="554"/>
       <c r="L41" s="26"/>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
       <c r="O41" s="26"/>
-      <c r="P41" s="646"/>
+      <c r="P41" s="534"/>
       <c r="Q41" s="53"/>
-      <c r="R41" s="608" t="s">
+      <c r="R41" s="598" t="s">
         <v>57</v>
       </c>
-      <c r="S41" s="531"/>
-      <c r="T41" s="642" t="s">
+      <c r="S41" s="554"/>
+      <c r="T41" s="605" t="s">
         <v>52</v>
       </c>
-      <c r="U41" s="612"/>
-      <c r="V41" s="612"/>
-      <c r="W41" s="612"/>
-      <c r="X41" s="612"/>
-      <c r="Y41" s="612"/>
-      <c r="Z41" s="612"/>
-      <c r="AA41" s="612"/>
-      <c r="AB41" s="574"/>
-      <c r="AC41" s="528"/>
-      <c r="AD41" s="528"/>
-      <c r="AE41" s="528"/>
+      <c r="U41" s="567"/>
+      <c r="V41" s="567"/>
+      <c r="W41" s="567"/>
+      <c r="X41" s="567"/>
+      <c r="Y41" s="567"/>
+      <c r="Z41" s="567"/>
+      <c r="AA41" s="567"/>
+      <c r="AB41" s="583"/>
+      <c r="AC41" s="562"/>
+      <c r="AD41" s="562"/>
+      <c r="AE41" s="562"/>
       <c r="AF41" s="52"/>
       <c r="AG41" s="53"/>
       <c r="AH41" s="53"/>
       <c r="AI41" s="62"/>
       <c r="AJ41" s="150"/>
       <c r="AK41" s="6"/>
-      <c r="AL41" s="6"/>
+      <c r="AL41" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
       <c r="AO41" s="6"/>
@@ -14787,13 +14820,13 @@
       <c r="HW41" s="6"/>
     </row>
     <row r="42" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="535"/>
-      <c r="B42" s="535"/>
-      <c r="C42" s="535"/>
-      <c r="D42" s="535"/>
-      <c r="E42" s="535"/>
-      <c r="F42" s="543"/>
-      <c r="G42" s="548"/>
+      <c r="A42" s="570"/>
+      <c r="B42" s="570"/>
+      <c r="C42" s="570"/>
+      <c r="D42" s="570"/>
+      <c r="E42" s="570"/>
+      <c r="F42" s="634"/>
+      <c r="G42" s="580"/>
       <c r="H42" s="223"/>
       <c r="I42" s="6"/>
       <c r="J42" s="143"/>
@@ -14802,18 +14835,18 @@
       <c r="M42" s="26"/>
       <c r="N42" s="26"/>
       <c r="O42" s="26"/>
-      <c r="P42" s="647"/>
+      <c r="P42" s="535"/>
       <c r="Q42" s="66"/>
-      <c r="R42" s="648"/>
+      <c r="R42" s="536"/>
       <c r="S42" s="84"/>
-      <c r="T42" s="533"/>
-      <c r="U42" s="533"/>
-      <c r="V42" s="533"/>
-      <c r="W42" s="533"/>
-      <c r="X42" s="533"/>
-      <c r="Y42" s="533"/>
-      <c r="Z42" s="533"/>
-      <c r="AA42" s="533"/>
+      <c r="T42" s="563"/>
+      <c r="U42" s="563"/>
+      <c r="V42" s="563"/>
+      <c r="W42" s="563"/>
+      <c r="X42" s="563"/>
+      <c r="Y42" s="563"/>
+      <c r="Z42" s="563"/>
+      <c r="AA42" s="563"/>
       <c r="AB42" s="63"/>
       <c r="AC42" s="64"/>
       <c r="AD42" s="64"/>
@@ -15020,27 +15053,27 @@
       <c r="HW42" s="6"/>
     </row>
     <row r="43" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="536"/>
-      <c r="B43" s="536"/>
-      <c r="C43" s="536"/>
-      <c r="D43" s="536"/>
-      <c r="E43" s="536"/>
-      <c r="F43" s="544"/>
-      <c r="G43" s="601"/>
+      <c r="A43" s="571"/>
+      <c r="B43" s="571"/>
+      <c r="C43" s="571"/>
+      <c r="D43" s="571"/>
+      <c r="E43" s="571"/>
+      <c r="F43" s="668"/>
+      <c r="G43" s="590"/>
       <c r="H43" s="378"/>
       <c r="I43" s="112"/>
-      <c r="J43" s="551"/>
-      <c r="K43" s="552"/>
+      <c r="J43" s="679"/>
+      <c r="K43" s="594"/>
       <c r="L43" s="113"/>
       <c r="M43" s="112"/>
       <c r="N43" s="112"/>
       <c r="O43" s="379"/>
       <c r="P43" s="380"/>
       <c r="Q43" s="379"/>
-      <c r="R43" s="572" t="s">
+      <c r="R43" s="662" t="s">
         <v>58</v>
       </c>
-      <c r="S43" s="573"/>
+      <c r="S43" s="663"/>
       <c r="T43" s="95" t="s">
         <v>53</v>
       </c>
@@ -15259,15 +15292,15 @@
       <c r="HW43" s="6"/>
     </row>
     <row r="44" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A44" s="541"/>
-      <c r="B44" s="537"/>
-      <c r="C44" s="537"/>
-      <c r="D44" s="537"/>
-      <c r="E44" s="537"/>
-      <c r="F44" s="579" t="s">
+      <c r="A44" s="573"/>
+      <c r="B44" s="602"/>
+      <c r="C44" s="602"/>
+      <c r="D44" s="602"/>
+      <c r="E44" s="602"/>
+      <c r="F44" s="633" t="s">
         <v>27</v>
       </c>
-      <c r="G44" s="569" t="s">
+      <c r="G44" s="610" t="s">
         <v>18</v>
       </c>
       <c r="H44" s="382"/>
@@ -15278,10 +15311,10 @@
       <c r="M44" s="231"/>
       <c r="N44" s="231"/>
       <c r="O44" s="232"/>
-      <c r="P44" s="649" t="s">
+      <c r="P44" s="636" t="s">
         <v>59</v>
       </c>
-      <c r="Q44" s="615"/>
+      <c r="Q44" s="637"/>
       <c r="R44" s="10"/>
       <c r="S44" s="10"/>
       <c r="T44" s="18"/>
@@ -15301,7 +15334,9 @@
       <c r="AH44" s="21"/>
       <c r="AI44" s="22"/>
       <c r="AJ44" s="6"/>
-      <c r="AK44" s="6"/>
+      <c r="AK44" s="680" t="s">
+        <v>84</v>
+      </c>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
@@ -15498,13 +15533,13 @@
       <c r="HW44" s="6"/>
     </row>
     <row r="45" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A45" s="535"/>
-      <c r="B45" s="535"/>
-      <c r="C45" s="535"/>
-      <c r="D45" s="535"/>
-      <c r="E45" s="535"/>
-      <c r="F45" s="543"/>
-      <c r="G45" s="548"/>
+      <c r="A45" s="570"/>
+      <c r="B45" s="570"/>
+      <c r="C45" s="570"/>
+      <c r="D45" s="570"/>
+      <c r="E45" s="570"/>
+      <c r="F45" s="634"/>
+      <c r="G45" s="580"/>
       <c r="H45" s="383"/>
       <c r="I45" s="60"/>
       <c r="J45" s="29"/>
@@ -15513,10 +15548,10 @@
       <c r="M45" s="384"/>
       <c r="N45" s="384"/>
       <c r="O45" s="385"/>
-      <c r="P45" s="550" t="s">
+      <c r="P45" s="600" t="s">
         <v>60</v>
       </c>
-      <c r="Q45" s="531"/>
+      <c r="Q45" s="554"/>
       <c r="R45" s="6"/>
       <c r="S45" s="6"/>
       <c r="T45" s="27"/>
@@ -15733,13 +15768,13 @@
       <c r="HW45" s="6"/>
     </row>
     <row r="46" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="536"/>
-      <c r="B46" s="536"/>
-      <c r="C46" s="536"/>
-      <c r="D46" s="536"/>
-      <c r="E46" s="536"/>
-      <c r="F46" s="543"/>
-      <c r="G46" s="554"/>
+      <c r="A46" s="571"/>
+      <c r="B46" s="571"/>
+      <c r="C46" s="571"/>
+      <c r="D46" s="571"/>
+      <c r="E46" s="571"/>
+      <c r="F46" s="634"/>
+      <c r="G46" s="592"/>
       <c r="H46" s="386"/>
       <c r="I46" s="205"/>
       <c r="J46" s="51"/>
@@ -15748,10 +15783,10 @@
       <c r="M46" s="388"/>
       <c r="N46" s="388"/>
       <c r="O46" s="375"/>
-      <c r="P46" s="650" t="s">
+      <c r="P46" s="651" t="s">
         <v>56</v>
       </c>
-      <c r="Q46" s="531"/>
+      <c r="Q46" s="554"/>
       <c r="R46" s="195"/>
       <c r="S46" s="195"/>
       <c r="T46" s="27"/>
@@ -15968,21 +16003,21 @@
       <c r="HW46" s="6"/>
     </row>
     <row r="47" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A47" s="534">
+      <c r="A47" s="673">
         <v>9</v>
       </c>
-      <c r="B47" s="538">
+      <c r="B47" s="585">
         <v>8</v>
       </c>
-      <c r="C47" s="538">
+      <c r="C47" s="585">
         <v>5</v>
       </c>
-      <c r="D47" s="538">
+      <c r="D47" s="585">
         <v>3</v>
       </c>
-      <c r="E47" s="538"/>
-      <c r="F47" s="543"/>
-      <c r="G47" s="560" t="s">
+      <c r="E47" s="585"/>
+      <c r="F47" s="634"/>
+      <c r="G47" s="591" t="s">
         <v>19</v>
       </c>
       <c r="H47" s="256"/>
@@ -15993,10 +16028,10 @@
       <c r="M47" s="389"/>
       <c r="N47" s="389"/>
       <c r="O47" s="390"/>
-      <c r="P47" s="651" t="s">
+      <c r="P47" s="632" t="s">
         <v>57</v>
       </c>
-      <c r="Q47" s="531"/>
+      <c r="Q47" s="554"/>
       <c r="R47" s="6"/>
       <c r="S47" s="6"/>
       <c r="T47" s="391"/>
@@ -16007,17 +16042,19 @@
       <c r="Y47" s="392"/>
       <c r="Z47" s="392"/>
       <c r="AA47" s="392"/>
-      <c r="AB47" s="563" t="s">
+      <c r="AB47" s="555" t="s">
         <v>62</v>
       </c>
-      <c r="AC47" s="529"/>
+      <c r="AC47" s="556"/>
       <c r="AD47" s="36"/>
       <c r="AF47" s="37"/>
       <c r="AG47" s="37"/>
       <c r="AH47" s="37"/>
       <c r="AI47" s="38"/>
       <c r="AJ47" s="6"/>
-      <c r="AK47" s="6"/>
+      <c r="AK47" s="680" t="s">
+        <v>84</v>
+      </c>
       <c r="AL47" s="6"/>
       <c r="AM47" s="6"/>
       <c r="AN47" s="6"/>
@@ -16214,13 +16251,13 @@
       <c r="HW47" s="6"/>
     </row>
     <row r="48" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A48" s="535"/>
-      <c r="B48" s="535"/>
-      <c r="C48" s="535"/>
-      <c r="D48" s="535"/>
-      <c r="E48" s="535"/>
-      <c r="F48" s="543"/>
-      <c r="G48" s="548"/>
+      <c r="A48" s="570"/>
+      <c r="B48" s="570"/>
+      <c r="C48" s="570"/>
+      <c r="D48" s="570"/>
+      <c r="E48" s="570"/>
+      <c r="F48" s="634"/>
+      <c r="G48" s="580"/>
       <c r="H48" s="263"/>
       <c r="I48" s="53"/>
       <c r="J48" s="53"/>
@@ -16241,10 +16278,10 @@
       <c r="Y48" s="24"/>
       <c r="Z48" s="24"/>
       <c r="AA48" s="24"/>
-      <c r="AB48" s="603" t="s">
+      <c r="AB48" s="557" t="s">
         <v>60</v>
       </c>
-      <c r="AC48" s="603"/>
+      <c r="AC48" s="557"/>
       <c r="AD48" s="10"/>
       <c r="AE48" s="39" t="s">
         <v>83</v>
@@ -16451,13 +16488,13 @@
       <c r="HW48" s="6"/>
     </row>
     <row r="49" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A49" s="536"/>
-      <c r="B49" s="536"/>
-      <c r="C49" s="536"/>
-      <c r="D49" s="536"/>
-      <c r="E49" s="536"/>
-      <c r="F49" s="543"/>
-      <c r="G49" s="554"/>
+      <c r="A49" s="571"/>
+      <c r="B49" s="571"/>
+      <c r="C49" s="571"/>
+      <c r="D49" s="571"/>
+      <c r="E49" s="571"/>
+      <c r="F49" s="634"/>
+      <c r="G49" s="592"/>
       <c r="H49" s="303"/>
       <c r="I49" s="83"/>
       <c r="J49" s="69"/>
@@ -16466,10 +16503,10 @@
       <c r="M49" s="388"/>
       <c r="N49" s="388"/>
       <c r="O49" s="375"/>
-      <c r="P49" s="652" t="s">
+      <c r="P49" s="553" t="s">
         <v>61</v>
       </c>
-      <c r="Q49" s="531"/>
+      <c r="Q49" s="554"/>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
       <c r="T49" s="394"/>
@@ -16480,10 +16517,10 @@
       <c r="Y49" s="395"/>
       <c r="Z49" s="395"/>
       <c r="AA49" s="50"/>
-      <c r="AB49" s="580" t="s">
+      <c r="AB49" s="558" t="s">
         <v>56</v>
       </c>
-      <c r="AC49" s="531"/>
+      <c r="AC49" s="554"/>
       <c r="AD49" s="46"/>
       <c r="AE49" s="97"/>
       <c r="AF49" s="49"/>
@@ -16688,41 +16725,41 @@
       <c r="HW49" s="6"/>
     </row>
     <row r="50" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="538">
+      <c r="A50" s="585">
         <v>22</v>
       </c>
-      <c r="B50" s="538">
+      <c r="B50" s="585">
         <v>22</v>
       </c>
-      <c r="C50" s="538">
+      <c r="C50" s="585">
         <v>19</v>
       </c>
-      <c r="D50" s="538">
+      <c r="D50" s="585">
         <v>17</v>
       </c>
-      <c r="E50" s="540"/>
-      <c r="F50" s="543"/>
-      <c r="G50" s="566" t="s">
+      <c r="E50" s="569"/>
+      <c r="F50" s="634"/>
+      <c r="G50" s="630" t="s">
         <v>20</v>
       </c>
-      <c r="H50" s="563"/>
-      <c r="I50" s="528"/>
-      <c r="J50" s="528"/>
-      <c r="K50" s="529"/>
-      <c r="L50" s="563" t="s">
+      <c r="H50" s="555"/>
+      <c r="I50" s="562"/>
+      <c r="J50" s="562"/>
+      <c r="K50" s="556"/>
+      <c r="L50" s="555" t="s">
         <v>62</v>
       </c>
-      <c r="M50" s="529"/>
-      <c r="N50" s="656" t="s">
+      <c r="M50" s="556"/>
+      <c r="N50" s="658" t="s">
         <v>63</v>
       </c>
-      <c r="O50" s="529"/>
-      <c r="P50" s="653"/>
-      <c r="Q50" s="654"/>
-      <c r="R50" s="655" t="s">
+      <c r="O50" s="556"/>
+      <c r="P50" s="537"/>
+      <c r="Q50" s="538"/>
+      <c r="R50" s="561" t="s">
         <v>59</v>
       </c>
-      <c r="S50" s="528"/>
+      <c r="S50" s="562"/>
       <c r="T50" s="56"/>
       <c r="U50" s="57"/>
       <c r="V50" s="57"/>
@@ -16731,20 +16768,26 @@
       <c r="Y50" s="57"/>
       <c r="Z50" s="57"/>
       <c r="AA50" s="57"/>
-      <c r="AB50" s="546" t="s">
+      <c r="AB50" s="559" t="s">
         <v>66</v>
       </c>
-      <c r="AC50" s="531"/>
+      <c r="AC50" s="554"/>
       <c r="AD50" s="10"/>
       <c r="AE50" s="44"/>
-      <c r="AF50" s="527"/>
-      <c r="AG50" s="528"/>
-      <c r="AH50" s="528"/>
-      <c r="AI50" s="529"/>
+      <c r="AF50" s="628"/>
+      <c r="AG50" s="562"/>
+      <c r="AH50" s="562"/>
+      <c r="AI50" s="556"/>
       <c r="AJ50" s="6"/>
-      <c r="AK50" s="151"/>
-      <c r="AL50" s="151"/>
-      <c r="AM50" s="151"/>
+      <c r="AK50" s="680" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL50" s="680" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM50" s="680" t="s">
+        <v>84</v>
+      </c>
       <c r="AN50" s="151"/>
       <c r="AO50" s="6"/>
       <c r="AP50" s="6"/>
@@ -16939,31 +16982,31 @@
       <c r="HW50" s="6"/>
     </row>
     <row r="51" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A51" s="535"/>
-      <c r="B51" s="535"/>
-      <c r="C51" s="535"/>
-      <c r="D51" s="535"/>
-      <c r="E51" s="535"/>
-      <c r="F51" s="543"/>
-      <c r="G51" s="548"/>
+      <c r="A51" s="570"/>
+      <c r="B51" s="570"/>
+      <c r="C51" s="570"/>
+      <c r="D51" s="570"/>
+      <c r="E51" s="570"/>
+      <c r="F51" s="634"/>
+      <c r="G51" s="580"/>
       <c r="H51" s="397"/>
       <c r="I51" s="81"/>
       <c r="J51" s="81"/>
       <c r="K51" s="215"/>
-      <c r="L51" s="568" t="s">
+      <c r="L51" s="596" t="s">
         <v>64</v>
       </c>
-      <c r="M51" s="531"/>
-      <c r="N51" s="657" t="s">
+      <c r="M51" s="554"/>
+      <c r="N51" s="574" t="s">
         <v>65</v>
       </c>
-      <c r="O51" s="531"/>
+      <c r="O51" s="554"/>
       <c r="P51" s="6"/>
       <c r="Q51" s="149"/>
-      <c r="R51" s="603" t="s">
+      <c r="R51" s="557" t="s">
         <v>60</v>
       </c>
-      <c r="S51" s="533"/>
+      <c r="S51" s="563"/>
       <c r="T51" s="59"/>
       <c r="U51" s="60"/>
       <c r="V51" s="60"/>
@@ -16972,13 +17015,13 @@
       <c r="Y51" s="60"/>
       <c r="Z51" s="60"/>
       <c r="AA51" s="60"/>
-      <c r="AB51" s="658"/>
-      <c r="AC51" s="659"/>
+      <c r="AB51" s="539"/>
+      <c r="AC51" s="540"/>
       <c r="AD51" s="10"/>
       <c r="AE51" s="44"/>
       <c r="AF51" s="398"/>
-      <c r="AG51" s="545"/>
-      <c r="AH51" s="533"/>
+      <c r="AG51" s="678"/>
+      <c r="AH51" s="563"/>
       <c r="AI51" s="399"/>
       <c r="AJ51" s="6"/>
       <c r="AK51" s="85"/>
@@ -17178,31 +17221,31 @@
       <c r="HW51" s="6"/>
     </row>
     <row r="52" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A52" s="536"/>
-      <c r="B52" s="536"/>
-      <c r="C52" s="536"/>
-      <c r="D52" s="536"/>
-      <c r="E52" s="536"/>
-      <c r="F52" s="543"/>
-      <c r="G52" s="567"/>
+      <c r="A52" s="571"/>
+      <c r="B52" s="571"/>
+      <c r="C52" s="571"/>
+      <c r="D52" s="571"/>
+      <c r="E52" s="571"/>
+      <c r="F52" s="634"/>
+      <c r="G52" s="631"/>
       <c r="H52" s="400"/>
       <c r="I52" s="190"/>
       <c r="J52" s="190"/>
       <c r="K52" s="362"/>
-      <c r="L52" s="580" t="s">
+      <c r="L52" s="558" t="s">
         <v>56</v>
       </c>
-      <c r="M52" s="531"/>
-      <c r="N52" s="650" t="s">
+      <c r="M52" s="554"/>
+      <c r="N52" s="651" t="s">
         <v>56</v>
       </c>
-      <c r="O52" s="531"/>
+      <c r="O52" s="554"/>
       <c r="P52" s="147"/>
       <c r="Q52" s="213"/>
-      <c r="R52" s="570" t="s">
+      <c r="R52" s="564" t="s">
         <v>56</v>
       </c>
-      <c r="S52" s="533"/>
+      <c r="S52" s="563"/>
       <c r="T52" s="247"/>
       <c r="U52" s="72"/>
       <c r="V52" s="72"/>
@@ -17211,10 +17254,10 @@
       <c r="Y52" s="72"/>
       <c r="Z52" s="72"/>
       <c r="AA52" s="72"/>
-      <c r="AB52" s="591" t="s">
+      <c r="AB52" s="560" t="s">
         <v>68</v>
       </c>
-      <c r="AC52" s="531"/>
+      <c r="AC52" s="554"/>
       <c r="AD52" s="10"/>
       <c r="AE52" s="44"/>
       <c r="AF52" s="216"/>
@@ -17419,43 +17462,43 @@
       <c r="HW52" s="6"/>
     </row>
     <row r="53" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A53" s="540">
+      <c r="A53" s="569">
         <v>0</v>
       </c>
-      <c r="B53" s="540">
+      <c r="B53" s="569">
         <v>0</v>
       </c>
-      <c r="C53" s="540">
+      <c r="C53" s="569">
         <v>0</v>
       </c>
-      <c r="D53" s="538">
+      <c r="D53" s="585">
         <v>31</v>
       </c>
-      <c r="E53" s="540">
+      <c r="E53" s="569">
         <v>0</v>
       </c>
-      <c r="F53" s="543"/>
-      <c r="G53" s="547" t="s">
+      <c r="F53" s="634"/>
+      <c r="G53" s="675" t="s">
         <v>22</v>
       </c>
-      <c r="H53" s="571"/>
-      <c r="I53" s="533"/>
-      <c r="J53" s="533"/>
-      <c r="K53" s="531"/>
-      <c r="L53" s="546" t="s">
+      <c r="H53" s="601"/>
+      <c r="I53" s="563"/>
+      <c r="J53" s="563"/>
+      <c r="K53" s="554"/>
+      <c r="L53" s="559" t="s">
         <v>66</v>
       </c>
-      <c r="M53" s="531"/>
-      <c r="N53" s="651" t="s">
+      <c r="M53" s="554"/>
+      <c r="N53" s="632" t="s">
         <v>67</v>
       </c>
-      <c r="O53" s="531"/>
+      <c r="O53" s="554"/>
       <c r="P53" s="6"/>
       <c r="Q53" s="149"/>
-      <c r="R53" s="624" t="s">
+      <c r="R53" s="565" t="s">
         <v>57</v>
       </c>
-      <c r="S53" s="533"/>
+      <c r="S53" s="563"/>
       <c r="T53" s="364"/>
       <c r="U53" s="365"/>
       <c r="V53" s="78"/>
@@ -17464,14 +17507,14 @@
       <c r="Y53" s="365"/>
       <c r="Z53" s="78"/>
       <c r="AA53" s="78"/>
-      <c r="AB53" s="675"/>
-      <c r="AC53" s="676"/>
-      <c r="AD53" s="676"/>
-      <c r="AE53" s="677"/>
-      <c r="AF53" s="561"/>
-      <c r="AG53" s="533"/>
-      <c r="AH53" s="533"/>
-      <c r="AI53" s="531"/>
+      <c r="AB53" s="551"/>
+      <c r="AC53" s="528"/>
+      <c r="AD53" s="528"/>
+      <c r="AE53" s="529"/>
+      <c r="AF53" s="666"/>
+      <c r="AG53" s="563"/>
+      <c r="AH53" s="563"/>
+      <c r="AI53" s="554"/>
       <c r="AJ53" s="3"/>
       <c r="AK53" s="151"/>
       <c r="AL53" s="151"/>
@@ -17670,19 +17713,19 @@
       <c r="HW53" s="6"/>
     </row>
     <row r="54" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="535"/>
-      <c r="B54" s="535"/>
-      <c r="C54" s="535"/>
-      <c r="D54" s="535"/>
-      <c r="E54" s="535"/>
-      <c r="F54" s="543"/>
-      <c r="G54" s="548"/>
+      <c r="A54" s="570"/>
+      <c r="B54" s="570"/>
+      <c r="C54" s="570"/>
+      <c r="D54" s="570"/>
+      <c r="E54" s="570"/>
+      <c r="F54" s="634"/>
+      <c r="G54" s="580"/>
       <c r="H54" s="397"/>
       <c r="I54" s="81"/>
       <c r="J54" s="81"/>
       <c r="K54" s="215"/>
-      <c r="L54" s="658"/>
-      <c r="M54" s="659"/>
+      <c r="L54" s="539"/>
+      <c r="M54" s="540"/>
       <c r="N54" s="6"/>
       <c r="O54" s="84"/>
       <c r="P54" s="6"/>
@@ -17903,31 +17946,31 @@
       <c r="HW54" s="6"/>
     </row>
     <row r="55" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A55" s="536"/>
-      <c r="B55" s="536"/>
-      <c r="C55" s="536"/>
-      <c r="D55" s="536"/>
-      <c r="E55" s="536"/>
-      <c r="F55" s="543"/>
-      <c r="G55" s="549"/>
+      <c r="A55" s="571"/>
+      <c r="B55" s="571"/>
+      <c r="C55" s="571"/>
+      <c r="D55" s="571"/>
+      <c r="E55" s="571"/>
+      <c r="F55" s="634"/>
+      <c r="G55" s="676"/>
       <c r="H55" s="402"/>
       <c r="I55" s="135"/>
       <c r="J55" s="87"/>
       <c r="K55" s="158"/>
-      <c r="L55" s="591" t="s">
+      <c r="L55" s="560" t="s">
         <v>68</v>
       </c>
-      <c r="M55" s="531"/>
-      <c r="N55" s="660" t="s">
+      <c r="M55" s="554"/>
+      <c r="N55" s="572" t="s">
         <v>69</v>
       </c>
-      <c r="O55" s="531"/>
+      <c r="O55" s="554"/>
       <c r="P55" s="195"/>
       <c r="Q55" s="103"/>
-      <c r="R55" s="652" t="s">
+      <c r="R55" s="553" t="s">
         <v>61</v>
       </c>
-      <c r="S55" s="531"/>
+      <c r="S55" s="554"/>
       <c r="T55" s="369"/>
       <c r="U55" s="370"/>
       <c r="V55" s="370"/>
@@ -18142,13 +18185,13 @@
       <c r="HW55" s="6"/>
     </row>
     <row r="56" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A56" s="541"/>
-      <c r="B56" s="541"/>
-      <c r="C56" s="541"/>
-      <c r="D56" s="541"/>
-      <c r="E56" s="541"/>
-      <c r="F56" s="543"/>
-      <c r="G56" s="560" t="s">
+      <c r="A56" s="573"/>
+      <c r="B56" s="573"/>
+      <c r="C56" s="573"/>
+      <c r="D56" s="573"/>
+      <c r="E56" s="573"/>
+      <c r="F56" s="634"/>
+      <c r="G56" s="591" t="s">
         <v>24</v>
       </c>
       <c r="H56" s="353"/>
@@ -18156,11 +18199,11 @@
       <c r="J56" s="105"/>
       <c r="K56" s="184"/>
       <c r="L56" s="377"/>
-      <c r="M56" s="661"/>
-      <c r="N56" s="656" t="s">
+      <c r="M56" s="541"/>
+      <c r="N56" s="658" t="s">
         <v>62</v>
       </c>
-      <c r="O56" s="529"/>
+      <c r="O56" s="556"/>
       <c r="P56" s="405"/>
       <c r="Q56" s="405"/>
       <c r="R56" s="405"/>
@@ -18173,19 +18216,23 @@
       <c r="Y56" s="81"/>
       <c r="Z56" s="81"/>
       <c r="AA56" s="224"/>
-      <c r="AB56" s="678"/>
-      <c r="AC56" s="679"/>
-      <c r="AD56" s="655" t="s">
+      <c r="AB56" s="552"/>
+      <c r="AC56" s="527"/>
+      <c r="AD56" s="561" t="s">
         <v>81</v>
       </c>
-      <c r="AE56" s="528"/>
+      <c r="AE56" s="562"/>
       <c r="AF56" s="36"/>
       <c r="AG56" s="36"/>
       <c r="AH56" s="36"/>
       <c r="AI56" s="39"/>
       <c r="AJ56" s="407"/>
-      <c r="AK56" s="151"/>
-      <c r="AL56" s="151"/>
+      <c r="AK56" s="680" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL56" s="680" t="s">
+        <v>84</v>
+      </c>
       <c r="AM56" s="151"/>
       <c r="AN56" s="151"/>
       <c r="AO56" s="6"/>
@@ -18381,23 +18428,23 @@
       <c r="HW56" s="6"/>
     </row>
     <row r="57" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A57" s="535"/>
-      <c r="B57" s="535"/>
-      <c r="C57" s="535"/>
-      <c r="D57" s="535"/>
-      <c r="E57" s="535"/>
-      <c r="F57" s="543"/>
-      <c r="G57" s="548"/>
+      <c r="A57" s="570"/>
+      <c r="B57" s="570"/>
+      <c r="C57" s="570"/>
+      <c r="D57" s="570"/>
+      <c r="E57" s="570"/>
+      <c r="F57" s="634"/>
+      <c r="G57" s="580"/>
       <c r="H57" s="167"/>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
       <c r="K57" s="166"/>
-      <c r="L57" s="662"/>
-      <c r="M57" s="663"/>
-      <c r="N57" s="657" t="s">
+      <c r="L57" s="542"/>
+      <c r="M57" s="543"/>
+      <c r="N57" s="574" t="s">
         <v>64</v>
       </c>
-      <c r="O57" s="531"/>
+      <c r="O57" s="554"/>
       <c r="P57" s="156"/>
       <c r="Q57" s="156"/>
       <c r="R57" s="156"/>
@@ -18412,10 +18459,10 @@
       <c r="AA57" s="165"/>
       <c r="AB57" s="63"/>
       <c r="AC57" s="64"/>
-      <c r="AD57" s="603" t="s">
+      <c r="AD57" s="557" t="s">
         <v>60</v>
       </c>
-      <c r="AE57" s="533"/>
+      <c r="AE57" s="563"/>
       <c r="AF57" s="10"/>
       <c r="AG57" s="10"/>
       <c r="AH57" s="10"/>
@@ -18618,23 +18665,23 @@
       <c r="HW57" s="6"/>
     </row>
     <row r="58" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A58" s="536"/>
-      <c r="B58" s="536"/>
-      <c r="C58" s="536"/>
-      <c r="D58" s="536"/>
-      <c r="E58" s="536"/>
-      <c r="F58" s="543"/>
-      <c r="G58" s="554"/>
+      <c r="A58" s="571"/>
+      <c r="B58" s="571"/>
+      <c r="C58" s="571"/>
+      <c r="D58" s="571"/>
+      <c r="E58" s="571"/>
+      <c r="F58" s="634"/>
+      <c r="G58" s="592"/>
       <c r="H58" s="330"/>
       <c r="I58" s="88"/>
       <c r="J58" s="88"/>
       <c r="K58" s="192"/>
       <c r="L58" s="331"/>
-      <c r="M58" s="664"/>
-      <c r="N58" s="650" t="s">
+      <c r="M58" s="544"/>
+      <c r="N58" s="651" t="s">
         <v>56</v>
       </c>
-      <c r="O58" s="531"/>
+      <c r="O58" s="554"/>
       <c r="P58" s="333"/>
       <c r="Q58" s="333"/>
       <c r="R58" s="159"/>
@@ -18649,10 +18696,10 @@
       <c r="AA58" s="411"/>
       <c r="AB58" s="86"/>
       <c r="AC58" s="95"/>
-      <c r="AD58" s="570" t="s">
+      <c r="AD58" s="564" t="s">
         <v>56</v>
       </c>
-      <c r="AE58" s="533"/>
+      <c r="AE58" s="563"/>
       <c r="AF58" s="46"/>
       <c r="AG58" s="46"/>
       <c r="AH58" s="46"/>
@@ -18855,25 +18902,25 @@
       <c r="HW58" s="6"/>
     </row>
     <row r="59" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A59" s="541"/>
-      <c r="B59" s="541"/>
-      <c r="C59" s="541"/>
-      <c r="D59" s="541"/>
-      <c r="E59" s="541"/>
-      <c r="F59" s="543"/>
-      <c r="G59" s="602" t="s">
+      <c r="A59" s="573"/>
+      <c r="B59" s="573"/>
+      <c r="C59" s="573"/>
+      <c r="D59" s="573"/>
+      <c r="E59" s="573"/>
+      <c r="F59" s="634"/>
+      <c r="G59" s="589" t="s">
         <v>25</v>
       </c>
       <c r="H59" s="167"/>
       <c r="I59" s="26"/>
       <c r="J59" s="26"/>
       <c r="K59" s="166"/>
-      <c r="L59" s="662"/>
-      <c r="M59" s="663"/>
-      <c r="N59" s="651" t="s">
+      <c r="L59" s="542"/>
+      <c r="M59" s="543"/>
+      <c r="N59" s="632" t="s">
         <v>66</v>
       </c>
-      <c r="O59" s="531"/>
+      <c r="O59" s="554"/>
       <c r="P59" s="81"/>
       <c r="Q59" s="81"/>
       <c r="R59" s="81"/>
@@ -18888,10 +18935,10 @@
       <c r="AA59" s="10"/>
       <c r="AB59" s="42"/>
       <c r="AC59" s="10"/>
-      <c r="AD59" s="624" t="s">
+      <c r="AD59" s="565" t="s">
         <v>57</v>
       </c>
-      <c r="AE59" s="533"/>
+      <c r="AE59" s="563"/>
       <c r="AF59" s="10"/>
       <c r="AG59" s="10"/>
       <c r="AH59" s="10"/>
@@ -19094,19 +19141,19 @@
       <c r="HW59" s="6"/>
     </row>
     <row r="60" spans="1:231" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="535"/>
-      <c r="B60" s="535"/>
-      <c r="C60" s="535"/>
-      <c r="D60" s="535"/>
-      <c r="E60" s="535"/>
-      <c r="F60" s="543"/>
-      <c r="G60" s="548"/>
+      <c r="A60" s="570"/>
+      <c r="B60" s="570"/>
+      <c r="C60" s="570"/>
+      <c r="D60" s="570"/>
+      <c r="E60" s="570"/>
+      <c r="F60" s="634"/>
+      <c r="G60" s="580"/>
       <c r="H60" s="167"/>
       <c r="I60" s="26"/>
       <c r="J60" s="26"/>
       <c r="K60" s="166"/>
-      <c r="L60" s="662"/>
-      <c r="M60" s="663"/>
+      <c r="L60" s="542"/>
+      <c r="M60" s="543"/>
       <c r="N60" s="75"/>
       <c r="O60" s="84"/>
       <c r="P60" s="81"/>
@@ -19327,23 +19374,23 @@
       <c r="HW60" s="6"/>
     </row>
     <row r="61" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A61" s="536"/>
-      <c r="B61" s="536"/>
-      <c r="C61" s="536"/>
-      <c r="D61" s="536"/>
-      <c r="E61" s="536"/>
-      <c r="F61" s="543"/>
-      <c r="G61" s="601"/>
+      <c r="A61" s="571"/>
+      <c r="B61" s="571"/>
+      <c r="C61" s="571"/>
+      <c r="D61" s="571"/>
+      <c r="E61" s="571"/>
+      <c r="F61" s="634"/>
+      <c r="G61" s="590"/>
       <c r="H61" s="167"/>
       <c r="I61" s="26"/>
       <c r="J61" s="26"/>
       <c r="K61" s="166"/>
       <c r="L61" s="412"/>
       <c r="M61" s="413"/>
-      <c r="N61" s="652" t="s">
+      <c r="N61" s="553" t="s">
         <v>68</v>
       </c>
-      <c r="O61" s="531"/>
+      <c r="O61" s="554"/>
       <c r="P61" s="195"/>
       <c r="Q61" s="195"/>
       <c r="R61" s="195"/>
@@ -19358,10 +19405,10 @@
       <c r="AA61" s="178"/>
       <c r="AB61" s="27"/>
       <c r="AC61" s="26"/>
-      <c r="AD61" s="652" t="s">
+      <c r="AD61" s="553" t="s">
         <v>82</v>
       </c>
-      <c r="AE61" s="531"/>
+      <c r="AE61" s="554"/>
       <c r="AF61" s="10"/>
       <c r="AG61" s="10"/>
       <c r="AH61" s="10"/>
@@ -19564,15 +19611,15 @@
       <c r="HW61" s="6"/>
     </row>
     <row r="62" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="541"/>
-      <c r="B62" s="537"/>
-      <c r="C62" s="537"/>
-      <c r="D62" s="537"/>
-      <c r="E62" s="630"/>
-      <c r="F62" s="542" t="s">
+      <c r="A62" s="573"/>
+      <c r="B62" s="602"/>
+      <c r="C62" s="602"/>
+      <c r="D62" s="602"/>
+      <c r="E62" s="616"/>
+      <c r="F62" s="667" t="s">
         <v>28</v>
       </c>
-      <c r="G62" s="614" t="s">
+      <c r="G62" s="635" t="s">
         <v>18</v>
       </c>
       <c r="H62" s="283"/>
@@ -19801,13 +19848,13 @@
       <c r="HW62" s="6"/>
     </row>
     <row r="63" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="535"/>
-      <c r="B63" s="535"/>
-      <c r="C63" s="535"/>
-      <c r="D63" s="535"/>
-      <c r="E63" s="535"/>
-      <c r="F63" s="543"/>
-      <c r="G63" s="548"/>
+      <c r="A63" s="570"/>
+      <c r="B63" s="570"/>
+      <c r="C63" s="570"/>
+      <c r="D63" s="570"/>
+      <c r="E63" s="570"/>
+      <c r="F63" s="634"/>
+      <c r="G63" s="580"/>
       <c r="H63" s="270"/>
       <c r="I63" s="29"/>
       <c r="J63" s="29"/>
@@ -20034,13 +20081,13 @@
       <c r="HW63" s="6"/>
     </row>
     <row r="64" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A64" s="536"/>
-      <c r="B64" s="536"/>
-      <c r="C64" s="536"/>
-      <c r="D64" s="536"/>
-      <c r="E64" s="536"/>
-      <c r="F64" s="543"/>
-      <c r="G64" s="548"/>
+      <c r="A64" s="571"/>
+      <c r="B64" s="571"/>
+      <c r="C64" s="571"/>
+      <c r="D64" s="571"/>
+      <c r="E64" s="571"/>
+      <c r="F64" s="634"/>
+      <c r="G64" s="580"/>
       <c r="H64" s="202"/>
       <c r="I64" s="32"/>
       <c r="J64" s="32"/>
@@ -20267,23 +20314,23 @@
       <c r="HW64" s="6"/>
     </row>
     <row r="65" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A65" s="538">
+      <c r="A65" s="585">
         <v>9</v>
       </c>
-      <c r="B65" s="538">
+      <c r="B65" s="585">
         <v>9</v>
       </c>
-      <c r="C65" s="538">
+      <c r="C65" s="585">
         <v>6</v>
       </c>
-      <c r="D65" s="538">
+      <c r="D65" s="585">
         <v>4</v>
       </c>
-      <c r="E65" s="538">
+      <c r="E65" s="585">
         <v>1</v>
       </c>
-      <c r="F65" s="543"/>
-      <c r="G65" s="560" t="s">
+      <c r="F65" s="634"/>
+      <c r="G65" s="591" t="s">
         <v>19</v>
       </c>
       <c r="H65" s="353"/>
@@ -20306,10 +20353,10 @@
       <c r="Y65" s="105"/>
       <c r="Z65" s="105"/>
       <c r="AA65" s="131"/>
-      <c r="AB65" s="637"/>
-      <c r="AC65" s="528"/>
-      <c r="AD65" s="528"/>
-      <c r="AE65" s="638"/>
+      <c r="AB65" s="577"/>
+      <c r="AC65" s="562"/>
+      <c r="AD65" s="562"/>
+      <c r="AE65" s="578"/>
       <c r="AF65" s="42"/>
       <c r="AG65" s="10"/>
       <c r="AH65" s="10"/>
@@ -20512,13 +20559,13 @@
       <c r="HW65" s="6"/>
     </row>
     <row r="66" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="535"/>
-      <c r="B66" s="535"/>
-      <c r="C66" s="535"/>
-      <c r="D66" s="535"/>
-      <c r="E66" s="535"/>
-      <c r="F66" s="543"/>
-      <c r="G66" s="548"/>
+      <c r="A66" s="570"/>
+      <c r="B66" s="570"/>
+      <c r="C66" s="570"/>
+      <c r="D66" s="570"/>
+      <c r="E66" s="570"/>
+      <c r="F66" s="634"/>
+      <c r="G66" s="580"/>
       <c r="H66" s="167"/>
       <c r="I66" s="26"/>
       <c r="J66" s="26"/>
@@ -20745,13 +20792,13 @@
       <c r="HW66" s="6"/>
     </row>
     <row r="67" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A67" s="536"/>
-      <c r="B67" s="536"/>
-      <c r="C67" s="536"/>
-      <c r="D67" s="536"/>
-      <c r="E67" s="536"/>
-      <c r="F67" s="543"/>
-      <c r="G67" s="554"/>
+      <c r="A67" s="571"/>
+      <c r="B67" s="571"/>
+      <c r="C67" s="571"/>
+      <c r="D67" s="571"/>
+      <c r="E67" s="571"/>
+      <c r="F67" s="634"/>
+      <c r="G67" s="592"/>
       <c r="H67" s="330"/>
       <c r="I67" s="88"/>
       <c r="J67" s="88"/>
@@ -20978,27 +21025,27 @@
       <c r="HW67" s="6"/>
     </row>
     <row r="68" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="538">
+      <c r="A68" s="585">
         <v>23</v>
       </c>
-      <c r="B68" s="538">
+      <c r="B68" s="585">
         <v>23</v>
       </c>
-      <c r="C68" s="538">
+      <c r="C68" s="585">
         <v>20</v>
       </c>
-      <c r="D68" s="538">
+      <c r="D68" s="585">
         <v>18</v>
       </c>
-      <c r="E68" s="538"/>
-      <c r="F68" s="543"/>
-      <c r="G68" s="609" t="s">
+      <c r="E68" s="585"/>
+      <c r="F68" s="634"/>
+      <c r="G68" s="623" t="s">
         <v>20</v>
       </c>
-      <c r="H68" s="563"/>
-      <c r="I68" s="528"/>
-      <c r="J68" s="528"/>
-      <c r="K68" s="529"/>
+      <c r="H68" s="555"/>
+      <c r="I68" s="562"/>
+      <c r="J68" s="562"/>
+      <c r="K68" s="556"/>
       <c r="L68" s="256"/>
       <c r="M68" s="57"/>
       <c r="N68" s="26"/>
@@ -21015,14 +21062,14 @@
       <c r="Y68" s="26"/>
       <c r="Z68" s="26"/>
       <c r="AA68" s="28"/>
-      <c r="AB68" s="635"/>
-      <c r="AC68" s="612"/>
-      <c r="AD68" s="612"/>
-      <c r="AE68" s="636"/>
-      <c r="AF68" s="539"/>
-      <c r="AG68" s="528"/>
-      <c r="AH68" s="528"/>
-      <c r="AI68" s="529"/>
+      <c r="AB68" s="566"/>
+      <c r="AC68" s="567"/>
+      <c r="AD68" s="567"/>
+      <c r="AE68" s="568"/>
+      <c r="AF68" s="621"/>
+      <c r="AG68" s="562"/>
+      <c r="AH68" s="562"/>
+      <c r="AI68" s="556"/>
       <c r="AJ68" s="121"/>
       <c r="AK68" s="6"/>
       <c r="AL68" s="6"/>
@@ -21221,13 +21268,13 @@
       <c r="HW68" s="6"/>
     </row>
     <row r="69" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A69" s="535"/>
-      <c r="B69" s="535"/>
-      <c r="C69" s="535"/>
-      <c r="D69" s="535"/>
-      <c r="E69" s="535"/>
-      <c r="F69" s="543"/>
-      <c r="G69" s="548"/>
+      <c r="A69" s="570"/>
+      <c r="B69" s="570"/>
+      <c r="C69" s="570"/>
+      <c r="D69" s="570"/>
+      <c r="E69" s="570"/>
+      <c r="F69" s="634"/>
+      <c r="G69" s="580"/>
       <c r="H69" s="397"/>
       <c r="I69" s="81"/>
       <c r="J69" s="81"/>
@@ -21454,13 +21501,13 @@
       <c r="HW69" s="6"/>
     </row>
     <row r="70" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A70" s="536"/>
-      <c r="B70" s="536"/>
-      <c r="C70" s="536"/>
-      <c r="D70" s="536"/>
-      <c r="E70" s="536"/>
-      <c r="F70" s="543"/>
-      <c r="G70" s="610"/>
+      <c r="A70" s="571"/>
+      <c r="B70" s="571"/>
+      <c r="C70" s="571"/>
+      <c r="D70" s="571"/>
+      <c r="E70" s="571"/>
+      <c r="F70" s="634"/>
+      <c r="G70" s="581"/>
       <c r="H70" s="400"/>
       <c r="I70" s="190"/>
       <c r="J70" s="190"/>
@@ -21687,37 +21734,37 @@
       <c r="HW70" s="6"/>
     </row>
     <row r="71" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="540">
+      <c r="A71" s="569">
         <v>0</v>
       </c>
-      <c r="B71" s="540">
+      <c r="B71" s="569">
         <v>0</v>
       </c>
-      <c r="C71" s="540">
+      <c r="C71" s="569">
         <v>0</v>
       </c>
-      <c r="D71" s="540">
+      <c r="D71" s="569">
         <v>0</v>
       </c>
-      <c r="E71" s="538">
+      <c r="E71" s="585">
         <v>0</v>
       </c>
-      <c r="F71" s="543"/>
-      <c r="G71" s="620" t="s">
+      <c r="F71" s="634"/>
+      <c r="G71" s="624" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="611"/>
-      <c r="I71" s="612"/>
-      <c r="J71" s="612"/>
-      <c r="K71" s="613"/>
-      <c r="L71" s="611"/>
-      <c r="M71" s="612"/>
-      <c r="N71" s="612"/>
-      <c r="O71" s="613"/>
-      <c r="P71" s="623"/>
-      <c r="Q71" s="612"/>
-      <c r="R71" s="612"/>
-      <c r="S71" s="613"/>
+      <c r="H71" s="575"/>
+      <c r="I71" s="567"/>
+      <c r="J71" s="567"/>
+      <c r="K71" s="576"/>
+      <c r="L71" s="575"/>
+      <c r="M71" s="567"/>
+      <c r="N71" s="567"/>
+      <c r="O71" s="576"/>
+      <c r="P71" s="627"/>
+      <c r="Q71" s="567"/>
+      <c r="R71" s="567"/>
+      <c r="S71" s="576"/>
       <c r="T71" s="241"/>
       <c r="U71" s="242"/>
       <c r="V71" s="242"/>
@@ -21726,14 +21773,14 @@
       <c r="Y71" s="242"/>
       <c r="Z71" s="242"/>
       <c r="AA71" s="427"/>
-      <c r="AB71" s="590"/>
-      <c r="AC71" s="533"/>
-      <c r="AD71" s="533"/>
-      <c r="AE71" s="533"/>
-      <c r="AF71" s="562"/>
-      <c r="AG71" s="533"/>
-      <c r="AH71" s="533"/>
-      <c r="AI71" s="531"/>
+      <c r="AB71" s="650"/>
+      <c r="AC71" s="563"/>
+      <c r="AD71" s="563"/>
+      <c r="AE71" s="563"/>
+      <c r="AF71" s="622"/>
+      <c r="AG71" s="563"/>
+      <c r="AH71" s="563"/>
+      <c r="AI71" s="554"/>
       <c r="AJ71" s="121"/>
       <c r="AK71" s="6"/>
       <c r="AL71" s="6"/>
@@ -21932,13 +21979,13 @@
       <c r="HW71" s="6"/>
     </row>
     <row r="72" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A72" s="535"/>
-      <c r="B72" s="535"/>
-      <c r="C72" s="535"/>
-      <c r="D72" s="535"/>
-      <c r="E72" s="535"/>
-      <c r="F72" s="543"/>
-      <c r="G72" s="548"/>
+      <c r="A72" s="570"/>
+      <c r="B72" s="570"/>
+      <c r="C72" s="570"/>
+      <c r="D72" s="570"/>
+      <c r="E72" s="570"/>
+      <c r="F72" s="634"/>
+      <c r="G72" s="580"/>
       <c r="H72" s="397"/>
       <c r="I72" s="81"/>
       <c r="J72" s="81"/>
@@ -22165,13 +22212,13 @@
       <c r="HW72" s="6"/>
     </row>
     <row r="73" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A73" s="536"/>
-      <c r="B73" s="536"/>
-      <c r="C73" s="536"/>
-      <c r="D73" s="536"/>
-      <c r="E73" s="536"/>
-      <c r="F73" s="543"/>
-      <c r="G73" s="554"/>
+      <c r="A73" s="571"/>
+      <c r="B73" s="571"/>
+      <c r="C73" s="571"/>
+      <c r="D73" s="571"/>
+      <c r="E73" s="571"/>
+      <c r="F73" s="634"/>
+      <c r="G73" s="592"/>
       <c r="H73" s="249"/>
       <c r="I73" s="95"/>
       <c r="J73" s="95"/>
@@ -22398,39 +22445,39 @@
       <c r="HW73" s="6"/>
     </row>
     <row r="74" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="541"/>
-      <c r="B74" s="541"/>
-      <c r="C74" s="541"/>
-      <c r="D74" s="541"/>
-      <c r="E74" s="577"/>
-      <c r="F74" s="543"/>
-      <c r="G74" s="569" t="s">
+      <c r="A74" s="573"/>
+      <c r="B74" s="573"/>
+      <c r="C74" s="573"/>
+      <c r="D74" s="573"/>
+      <c r="E74" s="642"/>
+      <c r="F74" s="634"/>
+      <c r="G74" s="610" t="s">
         <v>24</v>
       </c>
       <c r="H74" s="223"/>
       <c r="I74" s="6"/>
-      <c r="J74" s="562"/>
-      <c r="K74" s="531"/>
-      <c r="L74" s="562"/>
-      <c r="M74" s="533"/>
-      <c r="N74" s="533"/>
-      <c r="O74" s="533"/>
-      <c r="P74" s="533"/>
-      <c r="Q74" s="533"/>
-      <c r="R74" s="533"/>
-      <c r="S74" s="531"/>
-      <c r="T74" s="539"/>
-      <c r="U74" s="528"/>
-      <c r="V74" s="528"/>
-      <c r="W74" s="529"/>
-      <c r="X74" s="539"/>
-      <c r="Y74" s="528"/>
-      <c r="Z74" s="528"/>
-      <c r="AA74" s="529"/>
-      <c r="AB74" s="574"/>
-      <c r="AC74" s="528"/>
-      <c r="AD74" s="528"/>
-      <c r="AE74" s="528"/>
+      <c r="J74" s="622"/>
+      <c r="K74" s="554"/>
+      <c r="L74" s="622"/>
+      <c r="M74" s="563"/>
+      <c r="N74" s="563"/>
+      <c r="O74" s="563"/>
+      <c r="P74" s="563"/>
+      <c r="Q74" s="563"/>
+      <c r="R74" s="563"/>
+      <c r="S74" s="554"/>
+      <c r="T74" s="621"/>
+      <c r="U74" s="562"/>
+      <c r="V74" s="562"/>
+      <c r="W74" s="556"/>
+      <c r="X74" s="621"/>
+      <c r="Y74" s="562"/>
+      <c r="Z74" s="562"/>
+      <c r="AA74" s="556"/>
+      <c r="AB74" s="583"/>
+      <c r="AC74" s="562"/>
+      <c r="AD74" s="562"/>
+      <c r="AE74" s="562"/>
       <c r="AF74" s="143"/>
       <c r="AG74" s="6"/>
       <c r="AH74" s="6"/>
@@ -22633,33 +22680,33 @@
       <c r="HW74" s="6"/>
     </row>
     <row r="75" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A75" s="535"/>
-      <c r="B75" s="535"/>
-      <c r="C75" s="535"/>
-      <c r="D75" s="535"/>
-      <c r="E75" s="535"/>
-      <c r="F75" s="543"/>
-      <c r="G75" s="548"/>
+      <c r="A75" s="570"/>
+      <c r="B75" s="570"/>
+      <c r="C75" s="570"/>
+      <c r="D75" s="570"/>
+      <c r="E75" s="570"/>
+      <c r="F75" s="634"/>
+      <c r="G75" s="580"/>
       <c r="H75" s="223"/>
       <c r="I75" s="6"/>
-      <c r="J75" s="550"/>
-      <c r="K75" s="531"/>
-      <c r="L75" s="548"/>
-      <c r="M75" s="533"/>
-      <c r="N75" s="533"/>
-      <c r="O75" s="533"/>
-      <c r="P75" s="533"/>
-      <c r="Q75" s="533"/>
-      <c r="R75" s="533"/>
-      <c r="S75" s="531"/>
-      <c r="T75" s="550"/>
-      <c r="U75" s="533"/>
-      <c r="V75" s="533"/>
-      <c r="W75" s="531"/>
-      <c r="X75" s="550"/>
-      <c r="Y75" s="533"/>
-      <c r="Z75" s="533"/>
-      <c r="AA75" s="531"/>
+      <c r="J75" s="600"/>
+      <c r="K75" s="554"/>
+      <c r="L75" s="580"/>
+      <c r="M75" s="563"/>
+      <c r="N75" s="563"/>
+      <c r="O75" s="563"/>
+      <c r="P75" s="563"/>
+      <c r="Q75" s="563"/>
+      <c r="R75" s="563"/>
+      <c r="S75" s="554"/>
+      <c r="T75" s="600"/>
+      <c r="U75" s="563"/>
+      <c r="V75" s="563"/>
+      <c r="W75" s="554"/>
+      <c r="X75" s="600"/>
+      <c r="Y75" s="563"/>
+      <c r="Z75" s="563"/>
+      <c r="AA75" s="554"/>
       <c r="AB75" s="63"/>
       <c r="AC75" s="64"/>
       <c r="AD75" s="64"/>
@@ -22866,17 +22913,17 @@
       <c r="HW75" s="6"/>
     </row>
     <row r="76" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A76" s="536"/>
-      <c r="B76" s="536"/>
-      <c r="C76" s="536"/>
-      <c r="D76" s="536"/>
-      <c r="E76" s="536"/>
-      <c r="F76" s="543"/>
-      <c r="G76" s="554"/>
+      <c r="A76" s="571"/>
+      <c r="B76" s="571"/>
+      <c r="C76" s="571"/>
+      <c r="D76" s="571"/>
+      <c r="E76" s="571"/>
+      <c r="F76" s="634"/>
+      <c r="G76" s="592"/>
       <c r="H76" s="331"/>
       <c r="I76" s="195"/>
-      <c r="J76" s="619"/>
-      <c r="K76" s="531"/>
+      <c r="J76" s="582"/>
+      <c r="K76" s="554"/>
       <c r="L76" s="86"/>
       <c r="M76" s="95"/>
       <c r="N76" s="95"/>
@@ -22886,12 +22933,12 @@
       <c r="R76" s="195"/>
       <c r="S76" s="96"/>
       <c r="T76" s="225"/>
-      <c r="U76" s="570"/>
-      <c r="V76" s="533"/>
+      <c r="U76" s="564"/>
+      <c r="V76" s="563"/>
       <c r="W76" s="226"/>
       <c r="X76" s="227"/>
-      <c r="Y76" s="570"/>
-      <c r="Z76" s="533"/>
+      <c r="Y76" s="564"/>
+      <c r="Z76" s="563"/>
       <c r="AA76" s="429"/>
       <c r="AB76" s="86"/>
       <c r="AC76" s="95"/>
@@ -23099,19 +23146,19 @@
       <c r="HW76" s="6"/>
     </row>
     <row r="77" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A77" s="541"/>
-      <c r="B77" s="541"/>
-      <c r="C77" s="541"/>
-      <c r="D77" s="541"/>
-      <c r="E77" s="577"/>
-      <c r="F77" s="543"/>
-      <c r="G77" s="602" t="s">
+      <c r="A77" s="573"/>
+      <c r="B77" s="573"/>
+      <c r="C77" s="573"/>
+      <c r="D77" s="573"/>
+      <c r="E77" s="642"/>
+      <c r="F77" s="634"/>
+      <c r="G77" s="589" t="s">
         <v>25</v>
       </c>
       <c r="H77" s="223"/>
       <c r="I77" s="6"/>
-      <c r="J77" s="608"/>
-      <c r="K77" s="531"/>
+      <c r="J77" s="598"/>
+      <c r="K77" s="554"/>
       <c r="L77" s="6"/>
       <c r="M77" s="140"/>
       <c r="N77" s="430"/>
@@ -23334,13 +23381,13 @@
       <c r="HW77" s="6"/>
     </row>
     <row r="78" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A78" s="535"/>
-      <c r="B78" s="535"/>
-      <c r="C78" s="535"/>
-      <c r="D78" s="535"/>
-      <c r="E78" s="535"/>
-      <c r="F78" s="543"/>
-      <c r="G78" s="548"/>
+      <c r="A78" s="570"/>
+      <c r="B78" s="570"/>
+      <c r="C78" s="570"/>
+      <c r="D78" s="570"/>
+      <c r="E78" s="570"/>
+      <c r="F78" s="634"/>
+      <c r="G78" s="580"/>
       <c r="H78" s="167"/>
       <c r="I78" s="26"/>
       <c r="J78" s="42"/>
@@ -23567,17 +23614,17 @@
       <c r="HW78" s="6"/>
     </row>
     <row r="79" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A79" s="536"/>
-      <c r="B79" s="536"/>
-      <c r="C79" s="536"/>
-      <c r="D79" s="536"/>
-      <c r="E79" s="536"/>
-      <c r="F79" s="544"/>
-      <c r="G79" s="601"/>
+      <c r="A79" s="571"/>
+      <c r="B79" s="571"/>
+      <c r="C79" s="571"/>
+      <c r="D79" s="571"/>
+      <c r="E79" s="571"/>
+      <c r="F79" s="668"/>
+      <c r="G79" s="590"/>
       <c r="H79" s="167"/>
       <c r="I79" s="26"/>
-      <c r="J79" s="621"/>
-      <c r="K79" s="552"/>
+      <c r="J79" s="625"/>
+      <c r="K79" s="594"/>
       <c r="L79" s="201"/>
       <c r="M79" s="201"/>
       <c r="N79" s="344"/>
@@ -23800,15 +23847,15 @@
       <c r="HW79" s="6"/>
     </row>
     <row r="80" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="541"/>
-      <c r="B80" s="537"/>
-      <c r="C80" s="537"/>
-      <c r="D80" s="537"/>
-      <c r="E80" s="537"/>
-      <c r="F80" s="542" t="s">
+      <c r="A80" s="573"/>
+      <c r="B80" s="602"/>
+      <c r="C80" s="602"/>
+      <c r="D80" s="602"/>
+      <c r="E80" s="602"/>
+      <c r="F80" s="667" t="s">
         <v>29</v>
       </c>
-      <c r="G80" s="625" t="s">
+      <c r="G80" s="595" t="s">
         <v>18</v>
       </c>
       <c r="H80" s="233"/>
@@ -24037,13 +24084,13 @@
       <c r="HW80" s="6"/>
     </row>
     <row r="81" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="535"/>
-      <c r="B81" s="535"/>
-      <c r="C81" s="535"/>
-      <c r="D81" s="535"/>
-      <c r="E81" s="535"/>
-      <c r="F81" s="543"/>
-      <c r="G81" s="548"/>
+      <c r="A81" s="570"/>
+      <c r="B81" s="570"/>
+      <c r="C81" s="570"/>
+      <c r="D81" s="570"/>
+      <c r="E81" s="570"/>
+      <c r="F81" s="634"/>
+      <c r="G81" s="580"/>
       <c r="H81" s="167"/>
       <c r="I81" s="26"/>
       <c r="J81" s="26"/>
@@ -24270,13 +24317,13 @@
       <c r="HW81" s="6"/>
     </row>
     <row r="82" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A82" s="536"/>
-      <c r="B82" s="536"/>
-      <c r="C82" s="536"/>
-      <c r="D82" s="536"/>
-      <c r="E82" s="536"/>
-      <c r="F82" s="543"/>
-      <c r="G82" s="554"/>
+      <c r="A82" s="571"/>
+      <c r="B82" s="571"/>
+      <c r="C82" s="571"/>
+      <c r="D82" s="571"/>
+      <c r="E82" s="571"/>
+      <c r="F82" s="634"/>
+      <c r="G82" s="592"/>
       <c r="H82" s="167"/>
       <c r="I82" s="26"/>
       <c r="J82" s="26"/>
@@ -24503,23 +24550,23 @@
       <c r="HW82" s="6"/>
     </row>
     <row r="83" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A83" s="538">
+      <c r="A83" s="585">
         <v>10</v>
       </c>
-      <c r="B83" s="538">
+      <c r="B83" s="585">
         <v>10</v>
       </c>
-      <c r="C83" s="538">
+      <c r="C83" s="585">
         <v>7</v>
       </c>
-      <c r="D83" s="626">
+      <c r="D83" s="584">
         <v>5</v>
       </c>
-      <c r="E83" s="538">
+      <c r="E83" s="585">
         <v>2</v>
       </c>
-      <c r="F83" s="543"/>
-      <c r="G83" s="560" t="s">
+      <c r="F83" s="634"/>
+      <c r="G83" s="591" t="s">
         <v>19</v>
       </c>
       <c r="H83" s="353"/>
@@ -24530,10 +24577,10 @@
       <c r="M83" s="55"/>
       <c r="N83" s="55"/>
       <c r="O83" s="450"/>
-      <c r="P83" s="631"/>
-      <c r="Q83" s="565"/>
-      <c r="R83" s="565"/>
-      <c r="S83" s="632"/>
+      <c r="P83" s="611"/>
+      <c r="Q83" s="604"/>
+      <c r="R83" s="604"/>
+      <c r="S83" s="612"/>
       <c r="T83" s="451"/>
       <c r="U83" s="451"/>
       <c r="V83" s="451"/>
@@ -24748,13 +24795,13 @@
       <c r="HW83" s="6"/>
     </row>
     <row r="84" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A84" s="535"/>
-      <c r="B84" s="535"/>
-      <c r="C84" s="535"/>
-      <c r="D84" s="535"/>
-      <c r="E84" s="535"/>
-      <c r="F84" s="543"/>
-      <c r="G84" s="548"/>
+      <c r="A84" s="570"/>
+      <c r="B84" s="570"/>
+      <c r="C84" s="570"/>
+      <c r="D84" s="570"/>
+      <c r="E84" s="570"/>
+      <c r="F84" s="634"/>
+      <c r="G84" s="580"/>
       <c r="H84" s="167"/>
       <c r="I84" s="26"/>
       <c r="J84" s="26"/>
@@ -24981,13 +25028,13 @@
       <c r="HW84" s="6"/>
     </row>
     <row r="85" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A85" s="536"/>
-      <c r="B85" s="536"/>
-      <c r="C85" s="536"/>
-      <c r="D85" s="536"/>
-      <c r="E85" s="536"/>
-      <c r="F85" s="543"/>
-      <c r="G85" s="554"/>
+      <c r="A85" s="571"/>
+      <c r="B85" s="571"/>
+      <c r="C85" s="571"/>
+      <c r="D85" s="571"/>
+      <c r="E85" s="571"/>
+      <c r="F85" s="634"/>
+      <c r="G85" s="592"/>
       <c r="H85" s="167"/>
       <c r="I85" s="26"/>
       <c r="J85" s="26"/>
@@ -25214,35 +25261,35 @@
       <c r="HW85" s="6"/>
     </row>
     <row r="86" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="538">
+      <c r="A86" s="585">
         <v>24</v>
       </c>
-      <c r="B86" s="538">
+      <c r="B86" s="585">
         <v>24</v>
       </c>
-      <c r="C86" s="538">
+      <c r="C86" s="585">
         <v>21</v>
       </c>
-      <c r="D86" s="626">
+      <c r="D86" s="584">
         <v>19</v>
       </c>
-      <c r="E86" s="540"/>
-      <c r="F86" s="543"/>
-      <c r="G86" s="609" t="s">
+      <c r="E86" s="569"/>
+      <c r="F86" s="634"/>
+      <c r="G86" s="623" t="s">
         <v>20</v>
       </c>
       <c r="H86" s="351"/>
       <c r="I86" s="36"/>
       <c r="J86" s="36"/>
       <c r="K86" s="352"/>
-      <c r="L86" s="563"/>
-      <c r="M86" s="528"/>
-      <c r="N86" s="528"/>
-      <c r="O86" s="528"/>
-      <c r="P86" s="528"/>
-      <c r="Q86" s="528"/>
-      <c r="R86" s="528"/>
-      <c r="S86" s="529"/>
+      <c r="L86" s="555"/>
+      <c r="M86" s="562"/>
+      <c r="N86" s="562"/>
+      <c r="O86" s="562"/>
+      <c r="P86" s="562"/>
+      <c r="Q86" s="562"/>
+      <c r="R86" s="562"/>
+      <c r="S86" s="556"/>
       <c r="T86" s="56"/>
       <c r="U86" s="57"/>
       <c r="V86" s="57"/>
@@ -25251,10 +25298,10 @@
       <c r="Y86" s="57"/>
       <c r="Z86" s="57"/>
       <c r="AA86" s="57"/>
-      <c r="AB86" s="563"/>
-      <c r="AC86" s="528"/>
-      <c r="AD86" s="528"/>
-      <c r="AE86" s="529"/>
+      <c r="AB86" s="555"/>
+      <c r="AC86" s="562"/>
+      <c r="AD86" s="562"/>
+      <c r="AE86" s="556"/>
       <c r="AF86" s="56"/>
       <c r="AG86" s="57"/>
       <c r="AH86" s="57"/>
@@ -25457,25 +25504,25 @@
       <c r="HW86" s="6"/>
     </row>
     <row r="87" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A87" s="535"/>
-      <c r="B87" s="535"/>
-      <c r="C87" s="535"/>
-      <c r="D87" s="535"/>
-      <c r="E87" s="535"/>
-      <c r="F87" s="543"/>
-      <c r="G87" s="548"/>
+      <c r="A87" s="570"/>
+      <c r="B87" s="570"/>
+      <c r="C87" s="570"/>
+      <c r="D87" s="570"/>
+      <c r="E87" s="570"/>
+      <c r="F87" s="634"/>
+      <c r="G87" s="580"/>
       <c r="H87" s="152"/>
       <c r="I87" s="10"/>
       <c r="J87" s="10"/>
       <c r="K87" s="145"/>
-      <c r="L87" s="586"/>
-      <c r="M87" s="533"/>
-      <c r="N87" s="533"/>
-      <c r="O87" s="533"/>
-      <c r="P87" s="533"/>
-      <c r="Q87" s="533"/>
-      <c r="R87" s="533"/>
-      <c r="S87" s="531"/>
+      <c r="L87" s="671"/>
+      <c r="M87" s="563"/>
+      <c r="N87" s="563"/>
+      <c r="O87" s="563"/>
+      <c r="P87" s="563"/>
+      <c r="Q87" s="563"/>
+      <c r="R87" s="563"/>
+      <c r="S87" s="554"/>
       <c r="T87" s="59"/>
       <c r="U87" s="60"/>
       <c r="V87" s="60"/>
@@ -25484,10 +25531,10 @@
       <c r="Y87" s="60"/>
       <c r="Z87" s="60"/>
       <c r="AA87" s="60"/>
-      <c r="AB87" s="571"/>
-      <c r="AC87" s="533"/>
-      <c r="AD87" s="533"/>
-      <c r="AE87" s="531"/>
+      <c r="AB87" s="601"/>
+      <c r="AC87" s="563"/>
+      <c r="AD87" s="563"/>
+      <c r="AE87" s="554"/>
       <c r="AF87" s="134"/>
       <c r="AG87" s="66"/>
       <c r="AH87" s="66"/>
@@ -25690,13 +25737,13 @@
       <c r="HW87" s="6"/>
     </row>
     <row r="88" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A88" s="536"/>
-      <c r="B88" s="536"/>
-      <c r="C88" s="536"/>
-      <c r="D88" s="536"/>
-      <c r="E88" s="536"/>
-      <c r="F88" s="543"/>
-      <c r="G88" s="610"/>
+      <c r="A88" s="571"/>
+      <c r="B88" s="571"/>
+      <c r="C88" s="571"/>
+      <c r="D88" s="571"/>
+      <c r="E88" s="571"/>
+      <c r="F88" s="634"/>
+      <c r="G88" s="581"/>
       <c r="H88" s="455"/>
       <c r="I88" s="456"/>
       <c r="J88" s="456"/>
@@ -25718,8 +25765,8 @@
       <c r="Z88" s="72"/>
       <c r="AA88" s="72"/>
       <c r="AB88" s="223"/>
-      <c r="AC88" s="570"/>
-      <c r="AD88" s="533"/>
+      <c r="AC88" s="564"/>
+      <c r="AD88" s="563"/>
       <c r="AE88" s="149"/>
       <c r="AF88" s="458"/>
       <c r="AG88" s="262"/>
@@ -25923,37 +25970,37 @@
       <c r="HW88" s="6"/>
     </row>
     <row r="89" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A89" s="540">
+      <c r="A89" s="569">
         <v>0</v>
       </c>
-      <c r="B89" s="540">
+      <c r="B89" s="569">
         <v>0</v>
       </c>
-      <c r="C89" s="540">
+      <c r="C89" s="569">
         <v>0</v>
       </c>
-      <c r="D89" s="540">
+      <c r="D89" s="569">
         <v>0</v>
       </c>
-      <c r="E89" s="540">
+      <c r="E89" s="569">
         <v>0</v>
       </c>
-      <c r="F89" s="543"/>
-      <c r="G89" s="622" t="s">
+      <c r="F89" s="634"/>
+      <c r="G89" s="626" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="263"/>
       <c r="I89" s="53"/>
       <c r="J89" s="53"/>
       <c r="K89" s="264"/>
-      <c r="L89" s="562"/>
-      <c r="M89" s="533"/>
-      <c r="N89" s="533"/>
-      <c r="O89" s="533"/>
-      <c r="P89" s="533"/>
-      <c r="Q89" s="533"/>
-      <c r="R89" s="533"/>
-      <c r="S89" s="531"/>
+      <c r="L89" s="622"/>
+      <c r="M89" s="563"/>
+      <c r="N89" s="563"/>
+      <c r="O89" s="563"/>
+      <c r="P89" s="563"/>
+      <c r="Q89" s="563"/>
+      <c r="R89" s="563"/>
+      <c r="S89" s="554"/>
       <c r="T89" s="364"/>
       <c r="U89" s="365"/>
       <c r="V89" s="78"/>
@@ -26168,25 +26215,25 @@
       <c r="HW89" s="6"/>
     </row>
     <row r="90" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A90" s="535"/>
-      <c r="B90" s="535"/>
-      <c r="C90" s="535"/>
-      <c r="D90" s="535"/>
-      <c r="E90" s="535"/>
-      <c r="F90" s="543"/>
-      <c r="G90" s="548"/>
+      <c r="A90" s="570"/>
+      <c r="B90" s="570"/>
+      <c r="C90" s="570"/>
+      <c r="D90" s="570"/>
+      <c r="E90" s="570"/>
+      <c r="F90" s="634"/>
+      <c r="G90" s="580"/>
       <c r="H90" s="263"/>
       <c r="I90" s="53"/>
       <c r="J90" s="53"/>
       <c r="K90" s="261"/>
-      <c r="L90" s="548"/>
-      <c r="M90" s="533"/>
-      <c r="N90" s="533"/>
-      <c r="O90" s="533"/>
-      <c r="P90" s="533"/>
-      <c r="Q90" s="533"/>
-      <c r="R90" s="533"/>
-      <c r="S90" s="531"/>
+      <c r="L90" s="580"/>
+      <c r="M90" s="563"/>
+      <c r="N90" s="563"/>
+      <c r="O90" s="563"/>
+      <c r="P90" s="563"/>
+      <c r="Q90" s="563"/>
+      <c r="R90" s="563"/>
+      <c r="S90" s="554"/>
       <c r="T90" s="211"/>
       <c r="U90" s="83"/>
       <c r="V90" s="26"/>
@@ -26401,13 +26448,13 @@
       <c r="HW90" s="6"/>
     </row>
     <row r="91" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A91" s="536"/>
-      <c r="B91" s="536"/>
-      <c r="C91" s="536"/>
-      <c r="D91" s="536"/>
-      <c r="E91" s="536"/>
-      <c r="F91" s="543"/>
-      <c r="G91" s="548"/>
+      <c r="A91" s="571"/>
+      <c r="B91" s="571"/>
+      <c r="C91" s="571"/>
+      <c r="D91" s="571"/>
+      <c r="E91" s="571"/>
+      <c r="F91" s="634"/>
+      <c r="G91" s="580"/>
       <c r="H91" s="260"/>
       <c r="I91" s="69"/>
       <c r="J91" s="69"/>
@@ -26634,13 +26681,13 @@
       <c r="HW91" s="6"/>
     </row>
     <row r="92" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A92" s="541"/>
-      <c r="B92" s="541"/>
-      <c r="C92" s="541"/>
-      <c r="D92" s="541"/>
-      <c r="E92" s="541"/>
-      <c r="F92" s="543"/>
-      <c r="G92" s="560" t="s">
+      <c r="A92" s="573"/>
+      <c r="B92" s="573"/>
+      <c r="C92" s="573"/>
+      <c r="D92" s="573"/>
+      <c r="E92" s="573"/>
+      <c r="F92" s="634"/>
+      <c r="G92" s="591" t="s">
         <v>24</v>
       </c>
       <c r="H92" s="256"/>
@@ -26869,13 +26916,13 @@
       <c r="HW92" s="6"/>
     </row>
     <row r="93" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A93" s="535"/>
-      <c r="B93" s="535"/>
-      <c r="C93" s="535"/>
-      <c r="D93" s="535"/>
-      <c r="E93" s="535"/>
-      <c r="F93" s="543"/>
-      <c r="G93" s="548"/>
+      <c r="A93" s="570"/>
+      <c r="B93" s="570"/>
+      <c r="C93" s="570"/>
+      <c r="D93" s="570"/>
+      <c r="E93" s="570"/>
+      <c r="F93" s="634"/>
+      <c r="G93" s="580"/>
       <c r="H93" s="258"/>
       <c r="I93" s="66"/>
       <c r="J93" s="66"/>
@@ -27102,13 +27149,13 @@
       <c r="HW93" s="6"/>
     </row>
     <row r="94" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A94" s="536"/>
-      <c r="B94" s="536"/>
-      <c r="C94" s="536"/>
-      <c r="D94" s="536"/>
-      <c r="E94" s="536"/>
-      <c r="F94" s="543"/>
-      <c r="G94" s="554"/>
+      <c r="A94" s="571"/>
+      <c r="B94" s="571"/>
+      <c r="C94" s="571"/>
+      <c r="D94" s="571"/>
+      <c r="E94" s="571"/>
+      <c r="F94" s="634"/>
+      <c r="G94" s="592"/>
       <c r="H94" s="265"/>
       <c r="I94" s="93"/>
       <c r="J94" s="93"/>
@@ -27335,13 +27382,13 @@
       <c r="HW94" s="6"/>
     </row>
     <row r="95" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A95" s="541"/>
-      <c r="B95" s="541"/>
-      <c r="C95" s="541"/>
-      <c r="D95" s="541"/>
-      <c r="E95" s="541"/>
-      <c r="F95" s="543"/>
-      <c r="G95" s="602" t="s">
+      <c r="A95" s="573"/>
+      <c r="B95" s="573"/>
+      <c r="C95" s="573"/>
+      <c r="D95" s="573"/>
+      <c r="E95" s="573"/>
+      <c r="F95" s="634"/>
+      <c r="G95" s="589" t="s">
         <v>25</v>
       </c>
       <c r="H95" s="167"/>
@@ -27570,13 +27617,13 @@
       <c r="HW95" s="6"/>
     </row>
     <row r="96" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A96" s="535"/>
-      <c r="B96" s="535"/>
-      <c r="C96" s="535"/>
-      <c r="D96" s="535"/>
-      <c r="E96" s="535"/>
-      <c r="F96" s="543"/>
-      <c r="G96" s="548"/>
+      <c r="A96" s="570"/>
+      <c r="B96" s="570"/>
+      <c r="C96" s="570"/>
+      <c r="D96" s="570"/>
+      <c r="E96" s="570"/>
+      <c r="F96" s="634"/>
+      <c r="G96" s="580"/>
       <c r="H96" s="167"/>
       <c r="I96" s="26"/>
       <c r="J96" s="26"/>
@@ -27803,13 +27850,13 @@
       <c r="HW96" s="6"/>
     </row>
     <row r="97" spans="1:231" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A97" s="536"/>
-      <c r="B97" s="536"/>
-      <c r="C97" s="536"/>
-      <c r="D97" s="536"/>
-      <c r="E97" s="536"/>
-      <c r="F97" s="544"/>
-      <c r="G97" s="601"/>
+      <c r="A97" s="571"/>
+      <c r="B97" s="571"/>
+      <c r="C97" s="571"/>
+      <c r="D97" s="571"/>
+      <c r="E97" s="571"/>
+      <c r="F97" s="668"/>
+      <c r="G97" s="590"/>
       <c r="H97" s="167"/>
       <c r="I97" s="26"/>
       <c r="J97" s="26"/>
@@ -28036,15 +28083,15 @@
       <c r="HW97" s="6"/>
     </row>
     <row r="98" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A98" s="541"/>
-      <c r="B98" s="541"/>
-      <c r="C98" s="541"/>
-      <c r="D98" s="541"/>
-      <c r="E98" s="541"/>
-      <c r="F98" s="579" t="s">
+      <c r="A98" s="573"/>
+      <c r="B98" s="573"/>
+      <c r="C98" s="573"/>
+      <c r="D98" s="573"/>
+      <c r="E98" s="573"/>
+      <c r="F98" s="633" t="s">
         <v>30</v>
       </c>
-      <c r="G98" s="575" t="s">
+      <c r="G98" s="664" t="s">
         <v>18</v>
       </c>
       <c r="H98" s="474"/>
@@ -28273,13 +28320,13 @@
       <c r="HW98" s="6"/>
     </row>
     <row r="99" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="535"/>
-      <c r="B99" s="535"/>
-      <c r="C99" s="535"/>
-      <c r="D99" s="535"/>
-      <c r="E99" s="535"/>
-      <c r="F99" s="543"/>
-      <c r="G99" s="548"/>
+      <c r="A99" s="570"/>
+      <c r="B99" s="570"/>
+      <c r="C99" s="570"/>
+      <c r="D99" s="570"/>
+      <c r="E99" s="570"/>
+      <c r="F99" s="634"/>
+      <c r="G99" s="580"/>
       <c r="H99" s="223"/>
       <c r="I99" s="6"/>
       <c r="J99" s="6"/>
@@ -28506,13 +28553,13 @@
       <c r="HW99" s="6"/>
     </row>
     <row r="100" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A100" s="536"/>
-      <c r="B100" s="536"/>
-      <c r="C100" s="536"/>
-      <c r="D100" s="536"/>
-      <c r="E100" s="536"/>
-      <c r="F100" s="543"/>
-      <c r="G100" s="548"/>
+      <c r="A100" s="571"/>
+      <c r="B100" s="571"/>
+      <c r="C100" s="571"/>
+      <c r="D100" s="571"/>
+      <c r="E100" s="571"/>
+      <c r="F100" s="634"/>
+      <c r="G100" s="580"/>
       <c r="H100" s="223"/>
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
@@ -28739,21 +28786,21 @@
       <c r="HW100" s="6"/>
     </row>
     <row r="101" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="538">
+      <c r="A101" s="585">
         <v>11</v>
       </c>
-      <c r="B101" s="538">
+      <c r="B101" s="585">
         <v>11</v>
       </c>
-      <c r="C101" s="538">
+      <c r="C101" s="585">
         <v>8</v>
       </c>
-      <c r="D101" s="538">
+      <c r="D101" s="585">
         <v>6</v>
       </c>
-      <c r="E101" s="540"/>
-      <c r="F101" s="543"/>
-      <c r="G101" s="560" t="s">
+      <c r="E101" s="569"/>
+      <c r="F101" s="634"/>
+      <c r="G101" s="591" t="s">
         <v>19</v>
       </c>
       <c r="H101" s="351"/>
@@ -28982,13 +29029,13 @@
       <c r="HW101" s="6"/>
     </row>
     <row r="102" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A102" s="535"/>
-      <c r="B102" s="535"/>
-      <c r="C102" s="535"/>
-      <c r="D102" s="535"/>
-      <c r="E102" s="535"/>
-      <c r="F102" s="543"/>
-      <c r="G102" s="548"/>
+      <c r="A102" s="570"/>
+      <c r="B102" s="570"/>
+      <c r="C102" s="570"/>
+      <c r="D102" s="570"/>
+      <c r="E102" s="570"/>
+      <c r="F102" s="634"/>
+      <c r="G102" s="580"/>
       <c r="H102" s="152"/>
       <c r="I102" s="10"/>
       <c r="J102" s="10"/>
@@ -29215,13 +29262,13 @@
       <c r="HW102" s="6"/>
     </row>
     <row r="103" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A103" s="536"/>
-      <c r="B103" s="536"/>
-      <c r="C103" s="536"/>
-      <c r="D103" s="536"/>
-      <c r="E103" s="536"/>
-      <c r="F103" s="543"/>
-      <c r="G103" s="554"/>
+      <c r="A103" s="571"/>
+      <c r="B103" s="571"/>
+      <c r="C103" s="571"/>
+      <c r="D103" s="571"/>
+      <c r="E103" s="571"/>
+      <c r="F103" s="634"/>
+      <c r="G103" s="592"/>
       <c r="H103" s="481"/>
       <c r="I103" s="46"/>
       <c r="J103" s="46"/>
@@ -29448,23 +29495,23 @@
       <c r="HW103" s="6"/>
     </row>
     <row r="104" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="538">
+      <c r="A104" s="585">
         <v>25</v>
       </c>
-      <c r="B104" s="538">
+      <c r="B104" s="585">
         <v>25</v>
       </c>
-      <c r="C104" s="538">
+      <c r="C104" s="585">
         <v>22</v>
       </c>
-      <c r="D104" s="538">
+      <c r="D104" s="585">
         <v>20</v>
       </c>
-      <c r="E104" s="540">
+      <c r="E104" s="569">
         <v>0</v>
       </c>
-      <c r="F104" s="543"/>
-      <c r="G104" s="566" t="s">
+      <c r="F104" s="634"/>
+      <c r="G104" s="630" t="s">
         <v>20</v>
       </c>
       <c r="H104" s="351"/>
@@ -29693,13 +29740,13 @@
       <c r="HW104" s="6"/>
     </row>
     <row r="105" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="535"/>
-      <c r="B105" s="535"/>
-      <c r="C105" s="535"/>
-      <c r="D105" s="535"/>
-      <c r="E105" s="535"/>
-      <c r="F105" s="543"/>
-      <c r="G105" s="548"/>
+      <c r="A105" s="570"/>
+      <c r="B105" s="570"/>
+      <c r="C105" s="570"/>
+      <c r="D105" s="570"/>
+      <c r="E105" s="570"/>
+      <c r="F105" s="634"/>
+      <c r="G105" s="580"/>
       <c r="H105" s="152"/>
       <c r="I105" s="10"/>
       <c r="J105" s="10"/>
@@ -29926,13 +29973,13 @@
       <c r="HW105" s="6"/>
     </row>
     <row r="106" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A106" s="536"/>
-      <c r="B106" s="536"/>
-      <c r="C106" s="536"/>
-      <c r="D106" s="536"/>
-      <c r="E106" s="536"/>
-      <c r="F106" s="543"/>
-      <c r="G106" s="567"/>
+      <c r="A106" s="571"/>
+      <c r="B106" s="571"/>
+      <c r="C106" s="571"/>
+      <c r="D106" s="571"/>
+      <c r="E106" s="571"/>
+      <c r="F106" s="634"/>
+      <c r="G106" s="631"/>
       <c r="H106" s="455"/>
       <c r="I106" s="456"/>
       <c r="J106" s="456"/>
@@ -30159,23 +30206,23 @@
       <c r="HW106" s="6"/>
     </row>
     <row r="107" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A107" s="540">
+      <c r="A107" s="569">
         <v>0</v>
       </c>
-      <c r="B107" s="540">
+      <c r="B107" s="569">
         <v>0</v>
       </c>
-      <c r="C107" s="540">
+      <c r="C107" s="569">
         <v>0</v>
       </c>
-      <c r="D107" s="540">
+      <c r="D107" s="569">
         <v>0</v>
       </c>
-      <c r="E107" s="540">
+      <c r="E107" s="569">
         <v>0</v>
       </c>
-      <c r="F107" s="543"/>
-      <c r="G107" s="569" t="s">
+      <c r="F107" s="634"/>
+      <c r="G107" s="610" t="s">
         <v>22</v>
       </c>
       <c r="H107" s="152"/>
@@ -30404,13 +30451,13 @@
       <c r="HW107" s="6"/>
     </row>
     <row r="108" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A108" s="535"/>
-      <c r="B108" s="535"/>
-      <c r="C108" s="535"/>
-      <c r="D108" s="535"/>
-      <c r="E108" s="535"/>
-      <c r="F108" s="543"/>
-      <c r="G108" s="548"/>
+      <c r="A108" s="570"/>
+      <c r="B108" s="570"/>
+      <c r="C108" s="570"/>
+      <c r="D108" s="570"/>
+      <c r="E108" s="570"/>
+      <c r="F108" s="634"/>
+      <c r="G108" s="580"/>
       <c r="H108" s="152"/>
       <c r="I108" s="10"/>
       <c r="J108" s="10"/>
@@ -30637,13 +30684,13 @@
       <c r="HW108" s="6"/>
     </row>
     <row r="109" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A109" s="536"/>
-      <c r="B109" s="536"/>
-      <c r="C109" s="536"/>
-      <c r="D109" s="536"/>
-      <c r="E109" s="536"/>
-      <c r="F109" s="543"/>
-      <c r="G109" s="554"/>
+      <c r="A109" s="571"/>
+      <c r="B109" s="571"/>
+      <c r="C109" s="571"/>
+      <c r="D109" s="571"/>
+      <c r="E109" s="571"/>
+      <c r="F109" s="634"/>
+      <c r="G109" s="592"/>
       <c r="H109" s="152"/>
       <c r="I109" s="10"/>
       <c r="J109" s="10"/>
@@ -30870,13 +30917,13 @@
       <c r="HW109" s="6"/>
     </row>
     <row r="110" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A110" s="541"/>
-      <c r="B110" s="541"/>
-      <c r="C110" s="541"/>
-      <c r="D110" s="541"/>
-      <c r="E110" s="541"/>
-      <c r="F110" s="543"/>
-      <c r="G110" s="560" t="s">
+      <c r="A110" s="573"/>
+      <c r="B110" s="573"/>
+      <c r="C110" s="573"/>
+      <c r="D110" s="573"/>
+      <c r="E110" s="573"/>
+      <c r="F110" s="634"/>
+      <c r="G110" s="591" t="s">
         <v>24</v>
       </c>
       <c r="H110" s="491"/>
@@ -31105,13 +31152,13 @@
       <c r="HW110" s="6"/>
     </row>
     <row r="111" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A111" s="535"/>
-      <c r="B111" s="535"/>
-      <c r="C111" s="535"/>
-      <c r="D111" s="535"/>
-      <c r="E111" s="535"/>
-      <c r="F111" s="543"/>
-      <c r="G111" s="548"/>
+      <c r="A111" s="570"/>
+      <c r="B111" s="570"/>
+      <c r="C111" s="570"/>
+      <c r="D111" s="570"/>
+      <c r="E111" s="570"/>
+      <c r="F111" s="634"/>
+      <c r="G111" s="580"/>
       <c r="H111" s="500"/>
       <c r="I111" s="501"/>
       <c r="J111" s="501"/>
@@ -31338,13 +31385,13 @@
       <c r="HW111" s="6"/>
     </row>
     <row r="112" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A112" s="536"/>
-      <c r="B112" s="536"/>
-      <c r="C112" s="536"/>
-      <c r="D112" s="536"/>
-      <c r="E112" s="536"/>
-      <c r="F112" s="543"/>
-      <c r="G112" s="554"/>
+      <c r="A112" s="571"/>
+      <c r="B112" s="571"/>
+      <c r="C112" s="571"/>
+      <c r="D112" s="571"/>
+      <c r="E112" s="571"/>
+      <c r="F112" s="634"/>
+      <c r="G112" s="592"/>
       <c r="H112" s="505"/>
       <c r="I112" s="506"/>
       <c r="J112" s="507"/>
@@ -31571,13 +31618,13 @@
       <c r="HW112" s="6"/>
     </row>
     <row r="113" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A113" s="541"/>
-      <c r="B113" s="541"/>
-      <c r="C113" s="541"/>
-      <c r="D113" s="541"/>
-      <c r="E113" s="541"/>
-      <c r="F113" s="543"/>
-      <c r="G113" s="606" t="s">
+      <c r="A113" s="573"/>
+      <c r="B113" s="573"/>
+      <c r="C113" s="573"/>
+      <c r="D113" s="573"/>
+      <c r="E113" s="573"/>
+      <c r="F113" s="634"/>
+      <c r="G113" s="644" t="s">
         <v>25</v>
       </c>
       <c r="H113" s="500"/>
@@ -31806,13 +31853,13 @@
       <c r="HW113" s="6"/>
     </row>
     <row r="114" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A114" s="535"/>
-      <c r="B114" s="535"/>
-      <c r="C114" s="535"/>
-      <c r="D114" s="535"/>
-      <c r="E114" s="535"/>
-      <c r="F114" s="543"/>
-      <c r="G114" s="548"/>
+      <c r="A114" s="570"/>
+      <c r="B114" s="570"/>
+      <c r="C114" s="570"/>
+      <c r="D114" s="570"/>
+      <c r="E114" s="570"/>
+      <c r="F114" s="634"/>
+      <c r="G114" s="580"/>
       <c r="H114" s="500"/>
       <c r="I114" s="501"/>
       <c r="J114" s="219"/>
@@ -32039,13 +32086,13 @@
       <c r="HW114" s="6"/>
     </row>
     <row r="115" spans="1:231" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A115" s="536"/>
-      <c r="B115" s="536"/>
-      <c r="C115" s="536"/>
-      <c r="D115" s="536"/>
-      <c r="E115" s="536"/>
-      <c r="F115" s="543"/>
-      <c r="G115" s="607"/>
+      <c r="A115" s="571"/>
+      <c r="B115" s="571"/>
+      <c r="C115" s="571"/>
+      <c r="D115" s="571"/>
+      <c r="E115" s="571"/>
+      <c r="F115" s="634"/>
+      <c r="G115" s="645"/>
       <c r="H115" s="517"/>
       <c r="I115" s="518"/>
       <c r="J115" s="519"/>
@@ -32289,48 +32336,48 @@
       </c>
       <c r="F116" s="524"/>
       <c r="G116" s="525"/>
-      <c r="H116" s="598" t="s">
+      <c r="H116" s="639" t="s">
         <v>10</v>
       </c>
-      <c r="I116" s="557"/>
-      <c r="J116" s="557"/>
-      <c r="K116" s="596"/>
-      <c r="L116" s="556" t="s">
+      <c r="I116" s="587"/>
+      <c r="J116" s="587"/>
+      <c r="K116" s="640"/>
+      <c r="L116" s="629" t="s">
         <v>11</v>
       </c>
-      <c r="M116" s="557"/>
-      <c r="N116" s="557"/>
-      <c r="O116" s="558"/>
-      <c r="P116" s="604" t="s">
+      <c r="M116" s="587"/>
+      <c r="N116" s="587"/>
+      <c r="O116" s="588"/>
+      <c r="P116" s="586" t="s">
         <v>12</v>
       </c>
-      <c r="Q116" s="557"/>
-      <c r="R116" s="557"/>
-      <c r="S116" s="558"/>
-      <c r="T116" s="605" t="s">
+      <c r="Q116" s="587"/>
+      <c r="R116" s="587"/>
+      <c r="S116" s="588"/>
+      <c r="T116" s="643" t="s">
         <v>13</v>
       </c>
-      <c r="U116" s="557"/>
-      <c r="V116" s="557"/>
-      <c r="W116" s="596"/>
-      <c r="X116" s="585" t="s">
+      <c r="U116" s="587"/>
+      <c r="V116" s="587"/>
+      <c r="W116" s="640"/>
+      <c r="X116" s="638" t="s">
         <v>14</v>
       </c>
-      <c r="Y116" s="557"/>
-      <c r="Z116" s="557"/>
-      <c r="AA116" s="557"/>
-      <c r="AB116" s="604" t="s">
+      <c r="Y116" s="587"/>
+      <c r="Z116" s="587"/>
+      <c r="AA116" s="587"/>
+      <c r="AB116" s="586" t="s">
         <v>15</v>
       </c>
-      <c r="AC116" s="557"/>
-      <c r="AD116" s="557"/>
-      <c r="AE116" s="558"/>
-      <c r="AF116" s="581" t="s">
+      <c r="AC116" s="587"/>
+      <c r="AD116" s="587"/>
+      <c r="AE116" s="588"/>
+      <c r="AF116" s="657" t="s">
         <v>16</v>
       </c>
-      <c r="AG116" s="557"/>
-      <c r="AH116" s="557"/>
-      <c r="AI116" s="582"/>
+      <c r="AG116" s="587"/>
+      <c r="AH116" s="587"/>
+      <c r="AI116" s="649"/>
       <c r="AJ116" s="6"/>
       <c r="AK116" s="6"/>
       <c r="AL116" s="6"/>
@@ -33148,38 +33195,310 @@
     <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="362">
-    <mergeCell ref="AD61:AE61"/>
-    <mergeCell ref="AB47:AC47"/>
-    <mergeCell ref="AB48:AC48"/>
-    <mergeCell ref="AB49:AC49"/>
-    <mergeCell ref="AB50:AC50"/>
-    <mergeCell ref="AB52:AC52"/>
-    <mergeCell ref="AD56:AE56"/>
-    <mergeCell ref="AD57:AE57"/>
-    <mergeCell ref="AD58:AE58"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AB68:AE68"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="Y76:Z76"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="L71:O71"/>
-    <mergeCell ref="AB65:AE65"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="AB41:AE41"/>
-    <mergeCell ref="D86:D88"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A95:A97"/>
-    <mergeCell ref="C101:C103"/>
-    <mergeCell ref="C95:C97"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="D95:D97"/>
-    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="X74:AA74"/>
+    <mergeCell ref="D71:D73"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C80:C82"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="F80:F97"/>
+    <mergeCell ref="AG51:AH51"/>
+    <mergeCell ref="AF50:AI50"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="E107:E109"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="G53:G55"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="D113:D115"/>
+    <mergeCell ref="D98:D100"/>
+    <mergeCell ref="D101:D103"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="D65:D67"/>
+    <mergeCell ref="B89:B91"/>
+    <mergeCell ref="L116:O116"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="G110:G112"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="D110:D112"/>
+    <mergeCell ref="A113:A115"/>
+    <mergeCell ref="C113:C115"/>
+    <mergeCell ref="E113:E115"/>
+    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="AF53:AI53"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="AB86:AE86"/>
+    <mergeCell ref="AF71:AI71"/>
+    <mergeCell ref="E101:E103"/>
+    <mergeCell ref="E95:E97"/>
+    <mergeCell ref="G101:G103"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="F62:F79"/>
+    <mergeCell ref="T74:W74"/>
+    <mergeCell ref="L89:S90"/>
+    <mergeCell ref="B83:B85"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="F44:F61"/>
+    <mergeCell ref="D74:D76"/>
+    <mergeCell ref="L86:S87"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="AC88:AD88"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="E53:E55"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="AB87:AE87"/>
+    <mergeCell ref="T32:W32"/>
+    <mergeCell ref="E104:E106"/>
+    <mergeCell ref="X75:AA75"/>
+    <mergeCell ref="G104:G106"/>
+    <mergeCell ref="G98:G100"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="E74:E76"/>
+    <mergeCell ref="F26:F43"/>
+    <mergeCell ref="G35:G37"/>
+    <mergeCell ref="T33:W33"/>
+    <mergeCell ref="E26:E28"/>
+    <mergeCell ref="G26:G28"/>
+    <mergeCell ref="AF116:AI116"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="AF1:AI1"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="X116:AA116"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="E59:E61"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="G107:G109"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="B95:B97"/>
+    <mergeCell ref="E56:E58"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="AF38:AI38"/>
+    <mergeCell ref="AF6:AI6"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="AB71:AE71"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="D35:D37"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="G56:G58"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="F8:F25"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="T6:W6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="AF35:AI35"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="X6:AA6"/>
+    <mergeCell ref="A110:A112"/>
+    <mergeCell ref="C110:C112"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="H116:K116"/>
+    <mergeCell ref="T17:W17"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="AB74:AE74"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="G77:G79"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="P116:S116"/>
+    <mergeCell ref="G83:G85"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="T116:W116"/>
+    <mergeCell ref="G113:G115"/>
+    <mergeCell ref="B101:B103"/>
+    <mergeCell ref="AB116:AE116"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="E110:E112"/>
+    <mergeCell ref="U76:V76"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="P6:S6"/>
+    <mergeCell ref="A104:A106"/>
+    <mergeCell ref="T75:W75"/>
+    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="C98:C100"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="E98:E100"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="B98:B100"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="G68:G70"/>
+    <mergeCell ref="F98:F115"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="H71:K71"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="G59:G61"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="C35:C37"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="AB17:AE17"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="AF68:AI68"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="L74:S75"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="G86:G88"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="E89:E91"/>
+    <mergeCell ref="G89:G91"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="P71:S71"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="R53:S53"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="A101:A103"/>
+    <mergeCell ref="AB38:AE38"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="AB6:AE6"/>
+    <mergeCell ref="D83:D85"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="H68:K68"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="E62:E64"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="X14:AA14"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="E83:E85"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="C56:C58"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="P83:S83"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="X17:AA17"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="T38:AA39"/>
+    <mergeCell ref="T41:AA42"/>
+    <mergeCell ref="J29:K29"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="G95:G97"/>
     <mergeCell ref="A98:A100"/>
@@ -33204,313 +33523,42 @@
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="H29:I29"/>
+    <mergeCell ref="AB68:AE68"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="Y76:Z76"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="L71:O71"/>
+    <mergeCell ref="AB65:AE65"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="AB41:AE41"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A95:A97"/>
+    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="C95:C97"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="D95:D97"/>
+    <mergeCell ref="C89:C91"/>
     <mergeCell ref="R40:S40"/>
     <mergeCell ref="B38:B40"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="X17:AA17"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="T38:AA39"/>
-    <mergeCell ref="T41:AA42"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="E83:E85"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="C56:C58"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="P83:S83"/>
-    <mergeCell ref="AB38:AE38"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="D26:D28"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="AB6:AE6"/>
-    <mergeCell ref="D83:D85"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="H68:K68"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="E62:E64"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="AB14:AE14"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="X14:AA14"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="AB17:AE17"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="AF68:AI68"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="L74:S75"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="E92:E94"/>
-    <mergeCell ref="R55:S55"/>
-    <mergeCell ref="G86:G88"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="E89:E91"/>
-    <mergeCell ref="G89:G91"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="P71:S71"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="R53:S53"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="A101:A103"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="G59:G61"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="C35:C37"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="H53:K53"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="P6:S6"/>
-    <mergeCell ref="A104:A106"/>
-    <mergeCell ref="T75:W75"/>
-    <mergeCell ref="C104:C106"/>
-    <mergeCell ref="C98:C100"/>
-    <mergeCell ref="B59:B61"/>
-    <mergeCell ref="E98:E100"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D56:D58"/>
-    <mergeCell ref="B98:B100"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="G68:G70"/>
-    <mergeCell ref="F98:F115"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="H71:K71"/>
-    <mergeCell ref="G65:G67"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="G62:G64"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="X6:AA6"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="H116:K116"/>
-    <mergeCell ref="T17:W17"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="AB74:AE74"/>
-    <mergeCell ref="E77:E79"/>
-    <mergeCell ref="G77:G79"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="P116:S116"/>
-    <mergeCell ref="G83:G85"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="T116:W116"/>
-    <mergeCell ref="G113:G115"/>
-    <mergeCell ref="B101:B103"/>
-    <mergeCell ref="AB116:AE116"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="E110:E112"/>
-    <mergeCell ref="U76:V76"/>
-    <mergeCell ref="AF38:AI38"/>
-    <mergeCell ref="AF6:AI6"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="AB71:AE71"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="D35:D37"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="G56:G58"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="F8:F25"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="T6:W6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="AF35:AI35"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="AF116:AI116"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="AF1:AI1"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="X116:AA116"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="E59:E61"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="G107:G109"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="B95:B97"/>
-    <mergeCell ref="E56:E58"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="B92:B94"/>
-    <mergeCell ref="AC88:AD88"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="C59:C61"/>
-    <mergeCell ref="G17:G19"/>
-    <mergeCell ref="E53:E55"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="AB87:AE87"/>
-    <mergeCell ref="T32:W32"/>
-    <mergeCell ref="E104:E106"/>
-    <mergeCell ref="X75:AA75"/>
-    <mergeCell ref="G104:G106"/>
-    <mergeCell ref="G98:G100"/>
-    <mergeCell ref="G92:G94"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="E74:E76"/>
-    <mergeCell ref="AF53:AI53"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="B86:B88"/>
-    <mergeCell ref="AB86:AE86"/>
-    <mergeCell ref="AF71:AI71"/>
-    <mergeCell ref="E101:E103"/>
-    <mergeCell ref="E95:E97"/>
-    <mergeCell ref="G101:G103"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="F62:F79"/>
-    <mergeCell ref="T74:W74"/>
-    <mergeCell ref="L89:S90"/>
-    <mergeCell ref="F26:F43"/>
-    <mergeCell ref="B83:B85"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="F44:F61"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="D74:D76"/>
-    <mergeCell ref="T33:W33"/>
-    <mergeCell ref="L86:S87"/>
-    <mergeCell ref="E26:E28"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="G26:G28"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="L116:O116"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="G110:G112"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="D110:D112"/>
-    <mergeCell ref="A113:A115"/>
-    <mergeCell ref="C113:C115"/>
-    <mergeCell ref="E113:E115"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="E107:E109"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="G53:G55"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="D113:D115"/>
-    <mergeCell ref="D98:D100"/>
-    <mergeCell ref="D101:D103"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="B89:B91"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="X74:AA74"/>
-    <mergeCell ref="D71:D73"/>
-    <mergeCell ref="D59:D61"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C80:C82"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="F80:F97"/>
-    <mergeCell ref="AG51:AH51"/>
-    <mergeCell ref="AF50:AI50"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="AD61:AE61"/>
+    <mergeCell ref="AB47:AC47"/>
+    <mergeCell ref="AB48:AC48"/>
+    <mergeCell ref="AB49:AC49"/>
+    <mergeCell ref="AB50:AC50"/>
+    <mergeCell ref="AB52:AC52"/>
+    <mergeCell ref="AD56:AE56"/>
+    <mergeCell ref="AD57:AE57"/>
+    <mergeCell ref="AD58:AE58"/>
+    <mergeCell ref="AD59:AE59"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>